--- a/ProjetXLS/JournalDeBord/JournalDeBord.xlsx
+++ b/ProjetXLS/JournalDeBord/JournalDeBord.xlsx
@@ -5,19 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WorkSpaces\WS\GitHub\Navigation\NavigationBateau\ProjetXLS\JournalDeBord\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpaces\WS\GitHub\Navigation\NavigationBateau\ProjetXLS\JournalDeBord\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A457EE2-A0B6-4842-876F-EFEE541F5230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D8D7BC-6767-4550-A72C-0DD8DFA3CDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24495" yWindow="810" windowWidth="29580" windowHeight="13860" xr2:uid="{E20D9DF7-46DF-4441-A87B-8D054A4C81F1}"/>
+    <workbookView xWindow="990" yWindow="765" windowWidth="27405" windowHeight="14970" activeTab="3" xr2:uid="{E20D9DF7-46DF-4441-A87B-8D054A4C81F1}"/>
   </bookViews>
   <sheets>
     <sheet name="premiere page" sheetId="6" r:id="rId1"/>
     <sheet name="inverse pour impression" sheetId="1" r:id="rId2"/>
     <sheet name="Page prise meteo" sheetId="3" r:id="rId3"/>
+    <sheet name="GrilleCompas" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">GrilleCompas!$C$1:$AX$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'inverse pour impression'!$B$2:$AA$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Page prise meteo'!$B$2:$Q$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'premiere page'!$B$2:$AA$59</definedName>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="159">
   <si>
     <t xml:space="preserve">Date: </t>
   </si>
@@ -552,12 +554,63 @@
   <si>
     <t>(*)Date de l'elaboration</t>
   </si>
+  <si>
+    <t>Déviation du compas</t>
+  </si>
+  <si>
+    <t>Deviation du compas</t>
+  </si>
+  <si>
+    <t>Methodo</t>
+  </si>
+  <si>
+    <t>1. chercher un endroit a magnetique sur le bateau</t>
+  </si>
+  <si>
+    <t>prendre un compas de relevement</t>
+  </si>
+  <si>
+    <t>prendre un amer a &gt; 3 milles</t>
+  </si>
+  <si>
+    <t>faire un 360° pas trop largue</t>
+  </si>
+  <si>
+    <t>==&gt; le relevement doit etre constant</t>
+  </si>
+  <si>
+    <t>2. prendre un cap sur un alignement</t>
+  </si>
+  <si>
+    <t>Correction du W du compas de relevement</t>
+  </si>
+  <si>
+    <t>3. pour chaque cap (de 10 en 10 ou 20 en 20)</t>
+  </si>
+  <si>
+    <t>note la diff entre compas de relevement et compas de navigation fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note </t>
+  </si>
+  <si>
+    <t>W(cap) = D + d(cap)</t>
+  </si>
+  <si>
+    <t>Zc = Zv - W (cap)</t>
+  </si>
+  <si>
+    <t>Si Cap change, Zv cst, D cst =&gt; seul d(cap) change</t>
+  </si>
+  <si>
+    <t>d est lie au perturbation du bateau</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -634,8 +687,68 @@
       <name val="Garamond"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -654,8 +767,25 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="106">
+  <borders count="149">
     <border>
       <left/>
       <right/>
@@ -2040,11 +2170,575 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14990691854609822"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.14993743705557422"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2185,6 +2879,123 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2215,122 +3026,80 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2338,24 +3107,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2383,61 +3134,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2449,11 +3146,99 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2602,6 +3387,585 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>392723</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>126023</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2375720" cy="3443406"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF49AD10-206D-4540-B5F2-A6ED9C32C963}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7555523" y="1202348"/>
+          <a:ext cx="2375720" cy="3443406"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>74147</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>101792</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="98116" cy="436054"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74DADCEE-DAA0-4F9C-8F0F-D1711B808499}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3941297" y="635192"/>
+          <a:ext cx="98116" cy="436054"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>44586</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>134989</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="449975" cy="87143"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47A50FF2-940D-4912-A6A7-6F0EEB918776}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="5400000" flipH="1">
+          <a:off x="3988377" y="2363398"/>
+          <a:ext cx="87143" cy="449975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>77265</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>7060</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="90073" cy="438252"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85AB1506-50E1-4126-8007-C932BC14999E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipH="1">
+          <a:off x="3944415" y="4131385"/>
+          <a:ext cx="90073" cy="438252"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>7546</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>137106</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="449975" cy="87143"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CDAA482-14B9-4AED-99E2-0B149B01178C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="3846562" y="5794515"/>
+          <a:ext cx="87143" cy="449975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>65624</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>90670</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="90073" cy="438252"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{671DFAE3-EB98-40A2-AA98-1E9ACD9FBCD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3932774" y="7453495"/>
+          <a:ext cx="90073" cy="438252"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>10592</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>7062</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="87143" cy="438252"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{947017CD-84C5-4A62-986F-8133800DEE94}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="2645273" flipH="1">
+          <a:off x="3982517" y="1464387"/>
+          <a:ext cx="87143" cy="438252"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>111261</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>96891</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="449975" cy="87143"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E164A5C-B872-47E3-B330-08CDD4C63C4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="7857562" flipH="1">
+          <a:off x="3940752" y="3277800"/>
+          <a:ext cx="87143" cy="449975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>101735</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>11166</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="449975" cy="87143"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D60F626-453F-4BCA-B16E-701D8AFCBB3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="13648137" flipH="1">
+          <a:off x="3940751" y="4906575"/>
+          <a:ext cx="87143" cy="449975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>58214</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>35636</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="90073" cy="438252"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41272C66-1692-4946-A2B7-5A7EC7221654}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="19035933" flipH="1">
+          <a:off x="3925364" y="6445961"/>
+          <a:ext cx="90073" cy="438252"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>11724</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>11724</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25616213-B1D9-45C0-A6D7-F137A19A92DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4200525" y="545124"/>
+          <a:ext cx="657225" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>85726</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Straight Arrow Connector 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB1D7CD8-CF0B-4854-BDE5-B333985AA4A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3067050" y="533400"/>
+          <a:ext cx="676276" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="25400">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>351892</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>166320</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1841646" cy="2801271"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1102F63-3BEF-4FCB-94E6-BB91C9AF7EA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8124292" y="11291520"/>
+          <a:ext cx="1841646" cy="2801271"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>301921</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>12456</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3745470" cy="2591651"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFFB1BE9-F1F5-440B-B5EE-13DA3BB82297}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8074321" y="14376156"/>
+          <a:ext cx="3745470" cy="2591651"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3042,21 +4406,21 @@
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2"/>
-      <c r="O2" s="118" t="s">
+      <c r="O2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="120"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="82"/>
     </row>
     <row r="3" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3"/>
@@ -3072,19 +4436,19 @@
       <c r="L3"/>
       <c r="M3"/>
       <c r="N3"/>
-      <c r="O3" s="121"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
-      <c r="W3" s="122"/>
-      <c r="X3" s="122"/>
-      <c r="Y3" s="122"/>
-      <c r="Z3" s="122"/>
-      <c r="AA3" s="123"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="84"/>
+      <c r="Y3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="85"/>
     </row>
     <row r="4" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4"/>
@@ -3100,23 +4464,23 @@
       <c r="L4"/>
       <c r="M4"/>
       <c r="N4"/>
-      <c r="O4" s="124" t="s">
+      <c r="O4" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="125"/>
-      <c r="Q4" s="125"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="125"/>
-      <c r="T4" s="125"/>
-      <c r="U4" s="126"/>
-      <c r="V4" s="127" t="s">
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
+      <c r="R4" s="87"/>
+      <c r="S4" s="87"/>
+      <c r="T4" s="87"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="125"/>
-      <c r="X4" s="125"/>
-      <c r="Y4" s="125"/>
-      <c r="Z4" s="125"/>
-      <c r="AA4" s="128"/>
+      <c r="W4" s="87"/>
+      <c r="X4" s="87"/>
+      <c r="Y4" s="87"/>
+      <c r="Z4" s="87"/>
+      <c r="AA4" s="90"/>
     </row>
     <row r="5" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5"/>
@@ -3218,21 +4582,21 @@
       <c r="L8"/>
       <c r="M8"/>
       <c r="N8"/>
-      <c r="O8" s="112" t="s">
+      <c r="O8" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="113"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="113"/>
-      <c r="S8" s="113"/>
-      <c r="T8" s="113"/>
-      <c r="U8" s="113"/>
-      <c r="V8" s="113"/>
-      <c r="W8" s="113"/>
-      <c r="X8" s="113"/>
-      <c r="Y8" s="113"/>
-      <c r="Z8" s="113"/>
-      <c r="AA8" s="114"/>
+      <c r="P8" s="92"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="92"/>
+      <c r="S8" s="92"/>
+      <c r="T8" s="92"/>
+      <c r="U8" s="92"/>
+      <c r="V8" s="92"/>
+      <c r="W8" s="92"/>
+      <c r="X8" s="92"/>
+      <c r="Y8" s="92"/>
+      <c r="Z8" s="92"/>
+      <c r="AA8" s="93"/>
     </row>
     <row r="9" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9"/>
@@ -3248,25 +4612,25 @@
       <c r="L9"/>
       <c r="M9"/>
       <c r="N9"/>
-      <c r="O9" s="115" t="s">
+      <c r="O9" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="116"/>
-      <c r="Q9" s="116"/>
-      <c r="R9" s="116"/>
-      <c r="S9" s="116"/>
-      <c r="T9" s="116" t="s">
+      <c r="P9" s="101"/>
+      <c r="Q9" s="101"/>
+      <c r="R9" s="101"/>
+      <c r="S9" s="101"/>
+      <c r="T9" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="116"/>
-      <c r="V9" s="116"/>
-      <c r="W9" s="116"/>
-      <c r="X9" s="116"/>
-      <c r="Y9" s="116" t="s">
+      <c r="U9" s="101"/>
+      <c r="V9" s="101"/>
+      <c r="W9" s="101"/>
+      <c r="X9" s="101"/>
+      <c r="Y9" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="117"/>
+      <c r="Z9" s="101"/>
+      <c r="AA9" s="102"/>
     </row>
     <row r="10" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10"/>
@@ -3282,25 +4646,25 @@
       <c r="L10"/>
       <c r="M10"/>
       <c r="N10"/>
-      <c r="O10" s="109" t="s">
+      <c r="O10" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="110"/>
-      <c r="Q10" s="110"/>
-      <c r="R10" s="110"/>
-      <c r="S10" s="110"/>
-      <c r="T10" s="110" t="s">
+      <c r="P10" s="95"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="95"/>
+      <c r="T10" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="110"/>
-      <c r="V10" s="110"/>
-      <c r="W10" s="110"/>
-      <c r="X10" s="110"/>
-      <c r="Y10" s="110" t="s">
+      <c r="U10" s="95"/>
+      <c r="V10" s="95"/>
+      <c r="W10" s="95"/>
+      <c r="X10" s="95"/>
+      <c r="Y10" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="Z10" s="110"/>
-      <c r="AA10" s="111"/>
+      <c r="Z10" s="95"/>
+      <c r="AA10" s="96"/>
     </row>
     <row r="11" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11"/>
@@ -3316,25 +4680,25 @@
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11"/>
-      <c r="O11" s="109" t="s">
+      <c r="O11" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="110"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="110" t="s">
+      <c r="P11" s="95"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
+      <c r="S11" s="95"/>
+      <c r="T11" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="110"/>
-      <c r="V11" s="110"/>
-      <c r="W11" s="110"/>
-      <c r="X11" s="110"/>
-      <c r="Y11" s="110" t="s">
+      <c r="U11" s="95"/>
+      <c r="V11" s="95"/>
+      <c r="W11" s="95"/>
+      <c r="X11" s="95"/>
+      <c r="Y11" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="111"/>
+      <c r="Z11" s="95"/>
+      <c r="AA11" s="96"/>
     </row>
     <row r="12" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12"/>
@@ -3350,21 +4714,21 @@
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
-      <c r="O12" s="105" t="s">
+      <c r="O12" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="106"/>
-      <c r="T12" s="106"/>
-      <c r="U12" s="106"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="106"/>
-      <c r="X12" s="106"/>
-      <c r="Y12" s="106"/>
-      <c r="Z12" s="106"/>
-      <c r="AA12" s="107"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="98"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="99"/>
     </row>
     <row r="13" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13"/>
@@ -3380,21 +4744,21 @@
       <c r="L13"/>
       <c r="M13"/>
       <c r="N13"/>
-      <c r="O13" s="112" t="s">
+      <c r="O13" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="113"/>
-      <c r="R13" s="113"/>
-      <c r="S13" s="113"/>
-      <c r="T13" s="113"/>
-      <c r="U13" s="113"/>
-      <c r="V13" s="113"/>
-      <c r="W13" s="113"/>
-      <c r="X13" s="113"/>
-      <c r="Y13" s="113"/>
-      <c r="Z13" s="113"/>
-      <c r="AA13" s="114"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="92"/>
+      <c r="S13" s="92"/>
+      <c r="T13" s="92"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="92"/>
+      <c r="W13" s="92"/>
+      <c r="X13" s="92"/>
+      <c r="Y13" s="92"/>
+      <c r="Z13" s="92"/>
+      <c r="AA13" s="93"/>
     </row>
     <row r="14" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14"/>
@@ -3410,25 +4774,25 @@
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
-      <c r="O14" s="115" t="s">
+      <c r="O14" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="116"/>
-      <c r="S14" s="116"/>
-      <c r="T14" s="116" t="s">
+      <c r="P14" s="101"/>
+      <c r="Q14" s="101"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="101"/>
+      <c r="T14" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="U14" s="116"/>
-      <c r="V14" s="116"/>
-      <c r="W14" s="116"/>
-      <c r="X14" s="116"/>
-      <c r="Y14" s="116" t="s">
+      <c r="U14" s="101"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="101"/>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="116"/>
-      <c r="AA14" s="117"/>
+      <c r="Z14" s="101"/>
+      <c r="AA14" s="102"/>
     </row>
     <row r="15" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15"/>
@@ -3444,25 +4808,25 @@
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15"/>
-      <c r="O15" s="109" t="s">
+      <c r="O15" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="110"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="110" t="s">
+      <c r="P15" s="95"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="95"/>
+      <c r="S15" s="95"/>
+      <c r="T15" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="U15" s="110"/>
-      <c r="V15" s="110"/>
-      <c r="W15" s="110"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="110" t="s">
+      <c r="U15" s="95"/>
+      <c r="V15" s="95"/>
+      <c r="W15" s="95"/>
+      <c r="X15" s="95"/>
+      <c r="Y15" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="Z15" s="110"/>
-      <c r="AA15" s="111"/>
+      <c r="Z15" s="95"/>
+      <c r="AA15" s="96"/>
     </row>
     <row r="16" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16"/>
@@ -3478,25 +4842,25 @@
       <c r="L16"/>
       <c r="M16"/>
       <c r="N16"/>
-      <c r="O16" s="109" t="s">
+      <c r="O16" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="110"/>
-      <c r="S16" s="110"/>
-      <c r="T16" s="110" t="s">
+      <c r="P16" s="95"/>
+      <c r="Q16" s="95"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="95"/>
+      <c r="T16" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="110"/>
-      <c r="V16" s="110"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="110"/>
-      <c r="Y16" s="110" t="s">
+      <c r="U16" s="95"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="110"/>
-      <c r="AA16" s="111"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="96"/>
     </row>
     <row r="17" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17"/>
@@ -3512,21 +4876,21 @@
       <c r="L17"/>
       <c r="M17"/>
       <c r="N17"/>
-      <c r="O17" s="105" t="s">
+      <c r="O17" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="106"/>
-      <c r="R17" s="106"/>
-      <c r="S17" s="106"/>
-      <c r="T17" s="106"/>
-      <c r="U17" s="106"/>
-      <c r="V17" s="106"/>
-      <c r="W17" s="106"/>
-      <c r="X17" s="106"/>
-      <c r="Y17" s="106"/>
-      <c r="Z17" s="106"/>
-      <c r="AA17" s="107"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="98"/>
+      <c r="W17" s="98"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="99"/>
     </row>
     <row r="18" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18"/>
@@ -3542,21 +4906,21 @@
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
-      <c r="O18" s="112" t="s">
+      <c r="O18" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="P18" s="113"/>
-      <c r="Q18" s="113"/>
-      <c r="R18" s="113"/>
-      <c r="S18" s="113"/>
-      <c r="T18" s="113"/>
-      <c r="U18" s="113"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="113"/>
-      <c r="X18" s="113"/>
-      <c r="Y18" s="113"/>
-      <c r="Z18" s="113"/>
-      <c r="AA18" s="114"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="92"/>
+      <c r="S18" s="92"/>
+      <c r="T18" s="92"/>
+      <c r="U18" s="92"/>
+      <c r="V18" s="92"/>
+      <c r="W18" s="92"/>
+      <c r="X18" s="92"/>
+      <c r="Y18" s="92"/>
+      <c r="Z18" s="92"/>
+      <c r="AA18" s="93"/>
     </row>
     <row r="19" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19"/>
@@ -3572,25 +4936,25 @@
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19"/>
-      <c r="O19" s="115" t="s">
+      <c r="O19" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="P19" s="116"/>
-      <c r="Q19" s="116"/>
-      <c r="R19" s="116"/>
-      <c r="S19" s="116"/>
-      <c r="T19" s="116" t="s">
+      <c r="P19" s="101"/>
+      <c r="Q19" s="101"/>
+      <c r="R19" s="101"/>
+      <c r="S19" s="101"/>
+      <c r="T19" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="U19" s="116"/>
-      <c r="V19" s="116"/>
-      <c r="W19" s="116"/>
-      <c r="X19" s="116"/>
-      <c r="Y19" s="116" t="s">
+      <c r="U19" s="101"/>
+      <c r="V19" s="101"/>
+      <c r="W19" s="101"/>
+      <c r="X19" s="101"/>
+      <c r="Y19" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="Z19" s="116"/>
-      <c r="AA19" s="117"/>
+      <c r="Z19" s="101"/>
+      <c r="AA19" s="102"/>
     </row>
     <row r="20" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20"/>
@@ -3606,25 +4970,25 @@
       <c r="L20"/>
       <c r="M20"/>
       <c r="N20"/>
-      <c r="O20" s="109" t="s">
+      <c r="O20" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110" t="s">
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="U20" s="110"/>
-      <c r="V20" s="110"/>
-      <c r="W20" s="110"/>
-      <c r="X20" s="110"/>
-      <c r="Y20" s="110" t="s">
+      <c r="U20" s="95"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="95"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="Z20" s="110"/>
-      <c r="AA20" s="111"/>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="96"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21"/>
@@ -3640,25 +5004,25 @@
       <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
-      <c r="O21" s="109" t="s">
+      <c r="O21" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="110"/>
-      <c r="R21" s="110"/>
-      <c r="S21" s="110"/>
-      <c r="T21" s="110" t="s">
+      <c r="P21" s="95"/>
+      <c r="Q21" s="95"/>
+      <c r="R21" s="95"/>
+      <c r="S21" s="95"/>
+      <c r="T21" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="110"/>
-      <c r="V21" s="110"/>
-      <c r="W21" s="110"/>
-      <c r="X21" s="110"/>
-      <c r="Y21" s="110" t="s">
+      <c r="U21" s="95"/>
+      <c r="V21" s="95"/>
+      <c r="W21" s="95"/>
+      <c r="X21" s="95"/>
+      <c r="Y21" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="110"/>
-      <c r="AA21" s="111"/>
+      <c r="Z21" s="95"/>
+      <c r="AA21" s="96"/>
     </row>
     <row r="22" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22"/>
@@ -3674,21 +5038,21 @@
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
-      <c r="O22" s="105" t="s">
+      <c r="O22" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="106"/>
-      <c r="S22" s="106"/>
-      <c r="T22" s="106"/>
-      <c r="U22" s="106"/>
-      <c r="V22" s="106"/>
-      <c r="W22" s="106"/>
-      <c r="X22" s="106"/>
-      <c r="Y22" s="106"/>
-      <c r="Z22" s="106"/>
-      <c r="AA22" s="107"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="98"/>
+      <c r="R22" s="98"/>
+      <c r="S22" s="98"/>
+      <c r="T22" s="98"/>
+      <c r="U22" s="98"/>
+      <c r="V22" s="98"/>
+      <c r="W22" s="98"/>
+      <c r="X22" s="98"/>
+      <c r="Y22" s="98"/>
+      <c r="Z22" s="98"/>
+      <c r="AA22" s="99"/>
     </row>
     <row r="23" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23"/>
@@ -3704,35 +5068,35 @@
       <c r="L23"/>
       <c r="M23"/>
       <c r="N23"/>
-      <c r="O23" s="102" t="s">
+      <c r="O23" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="P23" s="102" t="s">
+      <c r="P23" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="108" t="s">
+      <c r="Q23" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="R23" s="99"/>
-      <c r="S23" s="98" t="s">
+      <c r="R23" s="106"/>
+      <c r="S23" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="99"/>
-      <c r="U23" s="98" t="s">
+      <c r="T23" s="106"/>
+      <c r="U23" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="V23" s="99"/>
-      <c r="W23" s="100" t="s">
+      <c r="V23" s="106"/>
+      <c r="W23" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="X23" s="98" t="s">
+      <c r="X23" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="99"/>
-      <c r="Z23" s="102" t="s">
+      <c r="Y23" s="106"/>
+      <c r="Z23" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="AA23" s="104" t="s">
+      <c r="AA23" s="118" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3750,8 +5114,8 @@
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
-      <c r="O24" s="103"/>
-      <c r="P24" s="103"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="104"/>
       <c r="Q24" s="41" t="s">
         <v>13</v>
       </c>
@@ -3770,15 +5134,15 @@
       <c r="V24" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="101"/>
+      <c r="W24" s="117"/>
       <c r="X24" s="41" t="s">
         <v>11</v>
       </c>
       <c r="Y24" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="Z24" s="103"/>
-      <c r="AA24" s="104"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="118"/>
     </row>
     <row r="25" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -4753,23 +6117,23 @@
       <c r="L55"/>
       <c r="M55"/>
       <c r="N55"/>
-      <c r="O55" s="90" t="s">
+      <c r="O55" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="P55" s="91"/>
-      <c r="Q55" s="91"/>
-      <c r="R55" s="91"/>
-      <c r="S55" s="91"/>
-      <c r="T55" s="91"/>
-      <c r="U55" s="92"/>
-      <c r="V55" s="90" t="s">
+      <c r="P55" s="108"/>
+      <c r="Q55" s="108"/>
+      <c r="R55" s="108"/>
+      <c r="S55" s="108"/>
+      <c r="T55" s="108"/>
+      <c r="U55" s="109"/>
+      <c r="V55" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="W55" s="91"/>
-      <c r="X55" s="91"/>
-      <c r="Y55" s="91"/>
-      <c r="Z55" s="91"/>
-      <c r="AA55" s="92"/>
+      <c r="W55" s="108"/>
+      <c r="X55" s="108"/>
+      <c r="Y55" s="108"/>
+      <c r="Z55" s="108"/>
+      <c r="AA55" s="109"/>
     </row>
     <row r="56" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56"/>
@@ -4785,19 +6149,19 @@
       <c r="L56"/>
       <c r="M56"/>
       <c r="N56"/>
-      <c r="O56" s="93"/>
-      <c r="P56" s="94"/>
-      <c r="Q56" s="94"/>
-      <c r="R56" s="94"/>
-      <c r="S56" s="94"/>
-      <c r="T56" s="94"/>
-      <c r="U56" s="95"/>
-      <c r="V56" s="96"/>
-      <c r="W56" s="97"/>
-      <c r="X56" s="97"/>
-      <c r="Y56" s="97"/>
-      <c r="Z56" s="97"/>
-      <c r="AA56" s="97"/>
+      <c r="O56" s="110"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="111"/>
+      <c r="S56" s="111"/>
+      <c r="T56" s="111"/>
+      <c r="U56" s="112"/>
+      <c r="V56" s="113"/>
+      <c r="W56" s="114"/>
+      <c r="X56" s="114"/>
+      <c r="Y56" s="114"/>
+      <c r="Z56" s="114"/>
+      <c r="AA56" s="114"/>
     </row>
     <row r="57" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57"/>
@@ -4813,19 +6177,19 @@
       <c r="L57"/>
       <c r="M57"/>
       <c r="N57"/>
-      <c r="O57" s="85"/>
-      <c r="P57" s="86"/>
-      <c r="Q57" s="86"/>
-      <c r="R57" s="86"/>
-      <c r="S57" s="86"/>
-      <c r="T57" s="86"/>
-      <c r="U57" s="87"/>
-      <c r="V57" s="88"/>
-      <c r="W57" s="89"/>
-      <c r="X57" s="89"/>
-      <c r="Y57" s="89"/>
-      <c r="Z57" s="89"/>
-      <c r="AA57" s="89"/>
+      <c r="O57" s="124"/>
+      <c r="P57" s="125"/>
+      <c r="Q57" s="125"/>
+      <c r="R57" s="125"/>
+      <c r="S57" s="125"/>
+      <c r="T57" s="125"/>
+      <c r="U57" s="126"/>
+      <c r="V57" s="127"/>
+      <c r="W57" s="128"/>
+      <c r="X57" s="128"/>
+      <c r="Y57" s="128"/>
+      <c r="Z57" s="128"/>
+      <c r="AA57" s="128"/>
     </row>
     <row r="58" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58"/>
@@ -4841,19 +6205,19 @@
       <c r="L58"/>
       <c r="M58"/>
       <c r="N58"/>
-      <c r="O58" s="85"/>
-      <c r="P58" s="86"/>
-      <c r="Q58" s="86"/>
-      <c r="R58" s="86"/>
-      <c r="S58" s="86"/>
-      <c r="T58" s="86"/>
-      <c r="U58" s="87"/>
-      <c r="V58" s="88"/>
-      <c r="W58" s="89"/>
-      <c r="X58" s="89"/>
-      <c r="Y58" s="89"/>
-      <c r="Z58" s="89"/>
-      <c r="AA58" s="89"/>
+      <c r="O58" s="124"/>
+      <c r="P58" s="125"/>
+      <c r="Q58" s="125"/>
+      <c r="R58" s="125"/>
+      <c r="S58" s="125"/>
+      <c r="T58" s="125"/>
+      <c r="U58" s="126"/>
+      <c r="V58" s="127"/>
+      <c r="W58" s="128"/>
+      <c r="X58" s="128"/>
+      <c r="Y58" s="128"/>
+      <c r="Z58" s="128"/>
+      <c r="AA58" s="128"/>
     </row>
     <row r="59" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59"/>
@@ -4869,51 +6233,38 @@
       <c r="L59"/>
       <c r="M59"/>
       <c r="N59"/>
-      <c r="O59" s="80"/>
-      <c r="P59" s="81"/>
-      <c r="Q59" s="81"/>
-      <c r="R59" s="81"/>
-      <c r="S59" s="81"/>
-      <c r="T59" s="81"/>
-      <c r="U59" s="82"/>
-      <c r="V59" s="83"/>
-      <c r="W59" s="84"/>
-      <c r="X59" s="84"/>
-      <c r="Y59" s="84"/>
-      <c r="Z59" s="84"/>
-      <c r="AA59" s="84"/>
+      <c r="O59" s="119"/>
+      <c r="P59" s="120"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="120"/>
+      <c r="S59" s="120"/>
+      <c r="T59" s="120"/>
+      <c r="U59" s="121"/>
+      <c r="V59" s="122"/>
+      <c r="W59" s="123"/>
+      <c r="X59" s="123"/>
+      <c r="Y59" s="123"/>
+      <c r="Z59" s="123"/>
+      <c r="AA59" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="O2:AA3"/>
-    <mergeCell ref="O4:U4"/>
-    <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="O8:AA8"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="O12:AA12"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:X15"/>
-    <mergeCell ref="Y15:AA15"/>
-    <mergeCell ref="O13:AA13"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:X14"/>
-    <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="O18:AA18"/>
-    <mergeCell ref="O19:S19"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:X16"/>
-    <mergeCell ref="Y16:AA16"/>
-    <mergeCell ref="O17:AA17"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="V59:AA59"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="V57:AA57"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="V58:AA58"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="V55:AA55"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="V56:AA56"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="Z23:Z24"/>
+    <mergeCell ref="AA23:AA24"/>
     <mergeCell ref="O22:AA22"/>
     <mergeCell ref="O23:O24"/>
     <mergeCell ref="P23:P24"/>
@@ -4924,22 +6275,35 @@
     <mergeCell ref="O21:S21"/>
     <mergeCell ref="T21:X21"/>
     <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="V55:AA55"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="V56:AA56"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:W24"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="Z23:Z24"/>
-    <mergeCell ref="AA23:AA24"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="V59:AA59"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="V57:AA57"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="V58:AA58"/>
+    <mergeCell ref="O18:AA18"/>
+    <mergeCell ref="O19:S19"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:X16"/>
+    <mergeCell ref="Y16:AA16"/>
+    <mergeCell ref="O17:AA17"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:X15"/>
+    <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="O13:AA13"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:X14"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="O12:AA12"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="O2:AA3"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="V4:AA4"/>
+    <mergeCell ref="O8:AA8"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -5114,21 +6478,21 @@
         <v>63</v>
       </c>
       <c r="N2" s="38"/>
-      <c r="O2" s="118" t="s">
+      <c r="O2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="120"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="82"/>
     </row>
     <row r="3" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
@@ -5159,19 +6523,19 @@
       <c r="N3" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="121"/>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="122"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122"/>
-      <c r="V3" s="122"/>
-      <c r="W3" s="122"/>
-      <c r="X3" s="122"/>
-      <c r="Y3" s="122"/>
-      <c r="Z3" s="122"/>
-      <c r="AA3" s="123"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="84"/>
+      <c r="Y3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="85"/>
     </row>
     <row r="4" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
@@ -5191,23 +6555,23 @@
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
       <c r="N4" s="25"/>
-      <c r="O4" s="124" t="s">
+      <c r="O4" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="125"/>
-      <c r="Q4" s="125"/>
-      <c r="R4" s="125"/>
-      <c r="S4" s="125"/>
-      <c r="T4" s="125"/>
-      <c r="U4" s="126"/>
-      <c r="V4" s="127" t="s">
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
+      <c r="R4" s="87"/>
+      <c r="S4" s="87"/>
+      <c r="T4" s="87"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="125"/>
-      <c r="X4" s="125"/>
-      <c r="Y4" s="125"/>
-      <c r="Z4" s="125"/>
-      <c r="AA4" s="128"/>
+      <c r="W4" s="87"/>
+      <c r="X4" s="87"/>
+      <c r="Y4" s="87"/>
+      <c r="Z4" s="87"/>
+      <c r="AA4" s="90"/>
     </row>
     <row r="5" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
@@ -5308,48 +6672,48 @@
       <c r="AA7" s="52"/>
     </row>
     <row r="8" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="131" t="s">
+      <c r="B8" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="131" t="s">
+      <c r="C8" s="149"/>
+      <c r="D8" s="149"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="149"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="132"/>
-      <c r="J8" s="133"/>
-      <c r="K8" s="143" t="s">
+      <c r="I8" s="149"/>
+      <c r="J8" s="150"/>
+      <c r="K8" s="162" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="144"/>
-      <c r="M8" s="144"/>
-      <c r="N8" s="145"/>
-      <c r="O8" s="112" t="s">
+      <c r="L8" s="163"/>
+      <c r="M8" s="163"/>
+      <c r="N8" s="164"/>
+      <c r="O8" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="113"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="113"/>
-      <c r="S8" s="113"/>
-      <c r="T8" s="113"/>
-      <c r="U8" s="113"/>
-      <c r="V8" s="113"/>
-      <c r="W8" s="113"/>
-      <c r="X8" s="113"/>
-      <c r="Y8" s="113"/>
-      <c r="Z8" s="113"/>
-      <c r="AA8" s="114"/>
+      <c r="P8" s="92"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="92"/>
+      <c r="S8" s="92"/>
+      <c r="T8" s="92"/>
+      <c r="U8" s="92"/>
+      <c r="V8" s="92"/>
+      <c r="W8" s="92"/>
+      <c r="X8" s="92"/>
+      <c r="Y8" s="92"/>
+      <c r="Z8" s="92"/>
+      <c r="AA8" s="93"/>
     </row>
     <row r="9" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="136"/>
+      <c r="B9" s="151"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="153"/>
       <c r="H9" s="30" t="s">
         <v>15</v>
       </c>
@@ -5361,33 +6725,33 @@
       <c r="L9" s="54"/>
       <c r="M9" s="54"/>
       <c r="N9" s="55"/>
-      <c r="O9" s="115" t="s">
+      <c r="O9" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="116"/>
-      <c r="Q9" s="116"/>
-      <c r="R9" s="116"/>
-      <c r="S9" s="116"/>
-      <c r="T9" s="116" t="s">
+      <c r="P9" s="101"/>
+      <c r="Q9" s="101"/>
+      <c r="R9" s="101"/>
+      <c r="S9" s="101"/>
+      <c r="T9" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="116"/>
-      <c r="V9" s="116"/>
-      <c r="W9" s="116"/>
-      <c r="X9" s="116"/>
-      <c r="Y9" s="116" t="s">
+      <c r="U9" s="101"/>
+      <c r="V9" s="101"/>
+      <c r="W9" s="101"/>
+      <c r="X9" s="101"/>
+      <c r="Y9" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="117"/>
+      <c r="Z9" s="101"/>
+      <c r="AA9" s="102"/>
     </row>
     <row r="10" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="137"/>
-      <c r="C10" s="138"/>
-      <c r="D10" s="138"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="139"/>
+      <c r="B10" s="156"/>
+      <c r="C10" s="157"/>
+      <c r="D10" s="157"/>
+      <c r="E10" s="157"/>
+      <c r="F10" s="157"/>
+      <c r="G10" s="158"/>
       <c r="H10" s="13" t="s">
         <v>16</v>
       </c>
@@ -5399,71 +6763,71 @@
       <c r="L10" s="57"/>
       <c r="M10" s="57"/>
       <c r="N10" s="58"/>
-      <c r="O10" s="109" t="s">
+      <c r="O10" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="110"/>
-      <c r="Q10" s="110"/>
-      <c r="R10" s="110"/>
-      <c r="S10" s="110"/>
-      <c r="T10" s="110" t="s">
+      <c r="P10" s="95"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="95"/>
+      <c r="T10" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="110"/>
-      <c r="V10" s="110"/>
-      <c r="W10" s="110"/>
-      <c r="X10" s="110"/>
-      <c r="Y10" s="110" t="s">
+      <c r="U10" s="95"/>
+      <c r="V10" s="95"/>
+      <c r="W10" s="95"/>
+      <c r="X10" s="95"/>
+      <c r="Y10" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="Z10" s="110"/>
-      <c r="AA10" s="111"/>
+      <c r="Z10" s="95"/>
+      <c r="AA10" s="96"/>
     </row>
     <row r="11" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="137"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="139"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="158"/>
       <c r="H11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="129" t="s">
+      <c r="I11" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="130"/>
+      <c r="J11" s="155"/>
       <c r="K11" s="56"/>
       <c r="L11" s="57"/>
       <c r="M11" s="57"/>
       <c r="N11" s="58"/>
-      <c r="O11" s="109" t="s">
+      <c r="O11" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="110"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="110" t="s">
+      <c r="P11" s="95"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
+      <c r="S11" s="95"/>
+      <c r="T11" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="110"/>
-      <c r="V11" s="110"/>
-      <c r="W11" s="110"/>
-      <c r="X11" s="110"/>
-      <c r="Y11" s="110" t="s">
+      <c r="U11" s="95"/>
+      <c r="V11" s="95"/>
+      <c r="W11" s="95"/>
+      <c r="X11" s="95"/>
+      <c r="Y11" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="111"/>
+      <c r="Z11" s="95"/>
+      <c r="AA11" s="96"/>
     </row>
     <row r="12" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="140"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="142"/>
+      <c r="B12" s="159"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="161"/>
       <c r="H12" s="13" t="s">
         <v>17</v>
       </c>
@@ -5475,31 +6839,31 @@
       <c r="L12" s="57"/>
       <c r="M12" s="57"/>
       <c r="N12" s="58"/>
-      <c r="O12" s="105" t="s">
+      <c r="O12" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="106"/>
-      <c r="T12" s="106"/>
-      <c r="U12" s="106"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="106"/>
-      <c r="X12" s="106"/>
-      <c r="Y12" s="106"/>
-      <c r="Z12" s="106"/>
-      <c r="AA12" s="107"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="98"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="99"/>
     </row>
     <row r="13" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="131" t="s">
+      <c r="B13" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="133"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="150"/>
       <c r="H13" s="13" t="s">
         <v>34</v>
       </c>
@@ -5511,100 +6875,100 @@
       <c r="L13" s="57"/>
       <c r="M13" s="57"/>
       <c r="N13" s="58"/>
-      <c r="O13" s="112" t="s">
+      <c r="O13" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="113"/>
-      <c r="R13" s="113"/>
-      <c r="S13" s="113"/>
-      <c r="T13" s="113"/>
-      <c r="U13" s="113"/>
-      <c r="V13" s="113"/>
-      <c r="W13" s="113"/>
-      <c r="X13" s="113"/>
-      <c r="Y13" s="113"/>
-      <c r="Z13" s="113"/>
-      <c r="AA13" s="114"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="92"/>
+      <c r="S13" s="92"/>
+      <c r="T13" s="92"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="92"/>
+      <c r="W13" s="92"/>
+      <c r="X13" s="92"/>
+      <c r="Y13" s="92"/>
+      <c r="Z13" s="92"/>
+      <c r="AA13" s="93"/>
     </row>
     <row r="14" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="134"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="136"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="153"/>
       <c r="H14" s="3"/>
       <c r="J14" s="4"/>
       <c r="K14" s="59"/>
       <c r="L14" s="60"/>
       <c r="M14" s="60"/>
       <c r="N14" s="61"/>
-      <c r="O14" s="115" t="s">
+      <c r="O14" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="116"/>
-      <c r="S14" s="116"/>
-      <c r="T14" s="116" t="s">
+      <c r="P14" s="101"/>
+      <c r="Q14" s="101"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="101"/>
+      <c r="T14" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="U14" s="116"/>
-      <c r="V14" s="116"/>
-      <c r="W14" s="116"/>
-      <c r="X14" s="116"/>
-      <c r="Y14" s="116" t="s">
+      <c r="U14" s="101"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="101"/>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="116"/>
-      <c r="AA14" s="117"/>
+      <c r="Z14" s="101"/>
+      <c r="AA14" s="102"/>
     </row>
     <row r="15" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="137"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="139"/>
-      <c r="H15" s="131" t="s">
+      <c r="B15" s="156"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="157"/>
+      <c r="F15" s="157"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="148" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="131" t="s">
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="148" t="s">
         <v>75</v>
       </c>
-      <c r="M15" s="132"/>
-      <c r="N15" s="133"/>
-      <c r="O15" s="109" t="s">
+      <c r="M15" s="149"/>
+      <c r="N15" s="150"/>
+      <c r="O15" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="110"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="110" t="s">
+      <c r="P15" s="95"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="95"/>
+      <c r="S15" s="95"/>
+      <c r="T15" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="U15" s="110"/>
-      <c r="V15" s="110"/>
-      <c r="W15" s="110"/>
-      <c r="X15" s="110"/>
-      <c r="Y15" s="110" t="s">
+      <c r="U15" s="95"/>
+      <c r="V15" s="95"/>
+      <c r="W15" s="95"/>
+      <c r="X15" s="95"/>
+      <c r="Y15" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="Z15" s="110"/>
-      <c r="AA15" s="111"/>
+      <c r="Z15" s="95"/>
+      <c r="AA15" s="96"/>
     </row>
     <row r="16" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="137"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="139"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="157"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="157"/>
+      <c r="G16" s="158"/>
       <c r="H16" s="14"/>
       <c r="I16" s="18" t="s">
         <v>18</v>
@@ -5618,33 +6982,33 @@
       <c r="L16" s="62"/>
       <c r="M16" s="63"/>
       <c r="N16" s="64"/>
-      <c r="O16" s="109" t="s">
+      <c r="O16" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="110"/>
-      <c r="S16" s="110"/>
-      <c r="T16" s="110" t="s">
+      <c r="P16" s="95"/>
+      <c r="Q16" s="95"/>
+      <c r="R16" s="95"/>
+      <c r="S16" s="95"/>
+      <c r="T16" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="110"/>
-      <c r="V16" s="110"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="110"/>
-      <c r="Y16" s="110" t="s">
+      <c r="U16" s="95"/>
+      <c r="V16" s="95"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="95"/>
+      <c r="Y16" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="110"/>
-      <c r="AA16" s="111"/>
+      <c r="Z16" s="95"/>
+      <c r="AA16" s="96"/>
     </row>
     <row r="17" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="137"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="139"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="158"/>
       <c r="H17" s="10" t="s">
         <v>59</v>
       </c>
@@ -5654,29 +7018,29 @@
       <c r="L17" s="56"/>
       <c r="M17" s="57"/>
       <c r="N17" s="58"/>
-      <c r="O17" s="105" t="s">
+      <c r="O17" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="106"/>
-      <c r="R17" s="106"/>
-      <c r="S17" s="106"/>
-      <c r="T17" s="106"/>
-      <c r="U17" s="106"/>
-      <c r="V17" s="106"/>
-      <c r="W17" s="106"/>
-      <c r="X17" s="106"/>
-      <c r="Y17" s="106"/>
-      <c r="Z17" s="106"/>
-      <c r="AA17" s="107"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="98"/>
+      <c r="W17" s="98"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="99"/>
     </row>
     <row r="18" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="137"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="139"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="157"/>
+      <c r="G18" s="158"/>
       <c r="H18" s="10" t="s">
         <v>53</v>
       </c>
@@ -5686,29 +7050,29 @@
       <c r="L18" s="56"/>
       <c r="M18" s="57"/>
       <c r="N18" s="58"/>
-      <c r="O18" s="112" t="s">
+      <c r="O18" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="P18" s="113"/>
-      <c r="Q18" s="113"/>
-      <c r="R18" s="113"/>
-      <c r="S18" s="113"/>
-      <c r="T18" s="113"/>
-      <c r="U18" s="113"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="113"/>
-      <c r="X18" s="113"/>
-      <c r="Y18" s="113"/>
-      <c r="Z18" s="113"/>
-      <c r="AA18" s="114"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="92"/>
+      <c r="S18" s="92"/>
+      <c r="T18" s="92"/>
+      <c r="U18" s="92"/>
+      <c r="V18" s="92"/>
+      <c r="W18" s="92"/>
+      <c r="X18" s="92"/>
+      <c r="Y18" s="92"/>
+      <c r="Z18" s="92"/>
+      <c r="AA18" s="93"/>
     </row>
     <row r="19" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="137"/>
-      <c r="C19" s="138"/>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="139"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="157"/>
+      <c r="G19" s="158"/>
       <c r="H19" s="10" t="s">
         <v>72</v>
       </c>
@@ -5718,33 +7082,33 @@
       <c r="L19" s="56"/>
       <c r="M19" s="57"/>
       <c r="N19" s="58"/>
-      <c r="O19" s="115" t="s">
+      <c r="O19" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="P19" s="116"/>
-      <c r="Q19" s="116"/>
-      <c r="R19" s="116"/>
-      <c r="S19" s="116"/>
-      <c r="T19" s="116" t="s">
+      <c r="P19" s="101"/>
+      <c r="Q19" s="101"/>
+      <c r="R19" s="101"/>
+      <c r="S19" s="101"/>
+      <c r="T19" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="U19" s="116"/>
-      <c r="V19" s="116"/>
-      <c r="W19" s="116"/>
-      <c r="X19" s="116"/>
-      <c r="Y19" s="116" t="s">
+      <c r="U19" s="101"/>
+      <c r="V19" s="101"/>
+      <c r="W19" s="101"/>
+      <c r="X19" s="101"/>
+      <c r="Y19" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="Z19" s="116"/>
-      <c r="AA19" s="117"/>
+      <c r="Z19" s="101"/>
+      <c r="AA19" s="102"/>
     </row>
     <row r="20" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="137"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="139"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="157"/>
+      <c r="D20" s="157"/>
+      <c r="E20" s="157"/>
+      <c r="F20" s="157"/>
+      <c r="G20" s="158"/>
       <c r="H20" s="10" t="s">
         <v>52</v>
       </c>
@@ -5754,33 +7118,33 @@
       <c r="L20" s="56"/>
       <c r="M20" s="57"/>
       <c r="N20" s="58"/>
-      <c r="O20" s="109" t="s">
+      <c r="O20" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110" t="s">
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="U20" s="110"/>
-      <c r="V20" s="110"/>
-      <c r="W20" s="110"/>
-      <c r="X20" s="110"/>
-      <c r="Y20" s="110" t="s">
+      <c r="U20" s="95"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="95"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="Z20" s="110"/>
-      <c r="AA20" s="111"/>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="96"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="137"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="139"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="157"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="157"/>
+      <c r="F21" s="157"/>
+      <c r="G21" s="158"/>
       <c r="H21" s="10" t="s">
         <v>54</v>
       </c>
@@ -5790,33 +7154,33 @@
       <c r="L21" s="56"/>
       <c r="M21" s="57"/>
       <c r="N21" s="58"/>
-      <c r="O21" s="109" t="s">
+      <c r="O21" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="110"/>
-      <c r="R21" s="110"/>
-      <c r="S21" s="110"/>
-      <c r="T21" s="110" t="s">
+      <c r="P21" s="95"/>
+      <c r="Q21" s="95"/>
+      <c r="R21" s="95"/>
+      <c r="S21" s="95"/>
+      <c r="T21" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="110"/>
-      <c r="V21" s="110"/>
-      <c r="W21" s="110"/>
-      <c r="X21" s="110"/>
-      <c r="Y21" s="110" t="s">
+      <c r="U21" s="95"/>
+      <c r="V21" s="95"/>
+      <c r="W21" s="95"/>
+      <c r="X21" s="95"/>
+      <c r="Y21" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="110"/>
-      <c r="AA21" s="111"/>
+      <c r="Z21" s="95"/>
+      <c r="AA21" s="96"/>
     </row>
     <row r="22" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="140"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="141"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="142"/>
+      <c r="B22" s="159"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="161"/>
       <c r="H22" s="15"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
@@ -5824,98 +7188,98 @@
       <c r="L22" s="59"/>
       <c r="M22" s="60"/>
       <c r="N22" s="61"/>
-      <c r="O22" s="105" t="s">
+      <c r="O22" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="106"/>
-      <c r="Q22" s="106"/>
-      <c r="R22" s="106"/>
-      <c r="S22" s="106"/>
-      <c r="T22" s="106"/>
-      <c r="U22" s="106"/>
-      <c r="V22" s="106"/>
-      <c r="W22" s="106"/>
-      <c r="X22" s="106"/>
-      <c r="Y22" s="106"/>
-      <c r="Z22" s="106"/>
-      <c r="AA22" s="107"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="98"/>
+      <c r="R22" s="98"/>
+      <c r="S22" s="98"/>
+      <c r="T22" s="98"/>
+      <c r="U22" s="98"/>
+      <c r="V22" s="98"/>
+      <c r="W22" s="98"/>
+      <c r="X22" s="98"/>
+      <c r="Y22" s="98"/>
+      <c r="Z22" s="98"/>
+      <c r="AA22" s="99"/>
     </row>
     <row r="23" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="102" t="s">
+      <c r="C23" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="98" t="s">
+      <c r="D23" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="99"/>
-      <c r="F23" s="102" t="s">
+      <c r="E23" s="106"/>
+      <c r="F23" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="153" t="s">
+      <c r="G23" s="136" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="154"/>
-      <c r="I23" s="154"/>
-      <c r="J23" s="154"/>
-      <c r="K23" s="154"/>
-      <c r="L23" s="154"/>
-      <c r="M23" s="154"/>
-      <c r="N23" s="155"/>
-      <c r="O23" s="102" t="s">
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="137"/>
+      <c r="M23" s="137"/>
+      <c r="N23" s="138"/>
+      <c r="O23" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="P23" s="102" t="s">
+      <c r="P23" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="108" t="s">
+      <c r="Q23" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="R23" s="99"/>
-      <c r="S23" s="98" t="s">
+      <c r="R23" s="106"/>
+      <c r="S23" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="99"/>
-      <c r="U23" s="98" t="s">
+      <c r="T23" s="106"/>
+      <c r="U23" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="V23" s="99"/>
-      <c r="W23" s="100" t="s">
+      <c r="V23" s="106"/>
+      <c r="W23" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="X23" s="98" t="s">
+      <c r="X23" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="99"/>
-      <c r="Z23" s="102" t="s">
+      <c r="Y23" s="106"/>
+      <c r="Z23" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="AA23" s="104" t="s">
+      <c r="AA23" s="118" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="39" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="103"/>
-      <c r="G24" s="156"/>
-      <c r="H24" s="157"/>
-      <c r="I24" s="157"/>
-      <c r="J24" s="157"/>
-      <c r="K24" s="157"/>
-      <c r="L24" s="157"/>
-      <c r="M24" s="157"/>
-      <c r="N24" s="158"/>
-      <c r="O24" s="103"/>
-      <c r="P24" s="103"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="140"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="140"/>
+      <c r="N24" s="141"/>
+      <c r="O24" s="104"/>
+      <c r="P24" s="104"/>
       <c r="Q24" s="39" t="s">
         <v>13</v>
       </c>
@@ -5934,15 +7298,15 @@
       <c r="V24" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="101"/>
+      <c r="W24" s="117"/>
       <c r="X24" s="39" t="s">
         <v>11</v>
       </c>
       <c r="Y24" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="Z24" s="103"/>
-      <c r="AA24" s="104"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="118"/>
     </row>
     <row r="25" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -5953,14 +7317,14 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="149"/>
-      <c r="H25" s="150"/>
-      <c r="I25" s="150"/>
-      <c r="J25" s="150"/>
-      <c r="K25" s="150"/>
-      <c r="L25" s="150"/>
-      <c r="M25" s="150"/>
-      <c r="N25" s="151"/>
+      <c r="G25" s="145"/>
+      <c r="H25" s="146"/>
+      <c r="I25" s="146"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="146"/>
+      <c r="L25" s="146"/>
+      <c r="M25" s="146"/>
+      <c r="N25" s="147"/>
       <c r="O25" s="31"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
@@ -5985,14 +7349,14 @@
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
-      <c r="G26" s="146"/>
-      <c r="H26" s="147"/>
-      <c r="I26" s="147"/>
-      <c r="J26" s="147"/>
-      <c r="K26" s="147"/>
-      <c r="L26" s="147"/>
-      <c r="M26" s="147"/>
-      <c r="N26" s="148"/>
+      <c r="G26" s="129"/>
+      <c r="H26" s="130"/>
+      <c r="I26" s="130"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="130"/>
+      <c r="L26" s="130"/>
+      <c r="M26" s="130"/>
+      <c r="N26" s="131"/>
       <c r="O26" s="20"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="43"/>
@@ -6017,14 +7381,14 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="146"/>
-      <c r="H27" s="147"/>
-      <c r="I27" s="147"/>
-      <c r="J27" s="147"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="147"/>
-      <c r="M27" s="147"/>
-      <c r="N27" s="148"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="130"/>
+      <c r="J27" s="130"/>
+      <c r="K27" s="130"/>
+      <c r="L27" s="130"/>
+      <c r="M27" s="130"/>
+      <c r="N27" s="131"/>
       <c r="O27" s="20"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
@@ -6049,14 +7413,14 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="146"/>
-      <c r="H28" s="147"/>
-      <c r="I28" s="147"/>
-      <c r="J28" s="147"/>
-      <c r="K28" s="147"/>
-      <c r="L28" s="147"/>
-      <c r="M28" s="147"/>
-      <c r="N28" s="148"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
+      <c r="L28" s="130"/>
+      <c r="M28" s="130"/>
+      <c r="N28" s="131"/>
       <c r="O28" s="20"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
@@ -6081,14 +7445,14 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="146"/>
-      <c r="H29" s="147"/>
-      <c r="I29" s="147"/>
-      <c r="J29" s="147"/>
-      <c r="K29" s="147"/>
-      <c r="L29" s="147"/>
-      <c r="M29" s="147"/>
-      <c r="N29" s="148"/>
+      <c r="G29" s="129"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="130"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="130"/>
+      <c r="M29" s="130"/>
+      <c r="N29" s="131"/>
       <c r="O29" s="20"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
@@ -6113,14 +7477,14 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="146"/>
-      <c r="H30" s="147"/>
-      <c r="I30" s="147"/>
-      <c r="J30" s="147"/>
-      <c r="K30" s="147"/>
-      <c r="L30" s="147"/>
-      <c r="M30" s="147"/>
-      <c r="N30" s="148"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
+      <c r="L30" s="130"/>
+      <c r="M30" s="130"/>
+      <c r="N30" s="131"/>
       <c r="O30" s="20"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
@@ -6145,14 +7509,14 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="146"/>
-      <c r="H31" s="147"/>
-      <c r="I31" s="147"/>
-      <c r="J31" s="147"/>
-      <c r="K31" s="147"/>
-      <c r="L31" s="147"/>
-      <c r="M31" s="147"/>
-      <c r="N31" s="148"/>
+      <c r="G31" s="129"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="130"/>
+      <c r="L31" s="130"/>
+      <c r="M31" s="130"/>
+      <c r="N31" s="131"/>
       <c r="O31" s="20"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
@@ -6177,14 +7541,14 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="146"/>
-      <c r="H32" s="147"/>
-      <c r="I32" s="147"/>
-      <c r="J32" s="147"/>
-      <c r="K32" s="147"/>
-      <c r="L32" s="147"/>
-      <c r="M32" s="147"/>
-      <c r="N32" s="148"/>
+      <c r="G32" s="129"/>
+      <c r="H32" s="130"/>
+      <c r="I32" s="130"/>
+      <c r="J32" s="130"/>
+      <c r="K32" s="130"/>
+      <c r="L32" s="130"/>
+      <c r="M32" s="130"/>
+      <c r="N32" s="131"/>
       <c r="O32" s="20"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
@@ -6209,14 +7573,14 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
-      <c r="G33" s="146"/>
-      <c r="H33" s="147"/>
-      <c r="I33" s="147"/>
-      <c r="J33" s="147"/>
-      <c r="K33" s="147"/>
-      <c r="L33" s="147"/>
-      <c r="M33" s="147"/>
-      <c r="N33" s="148"/>
+      <c r="G33" s="129"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="130"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="130"/>
+      <c r="L33" s="130"/>
+      <c r="M33" s="130"/>
+      <c r="N33" s="131"/>
       <c r="O33" s="20"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
@@ -6241,14 +7605,14 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="146"/>
-      <c r="H34" s="147"/>
-      <c r="I34" s="147"/>
-      <c r="J34" s="147"/>
-      <c r="K34" s="147"/>
-      <c r="L34" s="147"/>
-      <c r="M34" s="147"/>
-      <c r="N34" s="148"/>
+      <c r="G34" s="129"/>
+      <c r="H34" s="130"/>
+      <c r="I34" s="130"/>
+      <c r="J34" s="130"/>
+      <c r="K34" s="130"/>
+      <c r="L34" s="130"/>
+      <c r="M34" s="130"/>
+      <c r="N34" s="131"/>
       <c r="O34" s="20"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
@@ -6273,14 +7637,14 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
-      <c r="G35" s="146"/>
-      <c r="H35" s="147"/>
-      <c r="I35" s="147"/>
-      <c r="J35" s="147"/>
-      <c r="K35" s="147"/>
-      <c r="L35" s="147"/>
-      <c r="M35" s="147"/>
-      <c r="N35" s="148"/>
+      <c r="G35" s="129"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="130"/>
+      <c r="J35" s="130"/>
+      <c r="K35" s="130"/>
+      <c r="L35" s="130"/>
+      <c r="M35" s="130"/>
+      <c r="N35" s="131"/>
       <c r="O35" s="20"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
@@ -6305,14 +7669,14 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="146"/>
-      <c r="H36" s="147"/>
-      <c r="I36" s="147"/>
-      <c r="J36" s="147"/>
-      <c r="K36" s="147"/>
-      <c r="L36" s="147"/>
-      <c r="M36" s="147"/>
-      <c r="N36" s="148"/>
+      <c r="G36" s="129"/>
+      <c r="H36" s="130"/>
+      <c r="I36" s="130"/>
+      <c r="J36" s="130"/>
+      <c r="K36" s="130"/>
+      <c r="L36" s="130"/>
+      <c r="M36" s="130"/>
+      <c r="N36" s="131"/>
       <c r="O36" s="20"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
@@ -6337,14 +7701,14 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="146"/>
-      <c r="H37" s="147"/>
-      <c r="I37" s="147"/>
-      <c r="J37" s="147"/>
-      <c r="K37" s="147"/>
-      <c r="L37" s="147"/>
-      <c r="M37" s="147"/>
-      <c r="N37" s="148"/>
+      <c r="G37" s="129"/>
+      <c r="H37" s="130"/>
+      <c r="I37" s="130"/>
+      <c r="J37" s="130"/>
+      <c r="K37" s="130"/>
+      <c r="L37" s="130"/>
+      <c r="M37" s="130"/>
+      <c r="N37" s="131"/>
       <c r="O37" s="20"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
@@ -6369,14 +7733,14 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="146"/>
-      <c r="H38" s="147"/>
-      <c r="I38" s="147"/>
-      <c r="J38" s="147"/>
-      <c r="K38" s="147"/>
-      <c r="L38" s="147"/>
-      <c r="M38" s="147"/>
-      <c r="N38" s="148"/>
+      <c r="G38" s="129"/>
+      <c r="H38" s="130"/>
+      <c r="I38" s="130"/>
+      <c r="J38" s="130"/>
+      <c r="K38" s="130"/>
+      <c r="L38" s="130"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="131"/>
       <c r="O38" s="20"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
@@ -6401,14 +7765,14 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="146"/>
-      <c r="H39" s="147"/>
-      <c r="I39" s="147"/>
-      <c r="J39" s="147"/>
-      <c r="K39" s="147"/>
-      <c r="L39" s="147"/>
-      <c r="M39" s="147"/>
-      <c r="N39" s="148"/>
+      <c r="G39" s="129"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="130"/>
+      <c r="J39" s="130"/>
+      <c r="K39" s="130"/>
+      <c r="L39" s="130"/>
+      <c r="M39" s="130"/>
+      <c r="N39" s="131"/>
       <c r="O39" s="20"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
@@ -6433,14 +7797,14 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="146"/>
-      <c r="H40" s="147"/>
-      <c r="I40" s="147"/>
-      <c r="J40" s="147"/>
-      <c r="K40" s="147"/>
-      <c r="L40" s="147"/>
-      <c r="M40" s="147"/>
-      <c r="N40" s="148"/>
+      <c r="G40" s="129"/>
+      <c r="H40" s="130"/>
+      <c r="I40" s="130"/>
+      <c r="J40" s="130"/>
+      <c r="K40" s="130"/>
+      <c r="L40" s="130"/>
+      <c r="M40" s="130"/>
+      <c r="N40" s="131"/>
       <c r="O40" s="20"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
@@ -6465,14 +7829,14 @@
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
-      <c r="G41" s="146"/>
-      <c r="H41" s="147"/>
-      <c r="I41" s="147"/>
-      <c r="J41" s="147"/>
-      <c r="K41" s="147"/>
-      <c r="L41" s="147"/>
-      <c r="M41" s="147"/>
-      <c r="N41" s="148"/>
+      <c r="G41" s="129"/>
+      <c r="H41" s="130"/>
+      <c r="I41" s="130"/>
+      <c r="J41" s="130"/>
+      <c r="K41" s="130"/>
+      <c r="L41" s="130"/>
+      <c r="M41" s="130"/>
+      <c r="N41" s="131"/>
       <c r="O41" s="20"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
@@ -6497,14 +7861,14 @@
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="146"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-      <c r="L42" s="147"/>
-      <c r="M42" s="147"/>
-      <c r="N42" s="148"/>
+      <c r="G42" s="129"/>
+      <c r="H42" s="130"/>
+      <c r="I42" s="130"/>
+      <c r="J42" s="130"/>
+      <c r="K42" s="130"/>
+      <c r="L42" s="130"/>
+      <c r="M42" s="130"/>
+      <c r="N42" s="131"/>
       <c r="O42" s="20"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
@@ -6529,14 +7893,14 @@
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="146"/>
-      <c r="H43" s="147"/>
-      <c r="I43" s="147"/>
-      <c r="J43" s="147"/>
-      <c r="K43" s="147"/>
-      <c r="L43" s="147"/>
-      <c r="M43" s="147"/>
-      <c r="N43" s="148"/>
+      <c r="G43" s="129"/>
+      <c r="H43" s="130"/>
+      <c r="I43" s="130"/>
+      <c r="J43" s="130"/>
+      <c r="K43" s="130"/>
+      <c r="L43" s="130"/>
+      <c r="M43" s="130"/>
+      <c r="N43" s="131"/>
       <c r="O43" s="20"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
@@ -6561,14 +7925,14 @@
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="146"/>
-      <c r="H44" s="147"/>
-      <c r="I44" s="147"/>
-      <c r="J44" s="147"/>
-      <c r="K44" s="147"/>
-      <c r="L44" s="147"/>
-      <c r="M44" s="147"/>
-      <c r="N44" s="148"/>
+      <c r="G44" s="129"/>
+      <c r="H44" s="130"/>
+      <c r="I44" s="130"/>
+      <c r="J44" s="130"/>
+      <c r="K44" s="130"/>
+      <c r="L44" s="130"/>
+      <c r="M44" s="130"/>
+      <c r="N44" s="131"/>
       <c r="O44" s="20"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
@@ -6593,14 +7957,14 @@
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="146"/>
-      <c r="H45" s="147"/>
-      <c r="I45" s="147"/>
-      <c r="J45" s="147"/>
-      <c r="K45" s="147"/>
-      <c r="L45" s="147"/>
-      <c r="M45" s="147"/>
-      <c r="N45" s="148"/>
+      <c r="G45" s="129"/>
+      <c r="H45" s="130"/>
+      <c r="I45" s="130"/>
+      <c r="J45" s="130"/>
+      <c r="K45" s="130"/>
+      <c r="L45" s="130"/>
+      <c r="M45" s="130"/>
+      <c r="N45" s="131"/>
       <c r="O45" s="20"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
@@ -6625,14 +7989,14 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
-      <c r="G46" s="146"/>
-      <c r="H46" s="147"/>
-      <c r="I46" s="147"/>
-      <c r="J46" s="147"/>
-      <c r="K46" s="147"/>
-      <c r="L46" s="147"/>
-      <c r="M46" s="147"/>
-      <c r="N46" s="148"/>
+      <c r="G46" s="129"/>
+      <c r="H46" s="130"/>
+      <c r="I46" s="130"/>
+      <c r="J46" s="130"/>
+      <c r="K46" s="130"/>
+      <c r="L46" s="130"/>
+      <c r="M46" s="130"/>
+      <c r="N46" s="131"/>
       <c r="O46" s="20"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
@@ -6657,14 +8021,14 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
-      <c r="G47" s="146"/>
-      <c r="H47" s="147"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="147"/>
-      <c r="K47" s="147"/>
-      <c r="L47" s="147"/>
-      <c r="M47" s="147"/>
-      <c r="N47" s="148"/>
+      <c r="G47" s="129"/>
+      <c r="H47" s="130"/>
+      <c r="I47" s="130"/>
+      <c r="J47" s="130"/>
+      <c r="K47" s="130"/>
+      <c r="L47" s="130"/>
+      <c r="M47" s="130"/>
+      <c r="N47" s="131"/>
       <c r="O47" s="20"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
@@ -6689,14 +8053,14 @@
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="146"/>
-      <c r="H48" s="147"/>
-      <c r="I48" s="147"/>
-      <c r="J48" s="147"/>
-      <c r="K48" s="147"/>
-      <c r="L48" s="147"/>
-      <c r="M48" s="147"/>
-      <c r="N48" s="148"/>
+      <c r="G48" s="129"/>
+      <c r="H48" s="130"/>
+      <c r="I48" s="130"/>
+      <c r="J48" s="130"/>
+      <c r="K48" s="130"/>
+      <c r="L48" s="130"/>
+      <c r="M48" s="130"/>
+      <c r="N48" s="131"/>
       <c r="O48" s="20"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
@@ -6721,14 +8085,14 @@
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="146"/>
-      <c r="H49" s="147"/>
-      <c r="I49" s="147"/>
-      <c r="J49" s="147"/>
-      <c r="K49" s="147"/>
-      <c r="L49" s="147"/>
-      <c r="M49" s="147"/>
-      <c r="N49" s="148"/>
+      <c r="G49" s="129"/>
+      <c r="H49" s="130"/>
+      <c r="I49" s="130"/>
+      <c r="J49" s="130"/>
+      <c r="K49" s="130"/>
+      <c r="L49" s="130"/>
+      <c r="M49" s="130"/>
+      <c r="N49" s="131"/>
       <c r="O49" s="20"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
@@ -6753,14 +8117,14 @@
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="146"/>
-      <c r="H50" s="147"/>
-      <c r="I50" s="147"/>
-      <c r="J50" s="147"/>
-      <c r="K50" s="147"/>
-      <c r="L50" s="147"/>
-      <c r="M50" s="147"/>
-      <c r="N50" s="148"/>
+      <c r="G50" s="129"/>
+      <c r="H50" s="130"/>
+      <c r="I50" s="130"/>
+      <c r="J50" s="130"/>
+      <c r="K50" s="130"/>
+      <c r="L50" s="130"/>
+      <c r="M50" s="130"/>
+      <c r="N50" s="131"/>
       <c r="O50" s="20"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
@@ -6785,14 +8149,14 @@
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="146"/>
-      <c r="H51" s="147"/>
-      <c r="I51" s="147"/>
-      <c r="J51" s="147"/>
-      <c r="K51" s="147"/>
-      <c r="L51" s="147"/>
-      <c r="M51" s="147"/>
-      <c r="N51" s="148"/>
+      <c r="G51" s="129"/>
+      <c r="H51" s="130"/>
+      <c r="I51" s="130"/>
+      <c r="J51" s="130"/>
+      <c r="K51" s="130"/>
+      <c r="L51" s="130"/>
+      <c r="M51" s="130"/>
+      <c r="N51" s="131"/>
       <c r="O51" s="20"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
@@ -6817,14 +8181,14 @@
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="146"/>
-      <c r="H52" s="147"/>
-      <c r="I52" s="147"/>
-      <c r="J52" s="147"/>
-      <c r="K52" s="147"/>
-      <c r="L52" s="147"/>
-      <c r="M52" s="147"/>
-      <c r="N52" s="148"/>
+      <c r="G52" s="129"/>
+      <c r="H52" s="130"/>
+      <c r="I52" s="130"/>
+      <c r="J52" s="130"/>
+      <c r="K52" s="130"/>
+      <c r="L52" s="130"/>
+      <c r="M52" s="130"/>
+      <c r="N52" s="131"/>
       <c r="O52" s="20"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
@@ -6849,14 +8213,14 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
-      <c r="G53" s="146"/>
-      <c r="H53" s="147"/>
-      <c r="I53" s="147"/>
-      <c r="J53" s="147"/>
-      <c r="K53" s="147"/>
-      <c r="L53" s="147"/>
-      <c r="M53" s="147"/>
-      <c r="N53" s="148"/>
+      <c r="G53" s="129"/>
+      <c r="H53" s="130"/>
+      <c r="I53" s="130"/>
+      <c r="J53" s="130"/>
+      <c r="K53" s="130"/>
+      <c r="L53" s="130"/>
+      <c r="M53" s="130"/>
+      <c r="N53" s="131"/>
       <c r="O53" s="20"/>
       <c r="P53" s="9"/>
       <c r="Q53" s="9"/>
@@ -6881,14 +8245,14 @@
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
-      <c r="G54" s="159"/>
-      <c r="H54" s="160"/>
-      <c r="I54" s="160"/>
-      <c r="J54" s="160"/>
-      <c r="K54" s="160"/>
-      <c r="L54" s="160"/>
-      <c r="M54" s="160"/>
-      <c r="N54" s="161"/>
+      <c r="G54" s="142"/>
+      <c r="H54" s="143"/>
+      <c r="I54" s="143"/>
+      <c r="J54" s="143"/>
+      <c r="K54" s="143"/>
+      <c r="L54" s="143"/>
+      <c r="M54" s="143"/>
+      <c r="N54" s="144"/>
       <c r="O54" s="20"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
@@ -6904,155 +8268,251 @@
       <c r="AA54" s="9"/>
     </row>
     <row r="55" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="90" t="s">
+      <c r="B55" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="91"/>
-      <c r="D55" s="91"/>
-      <c r="E55" s="91"/>
-      <c r="F55" s="91"/>
-      <c r="G55" s="92"/>
-      <c r="H55" s="152" t="s">
+      <c r="C55" s="108"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="108"/>
+      <c r="G55" s="109"/>
+      <c r="H55" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="I55" s="152"/>
-      <c r="J55" s="152"/>
-      <c r="K55" s="152"/>
-      <c r="L55" s="152"/>
-      <c r="M55" s="152"/>
-      <c r="N55" s="152"/>
-      <c r="O55" s="90" t="s">
+      <c r="I55" s="135"/>
+      <c r="J55" s="135"/>
+      <c r="K55" s="135"/>
+      <c r="L55" s="135"/>
+      <c r="M55" s="135"/>
+      <c r="N55" s="135"/>
+      <c r="O55" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="P55" s="91"/>
-      <c r="Q55" s="91"/>
-      <c r="R55" s="91"/>
-      <c r="S55" s="91"/>
-      <c r="T55" s="91"/>
-      <c r="U55" s="92"/>
-      <c r="V55" s="90" t="s">
+      <c r="P55" s="108"/>
+      <c r="Q55" s="108"/>
+      <c r="R55" s="108"/>
+      <c r="S55" s="108"/>
+      <c r="T55" s="108"/>
+      <c r="U55" s="109"/>
+      <c r="V55" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="W55" s="91"/>
-      <c r="X55" s="91"/>
-      <c r="Y55" s="91"/>
-      <c r="Z55" s="91"/>
-      <c r="AA55" s="92"/>
+      <c r="W55" s="108"/>
+      <c r="X55" s="108"/>
+      <c r="Y55" s="108"/>
+      <c r="Z55" s="108"/>
+      <c r="AA55" s="109"/>
     </row>
     <row r="56" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="97"/>
-      <c r="C56" s="97"/>
-      <c r="D56" s="97"/>
-      <c r="E56" s="97"/>
-      <c r="F56" s="97"/>
-      <c r="G56" s="162"/>
-      <c r="H56" s="93"/>
-      <c r="I56" s="94"/>
-      <c r="J56" s="94"/>
-      <c r="K56" s="94"/>
-      <c r="L56" s="94"/>
-      <c r="M56" s="94"/>
-      <c r="N56" s="95"/>
-      <c r="O56" s="93"/>
-      <c r="P56" s="94"/>
-      <c r="Q56" s="94"/>
-      <c r="R56" s="94"/>
-      <c r="S56" s="94"/>
-      <c r="T56" s="94"/>
-      <c r="U56" s="95"/>
-      <c r="V56" s="96"/>
-      <c r="W56" s="97"/>
-      <c r="X56" s="97"/>
-      <c r="Y56" s="97"/>
-      <c r="Z56" s="97"/>
-      <c r="AA56" s="97"/>
+      <c r="B56" s="114"/>
+      <c r="C56" s="114"/>
+      <c r="D56" s="114"/>
+      <c r="E56" s="114"/>
+      <c r="F56" s="114"/>
+      <c r="G56" s="132"/>
+      <c r="H56" s="110"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="111"/>
+      <c r="N56" s="112"/>
+      <c r="O56" s="110"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="111"/>
+      <c r="S56" s="111"/>
+      <c r="T56" s="111"/>
+      <c r="U56" s="112"/>
+      <c r="V56" s="113"/>
+      <c r="W56" s="114"/>
+      <c r="X56" s="114"/>
+      <c r="Y56" s="114"/>
+      <c r="Z56" s="114"/>
+      <c r="AA56" s="114"/>
     </row>
     <row r="57" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="89"/>
-      <c r="C57" s="89"/>
-      <c r="D57" s="89"/>
-      <c r="E57" s="89"/>
-      <c r="F57" s="89"/>
-      <c r="G57" s="163"/>
-      <c r="H57" s="85"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="86"/>
-      <c r="N57" s="87"/>
-      <c r="O57" s="85"/>
-      <c r="P57" s="86"/>
-      <c r="Q57" s="86"/>
-      <c r="R57" s="86"/>
-      <c r="S57" s="86"/>
-      <c r="T57" s="86"/>
-      <c r="U57" s="87"/>
-      <c r="V57" s="88"/>
-      <c r="W57" s="89"/>
-      <c r="X57" s="89"/>
-      <c r="Y57" s="89"/>
-      <c r="Z57" s="89"/>
-      <c r="AA57" s="89"/>
+      <c r="B57" s="128"/>
+      <c r="C57" s="128"/>
+      <c r="D57" s="128"/>
+      <c r="E57" s="128"/>
+      <c r="F57" s="128"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="124"/>
+      <c r="I57" s="125"/>
+      <c r="J57" s="125"/>
+      <c r="K57" s="125"/>
+      <c r="L57" s="125"/>
+      <c r="M57" s="125"/>
+      <c r="N57" s="126"/>
+      <c r="O57" s="124"/>
+      <c r="P57" s="125"/>
+      <c r="Q57" s="125"/>
+      <c r="R57" s="125"/>
+      <c r="S57" s="125"/>
+      <c r="T57" s="125"/>
+      <c r="U57" s="126"/>
+      <c r="V57" s="127"/>
+      <c r="W57" s="128"/>
+      <c r="X57" s="128"/>
+      <c r="Y57" s="128"/>
+      <c r="Z57" s="128"/>
+      <c r="AA57" s="128"/>
     </row>
     <row r="58" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="89"/>
-      <c r="C58" s="89"/>
-      <c r="D58" s="89"/>
-      <c r="E58" s="89"/>
-      <c r="F58" s="89"/>
-      <c r="G58" s="163"/>
-      <c r="H58" s="85"/>
-      <c r="I58" s="86"/>
-      <c r="J58" s="86"/>
-      <c r="K58" s="86"/>
-      <c r="L58" s="86"/>
-      <c r="M58" s="86"/>
-      <c r="N58" s="87"/>
-      <c r="O58" s="85"/>
-      <c r="P58" s="86"/>
-      <c r="Q58" s="86"/>
-      <c r="R58" s="86"/>
-      <c r="S58" s="86"/>
-      <c r="T58" s="86"/>
-      <c r="U58" s="87"/>
-      <c r="V58" s="88"/>
-      <c r="W58" s="89"/>
-      <c r="X58" s="89"/>
-      <c r="Y58" s="89"/>
-      <c r="Z58" s="89"/>
-      <c r="AA58" s="89"/>
+      <c r="B58" s="128"/>
+      <c r="C58" s="128"/>
+      <c r="D58" s="128"/>
+      <c r="E58" s="128"/>
+      <c r="F58" s="128"/>
+      <c r="G58" s="133"/>
+      <c r="H58" s="124"/>
+      <c r="I58" s="125"/>
+      <c r="J58" s="125"/>
+      <c r="K58" s="125"/>
+      <c r="L58" s="125"/>
+      <c r="M58" s="125"/>
+      <c r="N58" s="126"/>
+      <c r="O58" s="124"/>
+      <c r="P58" s="125"/>
+      <c r="Q58" s="125"/>
+      <c r="R58" s="125"/>
+      <c r="S58" s="125"/>
+      <c r="T58" s="125"/>
+      <c r="U58" s="126"/>
+      <c r="V58" s="127"/>
+      <c r="W58" s="128"/>
+      <c r="X58" s="128"/>
+      <c r="Y58" s="128"/>
+      <c r="Z58" s="128"/>
+      <c r="AA58" s="128"/>
     </row>
     <row r="59" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="84"/>
-      <c r="C59" s="84"/>
-      <c r="D59" s="84"/>
-      <c r="E59" s="84"/>
-      <c r="F59" s="84"/>
-      <c r="G59" s="164"/>
-      <c r="H59" s="80"/>
-      <c r="I59" s="81"/>
-      <c r="J59" s="81"/>
-      <c r="K59" s="81"/>
-      <c r="L59" s="81"/>
-      <c r="M59" s="81"/>
-      <c r="N59" s="82"/>
-      <c r="O59" s="80"/>
-      <c r="P59" s="81"/>
-      <c r="Q59" s="81"/>
-      <c r="R59" s="81"/>
-      <c r="S59" s="81"/>
-      <c r="T59" s="81"/>
-      <c r="U59" s="82"/>
-      <c r="V59" s="83"/>
-      <c r="W59" s="84"/>
-      <c r="X59" s="84"/>
-      <c r="Y59" s="84"/>
-      <c r="Z59" s="84"/>
-      <c r="AA59" s="84"/>
+      <c r="B59" s="123"/>
+      <c r="C59" s="123"/>
+      <c r="D59" s="123"/>
+      <c r="E59" s="123"/>
+      <c r="F59" s="123"/>
+      <c r="G59" s="134"/>
+      <c r="H59" s="119"/>
+      <c r="I59" s="120"/>
+      <c r="J59" s="120"/>
+      <c r="K59" s="120"/>
+      <c r="L59" s="120"/>
+      <c r="M59" s="120"/>
+      <c r="N59" s="121"/>
+      <c r="O59" s="119"/>
+      <c r="P59" s="120"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="120"/>
+      <c r="S59" s="120"/>
+      <c r="T59" s="120"/>
+      <c r="U59" s="121"/>
+      <c r="V59" s="122"/>
+      <c r="W59" s="123"/>
+      <c r="X59" s="123"/>
+      <c r="Y59" s="123"/>
+      <c r="Z59" s="123"/>
+      <c r="AA59" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="120">
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="O55:U55"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:X15"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="G28:N28"/>
+    <mergeCell ref="O22:AA22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="Z23:Z24"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="AA23:AA24"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:X16"/>
+    <mergeCell ref="Y16:AA16"/>
+    <mergeCell ref="O17:AA17"/>
+    <mergeCell ref="O18:AA18"/>
+    <mergeCell ref="O19:S19"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="G25:N25"/>
+    <mergeCell ref="G26:N26"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="O2:AA3"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="V4:AA4"/>
+    <mergeCell ref="O8:AA8"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="O12:AA12"/>
+    <mergeCell ref="O13:AA13"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:X14"/>
+    <mergeCell ref="H57:N57"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="H55:N55"/>
+    <mergeCell ref="G23:N24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="V55:AA55"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="G29:N29"/>
+    <mergeCell ref="G30:N30"/>
+    <mergeCell ref="G31:N31"/>
+    <mergeCell ref="G50:N50"/>
+    <mergeCell ref="G51:N51"/>
+    <mergeCell ref="G52:N52"/>
+    <mergeCell ref="G53:N53"/>
+    <mergeCell ref="G54:N54"/>
+    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="G37:N37"/>
     <mergeCell ref="G38:N38"/>
     <mergeCell ref="G39:N39"/>
     <mergeCell ref="G40:N40"/>
@@ -7077,102 +8537,6 @@
     <mergeCell ref="H58:N58"/>
     <mergeCell ref="H59:N59"/>
     <mergeCell ref="H56:N56"/>
-    <mergeCell ref="H57:N57"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="H55:N55"/>
-    <mergeCell ref="G23:N24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="V55:AA55"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="G29:N29"/>
-    <mergeCell ref="G30:N30"/>
-    <mergeCell ref="G31:N31"/>
-    <mergeCell ref="G50:N50"/>
-    <mergeCell ref="G51:N51"/>
-    <mergeCell ref="G52:N52"/>
-    <mergeCell ref="G53:N53"/>
-    <mergeCell ref="G54:N54"/>
-    <mergeCell ref="G32:N32"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="G36:N36"/>
-    <mergeCell ref="G37:N37"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="G26:N26"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="O2:AA3"/>
-    <mergeCell ref="O4:U4"/>
-    <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="O8:AA8"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="Y15:AA15"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="O12:AA12"/>
-    <mergeCell ref="O13:AA13"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:X14"/>
-    <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:X16"/>
-    <mergeCell ref="Y16:AA16"/>
-    <mergeCell ref="O17:AA17"/>
-    <mergeCell ref="O18:AA18"/>
-    <mergeCell ref="O19:S19"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="O22:AA22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:W24"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="Z23:Z24"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="AA23:AA24"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="O55:U55"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:X15"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="G28:N28"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -7211,24 +8575,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B2" s="168" t="s">
+      <c r="B2" s="165" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="168"/>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
-      <c r="F2" s="168"/>
-      <c r="G2" s="168"/>
-      <c r="H2" s="168"/>
-      <c r="I2" s="168"/>
-      <c r="J2" s="168"/>
-      <c r="K2" s="168"/>
-      <c r="L2" s="168"/>
-      <c r="M2" s="168"/>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
+      <c r="G2" s="165"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="165"/>
+      <c r="J2" s="165"/>
+      <c r="K2" s="165"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="165"/>
+      <c r="N2" s="165"/>
+      <c r="O2" s="165"/>
+      <c r="P2" s="165"/>
+      <c r="Q2" s="165"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="67"/>
@@ -7267,24 +8631,24 @@
       <c r="Q4" s="67"/>
     </row>
     <row r="5" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="165" t="s">
+      <c r="B5" s="166" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="165"/>
-      <c r="D5" s="165"/>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="165"/>
-      <c r="I5" s="165"/>
-      <c r="J5" s="165"/>
-      <c r="K5" s="165"/>
-      <c r="L5" s="165"/>
-      <c r="M5" s="165"/>
-      <c r="N5" s="165"/>
-      <c r="O5" s="165"/>
-      <c r="P5" s="165"/>
-      <c r="Q5" s="165"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="166"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="166"/>
+      <c r="I5" s="166"/>
+      <c r="J5" s="166"/>
+      <c r="K5" s="166"/>
+      <c r="L5" s="166"/>
+      <c r="M5" s="166"/>
+      <c r="N5" s="166"/>
+      <c r="O5" s="166"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="166"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="67"/>
@@ -7435,24 +8799,24 @@
       <c r="Q12" s="67"/>
     </row>
     <row r="13" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="165" t="s">
+      <c r="B13" s="166" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="165"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165"/>
-      <c r="F13" s="165"/>
-      <c r="G13" s="165"/>
-      <c r="H13" s="165"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="165"/>
-      <c r="K13" s="165"/>
-      <c r="L13" s="165"/>
-      <c r="M13" s="165"/>
-      <c r="N13" s="165"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="165"/>
-      <c r="Q13" s="165"/>
+      <c r="C13" s="166"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="166"/>
+      <c r="K13" s="166"/>
+      <c r="L13" s="166"/>
+      <c r="M13" s="166"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="166"/>
+      <c r="P13" s="166"/>
+      <c r="Q13" s="166"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="67"/>
@@ -7460,12 +8824,12 @@
         <v>81</v>
       </c>
       <c r="D14" s="67"/>
-      <c r="E14" s="166" t="s">
+      <c r="E14" s="167" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="166"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="166"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="167"/>
+      <c r="H14" s="167"/>
       <c r="I14" s="72"/>
       <c r="J14" s="67"/>
       <c r="K14" s="67"/>
@@ -7504,8 +8868,8 @@
         <v>91</v>
       </c>
       <c r="F16" s="75"/>
-      <c r="G16" s="167"/>
-      <c r="H16" s="167"/>
+      <c r="G16" s="168"/>
+      <c r="H16" s="168"/>
       <c r="I16" s="72"/>
       <c r="J16" s="67"/>
       <c r="K16" s="74"/>
@@ -7593,24 +8957,24 @@
       <c r="Q20" s="67"/>
     </row>
     <row r="21" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="165" t="s">
+      <c r="B21" s="166" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="165"/>
-      <c r="D21" s="165"/>
-      <c r="E21" s="165"/>
-      <c r="F21" s="165"/>
-      <c r="G21" s="165"/>
-      <c r="H21" s="165"/>
-      <c r="I21" s="165"/>
-      <c r="J21" s="165"/>
-      <c r="K21" s="165"/>
-      <c r="L21" s="165"/>
-      <c r="M21" s="165"/>
-      <c r="N21" s="165"/>
-      <c r="O21" s="165"/>
-      <c r="P21" s="165"/>
-      <c r="Q21" s="165"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="166"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="166"/>
+      <c r="K21" s="166"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="166"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="166"/>
+      <c r="P21" s="166"/>
+      <c r="Q21" s="166"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="67"/>
@@ -7705,24 +9069,24 @@
       <c r="Q25" s="67"/>
     </row>
     <row r="26" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="165" t="s">
+      <c r="B26" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="165"/>
-      <c r="D26" s="165"/>
-      <c r="E26" s="165"/>
-      <c r="F26" s="165"/>
-      <c r="G26" s="165"/>
-      <c r="H26" s="165"/>
-      <c r="I26" s="165"/>
-      <c r="J26" s="165"/>
-      <c r="K26" s="165"/>
-      <c r="L26" s="165"/>
-      <c r="M26" s="165"/>
-      <c r="N26" s="165"/>
-      <c r="O26" s="165"/>
-      <c r="P26" s="165"/>
-      <c r="Q26" s="165"/>
+      <c r="C26" s="166"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="166"/>
+      <c r="F26" s="166"/>
+      <c r="G26" s="166"/>
+      <c r="H26" s="166"/>
+      <c r="I26" s="166"/>
+      <c r="J26" s="166"/>
+      <c r="K26" s="166"/>
+      <c r="L26" s="166"/>
+      <c r="M26" s="166"/>
+      <c r="N26" s="166"/>
+      <c r="O26" s="166"/>
+      <c r="P26" s="166"/>
+      <c r="Q26" s="166"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="67"/>
@@ -8269,24 +9633,24 @@
       <c r="Q52" s="67"/>
     </row>
     <row r="53" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="165" t="s">
+      <c r="B53" s="166" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="165"/>
-      <c r="D53" s="165"/>
-      <c r="E53" s="165"/>
-      <c r="F53" s="165"/>
-      <c r="G53" s="165"/>
-      <c r="H53" s="165"/>
-      <c r="I53" s="165"/>
-      <c r="J53" s="165"/>
-      <c r="K53" s="165"/>
-      <c r="L53" s="165"/>
-      <c r="M53" s="165"/>
-      <c r="N53" s="165"/>
-      <c r="O53" s="165"/>
-      <c r="P53" s="165"/>
-      <c r="Q53" s="165"/>
+      <c r="C53" s="166"/>
+      <c r="D53" s="166"/>
+      <c r="E53" s="166"/>
+      <c r="F53" s="166"/>
+      <c r="G53" s="166"/>
+      <c r="H53" s="166"/>
+      <c r="I53" s="166"/>
+      <c r="J53" s="166"/>
+      <c r="K53" s="166"/>
+      <c r="L53" s="166"/>
+      <c r="M53" s="166"/>
+      <c r="N53" s="166"/>
+      <c r="O53" s="166"/>
+      <c r="P53" s="166"/>
+      <c r="Q53" s="166"/>
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="67"/>
@@ -8582,17 +9946,2950 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B53:Q53"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B5:Q5"/>
     <mergeCell ref="B13:Q13"/>
     <mergeCell ref="B21:Q21"/>
     <mergeCell ref="B26:Q26"/>
-    <mergeCell ref="B53:Q53"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="74" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FBFCC4C-AA9B-410E-88E2-C384CCD47975}">
+  <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1:AY90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="3.85546875" customWidth="1"/>
+    <col min="4" max="4" width="2.140625" customWidth="1"/>
+    <col min="5" max="5" width="0.7109375" customWidth="1"/>
+    <col min="6" max="49" width="1.5703125" customWidth="1"/>
+    <col min="50" max="50" width="2" customWidth="1"/>
+    <col min="51" max="51" width="2.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="169" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="169"/>
+      <c r="O1" s="169"/>
+      <c r="P1" s="169"/>
+      <c r="Q1" s="169"/>
+      <c r="R1" s="169"/>
+      <c r="S1" s="169"/>
+      <c r="T1" s="169"/>
+      <c r="U1" s="169"/>
+      <c r="V1" s="169"/>
+      <c r="W1" s="169"/>
+      <c r="X1" s="169"/>
+      <c r="Y1" s="169"/>
+      <c r="Z1" s="169"/>
+      <c r="AA1" s="169"/>
+      <c r="AB1" s="169"/>
+      <c r="AC1" s="169"/>
+      <c r="AD1" s="169"/>
+      <c r="AE1" s="169"/>
+      <c r="AF1" s="169"/>
+      <c r="AG1" s="169"/>
+      <c r="AH1" s="169"/>
+      <c r="AI1" s="169"/>
+      <c r="AJ1" s="169"/>
+      <c r="AK1" s="169"/>
+      <c r="AL1" s="169"/>
+      <c r="AM1" s="169"/>
+      <c r="AN1" s="169"/>
+      <c r="AO1" s="169"/>
+      <c r="AP1" s="169"/>
+      <c r="AQ1" s="169"/>
+      <c r="AR1" s="169"/>
+      <c r="AS1" s="169"/>
+      <c r="AT1" s="169"/>
+      <c r="AU1" s="169"/>
+      <c r="AV1" s="169"/>
+      <c r="AW1" s="169"/>
+      <c r="AX1" s="169"/>
+    </row>
+    <row r="2" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="169"/>
+      <c r="Q2" s="169"/>
+      <c r="R2" s="169"/>
+      <c r="S2" s="169"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="169"/>
+      <c r="V2" s="169"/>
+      <c r="W2" s="169"/>
+      <c r="X2" s="169"/>
+      <c r="Y2" s="169"/>
+      <c r="Z2" s="169"/>
+      <c r="AA2" s="169"/>
+      <c r="AB2" s="169"/>
+      <c r="AC2" s="169"/>
+      <c r="AD2" s="169"/>
+      <c r="AE2" s="169"/>
+      <c r="AF2" s="169"/>
+      <c r="AG2" s="169"/>
+      <c r="AH2" s="169"/>
+      <c r="AI2" s="169"/>
+      <c r="AJ2" s="169"/>
+      <c r="AK2" s="169"/>
+      <c r="AL2" s="169"/>
+      <c r="AM2" s="169"/>
+      <c r="AN2" s="169"/>
+      <c r="AO2" s="169"/>
+      <c r="AP2" s="169"/>
+      <c r="AQ2" s="169"/>
+      <c r="AR2" s="169"/>
+      <c r="AS2" s="169"/>
+      <c r="AT2" s="169"/>
+      <c r="AU2" s="169"/>
+      <c r="AV2" s="169"/>
+      <c r="AW2" s="169"/>
+      <c r="AX2" s="169"/>
+    </row>
+    <row r="3" spans="1:51" ht="7.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <f>H3-1</f>
+        <v>9</v>
+      </c>
+      <c r="L3">
+        <f>J3-1</f>
+        <v>8</v>
+      </c>
+      <c r="N3">
+        <f>L3-1</f>
+        <v>7</v>
+      </c>
+      <c r="P3">
+        <f>N3-1</f>
+        <v>6</v>
+      </c>
+      <c r="R3">
+        <f>P3-1</f>
+        <v>5</v>
+      </c>
+      <c r="T3">
+        <f>R3-1</f>
+        <v>4</v>
+      </c>
+      <c r="V3">
+        <f>T3-1</f>
+        <v>3</v>
+      </c>
+      <c r="X3">
+        <f>V3-1</f>
+        <v>2</v>
+      </c>
+      <c r="Z3">
+        <f>X3-1</f>
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <f>AD3+1</f>
+        <v>2</v>
+      </c>
+      <c r="AH3">
+        <f>AF3+1</f>
+        <v>3</v>
+      </c>
+      <c r="AJ3">
+        <f>AH3+1</f>
+        <v>4</v>
+      </c>
+      <c r="AL3">
+        <f>AJ3+1</f>
+        <v>5</v>
+      </c>
+      <c r="AN3">
+        <f>AL3+1</f>
+        <v>6</v>
+      </c>
+      <c r="AP3">
+        <f>AN3+1</f>
+        <v>7</v>
+      </c>
+      <c r="AR3">
+        <f>AP3+1</f>
+        <v>8</v>
+      </c>
+      <c r="AT3">
+        <f>AR3+1</f>
+        <v>9</v>
+      </c>
+      <c r="AV3">
+        <v>10</v>
+      </c>
+      <c r="AW3">
+        <v>11</v>
+      </c>
+      <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
+        <f>AT3+1</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="171" t="str">
+        <f>CONCATENATE("-",H3,"°")</f>
+        <v>-10°</v>
+      </c>
+      <c r="H5" s="171"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="172"/>
+      <c r="O5" s="172"/>
+      <c r="P5" s="172"/>
+      <c r="Q5" s="173" t="str">
+        <f>CONCATENATE("-",R3,"°")</f>
+        <v>-5°</v>
+      </c>
+      <c r="R5" s="173"/>
+      <c r="S5" s="172"/>
+      <c r="T5" s="172"/>
+      <c r="U5" s="172"/>
+      <c r="V5" s="172"/>
+      <c r="W5" s="174"/>
+      <c r="X5" s="174"/>
+      <c r="Y5" s="172"/>
+      <c r="Z5" s="172"/>
+      <c r="AA5" s="173" t="str">
+        <f>CONCATENATE(AB3,"°")</f>
+        <v>0°</v>
+      </c>
+      <c r="AB5" s="173"/>
+      <c r="AC5" s="172"/>
+      <c r="AD5" s="172"/>
+      <c r="AE5" s="175"/>
+      <c r="AF5" s="175"/>
+      <c r="AG5" s="172"/>
+      <c r="AH5" s="172"/>
+      <c r="AI5" s="172"/>
+      <c r="AJ5" s="172"/>
+      <c r="AK5" s="173" t="str">
+        <f>CONCATENATE(AL3,"°")</f>
+        <v>5°</v>
+      </c>
+      <c r="AL5" s="173"/>
+      <c r="AM5" s="172"/>
+      <c r="AN5" s="172"/>
+      <c r="AO5" s="172"/>
+      <c r="AP5" s="172"/>
+      <c r="AQ5" s="172"/>
+      <c r="AR5" s="172"/>
+      <c r="AS5" s="172"/>
+      <c r="AT5" s="172"/>
+      <c r="AU5" s="173" t="str">
+        <f>CONCATENATE(AV3,"°")</f>
+        <v>10°</v>
+      </c>
+      <c r="AV5" s="173"/>
+      <c r="AW5" s="172"/>
+      <c r="AX5" s="170"/>
+      <c r="AY5" s="170"/>
+    </row>
+    <row r="6" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="170"/>
+      <c r="E6" s="176" t="str">
+        <f>CONCATENATE("-",F3,"°")</f>
+        <v>-11°</v>
+      </c>
+      <c r="F6" s="176"/>
+      <c r="G6" s="171"/>
+      <c r="H6" s="171"/>
+      <c r="I6" s="177" t="str">
+        <f>CONCATENATE("-",J3,"°")</f>
+        <v>-9°</v>
+      </c>
+      <c r="J6" s="177"/>
+      <c r="K6" s="177" t="str">
+        <f>CONCATENATE("-",L3,"°")</f>
+        <v>-8°</v>
+      </c>
+      <c r="L6" s="177"/>
+      <c r="M6" s="177" t="str">
+        <f>CONCATENATE("-",N3,"°")</f>
+        <v>-7°</v>
+      </c>
+      <c r="N6" s="177"/>
+      <c r="O6" s="177" t="str">
+        <f>CONCATENATE("-",P3,"°")</f>
+        <v>-6°</v>
+      </c>
+      <c r="P6" s="177"/>
+      <c r="Q6" s="173"/>
+      <c r="R6" s="173"/>
+      <c r="S6" s="177" t="str">
+        <f>CONCATENATE("-",T3,"°")</f>
+        <v>-4°</v>
+      </c>
+      <c r="T6" s="177"/>
+      <c r="U6" s="177" t="str">
+        <f>CONCATENATE("-",V3,"°")</f>
+        <v>-3°</v>
+      </c>
+      <c r="V6" s="177"/>
+      <c r="W6" s="177" t="str">
+        <f>CONCATENATE("-",X3,"°")</f>
+        <v>-2°</v>
+      </c>
+      <c r="X6" s="177"/>
+      <c r="Y6" s="177" t="str">
+        <f>CONCATENATE("-",Z3,"°")</f>
+        <v>-1°</v>
+      </c>
+      <c r="Z6" s="177"/>
+      <c r="AA6" s="173"/>
+      <c r="AB6" s="173"/>
+      <c r="AC6" s="177" t="str">
+        <f>CONCATENATE(AD3,"°")</f>
+        <v>1°</v>
+      </c>
+      <c r="AD6" s="177"/>
+      <c r="AE6" s="177" t="str">
+        <f>CONCATENATE(AF3,"°")</f>
+        <v>2°</v>
+      </c>
+      <c r="AF6" s="177"/>
+      <c r="AG6" s="177" t="str">
+        <f>CONCATENATE(AH3,"°")</f>
+        <v>3°</v>
+      </c>
+      <c r="AH6" s="177"/>
+      <c r="AI6" s="177" t="str">
+        <f>CONCATENATE(AJ3,"°")</f>
+        <v>4°</v>
+      </c>
+      <c r="AJ6" s="177"/>
+      <c r="AK6" s="173"/>
+      <c r="AL6" s="173"/>
+      <c r="AM6" s="177" t="str">
+        <f>CONCATENATE(AN3,"°")</f>
+        <v>6°</v>
+      </c>
+      <c r="AN6" s="177"/>
+      <c r="AO6" s="177" t="str">
+        <f>CONCATENATE(AP3,"°")</f>
+        <v>7°</v>
+      </c>
+      <c r="AP6" s="177"/>
+      <c r="AQ6" s="177" t="str">
+        <f>CONCATENATE(AR3,"°")</f>
+        <v>8°</v>
+      </c>
+      <c r="AR6" s="177"/>
+      <c r="AS6" s="177" t="str">
+        <f>CONCATENATE(AT3,"°")</f>
+        <v>9°</v>
+      </c>
+      <c r="AT6" s="177"/>
+      <c r="AU6" s="173"/>
+      <c r="AV6" s="173"/>
+      <c r="AW6" s="177" t="str">
+        <f>CONCATENATE(AX3,"°")</f>
+        <v>11°</v>
+      </c>
+      <c r="AX6" s="177"/>
+      <c r="AY6" s="170"/>
+    </row>
+    <row r="7" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="178"/>
+      <c r="G7" s="179"/>
+      <c r="H7" s="180"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="178"/>
+      <c r="M7" s="178"/>
+      <c r="N7" s="178"/>
+      <c r="O7" s="178"/>
+      <c r="P7" s="178"/>
+      <c r="Q7" s="179"/>
+      <c r="R7" s="181"/>
+      <c r="S7" s="182"/>
+      <c r="T7" s="178"/>
+      <c r="U7" s="178"/>
+      <c r="V7" s="178"/>
+      <c r="W7" s="178"/>
+      <c r="X7" s="178"/>
+      <c r="Y7" s="178"/>
+      <c r="Z7" s="178"/>
+      <c r="AA7" s="178"/>
+      <c r="AB7" s="180"/>
+      <c r="AC7" s="178"/>
+      <c r="AD7" s="178"/>
+      <c r="AE7" s="178"/>
+      <c r="AF7" s="178"/>
+      <c r="AG7" s="178"/>
+      <c r="AH7" s="178"/>
+      <c r="AI7" s="178"/>
+      <c r="AJ7" s="178"/>
+      <c r="AK7" s="178"/>
+      <c r="AL7" s="180"/>
+      <c r="AM7" s="178"/>
+      <c r="AN7" s="178"/>
+      <c r="AO7" s="178"/>
+      <c r="AP7" s="178"/>
+      <c r="AQ7" s="178"/>
+      <c r="AR7" s="178"/>
+      <c r="AS7" s="178"/>
+      <c r="AT7" s="178"/>
+      <c r="AU7" s="178"/>
+      <c r="AV7" s="180"/>
+      <c r="AW7" s="178"/>
+    </row>
+    <row r="8" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="183" t="str">
+        <f>CONCATENATE(B8,"°")</f>
+        <v>0°</v>
+      </c>
+      <c r="D8" s="183"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="178"/>
+      <c r="G8" s="179"/>
+      <c r="H8" s="180"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="178"/>
+      <c r="K8" s="178"/>
+      <c r="L8" s="178"/>
+      <c r="M8" s="178"/>
+      <c r="N8" s="178"/>
+      <c r="O8" s="178"/>
+      <c r="P8" s="178"/>
+      <c r="Q8" s="179"/>
+      <c r="R8" s="181"/>
+      <c r="S8" s="182"/>
+      <c r="T8" s="178"/>
+      <c r="U8" s="178"/>
+      <c r="V8" s="178"/>
+      <c r="W8" s="178"/>
+      <c r="X8" s="178"/>
+      <c r="Y8" s="178"/>
+      <c r="Z8" s="178"/>
+      <c r="AA8" s="178"/>
+      <c r="AB8" s="180"/>
+      <c r="AC8" s="178"/>
+      <c r="AD8" s="178"/>
+      <c r="AE8" s="178"/>
+      <c r="AF8" s="178"/>
+      <c r="AG8" s="178"/>
+      <c r="AH8" s="178"/>
+      <c r="AI8" s="178"/>
+      <c r="AJ8" s="178"/>
+      <c r="AK8" s="178"/>
+      <c r="AL8" s="180"/>
+      <c r="AM8" s="178"/>
+      <c r="AN8" s="178"/>
+      <c r="AO8" s="178"/>
+      <c r="AP8" s="178"/>
+      <c r="AQ8" s="178"/>
+      <c r="AR8" s="178"/>
+      <c r="AS8" s="178"/>
+      <c r="AT8" s="178"/>
+      <c r="AU8" s="178"/>
+      <c r="AV8" s="180"/>
+      <c r="AW8" s="178"/>
+    </row>
+    <row r="9" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="183"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="185"/>
+      <c r="G9" s="186"/>
+      <c r="H9" s="187"/>
+      <c r="I9" s="186"/>
+      <c r="J9" s="188"/>
+      <c r="K9" s="185"/>
+      <c r="L9" s="188"/>
+      <c r="M9" s="185"/>
+      <c r="N9" s="188"/>
+      <c r="O9" s="185"/>
+      <c r="P9" s="188"/>
+      <c r="Q9" s="186"/>
+      <c r="R9" s="187"/>
+      <c r="S9" s="185"/>
+      <c r="T9" s="188"/>
+      <c r="U9" s="185"/>
+      <c r="V9" s="188"/>
+      <c r="W9" s="185"/>
+      <c r="X9" s="188"/>
+      <c r="Y9" s="185"/>
+      <c r="Z9" s="188"/>
+      <c r="AA9" s="186"/>
+      <c r="AB9" s="187"/>
+      <c r="AC9" s="185"/>
+      <c r="AD9" s="188"/>
+      <c r="AE9" s="185"/>
+      <c r="AF9" s="188"/>
+      <c r="AG9" s="185"/>
+      <c r="AH9" s="188"/>
+      <c r="AI9" s="185"/>
+      <c r="AJ9" s="188"/>
+      <c r="AK9" s="186"/>
+      <c r="AL9" s="187"/>
+      <c r="AM9" s="185"/>
+      <c r="AN9" s="188"/>
+      <c r="AO9" s="185"/>
+      <c r="AP9" s="188"/>
+      <c r="AQ9" s="185"/>
+      <c r="AR9" s="188"/>
+      <c r="AS9" s="185"/>
+      <c r="AT9" s="188"/>
+      <c r="AU9" s="186"/>
+      <c r="AV9" s="187"/>
+      <c r="AW9" s="185"/>
+    </row>
+    <row r="10" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f>B8+$A$8</f>
+        <v>20</v>
+      </c>
+      <c r="C10" s="183" t="str">
+        <f>CONCATENATE(B10,"°")</f>
+        <v>20°</v>
+      </c>
+      <c r="D10" s="183"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="191"/>
+      <c r="I10" s="190"/>
+      <c r="J10" s="192"/>
+      <c r="K10" s="189"/>
+      <c r="L10" s="192"/>
+      <c r="M10" s="189"/>
+      <c r="N10" s="192"/>
+      <c r="O10" s="189"/>
+      <c r="P10" s="192"/>
+      <c r="Q10" s="190"/>
+      <c r="R10" s="191"/>
+      <c r="S10" s="189"/>
+      <c r="T10" s="192"/>
+      <c r="U10" s="189"/>
+      <c r="V10" s="192"/>
+      <c r="W10" s="189"/>
+      <c r="X10" s="192"/>
+      <c r="Y10" s="189"/>
+      <c r="Z10" s="192"/>
+      <c r="AA10" s="190"/>
+      <c r="AB10" s="191"/>
+      <c r="AC10" s="189"/>
+      <c r="AD10" s="192"/>
+      <c r="AE10" s="189"/>
+      <c r="AF10" s="192"/>
+      <c r="AG10" s="189"/>
+      <c r="AH10" s="192"/>
+      <c r="AI10" s="189"/>
+      <c r="AJ10" s="192"/>
+      <c r="AK10" s="190"/>
+      <c r="AL10" s="191"/>
+      <c r="AM10" s="189"/>
+      <c r="AN10" s="192"/>
+      <c r="AO10" s="189"/>
+      <c r="AP10" s="192"/>
+      <c r="AQ10" s="189"/>
+      <c r="AR10" s="192"/>
+      <c r="AS10" s="189"/>
+      <c r="AT10" s="192"/>
+      <c r="AU10" s="190"/>
+      <c r="AV10" s="191"/>
+      <c r="AW10" s="189"/>
+    </row>
+    <row r="11" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="193"/>
+      <c r="G11" s="194"/>
+      <c r="H11" s="195"/>
+      <c r="I11" s="194"/>
+      <c r="J11" s="196"/>
+      <c r="K11" s="193"/>
+      <c r="L11" s="196"/>
+      <c r="M11" s="193"/>
+      <c r="N11" s="196"/>
+      <c r="O11" s="193"/>
+      <c r="P11" s="196"/>
+      <c r="Q11" s="194"/>
+      <c r="R11" s="195"/>
+      <c r="S11" s="193"/>
+      <c r="T11" s="196"/>
+      <c r="U11" s="193"/>
+      <c r="V11" s="196"/>
+      <c r="W11" s="193"/>
+      <c r="X11" s="196"/>
+      <c r="Y11" s="193"/>
+      <c r="Z11" s="196"/>
+      <c r="AA11" s="194"/>
+      <c r="AB11" s="195"/>
+      <c r="AC11" s="193"/>
+      <c r="AD11" s="196"/>
+      <c r="AE11" s="193"/>
+      <c r="AF11" s="196"/>
+      <c r="AG11" s="193"/>
+      <c r="AH11" s="196"/>
+      <c r="AI11" s="193"/>
+      <c r="AJ11" s="196"/>
+      <c r="AK11" s="194"/>
+      <c r="AL11" s="195"/>
+      <c r="AM11" s="193"/>
+      <c r="AN11" s="196"/>
+      <c r="AO11" s="193"/>
+      <c r="AP11" s="196"/>
+      <c r="AQ11" s="193"/>
+      <c r="AR11" s="196"/>
+      <c r="AS11" s="193"/>
+      <c r="AT11" s="196"/>
+      <c r="AU11" s="194"/>
+      <c r="AV11" s="195"/>
+      <c r="AW11" s="193"/>
+    </row>
+    <row r="12" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f>B10+$A$8</f>
+        <v>40</v>
+      </c>
+      <c r="C12" s="183" t="str">
+        <f>CONCATENATE(B12,"°")</f>
+        <v>40°</v>
+      </c>
+      <c r="D12" s="183"/>
+      <c r="E12" s="184"/>
+      <c r="F12" s="197"/>
+      <c r="G12" s="198"/>
+      <c r="H12" s="199"/>
+      <c r="I12" s="198"/>
+      <c r="J12" s="200"/>
+      <c r="K12" s="197"/>
+      <c r="L12" s="200"/>
+      <c r="M12" s="197"/>
+      <c r="N12" s="200"/>
+      <c r="O12" s="197"/>
+      <c r="P12" s="200"/>
+      <c r="Q12" s="198"/>
+      <c r="R12" s="199"/>
+      <c r="S12" s="197"/>
+      <c r="T12" s="200"/>
+      <c r="U12" s="197"/>
+      <c r="V12" s="200"/>
+      <c r="W12" s="197"/>
+      <c r="X12" s="200"/>
+      <c r="Y12" s="197"/>
+      <c r="Z12" s="200"/>
+      <c r="AA12" s="198"/>
+      <c r="AB12" s="199"/>
+      <c r="AC12" s="197"/>
+      <c r="AD12" s="200"/>
+      <c r="AE12" s="197"/>
+      <c r="AF12" s="200"/>
+      <c r="AG12" s="197"/>
+      <c r="AH12" s="200"/>
+      <c r="AI12" s="197"/>
+      <c r="AJ12" s="200"/>
+      <c r="AK12" s="198"/>
+      <c r="AL12" s="199"/>
+      <c r="AM12" s="197"/>
+      <c r="AN12" s="200"/>
+      <c r="AO12" s="197"/>
+      <c r="AP12" s="200"/>
+      <c r="AQ12" s="197"/>
+      <c r="AR12" s="200"/>
+      <c r="AS12" s="197"/>
+      <c r="AT12" s="200"/>
+      <c r="AU12" s="198"/>
+      <c r="AV12" s="199"/>
+      <c r="AW12" s="197"/>
+    </row>
+    <row r="13" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="184"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="202"/>
+      <c r="H13" s="203"/>
+      <c r="I13" s="202"/>
+      <c r="J13" s="204"/>
+      <c r="K13" s="201"/>
+      <c r="L13" s="204"/>
+      <c r="M13" s="201"/>
+      <c r="N13" s="204"/>
+      <c r="O13" s="201"/>
+      <c r="P13" s="204"/>
+      <c r="Q13" s="202"/>
+      <c r="R13" s="203"/>
+      <c r="S13" s="201"/>
+      <c r="T13" s="204"/>
+      <c r="U13" s="201"/>
+      <c r="V13" s="204"/>
+      <c r="W13" s="201"/>
+      <c r="X13" s="204"/>
+      <c r="Y13" s="201"/>
+      <c r="Z13" s="204"/>
+      <c r="AA13" s="202"/>
+      <c r="AB13" s="203"/>
+      <c r="AC13" s="201"/>
+      <c r="AD13" s="204"/>
+      <c r="AE13" s="201"/>
+      <c r="AF13" s="204"/>
+      <c r="AG13" s="201"/>
+      <c r="AH13" s="204"/>
+      <c r="AI13" s="201"/>
+      <c r="AJ13" s="204"/>
+      <c r="AK13" s="202"/>
+      <c r="AL13" s="203"/>
+      <c r="AM13" s="201"/>
+      <c r="AN13" s="204"/>
+      <c r="AO13" s="201"/>
+      <c r="AP13" s="204"/>
+      <c r="AQ13" s="201"/>
+      <c r="AR13" s="204"/>
+      <c r="AS13" s="201"/>
+      <c r="AT13" s="204"/>
+      <c r="AU13" s="202"/>
+      <c r="AV13" s="203"/>
+      <c r="AW13" s="201"/>
+    </row>
+    <row r="14" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f>B12+$A$8</f>
+        <v>60</v>
+      </c>
+      <c r="C14" s="183" t="str">
+        <f>CONCATENATE(B14,"°")</f>
+        <v>60°</v>
+      </c>
+      <c r="D14" s="183"/>
+      <c r="E14" s="184"/>
+      <c r="F14" s="189"/>
+      <c r="G14" s="190"/>
+      <c r="H14" s="191"/>
+      <c r="I14" s="190"/>
+      <c r="J14" s="192"/>
+      <c r="K14" s="189"/>
+      <c r="L14" s="192"/>
+      <c r="M14" s="189"/>
+      <c r="N14" s="192"/>
+      <c r="O14" s="189"/>
+      <c r="P14" s="192"/>
+      <c r="Q14" s="190"/>
+      <c r="R14" s="191"/>
+      <c r="S14" s="189"/>
+      <c r="T14" s="192"/>
+      <c r="U14" s="189"/>
+      <c r="V14" s="192"/>
+      <c r="W14" s="189"/>
+      <c r="X14" s="192"/>
+      <c r="Y14" s="189"/>
+      <c r="Z14" s="192"/>
+      <c r="AA14" s="190"/>
+      <c r="AB14" s="191"/>
+      <c r="AC14" s="189"/>
+      <c r="AD14" s="192"/>
+      <c r="AE14" s="189"/>
+      <c r="AF14" s="192"/>
+      <c r="AG14" s="189"/>
+      <c r="AH14" s="192"/>
+      <c r="AI14" s="189"/>
+      <c r="AJ14" s="192"/>
+      <c r="AK14" s="190"/>
+      <c r="AL14" s="191"/>
+      <c r="AM14" s="189"/>
+      <c r="AN14" s="192"/>
+      <c r="AO14" s="189"/>
+      <c r="AP14" s="192"/>
+      <c r="AQ14" s="189"/>
+      <c r="AR14" s="192"/>
+      <c r="AS14" s="189"/>
+      <c r="AT14" s="192"/>
+      <c r="AU14" s="190"/>
+      <c r="AV14" s="191"/>
+      <c r="AW14" s="189"/>
+    </row>
+    <row r="15" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="183"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="184"/>
+      <c r="F15" s="193"/>
+      <c r="G15" s="194"/>
+      <c r="H15" s="195"/>
+      <c r="I15" s="194"/>
+      <c r="J15" s="196"/>
+      <c r="K15" s="193"/>
+      <c r="L15" s="196"/>
+      <c r="M15" s="193"/>
+      <c r="N15" s="196"/>
+      <c r="O15" s="193"/>
+      <c r="P15" s="196"/>
+      <c r="Q15" s="194"/>
+      <c r="R15" s="195"/>
+      <c r="S15" s="193"/>
+      <c r="T15" s="196"/>
+      <c r="U15" s="193"/>
+      <c r="V15" s="196"/>
+      <c r="W15" s="193"/>
+      <c r="X15" s="196"/>
+      <c r="Y15" s="193"/>
+      <c r="Z15" s="196"/>
+      <c r="AA15" s="194"/>
+      <c r="AB15" s="195"/>
+      <c r="AC15" s="193"/>
+      <c r="AD15" s="196"/>
+      <c r="AE15" s="193"/>
+      <c r="AF15" s="196"/>
+      <c r="AG15" s="193"/>
+      <c r="AH15" s="196"/>
+      <c r="AI15" s="193"/>
+      <c r="AJ15" s="196"/>
+      <c r="AK15" s="194"/>
+      <c r="AL15" s="195"/>
+      <c r="AM15" s="193"/>
+      <c r="AN15" s="196"/>
+      <c r="AO15" s="193"/>
+      <c r="AP15" s="196"/>
+      <c r="AQ15" s="193"/>
+      <c r="AR15" s="196"/>
+      <c r="AS15" s="193"/>
+      <c r="AT15" s="196"/>
+      <c r="AU15" s="194"/>
+      <c r="AV15" s="195"/>
+      <c r="AW15" s="193"/>
+    </row>
+    <row r="16" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f>B14+$A$8</f>
+        <v>80</v>
+      </c>
+      <c r="C16" s="183" t="str">
+        <f>CONCATENATE(B16,"°")</f>
+        <v>80°</v>
+      </c>
+      <c r="D16" s="183"/>
+      <c r="E16" s="184"/>
+      <c r="F16" s="205"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="206"/>
+      <c r="J16" s="208"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="208"/>
+      <c r="M16" s="205"/>
+      <c r="N16" s="208"/>
+      <c r="O16" s="205"/>
+      <c r="P16" s="208"/>
+      <c r="Q16" s="206"/>
+      <c r="R16" s="207"/>
+      <c r="S16" s="205"/>
+      <c r="T16" s="208"/>
+      <c r="U16" s="205"/>
+      <c r="V16" s="208"/>
+      <c r="W16" s="205"/>
+      <c r="X16" s="208"/>
+      <c r="Y16" s="205"/>
+      <c r="Z16" s="208"/>
+      <c r="AA16" s="206"/>
+      <c r="AB16" s="207"/>
+      <c r="AC16" s="205"/>
+      <c r="AD16" s="208"/>
+      <c r="AE16" s="205"/>
+      <c r="AF16" s="208"/>
+      <c r="AG16" s="205"/>
+      <c r="AH16" s="208"/>
+      <c r="AI16" s="205"/>
+      <c r="AJ16" s="208"/>
+      <c r="AK16" s="206"/>
+      <c r="AL16" s="207"/>
+      <c r="AM16" s="205"/>
+      <c r="AN16" s="208"/>
+      <c r="AO16" s="205"/>
+      <c r="AP16" s="208"/>
+      <c r="AQ16" s="205"/>
+      <c r="AR16" s="208"/>
+      <c r="AS16" s="205"/>
+      <c r="AT16" s="208"/>
+      <c r="AU16" s="206"/>
+      <c r="AV16" s="207"/>
+      <c r="AW16" s="205"/>
+    </row>
+    <row r="17" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="183"/>
+      <c r="D17" s="183"/>
+      <c r="E17" s="184"/>
+      <c r="F17" s="209"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="211"/>
+      <c r="I17" s="210"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="209"/>
+      <c r="L17" s="212"/>
+      <c r="M17" s="209"/>
+      <c r="N17" s="212"/>
+      <c r="O17" s="209"/>
+      <c r="P17" s="212"/>
+      <c r="Q17" s="210"/>
+      <c r="R17" s="211"/>
+      <c r="S17" s="209"/>
+      <c r="T17" s="212"/>
+      <c r="U17" s="209"/>
+      <c r="V17" s="212"/>
+      <c r="W17" s="209"/>
+      <c r="X17" s="212"/>
+      <c r="Y17" s="209"/>
+      <c r="Z17" s="212"/>
+      <c r="AA17" s="210"/>
+      <c r="AB17" s="211"/>
+      <c r="AC17" s="209"/>
+      <c r="AD17" s="212"/>
+      <c r="AE17" s="209"/>
+      <c r="AF17" s="212"/>
+      <c r="AG17" s="209"/>
+      <c r="AH17" s="212"/>
+      <c r="AI17" s="209"/>
+      <c r="AJ17" s="212"/>
+      <c r="AK17" s="210"/>
+      <c r="AL17" s="211"/>
+      <c r="AM17" s="209"/>
+      <c r="AN17" s="212"/>
+      <c r="AO17" s="209"/>
+      <c r="AP17" s="212"/>
+      <c r="AQ17" s="209"/>
+      <c r="AR17" s="212"/>
+      <c r="AS17" s="209"/>
+      <c r="AT17" s="212"/>
+      <c r="AU17" s="210"/>
+      <c r="AV17" s="211"/>
+      <c r="AW17" s="209"/>
+    </row>
+    <row r="18" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f>B16+$A$8</f>
+        <v>100</v>
+      </c>
+      <c r="C18" s="183" t="str">
+        <f>CONCATENATE(B18,"°")</f>
+        <v>100°</v>
+      </c>
+      <c r="D18" s="183"/>
+      <c r="E18" s="184"/>
+      <c r="F18" s="213"/>
+      <c r="G18" s="214"/>
+      <c r="H18" s="215"/>
+      <c r="I18" s="214"/>
+      <c r="J18" s="216"/>
+      <c r="K18" s="213"/>
+      <c r="L18" s="216"/>
+      <c r="M18" s="213"/>
+      <c r="N18" s="216"/>
+      <c r="O18" s="213"/>
+      <c r="P18" s="216"/>
+      <c r="Q18" s="214"/>
+      <c r="R18" s="215"/>
+      <c r="S18" s="213"/>
+      <c r="T18" s="216"/>
+      <c r="U18" s="213"/>
+      <c r="V18" s="216"/>
+      <c r="W18" s="213"/>
+      <c r="X18" s="216"/>
+      <c r="Y18" s="213"/>
+      <c r="Z18" s="216"/>
+      <c r="AA18" s="214"/>
+      <c r="AB18" s="215"/>
+      <c r="AC18" s="213"/>
+      <c r="AD18" s="216"/>
+      <c r="AE18" s="213"/>
+      <c r="AF18" s="216"/>
+      <c r="AG18" s="213"/>
+      <c r="AH18" s="216"/>
+      <c r="AI18" s="213"/>
+      <c r="AJ18" s="216"/>
+      <c r="AK18" s="214"/>
+      <c r="AL18" s="215"/>
+      <c r="AM18" s="213"/>
+      <c r="AN18" s="216"/>
+      <c r="AO18" s="213"/>
+      <c r="AP18" s="216"/>
+      <c r="AQ18" s="213"/>
+      <c r="AR18" s="216"/>
+      <c r="AS18" s="213"/>
+      <c r="AT18" s="216"/>
+      <c r="AU18" s="214"/>
+      <c r="AV18" s="215"/>
+      <c r="AW18" s="213"/>
+    </row>
+    <row r="19" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="184"/>
+      <c r="F19" s="193"/>
+      <c r="G19" s="194"/>
+      <c r="H19" s="195"/>
+      <c r="I19" s="194"/>
+      <c r="J19" s="196"/>
+      <c r="K19" s="193"/>
+      <c r="L19" s="196"/>
+      <c r="M19" s="193"/>
+      <c r="N19" s="196"/>
+      <c r="O19" s="193"/>
+      <c r="P19" s="196"/>
+      <c r="Q19" s="194"/>
+      <c r="R19" s="195"/>
+      <c r="S19" s="193"/>
+      <c r="T19" s="196"/>
+      <c r="U19" s="193"/>
+      <c r="V19" s="196"/>
+      <c r="W19" s="193"/>
+      <c r="X19" s="196"/>
+      <c r="Y19" s="193"/>
+      <c r="Z19" s="196"/>
+      <c r="AA19" s="194"/>
+      <c r="AB19" s="195"/>
+      <c r="AC19" s="193"/>
+      <c r="AD19" s="196"/>
+      <c r="AE19" s="193"/>
+      <c r="AF19" s="196"/>
+      <c r="AG19" s="193"/>
+      <c r="AH19" s="196"/>
+      <c r="AI19" s="193"/>
+      <c r="AJ19" s="196"/>
+      <c r="AK19" s="194"/>
+      <c r="AL19" s="195"/>
+      <c r="AM19" s="193"/>
+      <c r="AN19" s="196"/>
+      <c r="AO19" s="193"/>
+      <c r="AP19" s="196"/>
+      <c r="AQ19" s="193"/>
+      <c r="AR19" s="196"/>
+      <c r="AS19" s="193"/>
+      <c r="AT19" s="196"/>
+      <c r="AU19" s="194"/>
+      <c r="AV19" s="195"/>
+      <c r="AW19" s="193"/>
+    </row>
+    <row r="20" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f>B18+$A$8</f>
+        <v>120</v>
+      </c>
+      <c r="C20" s="183" t="str">
+        <f>CONCATENATE(B20,"°")</f>
+        <v>120°</v>
+      </c>
+      <c r="D20" s="183"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="205"/>
+      <c r="G20" s="206"/>
+      <c r="H20" s="207"/>
+      <c r="I20" s="206"/>
+      <c r="J20" s="208"/>
+      <c r="K20" s="205"/>
+      <c r="L20" s="208"/>
+      <c r="M20" s="205"/>
+      <c r="N20" s="208"/>
+      <c r="O20" s="205"/>
+      <c r="P20" s="208"/>
+      <c r="Q20" s="206"/>
+      <c r="R20" s="207"/>
+      <c r="S20" s="205"/>
+      <c r="T20" s="208"/>
+      <c r="U20" s="205"/>
+      <c r="V20" s="208"/>
+      <c r="W20" s="205"/>
+      <c r="X20" s="208"/>
+      <c r="Y20" s="205"/>
+      <c r="Z20" s="208"/>
+      <c r="AA20" s="206"/>
+      <c r="AB20" s="207"/>
+      <c r="AC20" s="205"/>
+      <c r="AD20" s="208"/>
+      <c r="AE20" s="205"/>
+      <c r="AF20" s="208"/>
+      <c r="AG20" s="205"/>
+      <c r="AH20" s="208"/>
+      <c r="AI20" s="205"/>
+      <c r="AJ20" s="208"/>
+      <c r="AK20" s="206"/>
+      <c r="AL20" s="207"/>
+      <c r="AM20" s="205"/>
+      <c r="AN20" s="208"/>
+      <c r="AO20" s="205"/>
+      <c r="AP20" s="208"/>
+      <c r="AQ20" s="205"/>
+      <c r="AR20" s="208"/>
+      <c r="AS20" s="205"/>
+      <c r="AT20" s="208"/>
+      <c r="AU20" s="206"/>
+      <c r="AV20" s="207"/>
+      <c r="AW20" s="205"/>
+    </row>
+    <row r="21" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="183"/>
+      <c r="D21" s="183"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="201"/>
+      <c r="G21" s="202"/>
+      <c r="H21" s="203"/>
+      <c r="I21" s="202"/>
+      <c r="J21" s="204"/>
+      <c r="K21" s="201"/>
+      <c r="L21" s="204"/>
+      <c r="M21" s="201"/>
+      <c r="N21" s="204"/>
+      <c r="O21" s="201"/>
+      <c r="P21" s="204"/>
+      <c r="Q21" s="202"/>
+      <c r="R21" s="203"/>
+      <c r="S21" s="201"/>
+      <c r="T21" s="204"/>
+      <c r="U21" s="201"/>
+      <c r="V21" s="204"/>
+      <c r="W21" s="201"/>
+      <c r="X21" s="204"/>
+      <c r="Y21" s="201"/>
+      <c r="Z21" s="204"/>
+      <c r="AA21" s="202"/>
+      <c r="AB21" s="203"/>
+      <c r="AC21" s="201"/>
+      <c r="AD21" s="204"/>
+      <c r="AE21" s="201"/>
+      <c r="AF21" s="204"/>
+      <c r="AG21" s="201"/>
+      <c r="AH21" s="204"/>
+      <c r="AI21" s="201"/>
+      <c r="AJ21" s="204"/>
+      <c r="AK21" s="202"/>
+      <c r="AL21" s="203"/>
+      <c r="AM21" s="201"/>
+      <c r="AN21" s="204"/>
+      <c r="AO21" s="201"/>
+      <c r="AP21" s="204"/>
+      <c r="AQ21" s="201"/>
+      <c r="AR21" s="204"/>
+      <c r="AS21" s="201"/>
+      <c r="AT21" s="204"/>
+      <c r="AU21" s="202"/>
+      <c r="AV21" s="203"/>
+      <c r="AW21" s="201"/>
+    </row>
+    <row r="22" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f>B20+$A$8</f>
+        <v>140</v>
+      </c>
+      <c r="C22" s="183" t="str">
+        <f>CONCATENATE(B22,"°")</f>
+        <v>140°</v>
+      </c>
+      <c r="D22" s="183"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="189"/>
+      <c r="G22" s="190"/>
+      <c r="H22" s="191"/>
+      <c r="I22" s="190"/>
+      <c r="J22" s="192"/>
+      <c r="K22" s="189"/>
+      <c r="L22" s="192"/>
+      <c r="M22" s="189"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="189"/>
+      <c r="P22" s="192"/>
+      <c r="Q22" s="190"/>
+      <c r="R22" s="191"/>
+      <c r="S22" s="189"/>
+      <c r="T22" s="192"/>
+      <c r="U22" s="189"/>
+      <c r="V22" s="192"/>
+      <c r="W22" s="189"/>
+      <c r="X22" s="192"/>
+      <c r="Y22" s="189"/>
+      <c r="Z22" s="192"/>
+      <c r="AA22" s="190"/>
+      <c r="AB22" s="191"/>
+      <c r="AC22" s="189"/>
+      <c r="AD22" s="192"/>
+      <c r="AE22" s="189"/>
+      <c r="AF22" s="192"/>
+      <c r="AG22" s="189"/>
+      <c r="AH22" s="192"/>
+      <c r="AI22" s="189"/>
+      <c r="AJ22" s="192"/>
+      <c r="AK22" s="190"/>
+      <c r="AL22" s="191"/>
+      <c r="AM22" s="189"/>
+      <c r="AN22" s="192"/>
+      <c r="AO22" s="189"/>
+      <c r="AP22" s="192"/>
+      <c r="AQ22" s="189"/>
+      <c r="AR22" s="192"/>
+      <c r="AS22" s="189"/>
+      <c r="AT22" s="192"/>
+      <c r="AU22" s="190"/>
+      <c r="AV22" s="191"/>
+      <c r="AW22" s="189"/>
+    </row>
+    <row r="23" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="183"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="205"/>
+      <c r="G23" s="206"/>
+      <c r="H23" s="207"/>
+      <c r="I23" s="206"/>
+      <c r="J23" s="208"/>
+      <c r="K23" s="205"/>
+      <c r="L23" s="208"/>
+      <c r="M23" s="205"/>
+      <c r="N23" s="208"/>
+      <c r="O23" s="205"/>
+      <c r="P23" s="208"/>
+      <c r="Q23" s="206"/>
+      <c r="R23" s="207"/>
+      <c r="S23" s="205"/>
+      <c r="T23" s="208"/>
+      <c r="U23" s="205"/>
+      <c r="V23" s="208"/>
+      <c r="W23" s="205"/>
+      <c r="X23" s="208"/>
+      <c r="Y23" s="205"/>
+      <c r="Z23" s="208"/>
+      <c r="AA23" s="206"/>
+      <c r="AB23" s="207"/>
+      <c r="AC23" s="205"/>
+      <c r="AD23" s="208"/>
+      <c r="AE23" s="205"/>
+      <c r="AF23" s="208"/>
+      <c r="AG23" s="205"/>
+      <c r="AH23" s="208"/>
+      <c r="AI23" s="205"/>
+      <c r="AJ23" s="208"/>
+      <c r="AK23" s="206"/>
+      <c r="AL23" s="207"/>
+      <c r="AM23" s="205"/>
+      <c r="AN23" s="208"/>
+      <c r="AO23" s="205"/>
+      <c r="AP23" s="208"/>
+      <c r="AQ23" s="205"/>
+      <c r="AR23" s="208"/>
+      <c r="AS23" s="205"/>
+      <c r="AT23" s="208"/>
+      <c r="AU23" s="206"/>
+      <c r="AV23" s="207"/>
+      <c r="AW23" s="205"/>
+    </row>
+    <row r="24" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f>B22+$A$8</f>
+        <v>160</v>
+      </c>
+      <c r="C24" s="183" t="str">
+        <f>CONCATENATE(B24,"°")</f>
+        <v>160°</v>
+      </c>
+      <c r="D24" s="183"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="205"/>
+      <c r="G24" s="206"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="206"/>
+      <c r="J24" s="208"/>
+      <c r="K24" s="205"/>
+      <c r="L24" s="208"/>
+      <c r="M24" s="205"/>
+      <c r="N24" s="208"/>
+      <c r="O24" s="205"/>
+      <c r="P24" s="208"/>
+      <c r="Q24" s="206"/>
+      <c r="R24" s="207"/>
+      <c r="S24" s="205"/>
+      <c r="T24" s="208"/>
+      <c r="U24" s="205"/>
+      <c r="V24" s="208"/>
+      <c r="W24" s="205"/>
+      <c r="X24" s="208"/>
+      <c r="Y24" s="205"/>
+      <c r="Z24" s="208"/>
+      <c r="AA24" s="206"/>
+      <c r="AB24" s="207"/>
+      <c r="AC24" s="205"/>
+      <c r="AD24" s="208"/>
+      <c r="AE24" s="205"/>
+      <c r="AF24" s="208"/>
+      <c r="AG24" s="205"/>
+      <c r="AH24" s="208"/>
+      <c r="AI24" s="205"/>
+      <c r="AJ24" s="208"/>
+      <c r="AK24" s="206"/>
+      <c r="AL24" s="207"/>
+      <c r="AM24" s="205"/>
+      <c r="AN24" s="208"/>
+      <c r="AO24" s="205"/>
+      <c r="AP24" s="208"/>
+      <c r="AQ24" s="205"/>
+      <c r="AR24" s="208"/>
+      <c r="AS24" s="205"/>
+      <c r="AT24" s="208"/>
+      <c r="AU24" s="206"/>
+      <c r="AV24" s="207"/>
+      <c r="AW24" s="205"/>
+    </row>
+    <row r="25" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="183"/>
+      <c r="D25" s="183"/>
+      <c r="E25" s="184"/>
+      <c r="F25" s="201"/>
+      <c r="G25" s="202"/>
+      <c r="H25" s="203"/>
+      <c r="I25" s="202"/>
+      <c r="J25" s="204"/>
+      <c r="K25" s="201"/>
+      <c r="L25" s="204"/>
+      <c r="M25" s="201"/>
+      <c r="N25" s="204"/>
+      <c r="O25" s="201"/>
+      <c r="P25" s="204"/>
+      <c r="Q25" s="202"/>
+      <c r="R25" s="203"/>
+      <c r="S25" s="201"/>
+      <c r="T25" s="204"/>
+      <c r="U25" s="201"/>
+      <c r="V25" s="204"/>
+      <c r="W25" s="201"/>
+      <c r="X25" s="204"/>
+      <c r="Y25" s="201"/>
+      <c r="Z25" s="204"/>
+      <c r="AA25" s="202"/>
+      <c r="AB25" s="203"/>
+      <c r="AC25" s="201"/>
+      <c r="AD25" s="204"/>
+      <c r="AE25" s="201"/>
+      <c r="AF25" s="204"/>
+      <c r="AG25" s="201"/>
+      <c r="AH25" s="204"/>
+      <c r="AI25" s="201"/>
+      <c r="AJ25" s="204"/>
+      <c r="AK25" s="202"/>
+      <c r="AL25" s="203"/>
+      <c r="AM25" s="201"/>
+      <c r="AN25" s="204"/>
+      <c r="AO25" s="201"/>
+      <c r="AP25" s="204"/>
+      <c r="AQ25" s="201"/>
+      <c r="AR25" s="204"/>
+      <c r="AS25" s="201"/>
+      <c r="AT25" s="204"/>
+      <c r="AU25" s="202"/>
+      <c r="AV25" s="203"/>
+      <c r="AW25" s="201"/>
+    </row>
+    <row r="26" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <f>B24+$A$8</f>
+        <v>180</v>
+      </c>
+      <c r="C26" s="183" t="str">
+        <f>CONCATENATE(B26,"°")</f>
+        <v>180°</v>
+      </c>
+      <c r="D26" s="183"/>
+      <c r="E26" s="184"/>
+      <c r="F26" s="197"/>
+      <c r="G26" s="198"/>
+      <c r="H26" s="199"/>
+      <c r="I26" s="198"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="197"/>
+      <c r="L26" s="200"/>
+      <c r="M26" s="197"/>
+      <c r="N26" s="200"/>
+      <c r="O26" s="197"/>
+      <c r="P26" s="200"/>
+      <c r="Q26" s="198"/>
+      <c r="R26" s="199"/>
+      <c r="S26" s="197"/>
+      <c r="T26" s="200"/>
+      <c r="U26" s="197"/>
+      <c r="V26" s="200"/>
+      <c r="W26" s="197"/>
+      <c r="X26" s="200"/>
+      <c r="Y26" s="197"/>
+      <c r="Z26" s="200"/>
+      <c r="AA26" s="198"/>
+      <c r="AB26" s="199"/>
+      <c r="AC26" s="197"/>
+      <c r="AD26" s="200"/>
+      <c r="AE26" s="197"/>
+      <c r="AF26" s="200"/>
+      <c r="AG26" s="197"/>
+      <c r="AH26" s="200"/>
+      <c r="AI26" s="197"/>
+      <c r="AJ26" s="200"/>
+      <c r="AK26" s="198"/>
+      <c r="AL26" s="199"/>
+      <c r="AM26" s="197"/>
+      <c r="AN26" s="200"/>
+      <c r="AO26" s="197"/>
+      <c r="AP26" s="200"/>
+      <c r="AQ26" s="197"/>
+      <c r="AR26" s="200"/>
+      <c r="AS26" s="197"/>
+      <c r="AT26" s="200"/>
+      <c r="AU26" s="198"/>
+      <c r="AV26" s="199"/>
+      <c r="AW26" s="197"/>
+    </row>
+    <row r="27" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="183"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="184"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="186"/>
+      <c r="H27" s="187"/>
+      <c r="I27" s="186"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="188"/>
+      <c r="M27" s="185"/>
+      <c r="N27" s="188"/>
+      <c r="O27" s="185"/>
+      <c r="P27" s="188"/>
+      <c r="Q27" s="186"/>
+      <c r="R27" s="187"/>
+      <c r="S27" s="185"/>
+      <c r="T27" s="188"/>
+      <c r="U27" s="185"/>
+      <c r="V27" s="188"/>
+      <c r="W27" s="185"/>
+      <c r="X27" s="188"/>
+      <c r="Y27" s="185"/>
+      <c r="Z27" s="188"/>
+      <c r="AA27" s="186"/>
+      <c r="AB27" s="187"/>
+      <c r="AC27" s="185"/>
+      <c r="AD27" s="188"/>
+      <c r="AE27" s="185"/>
+      <c r="AF27" s="188"/>
+      <c r="AG27" s="185"/>
+      <c r="AH27" s="188"/>
+      <c r="AI27" s="185"/>
+      <c r="AJ27" s="188"/>
+      <c r="AK27" s="186"/>
+      <c r="AL27" s="187"/>
+      <c r="AM27" s="185"/>
+      <c r="AN27" s="188"/>
+      <c r="AO27" s="185"/>
+      <c r="AP27" s="188"/>
+      <c r="AQ27" s="185"/>
+      <c r="AR27" s="188"/>
+      <c r="AS27" s="185"/>
+      <c r="AT27" s="188"/>
+      <c r="AU27" s="186"/>
+      <c r="AV27" s="187"/>
+      <c r="AW27" s="185"/>
+    </row>
+    <row r="28" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f>B26+$A$8</f>
+        <v>200</v>
+      </c>
+      <c r="C28" s="183" t="str">
+        <f>CONCATENATE(B28,"°")</f>
+        <v>200°</v>
+      </c>
+      <c r="D28" s="183"/>
+      <c r="E28" s="184"/>
+      <c r="F28" s="205"/>
+      <c r="G28" s="206"/>
+      <c r="H28" s="207"/>
+      <c r="I28" s="206"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="205"/>
+      <c r="L28" s="208"/>
+      <c r="M28" s="205"/>
+      <c r="N28" s="208"/>
+      <c r="O28" s="205"/>
+      <c r="P28" s="208"/>
+      <c r="Q28" s="206"/>
+      <c r="R28" s="207"/>
+      <c r="S28" s="205"/>
+      <c r="T28" s="208"/>
+      <c r="U28" s="205"/>
+      <c r="V28" s="208"/>
+      <c r="W28" s="205"/>
+      <c r="X28" s="208"/>
+      <c r="Y28" s="205"/>
+      <c r="Z28" s="208"/>
+      <c r="AA28" s="206"/>
+      <c r="AB28" s="207"/>
+      <c r="AC28" s="205"/>
+      <c r="AD28" s="208"/>
+      <c r="AE28" s="205"/>
+      <c r="AF28" s="208"/>
+      <c r="AG28" s="205"/>
+      <c r="AH28" s="208"/>
+      <c r="AI28" s="205"/>
+      <c r="AJ28" s="208"/>
+      <c r="AK28" s="206"/>
+      <c r="AL28" s="207"/>
+      <c r="AM28" s="205"/>
+      <c r="AN28" s="208"/>
+      <c r="AO28" s="205"/>
+      <c r="AP28" s="208"/>
+      <c r="AQ28" s="205"/>
+      <c r="AR28" s="208"/>
+      <c r="AS28" s="205"/>
+      <c r="AT28" s="208"/>
+      <c r="AU28" s="206"/>
+      <c r="AV28" s="207"/>
+      <c r="AW28" s="205"/>
+    </row>
+    <row r="29" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="183"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="201"/>
+      <c r="G29" s="202"/>
+      <c r="H29" s="203"/>
+      <c r="I29" s="202"/>
+      <c r="J29" s="204"/>
+      <c r="K29" s="201"/>
+      <c r="L29" s="204"/>
+      <c r="M29" s="201"/>
+      <c r="N29" s="204"/>
+      <c r="O29" s="201"/>
+      <c r="P29" s="204"/>
+      <c r="Q29" s="202"/>
+      <c r="R29" s="203"/>
+      <c r="S29" s="201"/>
+      <c r="T29" s="204"/>
+      <c r="U29" s="201"/>
+      <c r="V29" s="204"/>
+      <c r="W29" s="201"/>
+      <c r="X29" s="204"/>
+      <c r="Y29" s="201"/>
+      <c r="Z29" s="204"/>
+      <c r="AA29" s="202"/>
+      <c r="AB29" s="203"/>
+      <c r="AC29" s="201"/>
+      <c r="AD29" s="204"/>
+      <c r="AE29" s="201"/>
+      <c r="AF29" s="204"/>
+      <c r="AG29" s="201"/>
+      <c r="AH29" s="204"/>
+      <c r="AI29" s="201"/>
+      <c r="AJ29" s="204"/>
+      <c r="AK29" s="202"/>
+      <c r="AL29" s="203"/>
+      <c r="AM29" s="201"/>
+      <c r="AN29" s="204"/>
+      <c r="AO29" s="201"/>
+      <c r="AP29" s="204"/>
+      <c r="AQ29" s="201"/>
+      <c r="AR29" s="204"/>
+      <c r="AS29" s="201"/>
+      <c r="AT29" s="204"/>
+      <c r="AU29" s="202"/>
+      <c r="AV29" s="203"/>
+      <c r="AW29" s="201"/>
+    </row>
+    <row r="30" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <f>B28+$A$8</f>
+        <v>220</v>
+      </c>
+      <c r="C30" s="183" t="str">
+        <f>CONCATENATE(B30,"°")</f>
+        <v>220°</v>
+      </c>
+      <c r="D30" s="183"/>
+      <c r="E30" s="184"/>
+      <c r="F30" s="189"/>
+      <c r="G30" s="190"/>
+      <c r="H30" s="191"/>
+      <c r="I30" s="190"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="189"/>
+      <c r="L30" s="192"/>
+      <c r="M30" s="189"/>
+      <c r="N30" s="192"/>
+      <c r="O30" s="189"/>
+      <c r="P30" s="192"/>
+      <c r="Q30" s="190"/>
+      <c r="R30" s="191"/>
+      <c r="S30" s="189"/>
+      <c r="T30" s="192"/>
+      <c r="U30" s="189"/>
+      <c r="V30" s="192"/>
+      <c r="W30" s="189"/>
+      <c r="X30" s="192"/>
+      <c r="Y30" s="189"/>
+      <c r="Z30" s="192"/>
+      <c r="AA30" s="190"/>
+      <c r="AB30" s="191"/>
+      <c r="AC30" s="189"/>
+      <c r="AD30" s="192"/>
+      <c r="AE30" s="189"/>
+      <c r="AF30" s="192"/>
+      <c r="AG30" s="189"/>
+      <c r="AH30" s="192"/>
+      <c r="AI30" s="189"/>
+      <c r="AJ30" s="192"/>
+      <c r="AK30" s="190"/>
+      <c r="AL30" s="191"/>
+      <c r="AM30" s="189"/>
+      <c r="AN30" s="192"/>
+      <c r="AO30" s="189"/>
+      <c r="AP30" s="192"/>
+      <c r="AQ30" s="189"/>
+      <c r="AR30" s="192"/>
+      <c r="AS30" s="189"/>
+      <c r="AT30" s="192"/>
+      <c r="AU30" s="190"/>
+      <c r="AV30" s="191"/>
+      <c r="AW30" s="189"/>
+    </row>
+    <row r="31" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="183"/>
+      <c r="D31" s="183"/>
+      <c r="E31" s="184"/>
+      <c r="F31" s="205"/>
+      <c r="G31" s="206"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="206"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="205"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="205"/>
+      <c r="N31" s="208"/>
+      <c r="O31" s="205"/>
+      <c r="P31" s="208"/>
+      <c r="Q31" s="206"/>
+      <c r="R31" s="207"/>
+      <c r="S31" s="205"/>
+      <c r="T31" s="208"/>
+      <c r="U31" s="205"/>
+      <c r="V31" s="208"/>
+      <c r="W31" s="205"/>
+      <c r="X31" s="208"/>
+      <c r="Y31" s="205"/>
+      <c r="Z31" s="208"/>
+      <c r="AA31" s="206"/>
+      <c r="AB31" s="207"/>
+      <c r="AC31" s="205"/>
+      <c r="AD31" s="208"/>
+      <c r="AE31" s="205"/>
+      <c r="AF31" s="208"/>
+      <c r="AG31" s="205"/>
+      <c r="AH31" s="208"/>
+      <c r="AI31" s="205"/>
+      <c r="AJ31" s="208"/>
+      <c r="AK31" s="206"/>
+      <c r="AL31" s="207"/>
+      <c r="AM31" s="205"/>
+      <c r="AN31" s="208"/>
+      <c r="AO31" s="205"/>
+      <c r="AP31" s="208"/>
+      <c r="AQ31" s="205"/>
+      <c r="AR31" s="208"/>
+      <c r="AS31" s="205"/>
+      <c r="AT31" s="208"/>
+      <c r="AU31" s="206"/>
+      <c r="AV31" s="207"/>
+      <c r="AW31" s="205"/>
+    </row>
+    <row r="32" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <f>B30+$A$8</f>
+        <v>240</v>
+      </c>
+      <c r="C32" s="183" t="str">
+        <f>CONCATENATE(B32,"°")</f>
+        <v>240°</v>
+      </c>
+      <c r="D32" s="183"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="205"/>
+      <c r="G32" s="206"/>
+      <c r="H32" s="207"/>
+      <c r="I32" s="206"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="205"/>
+      <c r="L32" s="208"/>
+      <c r="M32" s="205"/>
+      <c r="N32" s="208"/>
+      <c r="O32" s="205"/>
+      <c r="P32" s="208"/>
+      <c r="Q32" s="206"/>
+      <c r="R32" s="207"/>
+      <c r="S32" s="205"/>
+      <c r="T32" s="208"/>
+      <c r="U32" s="205"/>
+      <c r="V32" s="208"/>
+      <c r="W32" s="205"/>
+      <c r="X32" s="208"/>
+      <c r="Y32" s="205"/>
+      <c r="Z32" s="208"/>
+      <c r="AA32" s="206"/>
+      <c r="AB32" s="207"/>
+      <c r="AC32" s="205"/>
+      <c r="AD32" s="208"/>
+      <c r="AE32" s="205"/>
+      <c r="AF32" s="208"/>
+      <c r="AG32" s="205"/>
+      <c r="AH32" s="208"/>
+      <c r="AI32" s="205"/>
+      <c r="AJ32" s="208"/>
+      <c r="AK32" s="206"/>
+      <c r="AL32" s="207"/>
+      <c r="AM32" s="205"/>
+      <c r="AN32" s="208"/>
+      <c r="AO32" s="205"/>
+      <c r="AP32" s="208"/>
+      <c r="AQ32" s="205"/>
+      <c r="AR32" s="208"/>
+      <c r="AS32" s="205"/>
+      <c r="AT32" s="208"/>
+      <c r="AU32" s="206"/>
+      <c r="AV32" s="207"/>
+      <c r="AW32" s="205"/>
+    </row>
+    <row r="33" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="183"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="184"/>
+      <c r="F33" s="201"/>
+      <c r="G33" s="202"/>
+      <c r="H33" s="203"/>
+      <c r="I33" s="202"/>
+      <c r="J33" s="204"/>
+      <c r="K33" s="201"/>
+      <c r="L33" s="204"/>
+      <c r="M33" s="201"/>
+      <c r="N33" s="204"/>
+      <c r="O33" s="201"/>
+      <c r="P33" s="204"/>
+      <c r="Q33" s="202"/>
+      <c r="R33" s="203"/>
+      <c r="S33" s="201"/>
+      <c r="T33" s="204"/>
+      <c r="U33" s="201"/>
+      <c r="V33" s="204"/>
+      <c r="W33" s="201"/>
+      <c r="X33" s="204"/>
+      <c r="Y33" s="201"/>
+      <c r="Z33" s="204"/>
+      <c r="AA33" s="202"/>
+      <c r="AB33" s="203"/>
+      <c r="AC33" s="201"/>
+      <c r="AD33" s="204"/>
+      <c r="AE33" s="201"/>
+      <c r="AF33" s="204"/>
+      <c r="AG33" s="201"/>
+      <c r="AH33" s="204"/>
+      <c r="AI33" s="201"/>
+      <c r="AJ33" s="204"/>
+      <c r="AK33" s="202"/>
+      <c r="AL33" s="203"/>
+      <c r="AM33" s="201"/>
+      <c r="AN33" s="204"/>
+      <c r="AO33" s="201"/>
+      <c r="AP33" s="204"/>
+      <c r="AQ33" s="201"/>
+      <c r="AR33" s="204"/>
+      <c r="AS33" s="201"/>
+      <c r="AT33" s="204"/>
+      <c r="AU33" s="202"/>
+      <c r="AV33" s="203"/>
+      <c r="AW33" s="201"/>
+    </row>
+    <row r="34" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <f>B32+$A$8</f>
+        <v>260</v>
+      </c>
+      <c r="C34" s="183" t="str">
+        <f>CONCATENATE(B34,"°")</f>
+        <v>260°</v>
+      </c>
+      <c r="D34" s="183"/>
+      <c r="E34" s="184"/>
+      <c r="F34" s="189"/>
+      <c r="G34" s="190"/>
+      <c r="H34" s="191"/>
+      <c r="I34" s="190"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="189"/>
+      <c r="L34" s="192"/>
+      <c r="M34" s="189"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="189"/>
+      <c r="P34" s="192"/>
+      <c r="Q34" s="190"/>
+      <c r="R34" s="191"/>
+      <c r="S34" s="189"/>
+      <c r="T34" s="192"/>
+      <c r="U34" s="189"/>
+      <c r="V34" s="192"/>
+      <c r="W34" s="189"/>
+      <c r="X34" s="192"/>
+      <c r="Y34" s="189"/>
+      <c r="Z34" s="192"/>
+      <c r="AA34" s="190"/>
+      <c r="AB34" s="191"/>
+      <c r="AC34" s="189"/>
+      <c r="AD34" s="192"/>
+      <c r="AE34" s="189"/>
+      <c r="AF34" s="192"/>
+      <c r="AG34" s="189"/>
+      <c r="AH34" s="192"/>
+      <c r="AI34" s="189"/>
+      <c r="AJ34" s="192"/>
+      <c r="AK34" s="190"/>
+      <c r="AL34" s="191"/>
+      <c r="AM34" s="189"/>
+      <c r="AN34" s="192"/>
+      <c r="AO34" s="189"/>
+      <c r="AP34" s="192"/>
+      <c r="AQ34" s="189"/>
+      <c r="AR34" s="192"/>
+      <c r="AS34" s="189"/>
+      <c r="AT34" s="192"/>
+      <c r="AU34" s="190"/>
+      <c r="AV34" s="191"/>
+      <c r="AW34" s="189"/>
+    </row>
+    <row r="35" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="183"/>
+      <c r="D35" s="183"/>
+      <c r="E35" s="184"/>
+      <c r="F35" s="197"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="199"/>
+      <c r="I35" s="198"/>
+      <c r="J35" s="200"/>
+      <c r="K35" s="197"/>
+      <c r="L35" s="200"/>
+      <c r="M35" s="197"/>
+      <c r="N35" s="200"/>
+      <c r="O35" s="197"/>
+      <c r="P35" s="200"/>
+      <c r="Q35" s="198"/>
+      <c r="R35" s="199"/>
+      <c r="S35" s="197"/>
+      <c r="T35" s="200"/>
+      <c r="U35" s="197"/>
+      <c r="V35" s="200"/>
+      <c r="W35" s="197"/>
+      <c r="X35" s="200"/>
+      <c r="Y35" s="197"/>
+      <c r="Z35" s="200"/>
+      <c r="AA35" s="198"/>
+      <c r="AB35" s="199"/>
+      <c r="AC35" s="197"/>
+      <c r="AD35" s="200"/>
+      <c r="AE35" s="197"/>
+      <c r="AF35" s="200"/>
+      <c r="AG35" s="197"/>
+      <c r="AH35" s="200"/>
+      <c r="AI35" s="197"/>
+      <c r="AJ35" s="200"/>
+      <c r="AK35" s="198"/>
+      <c r="AL35" s="199"/>
+      <c r="AM35" s="197"/>
+      <c r="AN35" s="200"/>
+      <c r="AO35" s="197"/>
+      <c r="AP35" s="200"/>
+      <c r="AQ35" s="197"/>
+      <c r="AR35" s="200"/>
+      <c r="AS35" s="197"/>
+      <c r="AT35" s="200"/>
+      <c r="AU35" s="198"/>
+      <c r="AV35" s="199"/>
+      <c r="AW35" s="197"/>
+    </row>
+    <row r="36" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <f>B34+$A$8</f>
+        <v>280</v>
+      </c>
+      <c r="C36" s="183" t="str">
+        <f>CONCATENATE(B36,"°")</f>
+        <v>280°</v>
+      </c>
+      <c r="D36" s="183"/>
+      <c r="E36" s="184"/>
+      <c r="F36" s="185"/>
+      <c r="G36" s="186"/>
+      <c r="H36" s="187"/>
+      <c r="I36" s="186"/>
+      <c r="J36" s="188"/>
+      <c r="K36" s="185"/>
+      <c r="L36" s="188"/>
+      <c r="M36" s="185"/>
+      <c r="N36" s="188"/>
+      <c r="O36" s="185"/>
+      <c r="P36" s="188"/>
+      <c r="Q36" s="186"/>
+      <c r="R36" s="187"/>
+      <c r="S36" s="185"/>
+      <c r="T36" s="188"/>
+      <c r="U36" s="185"/>
+      <c r="V36" s="188"/>
+      <c r="W36" s="185"/>
+      <c r="X36" s="188"/>
+      <c r="Y36" s="185"/>
+      <c r="Z36" s="188"/>
+      <c r="AA36" s="186"/>
+      <c r="AB36" s="187"/>
+      <c r="AC36" s="185"/>
+      <c r="AD36" s="188"/>
+      <c r="AE36" s="185"/>
+      <c r="AF36" s="188"/>
+      <c r="AG36" s="185"/>
+      <c r="AH36" s="188"/>
+      <c r="AI36" s="185"/>
+      <c r="AJ36" s="188"/>
+      <c r="AK36" s="186"/>
+      <c r="AL36" s="187"/>
+      <c r="AM36" s="185"/>
+      <c r="AN36" s="188"/>
+      <c r="AO36" s="185"/>
+      <c r="AP36" s="188"/>
+      <c r="AQ36" s="185"/>
+      <c r="AR36" s="188"/>
+      <c r="AS36" s="185"/>
+      <c r="AT36" s="188"/>
+      <c r="AU36" s="186"/>
+      <c r="AV36" s="187"/>
+      <c r="AW36" s="185"/>
+    </row>
+    <row r="37" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="183"/>
+      <c r="D37" s="183"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="201"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="203"/>
+      <c r="I37" s="202"/>
+      <c r="J37" s="204"/>
+      <c r="K37" s="201"/>
+      <c r="L37" s="204"/>
+      <c r="M37" s="201"/>
+      <c r="N37" s="204"/>
+      <c r="O37" s="201"/>
+      <c r="P37" s="204"/>
+      <c r="Q37" s="202"/>
+      <c r="R37" s="203"/>
+      <c r="S37" s="201"/>
+      <c r="T37" s="204"/>
+      <c r="U37" s="201"/>
+      <c r="V37" s="204"/>
+      <c r="W37" s="201"/>
+      <c r="X37" s="204"/>
+      <c r="Y37" s="201"/>
+      <c r="Z37" s="204"/>
+      <c r="AA37" s="202"/>
+      <c r="AB37" s="203"/>
+      <c r="AC37" s="201"/>
+      <c r="AD37" s="204"/>
+      <c r="AE37" s="201"/>
+      <c r="AF37" s="204"/>
+      <c r="AG37" s="201"/>
+      <c r="AH37" s="204"/>
+      <c r="AI37" s="201"/>
+      <c r="AJ37" s="204"/>
+      <c r="AK37" s="202"/>
+      <c r="AL37" s="203"/>
+      <c r="AM37" s="201"/>
+      <c r="AN37" s="204"/>
+      <c r="AO37" s="201"/>
+      <c r="AP37" s="204"/>
+      <c r="AQ37" s="201"/>
+      <c r="AR37" s="204"/>
+      <c r="AS37" s="201"/>
+      <c r="AT37" s="204"/>
+      <c r="AU37" s="202"/>
+      <c r="AV37" s="203"/>
+      <c r="AW37" s="201"/>
+    </row>
+    <row r="38" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <f>B36+$A$8</f>
+        <v>300</v>
+      </c>
+      <c r="C38" s="183" t="str">
+        <f>CONCATENATE(B38,"°")</f>
+        <v>300°</v>
+      </c>
+      <c r="D38" s="183"/>
+      <c r="E38" s="184"/>
+      <c r="F38" s="189"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="191"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="192"/>
+      <c r="K38" s="189"/>
+      <c r="L38" s="192"/>
+      <c r="M38" s="189"/>
+      <c r="N38" s="192"/>
+      <c r="O38" s="189"/>
+      <c r="P38" s="192"/>
+      <c r="Q38" s="190"/>
+      <c r="R38" s="191"/>
+      <c r="S38" s="189"/>
+      <c r="T38" s="192"/>
+      <c r="U38" s="189"/>
+      <c r="V38" s="192"/>
+      <c r="W38" s="189"/>
+      <c r="X38" s="192"/>
+      <c r="Y38" s="189"/>
+      <c r="Z38" s="192"/>
+      <c r="AA38" s="190"/>
+      <c r="AB38" s="191"/>
+      <c r="AC38" s="189"/>
+      <c r="AD38" s="192"/>
+      <c r="AE38" s="189"/>
+      <c r="AF38" s="192"/>
+      <c r="AG38" s="189"/>
+      <c r="AH38" s="192"/>
+      <c r="AI38" s="189"/>
+      <c r="AJ38" s="192"/>
+      <c r="AK38" s="190"/>
+      <c r="AL38" s="191"/>
+      <c r="AM38" s="189"/>
+      <c r="AN38" s="192"/>
+      <c r="AO38" s="189"/>
+      <c r="AP38" s="192"/>
+      <c r="AQ38" s="189"/>
+      <c r="AR38" s="192"/>
+      <c r="AS38" s="189"/>
+      <c r="AT38" s="192"/>
+      <c r="AU38" s="190"/>
+      <c r="AV38" s="191"/>
+      <c r="AW38" s="189"/>
+    </row>
+    <row r="39" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="183"/>
+      <c r="D39" s="183"/>
+      <c r="E39" s="184"/>
+      <c r="F39" s="205"/>
+      <c r="G39" s="206"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="206"/>
+      <c r="J39" s="208"/>
+      <c r="K39" s="205"/>
+      <c r="L39" s="208"/>
+      <c r="M39" s="205"/>
+      <c r="N39" s="208"/>
+      <c r="O39" s="205"/>
+      <c r="P39" s="208"/>
+      <c r="Q39" s="206"/>
+      <c r="R39" s="207"/>
+      <c r="S39" s="205"/>
+      <c r="T39" s="208"/>
+      <c r="U39" s="205"/>
+      <c r="V39" s="208"/>
+      <c r="W39" s="205"/>
+      <c r="X39" s="208"/>
+      <c r="Y39" s="205"/>
+      <c r="Z39" s="208"/>
+      <c r="AA39" s="206"/>
+      <c r="AB39" s="207"/>
+      <c r="AC39" s="205"/>
+      <c r="AD39" s="208"/>
+      <c r="AE39" s="205"/>
+      <c r="AF39" s="208"/>
+      <c r="AG39" s="205"/>
+      <c r="AH39" s="208"/>
+      <c r="AI39" s="205"/>
+      <c r="AJ39" s="208"/>
+      <c r="AK39" s="206"/>
+      <c r="AL39" s="207"/>
+      <c r="AM39" s="205"/>
+      <c r="AN39" s="208"/>
+      <c r="AO39" s="205"/>
+      <c r="AP39" s="208"/>
+      <c r="AQ39" s="205"/>
+      <c r="AR39" s="208"/>
+      <c r="AS39" s="205"/>
+      <c r="AT39" s="208"/>
+      <c r="AU39" s="206"/>
+      <c r="AV39" s="207"/>
+      <c r="AW39" s="205"/>
+    </row>
+    <row r="40" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <f>B38+$A$8</f>
+        <v>320</v>
+      </c>
+      <c r="C40" s="183" t="str">
+        <f>CONCATENATE(B40,"°")</f>
+        <v>320°</v>
+      </c>
+      <c r="D40" s="183"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="205"/>
+      <c r="G40" s="206"/>
+      <c r="H40" s="207"/>
+      <c r="I40" s="206"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="205"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="205"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="205"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="206"/>
+      <c r="R40" s="207"/>
+      <c r="S40" s="205"/>
+      <c r="T40" s="208"/>
+      <c r="U40" s="205"/>
+      <c r="V40" s="208"/>
+      <c r="W40" s="205"/>
+      <c r="X40" s="208"/>
+      <c r="Y40" s="205"/>
+      <c r="Z40" s="208"/>
+      <c r="AA40" s="206"/>
+      <c r="AB40" s="207"/>
+      <c r="AC40" s="205"/>
+      <c r="AD40" s="208"/>
+      <c r="AE40" s="205"/>
+      <c r="AF40" s="208"/>
+      <c r="AG40" s="205"/>
+      <c r="AH40" s="208"/>
+      <c r="AI40" s="205"/>
+      <c r="AJ40" s="208"/>
+      <c r="AK40" s="206"/>
+      <c r="AL40" s="207"/>
+      <c r="AM40" s="205"/>
+      <c r="AN40" s="208"/>
+      <c r="AO40" s="205"/>
+      <c r="AP40" s="208"/>
+      <c r="AQ40" s="205"/>
+      <c r="AR40" s="208"/>
+      <c r="AS40" s="205"/>
+      <c r="AT40" s="208"/>
+      <c r="AU40" s="206"/>
+      <c r="AV40" s="207"/>
+      <c r="AW40" s="205"/>
+    </row>
+    <row r="41" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="183"/>
+      <c r="D41" s="183"/>
+      <c r="E41" s="184"/>
+      <c r="F41" s="201"/>
+      <c r="G41" s="202"/>
+      <c r="H41" s="203"/>
+      <c r="I41" s="202"/>
+      <c r="J41" s="204"/>
+      <c r="K41" s="201"/>
+      <c r="L41" s="204"/>
+      <c r="M41" s="201"/>
+      <c r="N41" s="204"/>
+      <c r="O41" s="201"/>
+      <c r="P41" s="204"/>
+      <c r="Q41" s="202"/>
+      <c r="R41" s="203"/>
+      <c r="S41" s="201"/>
+      <c r="T41" s="204"/>
+      <c r="U41" s="201"/>
+      <c r="V41" s="204"/>
+      <c r="W41" s="201"/>
+      <c r="X41" s="204"/>
+      <c r="Y41" s="201"/>
+      <c r="Z41" s="204"/>
+      <c r="AA41" s="202"/>
+      <c r="AB41" s="203"/>
+      <c r="AC41" s="201"/>
+      <c r="AD41" s="204"/>
+      <c r="AE41" s="201"/>
+      <c r="AF41" s="204"/>
+      <c r="AG41" s="201"/>
+      <c r="AH41" s="204"/>
+      <c r="AI41" s="201"/>
+      <c r="AJ41" s="204"/>
+      <c r="AK41" s="202"/>
+      <c r="AL41" s="203"/>
+      <c r="AM41" s="201"/>
+      <c r="AN41" s="204"/>
+      <c r="AO41" s="201"/>
+      <c r="AP41" s="204"/>
+      <c r="AQ41" s="201"/>
+      <c r="AR41" s="204"/>
+      <c r="AS41" s="201"/>
+      <c r="AT41" s="204"/>
+      <c r="AU41" s="202"/>
+      <c r="AV41" s="203"/>
+      <c r="AW41" s="201"/>
+    </row>
+    <row r="42" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <f>B40+$A$8</f>
+        <v>340</v>
+      </c>
+      <c r="C42" s="183" t="str">
+        <f>CONCATENATE(B42,"°")</f>
+        <v>340°</v>
+      </c>
+      <c r="D42" s="183"/>
+      <c r="E42" s="184"/>
+      <c r="F42" s="189"/>
+      <c r="G42" s="190"/>
+      <c r="H42" s="191"/>
+      <c r="I42" s="190"/>
+      <c r="J42" s="192"/>
+      <c r="K42" s="189"/>
+      <c r="L42" s="192"/>
+      <c r="M42" s="189"/>
+      <c r="N42" s="192"/>
+      <c r="O42" s="189"/>
+      <c r="P42" s="192"/>
+      <c r="Q42" s="190"/>
+      <c r="R42" s="191"/>
+      <c r="S42" s="189"/>
+      <c r="T42" s="192"/>
+      <c r="U42" s="189"/>
+      <c r="V42" s="192"/>
+      <c r="W42" s="189"/>
+      <c r="X42" s="192"/>
+      <c r="Y42" s="189"/>
+      <c r="Z42" s="192"/>
+      <c r="AA42" s="190"/>
+      <c r="AB42" s="191"/>
+      <c r="AC42" s="189"/>
+      <c r="AD42" s="192"/>
+      <c r="AE42" s="189"/>
+      <c r="AF42" s="192"/>
+      <c r="AG42" s="189"/>
+      <c r="AH42" s="192"/>
+      <c r="AI42" s="189"/>
+      <c r="AJ42" s="192"/>
+      <c r="AK42" s="190"/>
+      <c r="AL42" s="191"/>
+      <c r="AM42" s="189"/>
+      <c r="AN42" s="192"/>
+      <c r="AO42" s="189"/>
+      <c r="AP42" s="192"/>
+      <c r="AQ42" s="189"/>
+      <c r="AR42" s="192"/>
+      <c r="AS42" s="189"/>
+      <c r="AT42" s="192"/>
+      <c r="AU42" s="190"/>
+      <c r="AV42" s="191"/>
+      <c r="AW42" s="189"/>
+    </row>
+    <row r="43" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="183"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="184"/>
+      <c r="F43" s="205"/>
+      <c r="G43" s="206"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="206"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="205"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="205"/>
+      <c r="N43" s="208"/>
+      <c r="O43" s="205"/>
+      <c r="P43" s="208"/>
+      <c r="Q43" s="206"/>
+      <c r="R43" s="207"/>
+      <c r="S43" s="205"/>
+      <c r="T43" s="208"/>
+      <c r="U43" s="205"/>
+      <c r="V43" s="208"/>
+      <c r="W43" s="205"/>
+      <c r="X43" s="208"/>
+      <c r="Y43" s="205"/>
+      <c r="Z43" s="208"/>
+      <c r="AA43" s="206"/>
+      <c r="AB43" s="207"/>
+      <c r="AC43" s="205"/>
+      <c r="AD43" s="208"/>
+      <c r="AE43" s="205"/>
+      <c r="AF43" s="208"/>
+      <c r="AG43" s="205"/>
+      <c r="AH43" s="208"/>
+      <c r="AI43" s="205"/>
+      <c r="AJ43" s="208"/>
+      <c r="AK43" s="206"/>
+      <c r="AL43" s="207"/>
+      <c r="AM43" s="205"/>
+      <c r="AN43" s="208"/>
+      <c r="AO43" s="205"/>
+      <c r="AP43" s="208"/>
+      <c r="AQ43" s="205"/>
+      <c r="AR43" s="208"/>
+      <c r="AS43" s="205"/>
+      <c r="AT43" s="208"/>
+      <c r="AU43" s="206"/>
+      <c r="AV43" s="207"/>
+      <c r="AW43" s="205"/>
+    </row>
+    <row r="44" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44" s="183" t="str">
+        <f>CONCATENATE(B44,"°")</f>
+        <v>0°</v>
+      </c>
+      <c r="D44" s="183"/>
+      <c r="E44" s="184"/>
+      <c r="F44" s="197"/>
+      <c r="G44" s="198"/>
+      <c r="H44" s="199"/>
+      <c r="I44" s="198"/>
+      <c r="J44" s="217"/>
+      <c r="K44" s="197"/>
+      <c r="L44" s="217"/>
+      <c r="M44" s="197"/>
+      <c r="N44" s="217"/>
+      <c r="O44" s="197"/>
+      <c r="P44" s="217"/>
+      <c r="Q44" s="198"/>
+      <c r="R44" s="199"/>
+      <c r="S44" s="197"/>
+      <c r="T44" s="217"/>
+      <c r="U44" s="197"/>
+      <c r="V44" s="217"/>
+      <c r="W44" s="197"/>
+      <c r="X44" s="217"/>
+      <c r="Y44" s="197"/>
+      <c r="Z44" s="217"/>
+      <c r="AA44" s="198"/>
+      <c r="AB44" s="199"/>
+      <c r="AC44" s="197"/>
+      <c r="AD44" s="217"/>
+      <c r="AE44" s="197"/>
+      <c r="AF44" s="217"/>
+      <c r="AG44" s="197"/>
+      <c r="AH44" s="217"/>
+      <c r="AI44" s="197"/>
+      <c r="AJ44" s="217"/>
+      <c r="AK44" s="198"/>
+      <c r="AL44" s="199"/>
+      <c r="AM44" s="197"/>
+      <c r="AN44" s="217"/>
+      <c r="AO44" s="197"/>
+      <c r="AP44" s="217"/>
+      <c r="AQ44" s="197"/>
+      <c r="AR44" s="217"/>
+      <c r="AS44" s="197"/>
+      <c r="AT44" s="217"/>
+      <c r="AU44" s="198"/>
+      <c r="AV44" s="199"/>
+      <c r="AW44" s="197"/>
+    </row>
+    <row r="45" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="183"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="184"/>
+      <c r="F45" s="185"/>
+      <c r="G45" s="186"/>
+      <c r="H45" s="187"/>
+      <c r="I45" s="185"/>
+      <c r="J45" s="185"/>
+      <c r="K45" s="185"/>
+      <c r="L45" s="185"/>
+      <c r="M45" s="185"/>
+      <c r="N45" s="185"/>
+      <c r="O45" s="185"/>
+      <c r="P45" s="185"/>
+      <c r="Q45" s="186"/>
+      <c r="R45" s="187"/>
+      <c r="S45" s="185"/>
+      <c r="T45" s="185"/>
+      <c r="U45" s="185"/>
+      <c r="V45" s="185"/>
+      <c r="W45" s="185"/>
+      <c r="X45" s="185"/>
+      <c r="Y45" s="185"/>
+      <c r="Z45" s="185"/>
+      <c r="AA45" s="186"/>
+      <c r="AB45" s="187"/>
+      <c r="AC45" s="185"/>
+      <c r="AD45" s="185"/>
+      <c r="AE45" s="185"/>
+      <c r="AF45" s="185"/>
+      <c r="AG45" s="185"/>
+      <c r="AH45" s="185"/>
+      <c r="AI45" s="185"/>
+      <c r="AJ45" s="185"/>
+      <c r="AK45" s="186"/>
+      <c r="AL45" s="187"/>
+      <c r="AM45" s="185"/>
+      <c r="AN45" s="185"/>
+      <c r="AO45" s="185"/>
+      <c r="AP45" s="185"/>
+      <c r="AQ45" s="185"/>
+      <c r="AR45" s="185"/>
+      <c r="AS45" s="185"/>
+      <c r="AT45" s="185"/>
+      <c r="AU45" s="186"/>
+      <c r="AV45" s="187"/>
+      <c r="AW45" s="185"/>
+    </row>
+    <row r="46" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <f>B44+$A$8</f>
+        <v>20</v>
+      </c>
+      <c r="C46" s="183" t="str">
+        <f>CONCATENATE(B46,"°")</f>
+        <v>20°</v>
+      </c>
+      <c r="D46" s="183"/>
+      <c r="E46" s="184"/>
+      <c r="F46" s="218"/>
+      <c r="G46" s="219"/>
+      <c r="H46" s="220"/>
+      <c r="I46" s="218"/>
+      <c r="J46" s="218"/>
+      <c r="K46" s="218"/>
+      <c r="L46" s="218"/>
+      <c r="M46" s="218"/>
+      <c r="N46" s="218"/>
+      <c r="O46" s="218"/>
+      <c r="P46" s="218"/>
+      <c r="Q46" s="218"/>
+      <c r="R46" s="221"/>
+      <c r="S46" s="222"/>
+      <c r="T46" s="218"/>
+      <c r="U46" s="218"/>
+      <c r="V46" s="218"/>
+      <c r="W46" s="218"/>
+      <c r="X46" s="218"/>
+      <c r="Y46" s="218"/>
+      <c r="Z46" s="218"/>
+      <c r="AA46" s="218"/>
+      <c r="AB46" s="220"/>
+      <c r="AC46" s="218"/>
+      <c r="AD46" s="218"/>
+      <c r="AE46" s="218"/>
+      <c r="AF46" s="218"/>
+      <c r="AG46" s="218"/>
+      <c r="AH46" s="218"/>
+      <c r="AI46" s="218"/>
+      <c r="AJ46" s="218"/>
+      <c r="AK46" s="218"/>
+      <c r="AL46" s="220"/>
+      <c r="AM46" s="218"/>
+      <c r="AN46" s="218"/>
+      <c r="AO46" s="218"/>
+      <c r="AP46" s="218"/>
+      <c r="AQ46" s="218"/>
+      <c r="AR46" s="218"/>
+      <c r="AS46" s="218"/>
+      <c r="AT46" s="218"/>
+      <c r="AU46" s="218"/>
+      <c r="AV46" s="220"/>
+      <c r="AW46" s="218"/>
+    </row>
+    <row r="47" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="183"/>
+      <c r="D47" s="183"/>
+      <c r="E47" s="184"/>
+      <c r="F47" s="184"/>
+      <c r="G47" s="184"/>
+    </row>
+    <row r="48" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <f>B46+$A$8</f>
+        <v>40</v>
+      </c>
+      <c r="C48" s="183" t="str">
+        <f>CONCATENATE(B48,"°")</f>
+        <v>40°</v>
+      </c>
+      <c r="D48" s="223"/>
+      <c r="E48" s="184"/>
+      <c r="F48" s="184"/>
+      <c r="G48" s="184"/>
+    </row>
+    <row r="49" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="183"/>
+      <c r="D49" s="223"/>
+      <c r="E49" s="184"/>
+      <c r="F49" s="184"/>
+      <c r="G49" s="184"/>
+    </row>
+    <row r="50" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <f>B48+$A$8</f>
+        <v>60</v>
+      </c>
+      <c r="C50" s="183" t="str">
+        <f>CONCATENATE(B50,"°")</f>
+        <v>60°</v>
+      </c>
+      <c r="D50" s="223"/>
+      <c r="E50" s="184"/>
+      <c r="F50" s="184"/>
+      <c r="G50" s="184"/>
+    </row>
+    <row r="51" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C51" s="183"/>
+      <c r="D51" s="223"/>
+      <c r="E51" s="184"/>
+      <c r="F51" s="184"/>
+      <c r="G51" s="184"/>
+    </row>
+    <row r="52" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <f>B50+$A$8</f>
+        <v>80</v>
+      </c>
+      <c r="C52" s="183" t="str">
+        <f>CONCATENATE(B52,"°")</f>
+        <v>80°</v>
+      </c>
+      <c r="D52" s="223"/>
+      <c r="E52" s="184"/>
+      <c r="F52" s="184"/>
+      <c r="G52" s="184"/>
+    </row>
+    <row r="53" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="183"/>
+      <c r="D53" s="223"/>
+      <c r="E53" s="184"/>
+      <c r="F53" s="184"/>
+      <c r="G53" s="184"/>
+    </row>
+    <row r="54" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <f>B52+$A$8</f>
+        <v>100</v>
+      </c>
+      <c r="C54" s="183" t="str">
+        <f>CONCATENATE(B54,"°")</f>
+        <v>100°</v>
+      </c>
+      <c r="D54" s="223"/>
+      <c r="E54" s="184"/>
+      <c r="F54" s="184"/>
+      <c r="G54" s="184"/>
+    </row>
+    <row r="55" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="183"/>
+      <c r="D55" s="223"/>
+      <c r="E55" s="184"/>
+      <c r="F55" s="184"/>
+      <c r="G55" s="184"/>
+    </row>
+    <row r="56" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <f>B54+$A$8</f>
+        <v>120</v>
+      </c>
+      <c r="C56" s="183" t="str">
+        <f>CONCATENATE(B56,"°")</f>
+        <v>120°</v>
+      </c>
+      <c r="D56" s="223"/>
+      <c r="E56" s="184"/>
+      <c r="F56" s="184"/>
+      <c r="G56" s="184"/>
+    </row>
+    <row r="57" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="183"/>
+      <c r="D57" s="223"/>
+      <c r="E57" s="184"/>
+      <c r="F57" s="184"/>
+      <c r="G57" s="184"/>
+    </row>
+    <row r="58" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <f>B56+$A$8</f>
+        <v>140</v>
+      </c>
+      <c r="C58" s="183" t="str">
+        <f>CONCATENATE(B58,"°")</f>
+        <v>140°</v>
+      </c>
+      <c r="D58" s="223"/>
+      <c r="E58" s="184"/>
+      <c r="F58" s="184"/>
+      <c r="G58" s="184"/>
+    </row>
+    <row r="59" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="183"/>
+      <c r="D59" s="223"/>
+      <c r="E59" s="184"/>
+      <c r="F59" s="184"/>
+      <c r="G59" s="184"/>
+    </row>
+    <row r="60" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <f>B58+$A$8</f>
+        <v>160</v>
+      </c>
+      <c r="C60" s="183" t="str">
+        <f>CONCATENATE(B60,"°")</f>
+        <v>160°</v>
+      </c>
+      <c r="D60" s="223"/>
+      <c r="E60" s="184"/>
+      <c r="F60" s="184"/>
+      <c r="G60" s="184"/>
+    </row>
+    <row r="61" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C61" s="183"/>
+      <c r="D61" s="223"/>
+      <c r="E61" s="184"/>
+      <c r="F61" s="184"/>
+      <c r="G61" s="184"/>
+    </row>
+    <row r="62" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <f>B60+$A$8</f>
+        <v>180</v>
+      </c>
+      <c r="C62" s="183" t="str">
+        <f>CONCATENATE(B62,"°")</f>
+        <v>180°</v>
+      </c>
+      <c r="D62" s="223"/>
+      <c r="E62" s="184"/>
+      <c r="F62" s="184"/>
+      <c r="G62" s="184"/>
+    </row>
+    <row r="63" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C63" s="183"/>
+      <c r="D63" s="223"/>
+      <c r="E63" s="184"/>
+      <c r="F63" s="184"/>
+      <c r="G63" s="184"/>
+    </row>
+    <row r="64" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <f>B62+$A$8</f>
+        <v>200</v>
+      </c>
+      <c r="C64" s="183" t="str">
+        <f>CONCATENATE(B64,"°")</f>
+        <v>200°</v>
+      </c>
+      <c r="D64" s="223"/>
+      <c r="E64" s="184"/>
+      <c r="F64" s="184"/>
+      <c r="G64" s="184"/>
+    </row>
+    <row r="65" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C65" s="183"/>
+      <c r="D65" s="223"/>
+      <c r="E65" s="184"/>
+      <c r="F65" s="184"/>
+      <c r="G65" s="184"/>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A68" s="169" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" s="169"/>
+      <c r="C68" s="169"/>
+      <c r="D68" s="169"/>
+      <c r="E68" s="169"/>
+      <c r="F68" s="169"/>
+      <c r="G68" s="169"/>
+      <c r="H68" s="169"/>
+      <c r="I68" s="169"/>
+      <c r="J68" s="169"/>
+      <c r="K68" s="169"/>
+      <c r="L68" s="169"/>
+      <c r="M68" s="169"/>
+      <c r="N68" s="169"/>
+      <c r="O68" s="169"/>
+      <c r="P68" s="169"/>
+      <c r="Q68" s="169"/>
+      <c r="R68" s="169"/>
+      <c r="S68" s="169"/>
+      <c r="T68" s="169"/>
+      <c r="U68" s="169"/>
+      <c r="V68" s="169"/>
+      <c r="W68" s="169"/>
+      <c r="X68" s="169"/>
+      <c r="Y68" s="169"/>
+      <c r="Z68" s="169"/>
+      <c r="AA68" s="169"/>
+      <c r="AB68" s="169"/>
+      <c r="AC68" s="169"/>
+      <c r="AD68" s="169"/>
+      <c r="AE68" s="169"/>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A69" s="169"/>
+      <c r="B69" s="169"/>
+      <c r="C69" s="169"/>
+      <c r="D69" s="169"/>
+      <c r="E69" s="169"/>
+      <c r="F69" s="169"/>
+      <c r="G69" s="169"/>
+      <c r="H69" s="169"/>
+      <c r="I69" s="169"/>
+      <c r="J69" s="169"/>
+      <c r="K69" s="169"/>
+      <c r="L69" s="169"/>
+      <c r="M69" s="169"/>
+      <c r="N69" s="169"/>
+      <c r="O69" s="169"/>
+      <c r="P69" s="169"/>
+      <c r="Q69" s="169"/>
+      <c r="R69" s="169"/>
+      <c r="S69" s="169"/>
+      <c r="T69" s="169"/>
+      <c r="U69" s="169"/>
+      <c r="V69" s="169"/>
+      <c r="W69" s="169"/>
+      <c r="X69" s="169"/>
+      <c r="Y69" s="169"/>
+      <c r="Z69" s="169"/>
+      <c r="AA69" s="169"/>
+      <c r="AB69" s="169"/>
+      <c r="AC69" s="169"/>
+      <c r="AD69" s="169"/>
+      <c r="AE69" s="169"/>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C72" s="224" t="s">
+        <v>145</v>
+      </c>
+      <c r="D72" s="224"/>
+      <c r="E72" s="224"/>
+      <c r="F72" s="224"/>
+      <c r="G72" s="224"/>
+      <c r="H72" s="224"/>
+      <c r="I72" s="224"/>
+      <c r="J72" s="224"/>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D76" s="225" t="s">
+        <v>149</v>
+      </c>
+      <c r="E76" s="225"/>
+      <c r="F76" s="225"/>
+      <c r="G76" s="225"/>
+      <c r="H76" s="226"/>
+      <c r="I76" s="226"/>
+      <c r="J76" s="226"/>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C78" s="224" t="s">
+        <v>150</v>
+      </c>
+      <c r="D78" s="224"/>
+      <c r="E78" s="224"/>
+      <c r="F78" s="224"/>
+      <c r="G78" s="224"/>
+      <c r="H78" s="224"/>
+      <c r="I78" s="224"/>
+      <c r="J78" s="224"/>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C81" s="224" t="s">
+        <v>152</v>
+      </c>
+      <c r="D81" s="224"/>
+      <c r="E81" s="224"/>
+      <c r="F81" s="224"/>
+      <c r="G81" s="224"/>
+      <c r="H81" s="224"/>
+      <c r="I81" s="224"/>
+      <c r="J81" s="224"/>
+    </row>
+    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>156</v>
+      </c>
+      <c r="I86" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="I87" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="78">
+    <mergeCell ref="C60:D61"/>
+    <mergeCell ref="C62:D63"/>
+    <mergeCell ref="C64:D65"/>
+    <mergeCell ref="A68:AE69"/>
+    <mergeCell ref="C48:D49"/>
+    <mergeCell ref="C50:D51"/>
+    <mergeCell ref="C52:D53"/>
+    <mergeCell ref="C54:D55"/>
+    <mergeCell ref="C56:D57"/>
+    <mergeCell ref="C58:D59"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="C44:D45"/>
+    <mergeCell ref="C46:D47"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="C32:D33"/>
+    <mergeCell ref="C34:D35"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="AP7:AQ8"/>
+    <mergeCell ref="AR7:AS8"/>
+    <mergeCell ref="AT7:AU8"/>
+    <mergeCell ref="AV7:AW8"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="AD7:AE8"/>
+    <mergeCell ref="AF7:AG8"/>
+    <mergeCell ref="AH7:AI8"/>
+    <mergeCell ref="AJ7:AK8"/>
+    <mergeCell ref="AL7:AM8"/>
+    <mergeCell ref="AN7:AO8"/>
+    <mergeCell ref="R7:S8"/>
+    <mergeCell ref="T7:U8"/>
+    <mergeCell ref="V7:W8"/>
+    <mergeCell ref="X7:Y8"/>
+    <mergeCell ref="Z7:AA8"/>
+    <mergeCell ref="AB7:AC8"/>
+    <mergeCell ref="AO6:AP6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="AS6:AT6"/>
+    <mergeCell ref="AW6:AX6"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="H7:I8"/>
+    <mergeCell ref="J7:K8"/>
+    <mergeCell ref="L7:M8"/>
+    <mergeCell ref="N7:O8"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AC6:AD6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AG6:AH6"/>
+    <mergeCell ref="AI6:AJ6"/>
+    <mergeCell ref="AM6:AN6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="C1:AX2"/>
+    <mergeCell ref="G5:H6"/>
+    <mergeCell ref="Q5:R6"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="AA5:AB6"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AK5:AL6"/>
+    <mergeCell ref="AU5:AV6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="I6:J6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/ProjetXLS/JournalDeBord/JournalDeBord.xlsx
+++ b/ProjetXLS/JournalDeBord/JournalDeBord.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpaces\WS\GitHub\Navigation\NavigationBateau\ProjetXLS\JournalDeBord\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D8D7BC-6767-4550-A72C-0DD8DFA3CDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CE6AB2-A9E4-40F3-AF2D-EDD7D8E53978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="990" yWindow="765" windowWidth="27405" windowHeight="14970" activeTab="3" xr2:uid="{E20D9DF7-46DF-4441-A87B-8D054A4C81F1}"/>
+    <workbookView xWindow="555" yWindow="510" windowWidth="27405" windowHeight="14970" activeTab="3" xr2:uid="{E20D9DF7-46DF-4441-A87B-8D054A4C81F1}"/>
   </bookViews>
   <sheets>
     <sheet name="premiere page" sheetId="6" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="GrilleCompas" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">GrilleCompas!$C$1:$AX$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">GrilleCompas!$C$1:$AX$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'inverse pour impression'!$B$2:$AA$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Page prise meteo'!$B$2:$Q$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'premiere page'!$B$2:$AA$59</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="160">
   <si>
     <t xml:space="preserve">Date: </t>
   </si>
@@ -604,6 +604,9 @@
   </si>
   <si>
     <t>d est lie au perturbation du bateau</t>
+  </si>
+  <si>
+    <t>Date de mise jour:</t>
   </si>
 </sst>
 </file>
@@ -2738,7 +2741,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2879,316 +2882,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="104" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3230,12 +2927,319 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="145" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="146" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -3396,7 +3400,7 @@
     <xdr:from>
       <xdr:col>52</xdr:col>
       <xdr:colOff>392723</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>126023</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2375720" cy="3443406"/>
@@ -3435,7 +3439,7 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>74147</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>101792</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="98116" cy="436054"/>
@@ -3474,7 +3478,7 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>44586</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>134989</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="449975" cy="87143"/>
@@ -3513,7 +3517,7 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>77265</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>7060</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="90073" cy="438252"/>
@@ -3552,7 +3556,7 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>7546</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>137106</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="449975" cy="87143"/>
@@ -3591,7 +3595,7 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>65624</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>90670</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="90073" cy="438252"/>
@@ -3630,7 +3634,7 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>10592</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>7062</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="87143" cy="438252"/>
@@ -3669,7 +3673,7 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>111261</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>96891</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="449975" cy="87143"/>
@@ -3708,7 +3712,7 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>101735</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>11166</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="449975" cy="87143"/>
@@ -3747,7 +3751,7 @@
     <xdr:from>
       <xdr:col>26</xdr:col>
       <xdr:colOff>58214</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>35636</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="90073" cy="438252"/>
@@ -3786,13 +3790,13 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>11724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>11724</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3839,13 +3843,13 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>85726</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3892,7 +3896,7 @@
     <xdr:from>
       <xdr:col>53</xdr:col>
       <xdr:colOff>351892</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>166320</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1841646" cy="2801271"/>
@@ -3931,7 +3935,7 @@
     <xdr:from>
       <xdr:col>53</xdr:col>
       <xdr:colOff>301921</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>12456</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3745470" cy="2591651"/>
@@ -4406,21 +4410,21 @@
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2"/>
-      <c r="O2" s="80" t="s">
+      <c r="O2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="82"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163"/>
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="163"/>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="164"/>
     </row>
     <row r="3" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3"/>
@@ -4436,19 +4440,19 @@
       <c r="L3"/>
       <c r="M3"/>
       <c r="N3"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="84"/>
-      <c r="X3" s="84"/>
-      <c r="Y3" s="84"/>
-      <c r="Z3" s="84"/>
-      <c r="AA3" s="85"/>
+      <c r="O3" s="165"/>
+      <c r="P3" s="166"/>
+      <c r="Q3" s="166"/>
+      <c r="R3" s="166"/>
+      <c r="S3" s="166"/>
+      <c r="T3" s="166"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="166"/>
+      <c r="Y3" s="166"/>
+      <c r="Z3" s="166"/>
+      <c r="AA3" s="167"/>
     </row>
     <row r="4" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4"/>
@@ -4464,23 +4468,23 @@
       <c r="L4"/>
       <c r="M4"/>
       <c r="N4"/>
-      <c r="O4" s="86" t="s">
+      <c r="O4" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="87"/>
-      <c r="T4" s="87"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="89" t="s">
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="169"/>
+      <c r="S4" s="169"/>
+      <c r="T4" s="169"/>
+      <c r="U4" s="170"/>
+      <c r="V4" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="90"/>
+      <c r="W4" s="169"/>
+      <c r="X4" s="169"/>
+      <c r="Y4" s="169"/>
+      <c r="Z4" s="169"/>
+      <c r="AA4" s="172"/>
     </row>
     <row r="5" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5"/>
@@ -4582,21 +4586,21 @@
       <c r="L8"/>
       <c r="M8"/>
       <c r="N8"/>
-      <c r="O8" s="91" t="s">
+      <c r="O8" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="92"/>
-      <c r="S8" s="92"/>
-      <c r="T8" s="92"/>
-      <c r="U8" s="92"/>
-      <c r="V8" s="92"/>
-      <c r="W8" s="92"/>
-      <c r="X8" s="92"/>
-      <c r="Y8" s="92"/>
-      <c r="Z8" s="92"/>
-      <c r="AA8" s="93"/>
+      <c r="P8" s="157"/>
+      <c r="Q8" s="157"/>
+      <c r="R8" s="157"/>
+      <c r="S8" s="157"/>
+      <c r="T8" s="157"/>
+      <c r="U8" s="157"/>
+      <c r="V8" s="157"/>
+      <c r="W8" s="157"/>
+      <c r="X8" s="157"/>
+      <c r="Y8" s="157"/>
+      <c r="Z8" s="157"/>
+      <c r="AA8" s="158"/>
     </row>
     <row r="9" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9"/>
@@ -4612,25 +4616,25 @@
       <c r="L9"/>
       <c r="M9"/>
       <c r="N9"/>
-      <c r="O9" s="100" t="s">
+      <c r="O9" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="101"/>
-      <c r="Q9" s="101"/>
-      <c r="R9" s="101"/>
-      <c r="S9" s="101"/>
-      <c r="T9" s="101" t="s">
+      <c r="P9" s="160"/>
+      <c r="Q9" s="160"/>
+      <c r="R9" s="160"/>
+      <c r="S9" s="160"/>
+      <c r="T9" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="101"/>
-      <c r="V9" s="101"/>
-      <c r="W9" s="101"/>
-      <c r="X9" s="101"/>
-      <c r="Y9" s="101" t="s">
+      <c r="U9" s="160"/>
+      <c r="V9" s="160"/>
+      <c r="W9" s="160"/>
+      <c r="X9" s="160"/>
+      <c r="Y9" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="Z9" s="101"/>
-      <c r="AA9" s="102"/>
+      <c r="Z9" s="160"/>
+      <c r="AA9" s="161"/>
     </row>
     <row r="10" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10"/>
@@ -4646,25 +4650,25 @@
       <c r="L10"/>
       <c r="M10"/>
       <c r="N10"/>
-      <c r="O10" s="94" t="s">
+      <c r="O10" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="95"/>
-      <c r="Q10" s="95"/>
-      <c r="R10" s="95"/>
-      <c r="S10" s="95"/>
-      <c r="T10" s="95" t="s">
+      <c r="P10" s="154"/>
+      <c r="Q10" s="154"/>
+      <c r="R10" s="154"/>
+      <c r="S10" s="154"/>
+      <c r="T10" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="95"/>
-      <c r="V10" s="95"/>
-      <c r="W10" s="95"/>
-      <c r="X10" s="95"/>
-      <c r="Y10" s="95" t="s">
+      <c r="U10" s="154"/>
+      <c r="V10" s="154"/>
+      <c r="W10" s="154"/>
+      <c r="X10" s="154"/>
+      <c r="Y10" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="Z10" s="95"/>
-      <c r="AA10" s="96"/>
+      <c r="Z10" s="154"/>
+      <c r="AA10" s="155"/>
     </row>
     <row r="11" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11"/>
@@ -4680,25 +4684,25 @@
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11"/>
-      <c r="O11" s="94" t="s">
+      <c r="O11" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="95"/>
-      <c r="S11" s="95"/>
-      <c r="T11" s="95" t="s">
+      <c r="P11" s="154"/>
+      <c r="Q11" s="154"/>
+      <c r="R11" s="154"/>
+      <c r="S11" s="154"/>
+      <c r="T11" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="95"/>
-      <c r="V11" s="95"/>
-      <c r="W11" s="95"/>
-      <c r="X11" s="95"/>
-      <c r="Y11" s="95" t="s">
+      <c r="U11" s="154"/>
+      <c r="V11" s="154"/>
+      <c r="W11" s="154"/>
+      <c r="X11" s="154"/>
+      <c r="Y11" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="95"/>
-      <c r="AA11" s="96"/>
+      <c r="Z11" s="154"/>
+      <c r="AA11" s="155"/>
     </row>
     <row r="12" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12"/>
@@ -4714,21 +4718,21 @@
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
-      <c r="O12" s="97" t="s">
+      <c r="O12" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="99"/>
+      <c r="P12" s="150"/>
+      <c r="Q12" s="150"/>
+      <c r="R12" s="150"/>
+      <c r="S12" s="150"/>
+      <c r="T12" s="150"/>
+      <c r="U12" s="150"/>
+      <c r="V12" s="150"/>
+      <c r="W12" s="150"/>
+      <c r="X12" s="150"/>
+      <c r="Y12" s="150"/>
+      <c r="Z12" s="150"/>
+      <c r="AA12" s="151"/>
     </row>
     <row r="13" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13"/>
@@ -4744,21 +4748,21 @@
       <c r="L13"/>
       <c r="M13"/>
       <c r="N13"/>
-      <c r="O13" s="91" t="s">
+      <c r="O13" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="92"/>
-      <c r="Q13" s="92"/>
-      <c r="R13" s="92"/>
-      <c r="S13" s="92"/>
-      <c r="T13" s="92"/>
-      <c r="U13" s="92"/>
-      <c r="V13" s="92"/>
-      <c r="W13" s="92"/>
-      <c r="X13" s="92"/>
-      <c r="Y13" s="92"/>
-      <c r="Z13" s="92"/>
-      <c r="AA13" s="93"/>
+      <c r="P13" s="157"/>
+      <c r="Q13" s="157"/>
+      <c r="R13" s="157"/>
+      <c r="S13" s="157"/>
+      <c r="T13" s="157"/>
+      <c r="U13" s="157"/>
+      <c r="V13" s="157"/>
+      <c r="W13" s="157"/>
+      <c r="X13" s="157"/>
+      <c r="Y13" s="157"/>
+      <c r="Z13" s="157"/>
+      <c r="AA13" s="158"/>
     </row>
     <row r="14" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14"/>
@@ -4774,25 +4778,25 @@
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
-      <c r="O14" s="100" t="s">
+      <c r="O14" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="101"/>
-      <c r="Q14" s="101"/>
-      <c r="R14" s="101"/>
-      <c r="S14" s="101"/>
-      <c r="T14" s="101" t="s">
+      <c r="P14" s="160"/>
+      <c r="Q14" s="160"/>
+      <c r="R14" s="160"/>
+      <c r="S14" s="160"/>
+      <c r="T14" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="U14" s="101"/>
-      <c r="V14" s="101"/>
-      <c r="W14" s="101"/>
-      <c r="X14" s="101"/>
-      <c r="Y14" s="101" t="s">
+      <c r="U14" s="160"/>
+      <c r="V14" s="160"/>
+      <c r="W14" s="160"/>
+      <c r="X14" s="160"/>
+      <c r="Y14" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="101"/>
-      <c r="AA14" s="102"/>
+      <c r="Z14" s="160"/>
+      <c r="AA14" s="161"/>
     </row>
     <row r="15" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15"/>
@@ -4808,25 +4812,25 @@
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15"/>
-      <c r="O15" s="94" t="s">
+      <c r="O15" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="95"/>
-      <c r="Q15" s="95"/>
-      <c r="R15" s="95"/>
-      <c r="S15" s="95"/>
-      <c r="T15" s="95" t="s">
+      <c r="P15" s="154"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="154"/>
+      <c r="S15" s="154"/>
+      <c r="T15" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="U15" s="95"/>
-      <c r="V15" s="95"/>
-      <c r="W15" s="95"/>
-      <c r="X15" s="95"/>
-      <c r="Y15" s="95" t="s">
+      <c r="U15" s="154"/>
+      <c r="V15" s="154"/>
+      <c r="W15" s="154"/>
+      <c r="X15" s="154"/>
+      <c r="Y15" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="Z15" s="95"/>
-      <c r="AA15" s="96"/>
+      <c r="Z15" s="154"/>
+      <c r="AA15" s="155"/>
     </row>
     <row r="16" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16"/>
@@ -4842,25 +4846,25 @@
       <c r="L16"/>
       <c r="M16"/>
       <c r="N16"/>
-      <c r="O16" s="94" t="s">
+      <c r="O16" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="95"/>
-      <c r="Q16" s="95"/>
-      <c r="R16" s="95"/>
-      <c r="S16" s="95"/>
-      <c r="T16" s="95" t="s">
+      <c r="P16" s="154"/>
+      <c r="Q16" s="154"/>
+      <c r="R16" s="154"/>
+      <c r="S16" s="154"/>
+      <c r="T16" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="95"/>
-      <c r="V16" s="95"/>
-      <c r="W16" s="95"/>
-      <c r="X16" s="95"/>
-      <c r="Y16" s="95" t="s">
+      <c r="U16" s="154"/>
+      <c r="V16" s="154"/>
+      <c r="W16" s="154"/>
+      <c r="X16" s="154"/>
+      <c r="Y16" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="95"/>
-      <c r="AA16" s="96"/>
+      <c r="Z16" s="154"/>
+      <c r="AA16" s="155"/>
     </row>
     <row r="17" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17"/>
@@ -4876,21 +4880,21 @@
       <c r="L17"/>
       <c r="M17"/>
       <c r="N17"/>
-      <c r="O17" s="97" t="s">
+      <c r="O17" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
-      <c r="AA17" s="99"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="150"/>
+      <c r="R17" s="150"/>
+      <c r="S17" s="150"/>
+      <c r="T17" s="150"/>
+      <c r="U17" s="150"/>
+      <c r="V17" s="150"/>
+      <c r="W17" s="150"/>
+      <c r="X17" s="150"/>
+      <c r="Y17" s="150"/>
+      <c r="Z17" s="150"/>
+      <c r="AA17" s="151"/>
     </row>
     <row r="18" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18"/>
@@ -4906,21 +4910,21 @@
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
-      <c r="O18" s="91" t="s">
+      <c r="O18" s="156" t="s">
         <v>49</v>
       </c>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="92"/>
-      <c r="S18" s="92"/>
-      <c r="T18" s="92"/>
-      <c r="U18" s="92"/>
-      <c r="V18" s="92"/>
-      <c r="W18" s="92"/>
-      <c r="X18" s="92"/>
-      <c r="Y18" s="92"/>
-      <c r="Z18" s="92"/>
-      <c r="AA18" s="93"/>
+      <c r="P18" s="157"/>
+      <c r="Q18" s="157"/>
+      <c r="R18" s="157"/>
+      <c r="S18" s="157"/>
+      <c r="T18" s="157"/>
+      <c r="U18" s="157"/>
+      <c r="V18" s="157"/>
+      <c r="W18" s="157"/>
+      <c r="X18" s="157"/>
+      <c r="Y18" s="157"/>
+      <c r="Z18" s="157"/>
+      <c r="AA18" s="158"/>
     </row>
     <row r="19" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19"/>
@@ -4936,25 +4940,25 @@
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19"/>
-      <c r="O19" s="100" t="s">
+      <c r="O19" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="101"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="101"/>
-      <c r="T19" s="101" t="s">
+      <c r="P19" s="160"/>
+      <c r="Q19" s="160"/>
+      <c r="R19" s="160"/>
+      <c r="S19" s="160"/>
+      <c r="T19" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="U19" s="101"/>
-      <c r="V19" s="101"/>
-      <c r="W19" s="101"/>
-      <c r="X19" s="101"/>
-      <c r="Y19" s="101" t="s">
+      <c r="U19" s="160"/>
+      <c r="V19" s="160"/>
+      <c r="W19" s="160"/>
+      <c r="X19" s="160"/>
+      <c r="Y19" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="Z19" s="101"/>
-      <c r="AA19" s="102"/>
+      <c r="Z19" s="160"/>
+      <c r="AA19" s="161"/>
     </row>
     <row r="20" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20"/>
@@ -4970,25 +4974,25 @@
       <c r="L20"/>
       <c r="M20"/>
       <c r="N20"/>
-      <c r="O20" s="94" t="s">
+      <c r="O20" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95" t="s">
+      <c r="P20" s="154"/>
+      <c r="Q20" s="154"/>
+      <c r="R20" s="154"/>
+      <c r="S20" s="154"/>
+      <c r="T20" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="U20" s="95"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="95"/>
-      <c r="X20" s="95"/>
-      <c r="Y20" s="95" t="s">
+      <c r="U20" s="154"/>
+      <c r="V20" s="154"/>
+      <c r="W20" s="154"/>
+      <c r="X20" s="154"/>
+      <c r="Y20" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="96"/>
+      <c r="Z20" s="154"/>
+      <c r="AA20" s="155"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21"/>
@@ -5004,25 +5008,25 @@
       <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
-      <c r="O21" s="94" t="s">
+      <c r="O21" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="95"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="95"/>
-      <c r="S21" s="95"/>
-      <c r="T21" s="95" t="s">
+      <c r="P21" s="154"/>
+      <c r="Q21" s="154"/>
+      <c r="R21" s="154"/>
+      <c r="S21" s="154"/>
+      <c r="T21" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="95"/>
-      <c r="V21" s="95"/>
-      <c r="W21" s="95"/>
-      <c r="X21" s="95"/>
-      <c r="Y21" s="95" t="s">
+      <c r="U21" s="154"/>
+      <c r="V21" s="154"/>
+      <c r="W21" s="154"/>
+      <c r="X21" s="154"/>
+      <c r="Y21" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="95"/>
-      <c r="AA21" s="96"/>
+      <c r="Z21" s="154"/>
+      <c r="AA21" s="155"/>
     </row>
     <row r="22" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22"/>
@@ -5038,21 +5042,21 @@
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
-      <c r="O22" s="97" t="s">
+      <c r="O22" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="98"/>
-      <c r="W22" s="98"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="98"/>
-      <c r="Z22" s="98"/>
-      <c r="AA22" s="99"/>
+      <c r="P22" s="150"/>
+      <c r="Q22" s="150"/>
+      <c r="R22" s="150"/>
+      <c r="S22" s="150"/>
+      <c r="T22" s="150"/>
+      <c r="U22" s="150"/>
+      <c r="V22" s="150"/>
+      <c r="W22" s="150"/>
+      <c r="X22" s="150"/>
+      <c r="Y22" s="150"/>
+      <c r="Z22" s="150"/>
+      <c r="AA22" s="151"/>
     </row>
     <row r="23" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23"/>
@@ -5068,35 +5072,35 @@
       <c r="L23"/>
       <c r="M23"/>
       <c r="N23"/>
-      <c r="O23" s="103" t="s">
+      <c r="O23" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="P23" s="103" t="s">
+      <c r="P23" s="146" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="105" t="s">
+      <c r="Q23" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="R23" s="106"/>
-      <c r="S23" s="115" t="s">
+      <c r="R23" s="143"/>
+      <c r="S23" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="106"/>
-      <c r="U23" s="115" t="s">
+      <c r="T23" s="143"/>
+      <c r="U23" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="V23" s="106"/>
-      <c r="W23" s="116" t="s">
+      <c r="V23" s="143"/>
+      <c r="W23" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="X23" s="115" t="s">
+      <c r="X23" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="106"/>
-      <c r="Z23" s="103" t="s">
+      <c r="Y23" s="143"/>
+      <c r="Z23" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="AA23" s="118" t="s">
+      <c r="AA23" s="148" t="s">
         <v>23</v>
       </c>
     </row>
@@ -5114,8 +5118,8 @@
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="104"/>
+      <c r="O24" s="147"/>
+      <c r="P24" s="147"/>
       <c r="Q24" s="41" t="s">
         <v>13</v>
       </c>
@@ -5134,15 +5138,15 @@
       <c r="V24" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="117"/>
+      <c r="W24" s="145"/>
       <c r="X24" s="41" t="s">
         <v>11</v>
       </c>
       <c r="Y24" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="Z24" s="104"/>
-      <c r="AA24" s="118"/>
+      <c r="Z24" s="147"/>
+      <c r="AA24" s="148"/>
     </row>
     <row r="25" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -6117,23 +6121,23 @@
       <c r="L55"/>
       <c r="M55"/>
       <c r="N55"/>
-      <c r="O55" s="107" t="s">
+      <c r="O55" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="P55" s="108"/>
-      <c r="Q55" s="108"/>
-      <c r="R55" s="108"/>
-      <c r="S55" s="108"/>
-      <c r="T55" s="108"/>
-      <c r="U55" s="109"/>
-      <c r="V55" s="107" t="s">
+      <c r="P55" s="135"/>
+      <c r="Q55" s="135"/>
+      <c r="R55" s="135"/>
+      <c r="S55" s="135"/>
+      <c r="T55" s="135"/>
+      <c r="U55" s="136"/>
+      <c r="V55" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="W55" s="108"/>
-      <c r="X55" s="108"/>
-      <c r="Y55" s="108"/>
-      <c r="Z55" s="108"/>
-      <c r="AA55" s="109"/>
+      <c r="W55" s="135"/>
+      <c r="X55" s="135"/>
+      <c r="Y55" s="135"/>
+      <c r="Z55" s="135"/>
+      <c r="AA55" s="136"/>
     </row>
     <row r="56" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56"/>
@@ -6149,19 +6153,19 @@
       <c r="L56"/>
       <c r="M56"/>
       <c r="N56"/>
-      <c r="O56" s="110"/>
-      <c r="P56" s="111"/>
-      <c r="Q56" s="111"/>
-      <c r="R56" s="111"/>
-      <c r="S56" s="111"/>
-      <c r="T56" s="111"/>
-      <c r="U56" s="112"/>
-      <c r="V56" s="113"/>
-      <c r="W56" s="114"/>
-      <c r="X56" s="114"/>
-      <c r="Y56" s="114"/>
-      <c r="Z56" s="114"/>
-      <c r="AA56" s="114"/>
+      <c r="O56" s="137"/>
+      <c r="P56" s="138"/>
+      <c r="Q56" s="138"/>
+      <c r="R56" s="138"/>
+      <c r="S56" s="138"/>
+      <c r="T56" s="138"/>
+      <c r="U56" s="139"/>
+      <c r="V56" s="140"/>
+      <c r="W56" s="141"/>
+      <c r="X56" s="141"/>
+      <c r="Y56" s="141"/>
+      <c r="Z56" s="141"/>
+      <c r="AA56" s="141"/>
     </row>
     <row r="57" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57"/>
@@ -6177,19 +6181,19 @@
       <c r="L57"/>
       <c r="M57"/>
       <c r="N57"/>
-      <c r="O57" s="124"/>
-      <c r="P57" s="125"/>
-      <c r="Q57" s="125"/>
-      <c r="R57" s="125"/>
-      <c r="S57" s="125"/>
-      <c r="T57" s="125"/>
-      <c r="U57" s="126"/>
-      <c r="V57" s="127"/>
-      <c r="W57" s="128"/>
-      <c r="X57" s="128"/>
-      <c r="Y57" s="128"/>
-      <c r="Z57" s="128"/>
-      <c r="AA57" s="128"/>
+      <c r="O57" s="129"/>
+      <c r="P57" s="130"/>
+      <c r="Q57" s="130"/>
+      <c r="R57" s="130"/>
+      <c r="S57" s="130"/>
+      <c r="T57" s="130"/>
+      <c r="U57" s="131"/>
+      <c r="V57" s="132"/>
+      <c r="W57" s="133"/>
+      <c r="X57" s="133"/>
+      <c r="Y57" s="133"/>
+      <c r="Z57" s="133"/>
+      <c r="AA57" s="133"/>
     </row>
     <row r="58" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58"/>
@@ -6205,19 +6209,19 @@
       <c r="L58"/>
       <c r="M58"/>
       <c r="N58"/>
-      <c r="O58" s="124"/>
-      <c r="P58" s="125"/>
-      <c r="Q58" s="125"/>
-      <c r="R58" s="125"/>
-      <c r="S58" s="125"/>
-      <c r="T58" s="125"/>
-      <c r="U58" s="126"/>
-      <c r="V58" s="127"/>
-      <c r="W58" s="128"/>
-      <c r="X58" s="128"/>
-      <c r="Y58" s="128"/>
-      <c r="Z58" s="128"/>
-      <c r="AA58" s="128"/>
+      <c r="O58" s="129"/>
+      <c r="P58" s="130"/>
+      <c r="Q58" s="130"/>
+      <c r="R58" s="130"/>
+      <c r="S58" s="130"/>
+      <c r="T58" s="130"/>
+      <c r="U58" s="131"/>
+      <c r="V58" s="132"/>
+      <c r="W58" s="133"/>
+      <c r="X58" s="133"/>
+      <c r="Y58" s="133"/>
+      <c r="Z58" s="133"/>
+      <c r="AA58" s="133"/>
     </row>
     <row r="59" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59"/>
@@ -6233,28 +6237,61 @@
       <c r="L59"/>
       <c r="M59"/>
       <c r="N59"/>
-      <c r="O59" s="119"/>
-      <c r="P59" s="120"/>
-      <c r="Q59" s="120"/>
-      <c r="R59" s="120"/>
-      <c r="S59" s="120"/>
-      <c r="T59" s="120"/>
-      <c r="U59" s="121"/>
-      <c r="V59" s="122"/>
-      <c r="W59" s="123"/>
-      <c r="X59" s="123"/>
-      <c r="Y59" s="123"/>
-      <c r="Z59" s="123"/>
-      <c r="AA59" s="123"/>
+      <c r="O59" s="124"/>
+      <c r="P59" s="125"/>
+      <c r="Q59" s="125"/>
+      <c r="R59" s="125"/>
+      <c r="S59" s="125"/>
+      <c r="T59" s="125"/>
+      <c r="U59" s="126"/>
+      <c r="V59" s="127"/>
+      <c r="W59" s="128"/>
+      <c r="X59" s="128"/>
+      <c r="Y59" s="128"/>
+      <c r="Z59" s="128"/>
+      <c r="AA59" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="V59:AA59"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="V57:AA57"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="V58:AA58"/>
+    <mergeCell ref="O2:AA3"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="V4:AA4"/>
+    <mergeCell ref="O8:AA8"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="O12:AA12"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:X15"/>
+    <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="O13:AA13"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:X14"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="O18:AA18"/>
+    <mergeCell ref="O19:S19"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:X16"/>
+    <mergeCell ref="Y16:AA16"/>
+    <mergeCell ref="O17:AA17"/>
+    <mergeCell ref="O22:AA22"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="O20:S20"/>
+    <mergeCell ref="T20:X20"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="Y21:AA21"/>
     <mergeCell ref="O55:U55"/>
     <mergeCell ref="V55:AA55"/>
     <mergeCell ref="O56:U56"/>
@@ -6265,45 +6302,12 @@
     <mergeCell ref="X23:Y23"/>
     <mergeCell ref="Z23:Z24"/>
     <mergeCell ref="AA23:AA24"/>
-    <mergeCell ref="O22:AA22"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="O20:S20"/>
-    <mergeCell ref="T20:X20"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="O18:AA18"/>
-    <mergeCell ref="O19:S19"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:X16"/>
-    <mergeCell ref="Y16:AA16"/>
-    <mergeCell ref="O17:AA17"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:X15"/>
-    <mergeCell ref="Y15:AA15"/>
-    <mergeCell ref="O13:AA13"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:X14"/>
-    <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="O12:AA12"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="O2:AA3"/>
-    <mergeCell ref="O4:U4"/>
-    <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="O8:AA8"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="V59:AA59"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="V57:AA57"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="V58:AA58"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -6478,21 +6482,21 @@
         <v>63</v>
       </c>
       <c r="N2" s="38"/>
-      <c r="O2" s="80" t="s">
+      <c r="O2" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="82"/>
+      <c r="P2" s="163"/>
+      <c r="Q2" s="163"/>
+      <c r="R2" s="163"/>
+      <c r="S2" s="163"/>
+      <c r="T2" s="163"/>
+      <c r="U2" s="163"/>
+      <c r="V2" s="163"/>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="163"/>
+      <c r="AA2" s="164"/>
     </row>
     <row r="3" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
@@ -6523,19 +6527,19 @@
       <c r="N3" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="83"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="84"/>
-      <c r="T3" s="84"/>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="84"/>
-      <c r="X3" s="84"/>
-      <c r="Y3" s="84"/>
-      <c r="Z3" s="84"/>
-      <c r="AA3" s="85"/>
+      <c r="O3" s="165"/>
+      <c r="P3" s="166"/>
+      <c r="Q3" s="166"/>
+      <c r="R3" s="166"/>
+      <c r="S3" s="166"/>
+      <c r="T3" s="166"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="166"/>
+      <c r="Y3" s="166"/>
+      <c r="Z3" s="166"/>
+      <c r="AA3" s="167"/>
     </row>
     <row r="4" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
@@ -6555,23 +6559,23 @@
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
       <c r="N4" s="25"/>
-      <c r="O4" s="86" t="s">
+      <c r="O4" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="87"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="87"/>
-      <c r="T4" s="87"/>
-      <c r="U4" s="88"/>
-      <c r="V4" s="89" t="s">
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="169"/>
+      <c r="S4" s="169"/>
+      <c r="T4" s="169"/>
+      <c r="U4" s="170"/>
+      <c r="V4" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="90"/>
+      <c r="W4" s="169"/>
+      <c r="X4" s="169"/>
+      <c r="Y4" s="169"/>
+      <c r="Z4" s="169"/>
+      <c r="AA4" s="172"/>
     </row>
     <row r="5" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
@@ -6672,48 +6676,48 @@
       <c r="AA7" s="52"/>
     </row>
     <row r="8" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="148" t="s">
+      <c r="B8" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="149"/>
-      <c r="D8" s="149"/>
-      <c r="E8" s="149"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="148" t="s">
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="176"/>
+      <c r="F8" s="176"/>
+      <c r="G8" s="177"/>
+      <c r="H8" s="175" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="149"/>
-      <c r="J8" s="150"/>
-      <c r="K8" s="162" t="s">
+      <c r="I8" s="176"/>
+      <c r="J8" s="177"/>
+      <c r="K8" s="187" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="163"/>
-      <c r="M8" s="163"/>
-      <c r="N8" s="164"/>
-      <c r="O8" s="91" t="s">
+      <c r="L8" s="188"/>
+      <c r="M8" s="188"/>
+      <c r="N8" s="189"/>
+      <c r="O8" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="92"/>
-      <c r="S8" s="92"/>
-      <c r="T8" s="92"/>
-      <c r="U8" s="92"/>
-      <c r="V8" s="92"/>
-      <c r="W8" s="92"/>
-      <c r="X8" s="92"/>
-      <c r="Y8" s="92"/>
-      <c r="Z8" s="92"/>
-      <c r="AA8" s="93"/>
+      <c r="P8" s="157"/>
+      <c r="Q8" s="157"/>
+      <c r="R8" s="157"/>
+      <c r="S8" s="157"/>
+      <c r="T8" s="157"/>
+      <c r="U8" s="157"/>
+      <c r="V8" s="157"/>
+      <c r="W8" s="157"/>
+      <c r="X8" s="157"/>
+      <c r="Y8" s="157"/>
+      <c r="Z8" s="157"/>
+      <c r="AA8" s="158"/>
     </row>
     <row r="9" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="151"/>
-      <c r="C9" s="152"/>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="153"/>
+      <c r="B9" s="178"/>
+      <c r="C9" s="179"/>
+      <c r="D9" s="179"/>
+      <c r="E9" s="179"/>
+      <c r="F9" s="179"/>
+      <c r="G9" s="180"/>
       <c r="H9" s="30" t="s">
         <v>15</v>
       </c>
@@ -6725,33 +6729,33 @@
       <c r="L9" s="54"/>
       <c r="M9" s="54"/>
       <c r="N9" s="55"/>
-      <c r="O9" s="100" t="s">
+      <c r="O9" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="101"/>
-      <c r="Q9" s="101"/>
-      <c r="R9" s="101"/>
-      <c r="S9" s="101"/>
-      <c r="T9" s="101" t="s">
+      <c r="P9" s="160"/>
+      <c r="Q9" s="160"/>
+      <c r="R9" s="160"/>
+      <c r="S9" s="160"/>
+      <c r="T9" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="101"/>
-      <c r="V9" s="101"/>
-      <c r="W9" s="101"/>
-      <c r="X9" s="101"/>
-      <c r="Y9" s="101" t="s">
+      <c r="U9" s="160"/>
+      <c r="V9" s="160"/>
+      <c r="W9" s="160"/>
+      <c r="X9" s="160"/>
+      <c r="Y9" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="Z9" s="101"/>
-      <c r="AA9" s="102"/>
+      <c r="Z9" s="160"/>
+      <c r="AA9" s="161"/>
     </row>
     <row r="10" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="156"/>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="158"/>
+      <c r="B10" s="181"/>
+      <c r="C10" s="182"/>
+      <c r="D10" s="182"/>
+      <c r="E10" s="182"/>
+      <c r="F10" s="182"/>
+      <c r="G10" s="183"/>
       <c r="H10" s="13" t="s">
         <v>16</v>
       </c>
@@ -6763,71 +6767,71 @@
       <c r="L10" s="57"/>
       <c r="M10" s="57"/>
       <c r="N10" s="58"/>
-      <c r="O10" s="94" t="s">
+      <c r="O10" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="95"/>
-      <c r="Q10" s="95"/>
-      <c r="R10" s="95"/>
-      <c r="S10" s="95"/>
-      <c r="T10" s="95" t="s">
+      <c r="P10" s="154"/>
+      <c r="Q10" s="154"/>
+      <c r="R10" s="154"/>
+      <c r="S10" s="154"/>
+      <c r="T10" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="95"/>
-      <c r="V10" s="95"/>
-      <c r="W10" s="95"/>
-      <c r="X10" s="95"/>
-      <c r="Y10" s="95" t="s">
+      <c r="U10" s="154"/>
+      <c r="V10" s="154"/>
+      <c r="W10" s="154"/>
+      <c r="X10" s="154"/>
+      <c r="Y10" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="Z10" s="95"/>
-      <c r="AA10" s="96"/>
+      <c r="Z10" s="154"/>
+      <c r="AA10" s="155"/>
     </row>
     <row r="11" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="156"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="158"/>
+      <c r="B11" s="181"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="182"/>
+      <c r="E11" s="182"/>
+      <c r="F11" s="182"/>
+      <c r="G11" s="183"/>
       <c r="H11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="154" t="s">
+      <c r="I11" s="173" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="155"/>
+      <c r="J11" s="174"/>
       <c r="K11" s="56"/>
       <c r="L11" s="57"/>
       <c r="M11" s="57"/>
       <c r="N11" s="58"/>
-      <c r="O11" s="94" t="s">
+      <c r="O11" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="95"/>
-      <c r="S11" s="95"/>
-      <c r="T11" s="95" t="s">
+      <c r="P11" s="154"/>
+      <c r="Q11" s="154"/>
+      <c r="R11" s="154"/>
+      <c r="S11" s="154"/>
+      <c r="T11" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="95"/>
-      <c r="V11" s="95"/>
-      <c r="W11" s="95"/>
-      <c r="X11" s="95"/>
-      <c r="Y11" s="95" t="s">
+      <c r="U11" s="154"/>
+      <c r="V11" s="154"/>
+      <c r="W11" s="154"/>
+      <c r="X11" s="154"/>
+      <c r="Y11" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="95"/>
-      <c r="AA11" s="96"/>
+      <c r="Z11" s="154"/>
+      <c r="AA11" s="155"/>
     </row>
     <row r="12" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="159"/>
-      <c r="C12" s="160"/>
-      <c r="D12" s="160"/>
-      <c r="E12" s="160"/>
-      <c r="F12" s="160"/>
-      <c r="G12" s="161"/>
+      <c r="B12" s="184"/>
+      <c r="C12" s="185"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="185"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="186"/>
       <c r="H12" s="13" t="s">
         <v>17</v>
       </c>
@@ -6839,31 +6843,31 @@
       <c r="L12" s="57"/>
       <c r="M12" s="57"/>
       <c r="N12" s="58"/>
-      <c r="O12" s="97" t="s">
+      <c r="O12" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="99"/>
+      <c r="P12" s="150"/>
+      <c r="Q12" s="150"/>
+      <c r="R12" s="150"/>
+      <c r="S12" s="150"/>
+      <c r="T12" s="150"/>
+      <c r="U12" s="150"/>
+      <c r="V12" s="150"/>
+      <c r="W12" s="150"/>
+      <c r="X12" s="150"/>
+      <c r="Y12" s="150"/>
+      <c r="Z12" s="150"/>
+      <c r="AA12" s="151"/>
     </row>
     <row r="13" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="148" t="s">
+      <c r="B13" s="175" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="150"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="176"/>
+      <c r="G13" s="177"/>
       <c r="H13" s="13" t="s">
         <v>34</v>
       </c>
@@ -6875,100 +6879,100 @@
       <c r="L13" s="57"/>
       <c r="M13" s="57"/>
       <c r="N13" s="58"/>
-      <c r="O13" s="91" t="s">
+      <c r="O13" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="92"/>
-      <c r="Q13" s="92"/>
-      <c r="R13" s="92"/>
-      <c r="S13" s="92"/>
-      <c r="T13" s="92"/>
-      <c r="U13" s="92"/>
-      <c r="V13" s="92"/>
-      <c r="W13" s="92"/>
-      <c r="X13" s="92"/>
-      <c r="Y13" s="92"/>
-      <c r="Z13" s="92"/>
-      <c r="AA13" s="93"/>
+      <c r="P13" s="157"/>
+      <c r="Q13" s="157"/>
+      <c r="R13" s="157"/>
+      <c r="S13" s="157"/>
+      <c r="T13" s="157"/>
+      <c r="U13" s="157"/>
+      <c r="V13" s="157"/>
+      <c r="W13" s="157"/>
+      <c r="X13" s="157"/>
+      <c r="Y13" s="157"/>
+      <c r="Z13" s="157"/>
+      <c r="AA13" s="158"/>
     </row>
     <row r="14" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="151"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
-      <c r="F14" s="152"/>
-      <c r="G14" s="153"/>
+      <c r="B14" s="178"/>
+      <c r="C14" s="179"/>
+      <c r="D14" s="179"/>
+      <c r="E14" s="179"/>
+      <c r="F14" s="179"/>
+      <c r="G14" s="180"/>
       <c r="H14" s="3"/>
       <c r="J14" s="4"/>
       <c r="K14" s="59"/>
       <c r="L14" s="60"/>
       <c r="M14" s="60"/>
       <c r="N14" s="61"/>
-      <c r="O14" s="100" t="s">
+      <c r="O14" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="101"/>
-      <c r="Q14" s="101"/>
-      <c r="R14" s="101"/>
-      <c r="S14" s="101"/>
-      <c r="T14" s="101" t="s">
+      <c r="P14" s="160"/>
+      <c r="Q14" s="160"/>
+      <c r="R14" s="160"/>
+      <c r="S14" s="160"/>
+      <c r="T14" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="U14" s="101"/>
-      <c r="V14" s="101"/>
-      <c r="W14" s="101"/>
-      <c r="X14" s="101"/>
-      <c r="Y14" s="101" t="s">
+      <c r="U14" s="160"/>
+      <c r="V14" s="160"/>
+      <c r="W14" s="160"/>
+      <c r="X14" s="160"/>
+      <c r="Y14" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="101"/>
-      <c r="AA14" s="102"/>
+      <c r="Z14" s="160"/>
+      <c r="AA14" s="161"/>
     </row>
     <row r="15" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="156"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="157"/>
-      <c r="F15" s="157"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="148" t="s">
+      <c r="B15" s="181"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="182"/>
+      <c r="G15" s="183"/>
+      <c r="H15" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="149"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="148" t="s">
+      <c r="I15" s="176"/>
+      <c r="J15" s="176"/>
+      <c r="K15" s="177"/>
+      <c r="L15" s="175" t="s">
         <v>75</v>
       </c>
-      <c r="M15" s="149"/>
-      <c r="N15" s="150"/>
-      <c r="O15" s="94" t="s">
+      <c r="M15" s="176"/>
+      <c r="N15" s="177"/>
+      <c r="O15" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="95"/>
-      <c r="Q15" s="95"/>
-      <c r="R15" s="95"/>
-      <c r="S15" s="95"/>
-      <c r="T15" s="95" t="s">
+      <c r="P15" s="154"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="154"/>
+      <c r="S15" s="154"/>
+      <c r="T15" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="U15" s="95"/>
-      <c r="V15" s="95"/>
-      <c r="W15" s="95"/>
-      <c r="X15" s="95"/>
-      <c r="Y15" s="95" t="s">
+      <c r="U15" s="154"/>
+      <c r="V15" s="154"/>
+      <c r="W15" s="154"/>
+      <c r="X15" s="154"/>
+      <c r="Y15" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="Z15" s="95"/>
-      <c r="AA15" s="96"/>
+      <c r="Z15" s="154"/>
+      <c r="AA15" s="155"/>
     </row>
     <row r="16" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="156"/>
-      <c r="C16" s="157"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="157"/>
-      <c r="F16" s="157"/>
-      <c r="G16" s="158"/>
+      <c r="B16" s="181"/>
+      <c r="C16" s="182"/>
+      <c r="D16" s="182"/>
+      <c r="E16" s="182"/>
+      <c r="F16" s="182"/>
+      <c r="G16" s="183"/>
       <c r="H16" s="14"/>
       <c r="I16" s="18" t="s">
         <v>18</v>
@@ -6982,33 +6986,33 @@
       <c r="L16" s="62"/>
       <c r="M16" s="63"/>
       <c r="N16" s="64"/>
-      <c r="O16" s="94" t="s">
+      <c r="O16" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="95"/>
-      <c r="Q16" s="95"/>
-      <c r="R16" s="95"/>
-      <c r="S16" s="95"/>
-      <c r="T16" s="95" t="s">
+      <c r="P16" s="154"/>
+      <c r="Q16" s="154"/>
+      <c r="R16" s="154"/>
+      <c r="S16" s="154"/>
+      <c r="T16" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="95"/>
-      <c r="V16" s="95"/>
-      <c r="W16" s="95"/>
-      <c r="X16" s="95"/>
-      <c r="Y16" s="95" t="s">
+      <c r="U16" s="154"/>
+      <c r="V16" s="154"/>
+      <c r="W16" s="154"/>
+      <c r="X16" s="154"/>
+      <c r="Y16" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="95"/>
-      <c r="AA16" s="96"/>
+      <c r="Z16" s="154"/>
+      <c r="AA16" s="155"/>
     </row>
     <row r="17" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="156"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
-      <c r="F17" s="157"/>
-      <c r="G17" s="158"/>
+      <c r="B17" s="181"/>
+      <c r="C17" s="182"/>
+      <c r="D17" s="182"/>
+      <c r="E17" s="182"/>
+      <c r="F17" s="182"/>
+      <c r="G17" s="183"/>
       <c r="H17" s="10" t="s">
         <v>59</v>
       </c>
@@ -7018,29 +7022,29 @@
       <c r="L17" s="56"/>
       <c r="M17" s="57"/>
       <c r="N17" s="58"/>
-      <c r="O17" s="97" t="s">
+      <c r="O17" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="98"/>
-      <c r="Q17" s="98"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="98"/>
-      <c r="T17" s="98"/>
-      <c r="U17" s="98"/>
-      <c r="V17" s="98"/>
-      <c r="W17" s="98"/>
-      <c r="X17" s="98"/>
-      <c r="Y17" s="98"/>
-      <c r="Z17" s="98"/>
-      <c r="AA17" s="99"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="150"/>
+      <c r="R17" s="150"/>
+      <c r="S17" s="150"/>
+      <c r="T17" s="150"/>
+      <c r="U17" s="150"/>
+      <c r="V17" s="150"/>
+      <c r="W17" s="150"/>
+      <c r="X17" s="150"/>
+      <c r="Y17" s="150"/>
+      <c r="Z17" s="150"/>
+      <c r="AA17" s="151"/>
     </row>
     <row r="18" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="156"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
-      <c r="E18" s="157"/>
-      <c r="F18" s="157"/>
-      <c r="G18" s="158"/>
+      <c r="B18" s="181"/>
+      <c r="C18" s="182"/>
+      <c r="D18" s="182"/>
+      <c r="E18" s="182"/>
+      <c r="F18" s="182"/>
+      <c r="G18" s="183"/>
       <c r="H18" s="10" t="s">
         <v>53</v>
       </c>
@@ -7050,29 +7054,29 @@
       <c r="L18" s="56"/>
       <c r="M18" s="57"/>
       <c r="N18" s="58"/>
-      <c r="O18" s="91" t="s">
+      <c r="O18" s="156" t="s">
         <v>49</v>
       </c>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="92"/>
-      <c r="S18" s="92"/>
-      <c r="T18" s="92"/>
-      <c r="U18" s="92"/>
-      <c r="V18" s="92"/>
-      <c r="W18" s="92"/>
-      <c r="X18" s="92"/>
-      <c r="Y18" s="92"/>
-      <c r="Z18" s="92"/>
-      <c r="AA18" s="93"/>
+      <c r="P18" s="157"/>
+      <c r="Q18" s="157"/>
+      <c r="R18" s="157"/>
+      <c r="S18" s="157"/>
+      <c r="T18" s="157"/>
+      <c r="U18" s="157"/>
+      <c r="V18" s="157"/>
+      <c r="W18" s="157"/>
+      <c r="X18" s="157"/>
+      <c r="Y18" s="157"/>
+      <c r="Z18" s="157"/>
+      <c r="AA18" s="158"/>
     </row>
     <row r="19" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="156"/>
-      <c r="C19" s="157"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="157"/>
-      <c r="F19" s="157"/>
-      <c r="G19" s="158"/>
+      <c r="B19" s="181"/>
+      <c r="C19" s="182"/>
+      <c r="D19" s="182"/>
+      <c r="E19" s="182"/>
+      <c r="F19" s="182"/>
+      <c r="G19" s="183"/>
       <c r="H19" s="10" t="s">
         <v>72</v>
       </c>
@@ -7082,33 +7086,33 @@
       <c r="L19" s="56"/>
       <c r="M19" s="57"/>
       <c r="N19" s="58"/>
-      <c r="O19" s="100" t="s">
+      <c r="O19" s="159" t="s">
         <v>44</v>
       </c>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="101"/>
-      <c r="R19" s="101"/>
-      <c r="S19" s="101"/>
-      <c r="T19" s="101" t="s">
+      <c r="P19" s="160"/>
+      <c r="Q19" s="160"/>
+      <c r="R19" s="160"/>
+      <c r="S19" s="160"/>
+      <c r="T19" s="160" t="s">
         <v>47</v>
       </c>
-      <c r="U19" s="101"/>
-      <c r="V19" s="101"/>
-      <c r="W19" s="101"/>
-      <c r="X19" s="101"/>
-      <c r="Y19" s="101" t="s">
+      <c r="U19" s="160"/>
+      <c r="V19" s="160"/>
+      <c r="W19" s="160"/>
+      <c r="X19" s="160"/>
+      <c r="Y19" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="Z19" s="101"/>
-      <c r="AA19" s="102"/>
+      <c r="Z19" s="160"/>
+      <c r="AA19" s="161"/>
     </row>
     <row r="20" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="156"/>
-      <c r="C20" s="157"/>
-      <c r="D20" s="157"/>
-      <c r="E20" s="157"/>
-      <c r="F20" s="157"/>
-      <c r="G20" s="158"/>
+      <c r="B20" s="181"/>
+      <c r="C20" s="182"/>
+      <c r="D20" s="182"/>
+      <c r="E20" s="182"/>
+      <c r="F20" s="182"/>
+      <c r="G20" s="183"/>
       <c r="H20" s="10" t="s">
         <v>52</v>
       </c>
@@ -7118,33 +7122,33 @@
       <c r="L20" s="56"/>
       <c r="M20" s="57"/>
       <c r="N20" s="58"/>
-      <c r="O20" s="94" t="s">
+      <c r="O20" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95" t="s">
+      <c r="P20" s="154"/>
+      <c r="Q20" s="154"/>
+      <c r="R20" s="154"/>
+      <c r="S20" s="154"/>
+      <c r="T20" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="U20" s="95"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="95"/>
-      <c r="X20" s="95"/>
-      <c r="Y20" s="95" t="s">
+      <c r="U20" s="154"/>
+      <c r="V20" s="154"/>
+      <c r="W20" s="154"/>
+      <c r="X20" s="154"/>
+      <c r="Y20" s="154" t="s">
         <v>67</v>
       </c>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="96"/>
+      <c r="Z20" s="154"/>
+      <c r="AA20" s="155"/>
     </row>
     <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="156"/>
-      <c r="C21" s="157"/>
-      <c r="D21" s="157"/>
-      <c r="E21" s="157"/>
-      <c r="F21" s="157"/>
-      <c r="G21" s="158"/>
+      <c r="B21" s="181"/>
+      <c r="C21" s="182"/>
+      <c r="D21" s="182"/>
+      <c r="E21" s="182"/>
+      <c r="F21" s="182"/>
+      <c r="G21" s="183"/>
       <c r="H21" s="10" t="s">
         <v>54</v>
       </c>
@@ -7154,33 +7158,33 @@
       <c r="L21" s="56"/>
       <c r="M21" s="57"/>
       <c r="N21" s="58"/>
-      <c r="O21" s="94" t="s">
+      <c r="O21" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="95"/>
-      <c r="Q21" s="95"/>
-      <c r="R21" s="95"/>
-      <c r="S21" s="95"/>
-      <c r="T21" s="95" t="s">
+      <c r="P21" s="154"/>
+      <c r="Q21" s="154"/>
+      <c r="R21" s="154"/>
+      <c r="S21" s="154"/>
+      <c r="T21" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="95"/>
-      <c r="V21" s="95"/>
-      <c r="W21" s="95"/>
-      <c r="X21" s="95"/>
-      <c r="Y21" s="95" t="s">
+      <c r="U21" s="154"/>
+      <c r="V21" s="154"/>
+      <c r="W21" s="154"/>
+      <c r="X21" s="154"/>
+      <c r="Y21" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="95"/>
-      <c r="AA21" s="96"/>
+      <c r="Z21" s="154"/>
+      <c r="AA21" s="155"/>
     </row>
     <row r="22" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="159"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="160"/>
-      <c r="E22" s="160"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="161"/>
+      <c r="B22" s="184"/>
+      <c r="C22" s="185"/>
+      <c r="D22" s="185"/>
+      <c r="E22" s="185"/>
+      <c r="F22" s="185"/>
+      <c r="G22" s="186"/>
       <c r="H22" s="15"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
@@ -7188,98 +7192,98 @@
       <c r="L22" s="59"/>
       <c r="M22" s="60"/>
       <c r="N22" s="61"/>
-      <c r="O22" s="97" t="s">
+      <c r="O22" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="98"/>
-      <c r="W22" s="98"/>
-      <c r="X22" s="98"/>
-      <c r="Y22" s="98"/>
-      <c r="Z22" s="98"/>
-      <c r="AA22" s="99"/>
+      <c r="P22" s="150"/>
+      <c r="Q22" s="150"/>
+      <c r="R22" s="150"/>
+      <c r="S22" s="150"/>
+      <c r="T22" s="150"/>
+      <c r="U22" s="150"/>
+      <c r="V22" s="150"/>
+      <c r="W22" s="150"/>
+      <c r="X22" s="150"/>
+      <c r="Y22" s="150"/>
+      <c r="Z22" s="150"/>
+      <c r="AA22" s="151"/>
     </row>
     <row r="23" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="103" t="s">
+      <c r="B23" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="103" t="s">
+      <c r="C23" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="115" t="s">
+      <c r="D23" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="106"/>
-      <c r="F23" s="103" t="s">
+      <c r="E23" s="143"/>
+      <c r="F23" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="136" t="s">
+      <c r="G23" s="197" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="137"/>
-      <c r="I23" s="137"/>
-      <c r="J23" s="137"/>
-      <c r="K23" s="137"/>
-      <c r="L23" s="137"/>
-      <c r="M23" s="137"/>
-      <c r="N23" s="138"/>
-      <c r="O23" s="103" t="s">
+      <c r="H23" s="198"/>
+      <c r="I23" s="198"/>
+      <c r="J23" s="198"/>
+      <c r="K23" s="198"/>
+      <c r="L23" s="198"/>
+      <c r="M23" s="198"/>
+      <c r="N23" s="199"/>
+      <c r="O23" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="P23" s="103" t="s">
+      <c r="P23" s="146" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="105" t="s">
+      <c r="Q23" s="152" t="s">
         <v>71</v>
       </c>
-      <c r="R23" s="106"/>
-      <c r="S23" s="115" t="s">
+      <c r="R23" s="143"/>
+      <c r="S23" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="106"/>
-      <c r="U23" s="115" t="s">
+      <c r="T23" s="143"/>
+      <c r="U23" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="V23" s="106"/>
-      <c r="W23" s="116" t="s">
+      <c r="V23" s="143"/>
+      <c r="W23" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="X23" s="115" t="s">
+      <c r="X23" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="106"/>
-      <c r="Z23" s="103" t="s">
+      <c r="Y23" s="143"/>
+      <c r="Z23" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="AA23" s="118" t="s">
+      <c r="AA23" s="148" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="104"/>
-      <c r="C24" s="104"/>
+      <c r="B24" s="147"/>
+      <c r="C24" s="147"/>
       <c r="D24" s="39" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="104"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="140"/>
-      <c r="I24" s="140"/>
-      <c r="J24" s="140"/>
-      <c r="K24" s="140"/>
-      <c r="L24" s="140"/>
-      <c r="M24" s="140"/>
-      <c r="N24" s="141"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="104"/>
+      <c r="F24" s="147"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="201"/>
+      <c r="I24" s="201"/>
+      <c r="J24" s="201"/>
+      <c r="K24" s="201"/>
+      <c r="L24" s="201"/>
+      <c r="M24" s="201"/>
+      <c r="N24" s="202"/>
+      <c r="O24" s="147"/>
+      <c r="P24" s="147"/>
       <c r="Q24" s="39" t="s">
         <v>13</v>
       </c>
@@ -7298,15 +7302,15 @@
       <c r="V24" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="117"/>
+      <c r="W24" s="145"/>
       <c r="X24" s="39" t="s">
         <v>11</v>
       </c>
       <c r="Y24" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="Z24" s="104"/>
-      <c r="AA24" s="118"/>
+      <c r="Z24" s="147"/>
+      <c r="AA24" s="148"/>
     </row>
     <row r="25" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -7317,14 +7321,14 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="145"/>
-      <c r="H25" s="146"/>
-      <c r="I25" s="146"/>
-      <c r="J25" s="146"/>
-      <c r="K25" s="146"/>
-      <c r="L25" s="146"/>
-      <c r="M25" s="146"/>
-      <c r="N25" s="147"/>
+      <c r="G25" s="193"/>
+      <c r="H25" s="194"/>
+      <c r="I25" s="194"/>
+      <c r="J25" s="194"/>
+      <c r="K25" s="194"/>
+      <c r="L25" s="194"/>
+      <c r="M25" s="194"/>
+      <c r="N25" s="195"/>
       <c r="O25" s="31"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
@@ -7349,14 +7353,14 @@
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
-      <c r="G26" s="129"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="130"/>
-      <c r="K26" s="130"/>
-      <c r="L26" s="130"/>
-      <c r="M26" s="130"/>
-      <c r="N26" s="131"/>
+      <c r="G26" s="190"/>
+      <c r="H26" s="191"/>
+      <c r="I26" s="191"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="191"/>
+      <c r="L26" s="191"/>
+      <c r="M26" s="191"/>
+      <c r="N26" s="192"/>
       <c r="O26" s="20"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="43"/>
@@ -7381,14 +7385,14 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="130"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="130"/>
-      <c r="L27" s="130"/>
-      <c r="M27" s="130"/>
-      <c r="N27" s="131"/>
+      <c r="G27" s="190"/>
+      <c r="H27" s="191"/>
+      <c r="I27" s="191"/>
+      <c r="J27" s="191"/>
+      <c r="K27" s="191"/>
+      <c r="L27" s="191"/>
+      <c r="M27" s="191"/>
+      <c r="N27" s="192"/>
       <c r="O27" s="20"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
@@ -7413,14 +7417,14 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="129"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
-      <c r="L28" s="130"/>
-      <c r="M28" s="130"/>
-      <c r="N28" s="131"/>
+      <c r="G28" s="190"/>
+      <c r="H28" s="191"/>
+      <c r="I28" s="191"/>
+      <c r="J28" s="191"/>
+      <c r="K28" s="191"/>
+      <c r="L28" s="191"/>
+      <c r="M28" s="191"/>
+      <c r="N28" s="192"/>
       <c r="O28" s="20"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
@@ -7445,14 +7449,14 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="129"/>
-      <c r="H29" s="130"/>
-      <c r="I29" s="130"/>
-      <c r="J29" s="130"/>
-      <c r="K29" s="130"/>
-      <c r="L29" s="130"/>
-      <c r="M29" s="130"/>
-      <c r="N29" s="131"/>
+      <c r="G29" s="190"/>
+      <c r="H29" s="191"/>
+      <c r="I29" s="191"/>
+      <c r="J29" s="191"/>
+      <c r="K29" s="191"/>
+      <c r="L29" s="191"/>
+      <c r="M29" s="191"/>
+      <c r="N29" s="192"/>
       <c r="O29" s="20"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
@@ -7477,14 +7481,14 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
-      <c r="L30" s="130"/>
-      <c r="M30" s="130"/>
-      <c r="N30" s="131"/>
+      <c r="G30" s="190"/>
+      <c r="H30" s="191"/>
+      <c r="I30" s="191"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="191"/>
+      <c r="L30" s="191"/>
+      <c r="M30" s="191"/>
+      <c r="N30" s="192"/>
       <c r="O30" s="20"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
@@ -7509,14 +7513,14 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="129"/>
-      <c r="H31" s="130"/>
-      <c r="I31" s="130"/>
-      <c r="J31" s="130"/>
-      <c r="K31" s="130"/>
-      <c r="L31" s="130"/>
-      <c r="M31" s="130"/>
-      <c r="N31" s="131"/>
+      <c r="G31" s="190"/>
+      <c r="H31" s="191"/>
+      <c r="I31" s="191"/>
+      <c r="J31" s="191"/>
+      <c r="K31" s="191"/>
+      <c r="L31" s="191"/>
+      <c r="M31" s="191"/>
+      <c r="N31" s="192"/>
       <c r="O31" s="20"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
@@ -7541,14 +7545,14 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="129"/>
-      <c r="H32" s="130"/>
-      <c r="I32" s="130"/>
-      <c r="J32" s="130"/>
-      <c r="K32" s="130"/>
-      <c r="L32" s="130"/>
-      <c r="M32" s="130"/>
-      <c r="N32" s="131"/>
+      <c r="G32" s="190"/>
+      <c r="H32" s="191"/>
+      <c r="I32" s="191"/>
+      <c r="J32" s="191"/>
+      <c r="K32" s="191"/>
+      <c r="L32" s="191"/>
+      <c r="M32" s="191"/>
+      <c r="N32" s="192"/>
       <c r="O32" s="20"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
@@ -7573,14 +7577,14 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
-      <c r="G33" s="129"/>
-      <c r="H33" s="130"/>
-      <c r="I33" s="130"/>
-      <c r="J33" s="130"/>
-      <c r="K33" s="130"/>
-      <c r="L33" s="130"/>
-      <c r="M33" s="130"/>
-      <c r="N33" s="131"/>
+      <c r="G33" s="190"/>
+      <c r="H33" s="191"/>
+      <c r="I33" s="191"/>
+      <c r="J33" s="191"/>
+      <c r="K33" s="191"/>
+      <c r="L33" s="191"/>
+      <c r="M33" s="191"/>
+      <c r="N33" s="192"/>
       <c r="O33" s="20"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
@@ -7605,14 +7609,14 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="129"/>
-      <c r="H34" s="130"/>
-      <c r="I34" s="130"/>
-      <c r="J34" s="130"/>
-      <c r="K34" s="130"/>
-      <c r="L34" s="130"/>
-      <c r="M34" s="130"/>
-      <c r="N34" s="131"/>
+      <c r="G34" s="190"/>
+      <c r="H34" s="191"/>
+      <c r="I34" s="191"/>
+      <c r="J34" s="191"/>
+      <c r="K34" s="191"/>
+      <c r="L34" s="191"/>
+      <c r="M34" s="191"/>
+      <c r="N34" s="192"/>
       <c r="O34" s="20"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
@@ -7637,14 +7641,14 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
-      <c r="G35" s="129"/>
-      <c r="H35" s="130"/>
-      <c r="I35" s="130"/>
-      <c r="J35" s="130"/>
-      <c r="K35" s="130"/>
-      <c r="L35" s="130"/>
-      <c r="M35" s="130"/>
-      <c r="N35" s="131"/>
+      <c r="G35" s="190"/>
+      <c r="H35" s="191"/>
+      <c r="I35" s="191"/>
+      <c r="J35" s="191"/>
+      <c r="K35" s="191"/>
+      <c r="L35" s="191"/>
+      <c r="M35" s="191"/>
+      <c r="N35" s="192"/>
       <c r="O35" s="20"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
@@ -7669,14 +7673,14 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="129"/>
-      <c r="H36" s="130"/>
-      <c r="I36" s="130"/>
-      <c r="J36" s="130"/>
-      <c r="K36" s="130"/>
-      <c r="L36" s="130"/>
-      <c r="M36" s="130"/>
-      <c r="N36" s="131"/>
+      <c r="G36" s="190"/>
+      <c r="H36" s="191"/>
+      <c r="I36" s="191"/>
+      <c r="J36" s="191"/>
+      <c r="K36" s="191"/>
+      <c r="L36" s="191"/>
+      <c r="M36" s="191"/>
+      <c r="N36" s="192"/>
       <c r="O36" s="20"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
@@ -7701,14 +7705,14 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="129"/>
-      <c r="H37" s="130"/>
-      <c r="I37" s="130"/>
-      <c r="J37" s="130"/>
-      <c r="K37" s="130"/>
-      <c r="L37" s="130"/>
-      <c r="M37" s="130"/>
-      <c r="N37" s="131"/>
+      <c r="G37" s="190"/>
+      <c r="H37" s="191"/>
+      <c r="I37" s="191"/>
+      <c r="J37" s="191"/>
+      <c r="K37" s="191"/>
+      <c r="L37" s="191"/>
+      <c r="M37" s="191"/>
+      <c r="N37" s="192"/>
       <c r="O37" s="20"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
@@ -7733,14 +7737,14 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="129"/>
-      <c r="H38" s="130"/>
-      <c r="I38" s="130"/>
-      <c r="J38" s="130"/>
-      <c r="K38" s="130"/>
-      <c r="L38" s="130"/>
-      <c r="M38" s="130"/>
-      <c r="N38" s="131"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="191"/>
+      <c r="I38" s="191"/>
+      <c r="J38" s="191"/>
+      <c r="K38" s="191"/>
+      <c r="L38" s="191"/>
+      <c r="M38" s="191"/>
+      <c r="N38" s="192"/>
       <c r="O38" s="20"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
@@ -7765,14 +7769,14 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="129"/>
-      <c r="H39" s="130"/>
-      <c r="I39" s="130"/>
-      <c r="J39" s="130"/>
-      <c r="K39" s="130"/>
-      <c r="L39" s="130"/>
-      <c r="M39" s="130"/>
-      <c r="N39" s="131"/>
+      <c r="G39" s="190"/>
+      <c r="H39" s="191"/>
+      <c r="I39" s="191"/>
+      <c r="J39" s="191"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="191"/>
+      <c r="N39" s="192"/>
       <c r="O39" s="20"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
@@ -7797,14 +7801,14 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="129"/>
-      <c r="H40" s="130"/>
-      <c r="I40" s="130"/>
-      <c r="J40" s="130"/>
-      <c r="K40" s="130"/>
-      <c r="L40" s="130"/>
-      <c r="M40" s="130"/>
-      <c r="N40" s="131"/>
+      <c r="G40" s="190"/>
+      <c r="H40" s="191"/>
+      <c r="I40" s="191"/>
+      <c r="J40" s="191"/>
+      <c r="K40" s="191"/>
+      <c r="L40" s="191"/>
+      <c r="M40" s="191"/>
+      <c r="N40" s="192"/>
       <c r="O40" s="20"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
@@ -7829,14 +7833,14 @@
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
-      <c r="G41" s="129"/>
-      <c r="H41" s="130"/>
-      <c r="I41" s="130"/>
-      <c r="J41" s="130"/>
-      <c r="K41" s="130"/>
-      <c r="L41" s="130"/>
-      <c r="M41" s="130"/>
-      <c r="N41" s="131"/>
+      <c r="G41" s="190"/>
+      <c r="H41" s="191"/>
+      <c r="I41" s="191"/>
+      <c r="J41" s="191"/>
+      <c r="K41" s="191"/>
+      <c r="L41" s="191"/>
+      <c r="M41" s="191"/>
+      <c r="N41" s="192"/>
       <c r="O41" s="20"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
@@ -7861,14 +7865,14 @@
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="129"/>
-      <c r="H42" s="130"/>
-      <c r="I42" s="130"/>
-      <c r="J42" s="130"/>
-      <c r="K42" s="130"/>
-      <c r="L42" s="130"/>
-      <c r="M42" s="130"/>
-      <c r="N42" s="131"/>
+      <c r="G42" s="190"/>
+      <c r="H42" s="191"/>
+      <c r="I42" s="191"/>
+      <c r="J42" s="191"/>
+      <c r="K42" s="191"/>
+      <c r="L42" s="191"/>
+      <c r="M42" s="191"/>
+      <c r="N42" s="192"/>
       <c r="O42" s="20"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
@@ -7893,14 +7897,14 @@
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="129"/>
-      <c r="H43" s="130"/>
-      <c r="I43" s="130"/>
-      <c r="J43" s="130"/>
-      <c r="K43" s="130"/>
-      <c r="L43" s="130"/>
-      <c r="M43" s="130"/>
-      <c r="N43" s="131"/>
+      <c r="G43" s="190"/>
+      <c r="H43" s="191"/>
+      <c r="I43" s="191"/>
+      <c r="J43" s="191"/>
+      <c r="K43" s="191"/>
+      <c r="L43" s="191"/>
+      <c r="M43" s="191"/>
+      <c r="N43" s="192"/>
       <c r="O43" s="20"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
@@ -7925,14 +7929,14 @@
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="129"/>
-      <c r="H44" s="130"/>
-      <c r="I44" s="130"/>
-      <c r="J44" s="130"/>
-      <c r="K44" s="130"/>
-      <c r="L44" s="130"/>
-      <c r="M44" s="130"/>
-      <c r="N44" s="131"/>
+      <c r="G44" s="190"/>
+      <c r="H44" s="191"/>
+      <c r="I44" s="191"/>
+      <c r="J44" s="191"/>
+      <c r="K44" s="191"/>
+      <c r="L44" s="191"/>
+      <c r="M44" s="191"/>
+      <c r="N44" s="192"/>
       <c r="O44" s="20"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
@@ -7957,14 +7961,14 @@
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="129"/>
-      <c r="H45" s="130"/>
-      <c r="I45" s="130"/>
-      <c r="J45" s="130"/>
-      <c r="K45" s="130"/>
-      <c r="L45" s="130"/>
-      <c r="M45" s="130"/>
-      <c r="N45" s="131"/>
+      <c r="G45" s="190"/>
+      <c r="H45" s="191"/>
+      <c r="I45" s="191"/>
+      <c r="J45" s="191"/>
+      <c r="K45" s="191"/>
+      <c r="L45" s="191"/>
+      <c r="M45" s="191"/>
+      <c r="N45" s="192"/>
       <c r="O45" s="20"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
@@ -7989,14 +7993,14 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
-      <c r="G46" s="129"/>
-      <c r="H46" s="130"/>
-      <c r="I46" s="130"/>
-      <c r="J46" s="130"/>
-      <c r="K46" s="130"/>
-      <c r="L46" s="130"/>
-      <c r="M46" s="130"/>
-      <c r="N46" s="131"/>
+      <c r="G46" s="190"/>
+      <c r="H46" s="191"/>
+      <c r="I46" s="191"/>
+      <c r="J46" s="191"/>
+      <c r="K46" s="191"/>
+      <c r="L46" s="191"/>
+      <c r="M46" s="191"/>
+      <c r="N46" s="192"/>
       <c r="O46" s="20"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
@@ -8021,14 +8025,14 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
-      <c r="G47" s="129"/>
-      <c r="H47" s="130"/>
-      <c r="I47" s="130"/>
-      <c r="J47" s="130"/>
-      <c r="K47" s="130"/>
-      <c r="L47" s="130"/>
-      <c r="M47" s="130"/>
-      <c r="N47" s="131"/>
+      <c r="G47" s="190"/>
+      <c r="H47" s="191"/>
+      <c r="I47" s="191"/>
+      <c r="J47" s="191"/>
+      <c r="K47" s="191"/>
+      <c r="L47" s="191"/>
+      <c r="M47" s="191"/>
+      <c r="N47" s="192"/>
       <c r="O47" s="20"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
@@ -8053,14 +8057,14 @@
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="129"/>
-      <c r="H48" s="130"/>
-      <c r="I48" s="130"/>
-      <c r="J48" s="130"/>
-      <c r="K48" s="130"/>
-      <c r="L48" s="130"/>
-      <c r="M48" s="130"/>
-      <c r="N48" s="131"/>
+      <c r="G48" s="190"/>
+      <c r="H48" s="191"/>
+      <c r="I48" s="191"/>
+      <c r="J48" s="191"/>
+      <c r="K48" s="191"/>
+      <c r="L48" s="191"/>
+      <c r="M48" s="191"/>
+      <c r="N48" s="192"/>
       <c r="O48" s="20"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
@@ -8085,14 +8089,14 @@
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="129"/>
-      <c r="H49" s="130"/>
-      <c r="I49" s="130"/>
-      <c r="J49" s="130"/>
-      <c r="K49" s="130"/>
-      <c r="L49" s="130"/>
-      <c r="M49" s="130"/>
-      <c r="N49" s="131"/>
+      <c r="G49" s="190"/>
+      <c r="H49" s="191"/>
+      <c r="I49" s="191"/>
+      <c r="J49" s="191"/>
+      <c r="K49" s="191"/>
+      <c r="L49" s="191"/>
+      <c r="M49" s="191"/>
+      <c r="N49" s="192"/>
       <c r="O49" s="20"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
@@ -8117,14 +8121,14 @@
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="129"/>
-      <c r="H50" s="130"/>
-      <c r="I50" s="130"/>
-      <c r="J50" s="130"/>
-      <c r="K50" s="130"/>
-      <c r="L50" s="130"/>
-      <c r="M50" s="130"/>
-      <c r="N50" s="131"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="191"/>
+      <c r="I50" s="191"/>
+      <c r="J50" s="191"/>
+      <c r="K50" s="191"/>
+      <c r="L50" s="191"/>
+      <c r="M50" s="191"/>
+      <c r="N50" s="192"/>
       <c r="O50" s="20"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
@@ -8149,14 +8153,14 @@
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="129"/>
-      <c r="H51" s="130"/>
-      <c r="I51" s="130"/>
-      <c r="J51" s="130"/>
-      <c r="K51" s="130"/>
-      <c r="L51" s="130"/>
-      <c r="M51" s="130"/>
-      <c r="N51" s="131"/>
+      <c r="G51" s="190"/>
+      <c r="H51" s="191"/>
+      <c r="I51" s="191"/>
+      <c r="J51" s="191"/>
+      <c r="K51" s="191"/>
+      <c r="L51" s="191"/>
+      <c r="M51" s="191"/>
+      <c r="N51" s="192"/>
       <c r="O51" s="20"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
@@ -8181,14 +8185,14 @@
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="129"/>
-      <c r="H52" s="130"/>
-      <c r="I52" s="130"/>
-      <c r="J52" s="130"/>
-      <c r="K52" s="130"/>
-      <c r="L52" s="130"/>
-      <c r="M52" s="130"/>
-      <c r="N52" s="131"/>
+      <c r="G52" s="190"/>
+      <c r="H52" s="191"/>
+      <c r="I52" s="191"/>
+      <c r="J52" s="191"/>
+      <c r="K52" s="191"/>
+      <c r="L52" s="191"/>
+      <c r="M52" s="191"/>
+      <c r="N52" s="192"/>
       <c r="O52" s="20"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
@@ -8213,14 +8217,14 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
-      <c r="G53" s="129"/>
-      <c r="H53" s="130"/>
-      <c r="I53" s="130"/>
-      <c r="J53" s="130"/>
-      <c r="K53" s="130"/>
-      <c r="L53" s="130"/>
-      <c r="M53" s="130"/>
-      <c r="N53" s="131"/>
+      <c r="G53" s="190"/>
+      <c r="H53" s="191"/>
+      <c r="I53" s="191"/>
+      <c r="J53" s="191"/>
+      <c r="K53" s="191"/>
+      <c r="L53" s="191"/>
+      <c r="M53" s="191"/>
+      <c r="N53" s="192"/>
       <c r="O53" s="20"/>
       <c r="P53" s="9"/>
       <c r="Q53" s="9"/>
@@ -8245,14 +8249,14 @@
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
-      <c r="G54" s="142"/>
-      <c r="H54" s="143"/>
-      <c r="I54" s="143"/>
-      <c r="J54" s="143"/>
-      <c r="K54" s="143"/>
-      <c r="L54" s="143"/>
-      <c r="M54" s="143"/>
-      <c r="N54" s="144"/>
+      <c r="G54" s="203"/>
+      <c r="H54" s="204"/>
+      <c r="I54" s="204"/>
+      <c r="J54" s="204"/>
+      <c r="K54" s="204"/>
+      <c r="L54" s="204"/>
+      <c r="M54" s="204"/>
+      <c r="N54" s="205"/>
       <c r="O54" s="20"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
@@ -8268,155 +8272,251 @@
       <c r="AA54" s="9"/>
     </row>
     <row r="55" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="107" t="s">
+      <c r="B55" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="108"/>
-      <c r="D55" s="108"/>
-      <c r="E55" s="108"/>
-      <c r="F55" s="108"/>
-      <c r="G55" s="109"/>
-      <c r="H55" s="135" t="s">
+      <c r="C55" s="135"/>
+      <c r="D55" s="135"/>
+      <c r="E55" s="135"/>
+      <c r="F55" s="135"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="196" t="s">
         <v>58</v>
       </c>
-      <c r="I55" s="135"/>
-      <c r="J55" s="135"/>
-      <c r="K55" s="135"/>
-      <c r="L55" s="135"/>
-      <c r="M55" s="135"/>
-      <c r="N55" s="135"/>
-      <c r="O55" s="107" t="s">
+      <c r="I55" s="196"/>
+      <c r="J55" s="196"/>
+      <c r="K55" s="196"/>
+      <c r="L55" s="196"/>
+      <c r="M55" s="196"/>
+      <c r="N55" s="196"/>
+      <c r="O55" s="134" t="s">
         <v>57</v>
       </c>
-      <c r="P55" s="108"/>
-      <c r="Q55" s="108"/>
-      <c r="R55" s="108"/>
-      <c r="S55" s="108"/>
-      <c r="T55" s="108"/>
-      <c r="U55" s="109"/>
-      <c r="V55" s="107" t="s">
+      <c r="P55" s="135"/>
+      <c r="Q55" s="135"/>
+      <c r="R55" s="135"/>
+      <c r="S55" s="135"/>
+      <c r="T55" s="135"/>
+      <c r="U55" s="136"/>
+      <c r="V55" s="134" t="s">
         <v>60</v>
       </c>
-      <c r="W55" s="108"/>
-      <c r="X55" s="108"/>
-      <c r="Y55" s="108"/>
-      <c r="Z55" s="108"/>
-      <c r="AA55" s="109"/>
+      <c r="W55" s="135"/>
+      <c r="X55" s="135"/>
+      <c r="Y55" s="135"/>
+      <c r="Z55" s="135"/>
+      <c r="AA55" s="136"/>
     </row>
     <row r="56" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="114"/>
-      <c r="C56" s="114"/>
-      <c r="D56" s="114"/>
-      <c r="E56" s="114"/>
-      <c r="F56" s="114"/>
-      <c r="G56" s="132"/>
-      <c r="H56" s="110"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="111"/>
-      <c r="K56" s="111"/>
-      <c r="L56" s="111"/>
-      <c r="M56" s="111"/>
-      <c r="N56" s="112"/>
-      <c r="O56" s="110"/>
-      <c r="P56" s="111"/>
-      <c r="Q56" s="111"/>
-      <c r="R56" s="111"/>
-      <c r="S56" s="111"/>
-      <c r="T56" s="111"/>
-      <c r="U56" s="112"/>
-      <c r="V56" s="113"/>
-      <c r="W56" s="114"/>
-      <c r="X56" s="114"/>
-      <c r="Y56" s="114"/>
-      <c r="Z56" s="114"/>
-      <c r="AA56" s="114"/>
+      <c r="B56" s="141"/>
+      <c r="C56" s="141"/>
+      <c r="D56" s="141"/>
+      <c r="E56" s="141"/>
+      <c r="F56" s="141"/>
+      <c r="G56" s="206"/>
+      <c r="H56" s="137"/>
+      <c r="I56" s="138"/>
+      <c r="J56" s="138"/>
+      <c r="K56" s="138"/>
+      <c r="L56" s="138"/>
+      <c r="M56" s="138"/>
+      <c r="N56" s="139"/>
+      <c r="O56" s="137"/>
+      <c r="P56" s="138"/>
+      <c r="Q56" s="138"/>
+      <c r="R56" s="138"/>
+      <c r="S56" s="138"/>
+      <c r="T56" s="138"/>
+      <c r="U56" s="139"/>
+      <c r="V56" s="140"/>
+      <c r="W56" s="141"/>
+      <c r="X56" s="141"/>
+      <c r="Y56" s="141"/>
+      <c r="Z56" s="141"/>
+      <c r="AA56" s="141"/>
     </row>
     <row r="57" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="128"/>
-      <c r="C57" s="128"/>
-      <c r="D57" s="128"/>
-      <c r="E57" s="128"/>
-      <c r="F57" s="128"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="124"/>
-      <c r="I57" s="125"/>
-      <c r="J57" s="125"/>
-      <c r="K57" s="125"/>
-      <c r="L57" s="125"/>
-      <c r="M57" s="125"/>
-      <c r="N57" s="126"/>
-      <c r="O57" s="124"/>
-      <c r="P57" s="125"/>
-      <c r="Q57" s="125"/>
-      <c r="R57" s="125"/>
-      <c r="S57" s="125"/>
-      <c r="T57" s="125"/>
-      <c r="U57" s="126"/>
-      <c r="V57" s="127"/>
-      <c r="W57" s="128"/>
-      <c r="X57" s="128"/>
-      <c r="Y57" s="128"/>
-      <c r="Z57" s="128"/>
-      <c r="AA57" s="128"/>
+      <c r="B57" s="133"/>
+      <c r="C57" s="133"/>
+      <c r="D57" s="133"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="133"/>
+      <c r="G57" s="207"/>
+      <c r="H57" s="129"/>
+      <c r="I57" s="130"/>
+      <c r="J57" s="130"/>
+      <c r="K57" s="130"/>
+      <c r="L57" s="130"/>
+      <c r="M57" s="130"/>
+      <c r="N57" s="131"/>
+      <c r="O57" s="129"/>
+      <c r="P57" s="130"/>
+      <c r="Q57" s="130"/>
+      <c r="R57" s="130"/>
+      <c r="S57" s="130"/>
+      <c r="T57" s="130"/>
+      <c r="U57" s="131"/>
+      <c r="V57" s="132"/>
+      <c r="W57" s="133"/>
+      <c r="X57" s="133"/>
+      <c r="Y57" s="133"/>
+      <c r="Z57" s="133"/>
+      <c r="AA57" s="133"/>
     </row>
     <row r="58" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="128"/>
-      <c r="C58" s="128"/>
-      <c r="D58" s="128"/>
-      <c r="E58" s="128"/>
-      <c r="F58" s="128"/>
-      <c r="G58" s="133"/>
-      <c r="H58" s="124"/>
-      <c r="I58" s="125"/>
-      <c r="J58" s="125"/>
-      <c r="K58" s="125"/>
-      <c r="L58" s="125"/>
-      <c r="M58" s="125"/>
-      <c r="N58" s="126"/>
-      <c r="O58" s="124"/>
-      <c r="P58" s="125"/>
-      <c r="Q58" s="125"/>
-      <c r="R58" s="125"/>
-      <c r="S58" s="125"/>
-      <c r="T58" s="125"/>
-      <c r="U58" s="126"/>
-      <c r="V58" s="127"/>
-      <c r="W58" s="128"/>
-      <c r="X58" s="128"/>
-      <c r="Y58" s="128"/>
-      <c r="Z58" s="128"/>
-      <c r="AA58" s="128"/>
+      <c r="B58" s="133"/>
+      <c r="C58" s="133"/>
+      <c r="D58" s="133"/>
+      <c r="E58" s="133"/>
+      <c r="F58" s="133"/>
+      <c r="G58" s="207"/>
+      <c r="H58" s="129"/>
+      <c r="I58" s="130"/>
+      <c r="J58" s="130"/>
+      <c r="K58" s="130"/>
+      <c r="L58" s="130"/>
+      <c r="M58" s="130"/>
+      <c r="N58" s="131"/>
+      <c r="O58" s="129"/>
+      <c r="P58" s="130"/>
+      <c r="Q58" s="130"/>
+      <c r="R58" s="130"/>
+      <c r="S58" s="130"/>
+      <c r="T58" s="130"/>
+      <c r="U58" s="131"/>
+      <c r="V58" s="132"/>
+      <c r="W58" s="133"/>
+      <c r="X58" s="133"/>
+      <c r="Y58" s="133"/>
+      <c r="Z58" s="133"/>
+      <c r="AA58" s="133"/>
     </row>
     <row r="59" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="123"/>
-      <c r="C59" s="123"/>
-      <c r="D59" s="123"/>
-      <c r="E59" s="123"/>
-      <c r="F59" s="123"/>
-      <c r="G59" s="134"/>
-      <c r="H59" s="119"/>
-      <c r="I59" s="120"/>
-      <c r="J59" s="120"/>
-      <c r="K59" s="120"/>
-      <c r="L59" s="120"/>
-      <c r="M59" s="120"/>
-      <c r="N59" s="121"/>
-      <c r="O59" s="119"/>
-      <c r="P59" s="120"/>
-      <c r="Q59" s="120"/>
-      <c r="R59" s="120"/>
-      <c r="S59" s="120"/>
-      <c r="T59" s="120"/>
-      <c r="U59" s="121"/>
-      <c r="V59" s="122"/>
-      <c r="W59" s="123"/>
-      <c r="X59" s="123"/>
-      <c r="Y59" s="123"/>
-      <c r="Z59" s="123"/>
-      <c r="AA59" s="123"/>
+      <c r="B59" s="128"/>
+      <c r="C59" s="128"/>
+      <c r="D59" s="128"/>
+      <c r="E59" s="128"/>
+      <c r="F59" s="128"/>
+      <c r="G59" s="208"/>
+      <c r="H59" s="124"/>
+      <c r="I59" s="125"/>
+      <c r="J59" s="125"/>
+      <c r="K59" s="125"/>
+      <c r="L59" s="125"/>
+      <c r="M59" s="125"/>
+      <c r="N59" s="126"/>
+      <c r="O59" s="124"/>
+      <c r="P59" s="125"/>
+      <c r="Q59" s="125"/>
+      <c r="R59" s="125"/>
+      <c r="S59" s="125"/>
+      <c r="T59" s="125"/>
+      <c r="U59" s="126"/>
+      <c r="V59" s="127"/>
+      <c r="W59" s="128"/>
+      <c r="X59" s="128"/>
+      <c r="Y59" s="128"/>
+      <c r="Z59" s="128"/>
+      <c r="AA59" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="120">
+    <mergeCell ref="G39:N39"/>
+    <mergeCell ref="G40:N40"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="V56:AA56"/>
+    <mergeCell ref="V57:AA57"/>
+    <mergeCell ref="V58:AA58"/>
+    <mergeCell ref="V59:AA59"/>
+    <mergeCell ref="G41:N41"/>
+    <mergeCell ref="G42:N42"/>
+    <mergeCell ref="G43:N43"/>
+    <mergeCell ref="G44:N44"/>
+    <mergeCell ref="G45:N45"/>
+    <mergeCell ref="G46:N46"/>
+    <mergeCell ref="G47:N47"/>
+    <mergeCell ref="G48:N48"/>
+    <mergeCell ref="G49:N49"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="H58:N58"/>
+    <mergeCell ref="H59:N59"/>
+    <mergeCell ref="H56:N56"/>
+    <mergeCell ref="H57:N57"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="H55:N55"/>
+    <mergeCell ref="G23:N24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="V55:AA55"/>
+    <mergeCell ref="O56:U56"/>
+    <mergeCell ref="G29:N29"/>
+    <mergeCell ref="G30:N30"/>
+    <mergeCell ref="G31:N31"/>
+    <mergeCell ref="G50:N50"/>
+    <mergeCell ref="G51:N51"/>
+    <mergeCell ref="G52:N52"/>
+    <mergeCell ref="G53:N53"/>
+    <mergeCell ref="G54:N54"/>
+    <mergeCell ref="G32:N32"/>
+    <mergeCell ref="G33:N33"/>
+    <mergeCell ref="G34:N34"/>
+    <mergeCell ref="G35:N35"/>
+    <mergeCell ref="G36:N36"/>
+    <mergeCell ref="G37:N37"/>
+    <mergeCell ref="G38:N38"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="G25:N25"/>
+    <mergeCell ref="G26:N26"/>
+    <mergeCell ref="G27:N27"/>
+    <mergeCell ref="O2:AA3"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="V4:AA4"/>
+    <mergeCell ref="O8:AA8"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="Y15:AA15"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="T10:X10"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="O11:S11"/>
+    <mergeCell ref="T11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="O12:AA12"/>
+    <mergeCell ref="O13:AA13"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:X14"/>
+    <mergeCell ref="Y14:AA14"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:X16"/>
+    <mergeCell ref="Y16:AA16"/>
+    <mergeCell ref="O17:AA17"/>
+    <mergeCell ref="O18:AA18"/>
+    <mergeCell ref="O19:S19"/>
+    <mergeCell ref="T19:X19"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="O22:AA22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="Z23:Z24"/>
+    <mergeCell ref="O58:U58"/>
+    <mergeCell ref="O59:U59"/>
+    <mergeCell ref="O57:U57"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="AA23:AA24"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="B9:G9"/>
@@ -8441,102 +8541,6 @@
     <mergeCell ref="H15:K15"/>
     <mergeCell ref="L15:N15"/>
     <mergeCell ref="G28:N28"/>
-    <mergeCell ref="O22:AA22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:W24"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="Z23:Z24"/>
-    <mergeCell ref="O58:U58"/>
-    <mergeCell ref="O59:U59"/>
-    <mergeCell ref="O57:U57"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="AA23:AA24"/>
-    <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="T21:X21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:X16"/>
-    <mergeCell ref="Y16:AA16"/>
-    <mergeCell ref="O17:AA17"/>
-    <mergeCell ref="O18:AA18"/>
-    <mergeCell ref="O19:S19"/>
-    <mergeCell ref="T19:X19"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="G25:N25"/>
-    <mergeCell ref="G26:N26"/>
-    <mergeCell ref="G27:N27"/>
-    <mergeCell ref="O2:AA3"/>
-    <mergeCell ref="O4:U4"/>
-    <mergeCell ref="V4:AA4"/>
-    <mergeCell ref="O8:AA8"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="Y15:AA15"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="T10:X10"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="O11:S11"/>
-    <mergeCell ref="T11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="O12:AA12"/>
-    <mergeCell ref="O13:AA13"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:X14"/>
-    <mergeCell ref="H57:N57"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="H55:N55"/>
-    <mergeCell ref="G23:N24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="V55:AA55"/>
-    <mergeCell ref="O56:U56"/>
-    <mergeCell ref="G29:N29"/>
-    <mergeCell ref="G30:N30"/>
-    <mergeCell ref="G31:N31"/>
-    <mergeCell ref="G50:N50"/>
-    <mergeCell ref="G51:N51"/>
-    <mergeCell ref="G52:N52"/>
-    <mergeCell ref="G53:N53"/>
-    <mergeCell ref="G54:N54"/>
-    <mergeCell ref="G32:N32"/>
-    <mergeCell ref="G33:N33"/>
-    <mergeCell ref="G34:N34"/>
-    <mergeCell ref="G35:N35"/>
-    <mergeCell ref="G36:N36"/>
-    <mergeCell ref="G37:N37"/>
-    <mergeCell ref="G38:N38"/>
-    <mergeCell ref="G39:N39"/>
-    <mergeCell ref="G40:N40"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="V56:AA56"/>
-    <mergeCell ref="V57:AA57"/>
-    <mergeCell ref="V58:AA58"/>
-    <mergeCell ref="V59:AA59"/>
-    <mergeCell ref="G41:N41"/>
-    <mergeCell ref="G42:N42"/>
-    <mergeCell ref="G43:N43"/>
-    <mergeCell ref="G44:N44"/>
-    <mergeCell ref="G45:N45"/>
-    <mergeCell ref="G46:N46"/>
-    <mergeCell ref="G47:N47"/>
-    <mergeCell ref="G48:N48"/>
-    <mergeCell ref="G49:N49"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="H58:N58"/>
-    <mergeCell ref="H59:N59"/>
-    <mergeCell ref="H56:N56"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -8575,24 +8579,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B2" s="165" t="s">
+      <c r="B2" s="212" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
-      <c r="L2" s="165"/>
-      <c r="M2" s="165"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="165"/>
-      <c r="Q2" s="165"/>
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="212"/>
+      <c r="O2" s="212"/>
+      <c r="P2" s="212"/>
+      <c r="Q2" s="212"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="67"/>
@@ -8631,24 +8635,24 @@
       <c r="Q4" s="67"/>
     </row>
     <row r="5" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="166" t="s">
+      <c r="B5" s="209" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="166"/>
-      <c r="I5" s="166"/>
-      <c r="J5" s="166"/>
-      <c r="K5" s="166"/>
-      <c r="L5" s="166"/>
-      <c r="M5" s="166"/>
-      <c r="N5" s="166"/>
-      <c r="O5" s="166"/>
-      <c r="P5" s="166"/>
-      <c r="Q5" s="166"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
+      <c r="M5" s="209"/>
+      <c r="N5" s="209"/>
+      <c r="O5" s="209"/>
+      <c r="P5" s="209"/>
+      <c r="Q5" s="209"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="67"/>
@@ -8799,24 +8803,24 @@
       <c r="Q12" s="67"/>
     </row>
     <row r="13" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="166" t="s">
+      <c r="B13" s="209" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="166"/>
-      <c r="L13" s="166"/>
-      <c r="M13" s="166"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="166"/>
-      <c r="Q13" s="166"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
+      <c r="F13" s="209"/>
+      <c r="G13" s="209"/>
+      <c r="H13" s="209"/>
+      <c r="I13" s="209"/>
+      <c r="J13" s="209"/>
+      <c r="K13" s="209"/>
+      <c r="L13" s="209"/>
+      <c r="M13" s="209"/>
+      <c r="N13" s="209"/>
+      <c r="O13" s="209"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="67"/>
@@ -8824,12 +8828,12 @@
         <v>81</v>
       </c>
       <c r="D14" s="67"/>
-      <c r="E14" s="167" t="s">
+      <c r="E14" s="210" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="167"/>
-      <c r="G14" s="167"/>
-      <c r="H14" s="167"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="210"/>
       <c r="I14" s="72"/>
       <c r="J14" s="67"/>
       <c r="K14" s="67"/>
@@ -8868,8 +8872,8 @@
         <v>91</v>
       </c>
       <c r="F16" s="75"/>
-      <c r="G16" s="168"/>
-      <c r="H16" s="168"/>
+      <c r="G16" s="211"/>
+      <c r="H16" s="211"/>
       <c r="I16" s="72"/>
       <c r="J16" s="67"/>
       <c r="K16" s="74"/>
@@ -8957,24 +8961,24 @@
       <c r="Q20" s="67"/>
     </row>
     <row r="21" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="166" t="s">
+      <c r="B21" s="209" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="166"/>
-      <c r="D21" s="166"/>
-      <c r="E21" s="166"/>
-      <c r="F21" s="166"/>
-      <c r="G21" s="166"/>
-      <c r="H21" s="166"/>
-      <c r="I21" s="166"/>
-      <c r="J21" s="166"/>
-      <c r="K21" s="166"/>
-      <c r="L21" s="166"/>
-      <c r="M21" s="166"/>
-      <c r="N21" s="166"/>
-      <c r="O21" s="166"/>
-      <c r="P21" s="166"/>
-      <c r="Q21" s="166"/>
+      <c r="C21" s="209"/>
+      <c r="D21" s="209"/>
+      <c r="E21" s="209"/>
+      <c r="F21" s="209"/>
+      <c r="G21" s="209"/>
+      <c r="H21" s="209"/>
+      <c r="I21" s="209"/>
+      <c r="J21" s="209"/>
+      <c r="K21" s="209"/>
+      <c r="L21" s="209"/>
+      <c r="M21" s="209"/>
+      <c r="N21" s="209"/>
+      <c r="O21" s="209"/>
+      <c r="P21" s="209"/>
+      <c r="Q21" s="209"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="67"/>
@@ -9069,24 +9073,24 @@
       <c r="Q25" s="67"/>
     </row>
     <row r="26" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="166" t="s">
+      <c r="B26" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="166"/>
-      <c r="D26" s="166"/>
-      <c r="E26" s="166"/>
-      <c r="F26" s="166"/>
-      <c r="G26" s="166"/>
-      <c r="H26" s="166"/>
-      <c r="I26" s="166"/>
-      <c r="J26" s="166"/>
-      <c r="K26" s="166"/>
-      <c r="L26" s="166"/>
-      <c r="M26" s="166"/>
-      <c r="N26" s="166"/>
-      <c r="O26" s="166"/>
-      <c r="P26" s="166"/>
-      <c r="Q26" s="166"/>
+      <c r="C26" s="209"/>
+      <c r="D26" s="209"/>
+      <c r="E26" s="209"/>
+      <c r="F26" s="209"/>
+      <c r="G26" s="209"/>
+      <c r="H26" s="209"/>
+      <c r="I26" s="209"/>
+      <c r="J26" s="209"/>
+      <c r="K26" s="209"/>
+      <c r="L26" s="209"/>
+      <c r="M26" s="209"/>
+      <c r="N26" s="209"/>
+      <c r="O26" s="209"/>
+      <c r="P26" s="209"/>
+      <c r="Q26" s="209"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="67"/>
@@ -9633,24 +9637,24 @@
       <c r="Q52" s="67"/>
     </row>
     <row r="53" spans="2:17" s="69" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="166" t="s">
+      <c r="B53" s="209" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="166"/>
-      <c r="D53" s="166"/>
-      <c r="E53" s="166"/>
-      <c r="F53" s="166"/>
-      <c r="G53" s="166"/>
-      <c r="H53" s="166"/>
-      <c r="I53" s="166"/>
-      <c r="J53" s="166"/>
-      <c r="K53" s="166"/>
-      <c r="L53" s="166"/>
-      <c r="M53" s="166"/>
-      <c r="N53" s="166"/>
-      <c r="O53" s="166"/>
-      <c r="P53" s="166"/>
-      <c r="Q53" s="166"/>
+      <c r="C53" s="209"/>
+      <c r="D53" s="209"/>
+      <c r="E53" s="209"/>
+      <c r="F53" s="209"/>
+      <c r="G53" s="209"/>
+      <c r="H53" s="209"/>
+      <c r="I53" s="209"/>
+      <c r="J53" s="209"/>
+      <c r="K53" s="209"/>
+      <c r="L53" s="209"/>
+      <c r="M53" s="209"/>
+      <c r="N53" s="209"/>
+      <c r="O53" s="209"/>
+      <c r="P53" s="209"/>
+      <c r="Q53" s="209"/>
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="67"/>
@@ -9964,7 +9968,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FBFCC4C-AA9B-410E-88E2-C384CCD47975}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A2:AY93"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="3.85546875" customWidth="1"/>
@@ -9975,2917 +9979,2942 @@
     <col min="51" max="51" width="2.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="169" t="s">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T2" s="227"/>
+      <c r="U2" s="227"/>
+      <c r="V2" s="227"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="227"/>
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="227"/>
+      <c r="AB2" s="227"/>
+      <c r="AC2" s="227"/>
+      <c r="AD2" s="227"/>
+      <c r="AE2" s="227"/>
+      <c r="AF2" s="227"/>
+      <c r="AG2" s="227"/>
+      <c r="AH2" s="227"/>
+      <c r="AI2" s="227"/>
+      <c r="AJ2" s="227"/>
+      <c r="AK2" s="227"/>
+      <c r="AL2" s="227"/>
+      <c r="AM2" s="227"/>
+    </row>
+    <row r="4" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="215" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
-      <c r="T1" s="169"/>
-      <c r="U1" s="169"/>
-      <c r="V1" s="169"/>
-      <c r="W1" s="169"/>
-      <c r="X1" s="169"/>
-      <c r="Y1" s="169"/>
-      <c r="Z1" s="169"/>
-      <c r="AA1" s="169"/>
-      <c r="AB1" s="169"/>
-      <c r="AC1" s="169"/>
-      <c r="AD1" s="169"/>
-      <c r="AE1" s="169"/>
-      <c r="AF1" s="169"/>
-      <c r="AG1" s="169"/>
-      <c r="AH1" s="169"/>
-      <c r="AI1" s="169"/>
-      <c r="AJ1" s="169"/>
-      <c r="AK1" s="169"/>
-      <c r="AL1" s="169"/>
-      <c r="AM1" s="169"/>
-      <c r="AN1" s="169"/>
-      <c r="AO1" s="169"/>
-      <c r="AP1" s="169"/>
-      <c r="AQ1" s="169"/>
-      <c r="AR1" s="169"/>
-      <c r="AS1" s="169"/>
-      <c r="AT1" s="169"/>
-      <c r="AU1" s="169"/>
-      <c r="AV1" s="169"/>
-      <c r="AW1" s="169"/>
-      <c r="AX1" s="169"/>
-    </row>
-    <row r="2" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169"/>
-      <c r="R2" s="169"/>
-      <c r="S2" s="169"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="169"/>
-      <c r="AA2" s="169"/>
-      <c r="AB2" s="169"/>
-      <c r="AC2" s="169"/>
-      <c r="AD2" s="169"/>
-      <c r="AE2" s="169"/>
-      <c r="AF2" s="169"/>
-      <c r="AG2" s="169"/>
-      <c r="AH2" s="169"/>
-      <c r="AI2" s="169"/>
-      <c r="AJ2" s="169"/>
-      <c r="AK2" s="169"/>
-      <c r="AL2" s="169"/>
-      <c r="AM2" s="169"/>
-      <c r="AN2" s="169"/>
-      <c r="AO2" s="169"/>
-      <c r="AP2" s="169"/>
-      <c r="AQ2" s="169"/>
-      <c r="AR2" s="169"/>
-      <c r="AS2" s="169"/>
-      <c r="AT2" s="169"/>
-      <c r="AU2" s="169"/>
-      <c r="AV2" s="169"/>
-      <c r="AW2" s="169"/>
-      <c r="AX2" s="169"/>
-    </row>
-    <row r="3" spans="1:51" ht="7.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F3">
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
+      <c r="L4" s="215"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="215"/>
+      <c r="T4" s="215"/>
+      <c r="U4" s="215"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="215"/>
+      <c r="Y4" s="215"/>
+      <c r="Z4" s="215"/>
+      <c r="AA4" s="215"/>
+      <c r="AB4" s="215"/>
+      <c r="AC4" s="215"/>
+      <c r="AD4" s="215"/>
+      <c r="AE4" s="215"/>
+      <c r="AF4" s="215"/>
+      <c r="AG4" s="215"/>
+      <c r="AH4" s="215"/>
+      <c r="AI4" s="215"/>
+      <c r="AJ4" s="215"/>
+      <c r="AK4" s="215"/>
+      <c r="AL4" s="215"/>
+      <c r="AM4" s="215"/>
+      <c r="AN4" s="215"/>
+      <c r="AO4" s="215"/>
+      <c r="AP4" s="215"/>
+      <c r="AQ4" s="215"/>
+      <c r="AR4" s="215"/>
+      <c r="AS4" s="215"/>
+      <c r="AT4" s="215"/>
+      <c r="AU4" s="215"/>
+      <c r="AV4" s="215"/>
+      <c r="AW4" s="215"/>
+      <c r="AX4" s="215"/>
+    </row>
+    <row r="5" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="215"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="215"/>
+      <c r="K5" s="215"/>
+      <c r="L5" s="215"/>
+      <c r="M5" s="215"/>
+      <c r="N5" s="215"/>
+      <c r="O5" s="215"/>
+      <c r="P5" s="215"/>
+      <c r="Q5" s="215"/>
+      <c r="R5" s="215"/>
+      <c r="S5" s="215"/>
+      <c r="T5" s="215"/>
+      <c r="U5" s="215"/>
+      <c r="V5" s="215"/>
+      <c r="W5" s="215"/>
+      <c r="X5" s="215"/>
+      <c r="Y5" s="215"/>
+      <c r="Z5" s="215"/>
+      <c r="AA5" s="215"/>
+      <c r="AB5" s="215"/>
+      <c r="AC5" s="215"/>
+      <c r="AD5" s="215"/>
+      <c r="AE5" s="215"/>
+      <c r="AF5" s="215"/>
+      <c r="AG5" s="215"/>
+      <c r="AH5" s="215"/>
+      <c r="AI5" s="215"/>
+      <c r="AJ5" s="215"/>
+      <c r="AK5" s="215"/>
+      <c r="AL5" s="215"/>
+      <c r="AM5" s="215"/>
+      <c r="AN5" s="215"/>
+      <c r="AO5" s="215"/>
+      <c r="AP5" s="215"/>
+      <c r="AQ5" s="215"/>
+      <c r="AR5" s="215"/>
+      <c r="AS5" s="215"/>
+      <c r="AT5" s="215"/>
+      <c r="AU5" s="215"/>
+      <c r="AV5" s="215"/>
+      <c r="AW5" s="215"/>
+      <c r="AX5" s="215"/>
+    </row>
+    <row r="6" spans="1:51" ht="7.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6">
         <v>11</v>
       </c>
-      <c r="H3">
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="J3">
-        <f>H3-1</f>
+      <c r="J6">
+        <f>H6-1</f>
         <v>9</v>
       </c>
-      <c r="L3">
-        <f>J3-1</f>
+      <c r="L6">
+        <f>J6-1</f>
         <v>8</v>
       </c>
-      <c r="N3">
-        <f>L3-1</f>
+      <c r="N6">
+        <f>L6-1</f>
         <v>7</v>
       </c>
-      <c r="P3">
-        <f>N3-1</f>
+      <c r="P6">
+        <f>N6-1</f>
         <v>6</v>
       </c>
-      <c r="R3">
-        <f>P3-1</f>
+      <c r="R6">
+        <f>P6-1</f>
         <v>5</v>
       </c>
-      <c r="T3">
-        <f>R3-1</f>
+      <c r="T6">
+        <f>R6-1</f>
         <v>4</v>
       </c>
-      <c r="V3">
-        <f>T3-1</f>
+      <c r="V6">
+        <f>T6-1</f>
         <v>3</v>
       </c>
-      <c r="X3">
-        <f>V3-1</f>
+      <c r="X6">
+        <f>V6-1</f>
         <v>2</v>
       </c>
-      <c r="Z3">
-        <f>X3-1</f>
+      <c r="Z6">
+        <f>X6-1</f>
         <v>1</v>
       </c>
-      <c r="AB3">
+      <c r="AB6">
         <v>0</v>
       </c>
-      <c r="AD3">
+      <c r="AD6">
         <v>1</v>
       </c>
-      <c r="AF3">
-        <f>AD3+1</f>
+      <c r="AF6">
+        <f>AD6+1</f>
         <v>2</v>
       </c>
-      <c r="AH3">
-        <f>AF3+1</f>
+      <c r="AH6">
+        <f>AF6+1</f>
         <v>3</v>
       </c>
-      <c r="AJ3">
-        <f>AH3+1</f>
+      <c r="AJ6">
+        <f>AH6+1</f>
         <v>4</v>
       </c>
-      <c r="AL3">
-        <f>AJ3+1</f>
+      <c r="AL6">
+        <f>AJ6+1</f>
         <v>5</v>
       </c>
-      <c r="AN3">
-        <f>AL3+1</f>
+      <c r="AN6">
+        <f>AL6+1</f>
         <v>6</v>
       </c>
-      <c r="AP3">
-        <f>AN3+1</f>
+      <c r="AP6">
+        <f>AN6+1</f>
         <v>7</v>
       </c>
-      <c r="AR3">
-        <f>AP3+1</f>
+      <c r="AR6">
+        <f>AP6+1</f>
         <v>8</v>
       </c>
-      <c r="AT3">
-        <f>AR3+1</f>
+      <c r="AT6">
+        <f>AR6+1</f>
         <v>9</v>
       </c>
-      <c r="AV3">
+      <c r="AV6">
         <v>10</v>
       </c>
-      <c r="AW3">
+      <c r="AW6">
         <v>11</v>
       </c>
-      <c r="AX3">
+      <c r="AX6">
         <v>11</v>
       </c>
-      <c r="AY3">
-        <f>AT3+1</f>
+      <c r="AY6">
+        <f>AT6+1</f>
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="170"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="171" t="str">
-        <f>CONCATENATE("-",H3,"°")</f>
+    <row r="7" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="222" t="str">
+        <f>CONCATENATE("-",H6,"°")</f>
         <v>-10°</v>
       </c>
-      <c r="H5" s="171"/>
-      <c r="I5" s="172"/>
-      <c r="J5" s="172"/>
-      <c r="K5" s="172"/>
-      <c r="L5" s="172"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="172"/>
-      <c r="O5" s="172"/>
-      <c r="P5" s="172"/>
-      <c r="Q5" s="173" t="str">
-        <f>CONCATENATE("-",R3,"°")</f>
+      <c r="H8" s="222"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="223" t="str">
+        <f>CONCATENATE("-",R6,"°")</f>
         <v>-5°</v>
       </c>
-      <c r="R5" s="173"/>
-      <c r="S5" s="172"/>
-      <c r="T5" s="172"/>
-      <c r="U5" s="172"/>
-      <c r="V5" s="172"/>
-      <c r="W5" s="174"/>
-      <c r="X5" s="174"/>
-      <c r="Y5" s="172"/>
-      <c r="Z5" s="172"/>
-      <c r="AA5" s="173" t="str">
-        <f>CONCATENATE(AB3,"°")</f>
+      <c r="R8" s="223"/>
+      <c r="S8" s="81"/>
+      <c r="T8" s="81"/>
+      <c r="U8" s="81"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="224"/>
+      <c r="X8" s="224"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="223" t="str">
+        <f>CONCATENATE(AB6,"°")</f>
         <v>0°</v>
       </c>
-      <c r="AB5" s="173"/>
-      <c r="AC5" s="172"/>
-      <c r="AD5" s="172"/>
-      <c r="AE5" s="175"/>
-      <c r="AF5" s="175"/>
-      <c r="AG5" s="172"/>
-      <c r="AH5" s="172"/>
-      <c r="AI5" s="172"/>
-      <c r="AJ5" s="172"/>
-      <c r="AK5" s="173" t="str">
-        <f>CONCATENATE(AL3,"°")</f>
+      <c r="AB8" s="223"/>
+      <c r="AC8" s="81"/>
+      <c r="AD8" s="81"/>
+      <c r="AE8" s="225"/>
+      <c r="AF8" s="225"/>
+      <c r="AG8" s="81"/>
+      <c r="AH8" s="81"/>
+      <c r="AI8" s="81"/>
+      <c r="AJ8" s="81"/>
+      <c r="AK8" s="223" t="str">
+        <f>CONCATENATE(AL6,"°")</f>
         <v>5°</v>
       </c>
-      <c r="AL5" s="173"/>
-      <c r="AM5" s="172"/>
-      <c r="AN5" s="172"/>
-      <c r="AO5" s="172"/>
-      <c r="AP5" s="172"/>
-      <c r="AQ5" s="172"/>
-      <c r="AR5" s="172"/>
-      <c r="AS5" s="172"/>
-      <c r="AT5" s="172"/>
-      <c r="AU5" s="173" t="str">
-        <f>CONCATENATE(AV3,"°")</f>
+      <c r="AL8" s="223"/>
+      <c r="AM8" s="81"/>
+      <c r="AN8" s="81"/>
+      <c r="AO8" s="81"/>
+      <c r="AP8" s="81"/>
+      <c r="AQ8" s="81"/>
+      <c r="AR8" s="81"/>
+      <c r="AS8" s="81"/>
+      <c r="AT8" s="81"/>
+      <c r="AU8" s="223" t="str">
+        <f>CONCATENATE(AV6,"°")</f>
         <v>10°</v>
       </c>
-      <c r="AV5" s="173"/>
-      <c r="AW5" s="172"/>
-      <c r="AX5" s="170"/>
-      <c r="AY5" s="170"/>
-    </row>
-    <row r="6" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="170"/>
-      <c r="E6" s="176" t="str">
-        <f>CONCATENATE("-",F3,"°")</f>
+      <c r="AV8" s="223"/>
+      <c r="AW8" s="81"/>
+      <c r="AX8" s="80"/>
+      <c r="AY8" s="80"/>
+    </row>
+    <row r="9" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="80"/>
+      <c r="E9" s="226" t="str">
+        <f>CONCATENATE("-",F6,"°")</f>
         <v>-11°</v>
       </c>
-      <c r="F6" s="176"/>
-      <c r="G6" s="171"/>
-      <c r="H6" s="171"/>
-      <c r="I6" s="177" t="str">
-        <f>CONCATENATE("-",J3,"°")</f>
+      <c r="F9" s="226"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="222"/>
+      <c r="I9" s="220" t="str">
+        <f>CONCATENATE("-",J6,"°")</f>
         <v>-9°</v>
       </c>
-      <c r="J6" s="177"/>
-      <c r="K6" s="177" t="str">
-        <f>CONCATENATE("-",L3,"°")</f>
+      <c r="J9" s="220"/>
+      <c r="K9" s="220" t="str">
+        <f>CONCATENATE("-",L6,"°")</f>
         <v>-8°</v>
       </c>
-      <c r="L6" s="177"/>
-      <c r="M6" s="177" t="str">
-        <f>CONCATENATE("-",N3,"°")</f>
+      <c r="L9" s="220"/>
+      <c r="M9" s="220" t="str">
+        <f>CONCATENATE("-",N6,"°")</f>
         <v>-7°</v>
       </c>
-      <c r="N6" s="177"/>
-      <c r="O6" s="177" t="str">
-        <f>CONCATENATE("-",P3,"°")</f>
+      <c r="N9" s="220"/>
+      <c r="O9" s="220" t="str">
+        <f>CONCATENATE("-",P6,"°")</f>
         <v>-6°</v>
       </c>
-      <c r="P6" s="177"/>
-      <c r="Q6" s="173"/>
-      <c r="R6" s="173"/>
-      <c r="S6" s="177" t="str">
-        <f>CONCATENATE("-",T3,"°")</f>
+      <c r="P9" s="220"/>
+      <c r="Q9" s="223"/>
+      <c r="R9" s="223"/>
+      <c r="S9" s="220" t="str">
+        <f>CONCATENATE("-",T6,"°")</f>
         <v>-4°</v>
       </c>
-      <c r="T6" s="177"/>
-      <c r="U6" s="177" t="str">
-        <f>CONCATENATE("-",V3,"°")</f>
+      <c r="T9" s="220"/>
+      <c r="U9" s="220" t="str">
+        <f>CONCATENATE("-",V6,"°")</f>
         <v>-3°</v>
       </c>
-      <c r="V6" s="177"/>
-      <c r="W6" s="177" t="str">
-        <f>CONCATENATE("-",X3,"°")</f>
+      <c r="V9" s="220"/>
+      <c r="W9" s="220" t="str">
+        <f>CONCATENATE("-",X6,"°")</f>
         <v>-2°</v>
       </c>
-      <c r="X6" s="177"/>
-      <c r="Y6" s="177" t="str">
-        <f>CONCATENATE("-",Z3,"°")</f>
+      <c r="X9" s="220"/>
+      <c r="Y9" s="220" t="str">
+        <f>CONCATENATE("-",Z6,"°")</f>
         <v>-1°</v>
       </c>
-      <c r="Z6" s="177"/>
-      <c r="AA6" s="173"/>
-      <c r="AB6" s="173"/>
-      <c r="AC6" s="177" t="str">
-        <f>CONCATENATE(AD3,"°")</f>
+      <c r="Z9" s="220"/>
+      <c r="AA9" s="223"/>
+      <c r="AB9" s="223"/>
+      <c r="AC9" s="220" t="str">
+        <f>CONCATENATE(AD6,"°")</f>
         <v>1°</v>
       </c>
-      <c r="AD6" s="177"/>
-      <c r="AE6" s="177" t="str">
-        <f>CONCATENATE(AF3,"°")</f>
+      <c r="AD9" s="220"/>
+      <c r="AE9" s="220" t="str">
+        <f>CONCATENATE(AF6,"°")</f>
         <v>2°</v>
       </c>
-      <c r="AF6" s="177"/>
-      <c r="AG6" s="177" t="str">
-        <f>CONCATENATE(AH3,"°")</f>
+      <c r="AF9" s="220"/>
+      <c r="AG9" s="220" t="str">
+        <f>CONCATENATE(AH6,"°")</f>
         <v>3°</v>
       </c>
-      <c r="AH6" s="177"/>
-      <c r="AI6" s="177" t="str">
-        <f>CONCATENATE(AJ3,"°")</f>
+      <c r="AH9" s="220"/>
+      <c r="AI9" s="220" t="str">
+        <f>CONCATENATE(AJ6,"°")</f>
         <v>4°</v>
       </c>
-      <c r="AJ6" s="177"/>
-      <c r="AK6" s="173"/>
-      <c r="AL6" s="173"/>
-      <c r="AM6" s="177" t="str">
-        <f>CONCATENATE(AN3,"°")</f>
+      <c r="AJ9" s="220"/>
+      <c r="AK9" s="223"/>
+      <c r="AL9" s="223"/>
+      <c r="AM9" s="220" t="str">
+        <f>CONCATENATE(AN6,"°")</f>
         <v>6°</v>
       </c>
-      <c r="AN6" s="177"/>
-      <c r="AO6" s="177" t="str">
-        <f>CONCATENATE(AP3,"°")</f>
+      <c r="AN9" s="220"/>
+      <c r="AO9" s="220" t="str">
+        <f>CONCATENATE(AP6,"°")</f>
         <v>7°</v>
       </c>
-      <c r="AP6" s="177"/>
-      <c r="AQ6" s="177" t="str">
-        <f>CONCATENATE(AR3,"°")</f>
+      <c r="AP9" s="220"/>
+      <c r="AQ9" s="220" t="str">
+        <f>CONCATENATE(AR6,"°")</f>
         <v>8°</v>
       </c>
-      <c r="AR6" s="177"/>
-      <c r="AS6" s="177" t="str">
-        <f>CONCATENATE(AT3,"°")</f>
+      <c r="AR9" s="220"/>
+      <c r="AS9" s="220" t="str">
+        <f>CONCATENATE(AT6,"°")</f>
         <v>9°</v>
       </c>
-      <c r="AT6" s="177"/>
-      <c r="AU6" s="173"/>
-      <c r="AV6" s="173"/>
-      <c r="AW6" s="177" t="str">
-        <f>CONCATENATE(AX3,"°")</f>
+      <c r="AT9" s="220"/>
+      <c r="AU9" s="223"/>
+      <c r="AV9" s="223"/>
+      <c r="AW9" s="220" t="str">
+        <f>CONCATENATE(AX6,"°")</f>
         <v>11°</v>
       </c>
-      <c r="AX6" s="177"/>
-      <c r="AY6" s="170"/>
-    </row>
-    <row r="7" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F7" s="178"/>
-      <c r="G7" s="179"/>
-      <c r="H7" s="180"/>
-      <c r="I7" s="178"/>
-      <c r="J7" s="178"/>
-      <c r="K7" s="178"/>
-      <c r="L7" s="178"/>
-      <c r="M7" s="178"/>
-      <c r="N7" s="178"/>
-      <c r="O7" s="178"/>
-      <c r="P7" s="178"/>
-      <c r="Q7" s="179"/>
-      <c r="R7" s="181"/>
-      <c r="S7" s="182"/>
-      <c r="T7" s="178"/>
-      <c r="U7" s="178"/>
-      <c r="V7" s="178"/>
-      <c r="W7" s="178"/>
-      <c r="X7" s="178"/>
-      <c r="Y7" s="178"/>
-      <c r="Z7" s="178"/>
-      <c r="AA7" s="178"/>
-      <c r="AB7" s="180"/>
-      <c r="AC7" s="178"/>
-      <c r="AD7" s="178"/>
-      <c r="AE7" s="178"/>
-      <c r="AF7" s="178"/>
-      <c r="AG7" s="178"/>
-      <c r="AH7" s="178"/>
-      <c r="AI7" s="178"/>
-      <c r="AJ7" s="178"/>
-      <c r="AK7" s="178"/>
-      <c r="AL7" s="180"/>
-      <c r="AM7" s="178"/>
-      <c r="AN7" s="178"/>
-      <c r="AO7" s="178"/>
-      <c r="AP7" s="178"/>
-      <c r="AQ7" s="178"/>
-      <c r="AR7" s="178"/>
-      <c r="AS7" s="178"/>
-      <c r="AT7" s="178"/>
-      <c r="AU7" s="178"/>
-      <c r="AV7" s="180"/>
-      <c r="AW7" s="178"/>
-    </row>
-    <row r="8" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="AX9" s="220"/>
+      <c r="AY9" s="80"/>
+    </row>
+    <row r="10" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="216"/>
+      <c r="G10" s="221"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="216"/>
+      <c r="J10" s="216"/>
+      <c r="K10" s="216"/>
+      <c r="L10" s="216"/>
+      <c r="M10" s="216"/>
+      <c r="N10" s="216"/>
+      <c r="O10" s="216"/>
+      <c r="P10" s="216"/>
+      <c r="Q10" s="221"/>
+      <c r="R10" s="218"/>
+      <c r="S10" s="219"/>
+      <c r="T10" s="216"/>
+      <c r="U10" s="216"/>
+      <c r="V10" s="216"/>
+      <c r="W10" s="216"/>
+      <c r="X10" s="216"/>
+      <c r="Y10" s="216"/>
+      <c r="Z10" s="216"/>
+      <c r="AA10" s="216"/>
+      <c r="AB10" s="217"/>
+      <c r="AC10" s="216"/>
+      <c r="AD10" s="216"/>
+      <c r="AE10" s="216"/>
+      <c r="AF10" s="216"/>
+      <c r="AG10" s="216"/>
+      <c r="AH10" s="216"/>
+      <c r="AI10" s="216"/>
+      <c r="AJ10" s="216"/>
+      <c r="AK10" s="216"/>
+      <c r="AL10" s="217"/>
+      <c r="AM10" s="216"/>
+      <c r="AN10" s="216"/>
+      <c r="AO10" s="216"/>
+      <c r="AP10" s="216"/>
+      <c r="AQ10" s="216"/>
+      <c r="AR10" s="216"/>
+      <c r="AS10" s="216"/>
+      <c r="AT10" s="216"/>
+      <c r="AU10" s="216"/>
+      <c r="AV10" s="217"/>
+      <c r="AW10" s="216"/>
+    </row>
+    <row r="11" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>20</v>
       </c>
-      <c r="B8">
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="C8" s="183" t="str">
-        <f>CONCATENATE(B8,"°")</f>
+      <c r="C11" s="213" t="str">
+        <f>CONCATENATE(B11,"°")</f>
         <v>0°</v>
       </c>
-      <c r="D8" s="183"/>
-      <c r="E8" s="184"/>
-      <c r="F8" s="178"/>
-      <c r="G8" s="179"/>
-      <c r="H8" s="180"/>
-      <c r="I8" s="178"/>
-      <c r="J8" s="178"/>
-      <c r="K8" s="178"/>
-      <c r="L8" s="178"/>
-      <c r="M8" s="178"/>
-      <c r="N8" s="178"/>
-      <c r="O8" s="178"/>
-      <c r="P8" s="178"/>
-      <c r="Q8" s="179"/>
-      <c r="R8" s="181"/>
-      <c r="S8" s="182"/>
-      <c r="T8" s="178"/>
-      <c r="U8" s="178"/>
-      <c r="V8" s="178"/>
-      <c r="W8" s="178"/>
-      <c r="X8" s="178"/>
-      <c r="Y8" s="178"/>
-      <c r="Z8" s="178"/>
-      <c r="AA8" s="178"/>
-      <c r="AB8" s="180"/>
-      <c r="AC8" s="178"/>
-      <c r="AD8" s="178"/>
-      <c r="AE8" s="178"/>
-      <c r="AF8" s="178"/>
-      <c r="AG8" s="178"/>
-      <c r="AH8" s="178"/>
-      <c r="AI8" s="178"/>
-      <c r="AJ8" s="178"/>
-      <c r="AK8" s="178"/>
-      <c r="AL8" s="180"/>
-      <c r="AM8" s="178"/>
-      <c r="AN8" s="178"/>
-      <c r="AO8" s="178"/>
-      <c r="AP8" s="178"/>
-      <c r="AQ8" s="178"/>
-      <c r="AR8" s="178"/>
-      <c r="AS8" s="178"/>
-      <c r="AT8" s="178"/>
-      <c r="AU8" s="178"/>
-      <c r="AV8" s="180"/>
-      <c r="AW8" s="178"/>
-    </row>
-    <row r="9" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="183"/>
-      <c r="D9" s="183"/>
-      <c r="E9" s="184"/>
-      <c r="F9" s="185"/>
-      <c r="G9" s="186"/>
-      <c r="H9" s="187"/>
-      <c r="I9" s="186"/>
-      <c r="J9" s="188"/>
-      <c r="K9" s="185"/>
-      <c r="L9" s="188"/>
-      <c r="M9" s="185"/>
-      <c r="N9" s="188"/>
-      <c r="O9" s="185"/>
-      <c r="P9" s="188"/>
-      <c r="Q9" s="186"/>
-      <c r="R9" s="187"/>
-      <c r="S9" s="185"/>
-      <c r="T9" s="188"/>
-      <c r="U9" s="185"/>
-      <c r="V9" s="188"/>
-      <c r="W9" s="185"/>
-      <c r="X9" s="188"/>
-      <c r="Y9" s="185"/>
-      <c r="Z9" s="188"/>
-      <c r="AA9" s="186"/>
-      <c r="AB9" s="187"/>
-      <c r="AC9" s="185"/>
-      <c r="AD9" s="188"/>
-      <c r="AE9" s="185"/>
-      <c r="AF9" s="188"/>
-      <c r="AG9" s="185"/>
-      <c r="AH9" s="188"/>
-      <c r="AI9" s="185"/>
-      <c r="AJ9" s="188"/>
-      <c r="AK9" s="186"/>
-      <c r="AL9" s="187"/>
-      <c r="AM9" s="185"/>
-      <c r="AN9" s="188"/>
-      <c r="AO9" s="185"/>
-      <c r="AP9" s="188"/>
-      <c r="AQ9" s="185"/>
-      <c r="AR9" s="188"/>
-      <c r="AS9" s="185"/>
-      <c r="AT9" s="188"/>
-      <c r="AU9" s="186"/>
-      <c r="AV9" s="187"/>
-      <c r="AW9" s="185"/>
-    </row>
-    <row r="10" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10">
-        <f>B8+$A$8</f>
+      <c r="D11" s="213"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="221"/>
+      <c r="H11" s="217"/>
+      <c r="I11" s="216"/>
+      <c r="J11" s="216"/>
+      <c r="K11" s="216"/>
+      <c r="L11" s="216"/>
+      <c r="M11" s="216"/>
+      <c r="N11" s="216"/>
+      <c r="O11" s="216"/>
+      <c r="P11" s="216"/>
+      <c r="Q11" s="221"/>
+      <c r="R11" s="218"/>
+      <c r="S11" s="219"/>
+      <c r="T11" s="216"/>
+      <c r="U11" s="216"/>
+      <c r="V11" s="216"/>
+      <c r="W11" s="216"/>
+      <c r="X11" s="216"/>
+      <c r="Y11" s="216"/>
+      <c r="Z11" s="216"/>
+      <c r="AA11" s="216"/>
+      <c r="AB11" s="217"/>
+      <c r="AC11" s="216"/>
+      <c r="AD11" s="216"/>
+      <c r="AE11" s="216"/>
+      <c r="AF11" s="216"/>
+      <c r="AG11" s="216"/>
+      <c r="AH11" s="216"/>
+      <c r="AI11" s="216"/>
+      <c r="AJ11" s="216"/>
+      <c r="AK11" s="216"/>
+      <c r="AL11" s="217"/>
+      <c r="AM11" s="216"/>
+      <c r="AN11" s="216"/>
+      <c r="AO11" s="216"/>
+      <c r="AP11" s="216"/>
+      <c r="AQ11" s="216"/>
+      <c r="AR11" s="216"/>
+      <c r="AS11" s="216"/>
+      <c r="AT11" s="216"/>
+      <c r="AU11" s="216"/>
+      <c r="AV11" s="217"/>
+      <c r="AW11" s="216"/>
+    </row>
+    <row r="12" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="213"/>
+      <c r="D12" s="213"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="86"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="85"/>
+      <c r="S12" s="83"/>
+      <c r="T12" s="86"/>
+      <c r="U12" s="83"/>
+      <c r="V12" s="86"/>
+      <c r="W12" s="83"/>
+      <c r="X12" s="86"/>
+      <c r="Y12" s="83"/>
+      <c r="Z12" s="86"/>
+      <c r="AA12" s="84"/>
+      <c r="AB12" s="85"/>
+      <c r="AC12" s="83"/>
+      <c r="AD12" s="86"/>
+      <c r="AE12" s="83"/>
+      <c r="AF12" s="86"/>
+      <c r="AG12" s="83"/>
+      <c r="AH12" s="86"/>
+      <c r="AI12" s="83"/>
+      <c r="AJ12" s="86"/>
+      <c r="AK12" s="84"/>
+      <c r="AL12" s="85"/>
+      <c r="AM12" s="83"/>
+      <c r="AN12" s="86"/>
+      <c r="AO12" s="83"/>
+      <c r="AP12" s="86"/>
+      <c r="AQ12" s="83"/>
+      <c r="AR12" s="86"/>
+      <c r="AS12" s="83"/>
+      <c r="AT12" s="86"/>
+      <c r="AU12" s="84"/>
+      <c r="AV12" s="85"/>
+      <c r="AW12" s="83"/>
+    </row>
+    <row r="13" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f>B11+$A$11</f>
         <v>20</v>
       </c>
-      <c r="C10" s="183" t="str">
-        <f>CONCATENATE(B10,"°")</f>
+      <c r="C13" s="213" t="str">
+        <f>CONCATENATE(B13,"°")</f>
         <v>20°</v>
       </c>
-      <c r="D10" s="183"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="189"/>
-      <c r="G10" s="190"/>
-      <c r="H10" s="191"/>
-      <c r="I10" s="190"/>
-      <c r="J10" s="192"/>
-      <c r="K10" s="189"/>
-      <c r="L10" s="192"/>
-      <c r="M10" s="189"/>
-      <c r="N10" s="192"/>
-      <c r="O10" s="189"/>
-      <c r="P10" s="192"/>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="191"/>
-      <c r="S10" s="189"/>
-      <c r="T10" s="192"/>
-      <c r="U10" s="189"/>
-      <c r="V10" s="192"/>
-      <c r="W10" s="189"/>
-      <c r="X10" s="192"/>
-      <c r="Y10" s="189"/>
-      <c r="Z10" s="192"/>
-      <c r="AA10" s="190"/>
-      <c r="AB10" s="191"/>
-      <c r="AC10" s="189"/>
-      <c r="AD10" s="192"/>
-      <c r="AE10" s="189"/>
-      <c r="AF10" s="192"/>
-      <c r="AG10" s="189"/>
-      <c r="AH10" s="192"/>
-      <c r="AI10" s="189"/>
-      <c r="AJ10" s="192"/>
-      <c r="AK10" s="190"/>
-      <c r="AL10" s="191"/>
-      <c r="AM10" s="189"/>
-      <c r="AN10" s="192"/>
-      <c r="AO10" s="189"/>
-      <c r="AP10" s="192"/>
-      <c r="AQ10" s="189"/>
-      <c r="AR10" s="192"/>
-      <c r="AS10" s="189"/>
-      <c r="AT10" s="192"/>
-      <c r="AU10" s="190"/>
-      <c r="AV10" s="191"/>
-      <c r="AW10" s="189"/>
-    </row>
-    <row r="11" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="183"/>
-      <c r="D11" s="183"/>
-      <c r="E11" s="184"/>
-      <c r="F11" s="193"/>
-      <c r="G11" s="194"/>
-      <c r="H11" s="195"/>
-      <c r="I11" s="194"/>
-      <c r="J11" s="196"/>
-      <c r="K11" s="193"/>
-      <c r="L11" s="196"/>
-      <c r="M11" s="193"/>
-      <c r="N11" s="196"/>
-      <c r="O11" s="193"/>
-      <c r="P11" s="196"/>
-      <c r="Q11" s="194"/>
-      <c r="R11" s="195"/>
-      <c r="S11" s="193"/>
-      <c r="T11" s="196"/>
-      <c r="U11" s="193"/>
-      <c r="V11" s="196"/>
-      <c r="W11" s="193"/>
-      <c r="X11" s="196"/>
-      <c r="Y11" s="193"/>
-      <c r="Z11" s="196"/>
-      <c r="AA11" s="194"/>
-      <c r="AB11" s="195"/>
-      <c r="AC11" s="193"/>
-      <c r="AD11" s="196"/>
-      <c r="AE11" s="193"/>
-      <c r="AF11" s="196"/>
-      <c r="AG11" s="193"/>
-      <c r="AH11" s="196"/>
-      <c r="AI11" s="193"/>
-      <c r="AJ11" s="196"/>
-      <c r="AK11" s="194"/>
-      <c r="AL11" s="195"/>
-      <c r="AM11" s="193"/>
-      <c r="AN11" s="196"/>
-      <c r="AO11" s="193"/>
-      <c r="AP11" s="196"/>
-      <c r="AQ11" s="193"/>
-      <c r="AR11" s="196"/>
-      <c r="AS11" s="193"/>
-      <c r="AT11" s="196"/>
-      <c r="AU11" s="194"/>
-      <c r="AV11" s="195"/>
-      <c r="AW11" s="193"/>
-    </row>
-    <row r="12" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <f>B10+$A$8</f>
+      <c r="D13" s="213"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="90"/>
+      <c r="M13" s="87"/>
+      <c r="N13" s="90"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="88"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="87"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="87"/>
+      <c r="V13" s="90"/>
+      <c r="W13" s="87"/>
+      <c r="X13" s="90"/>
+      <c r="Y13" s="87"/>
+      <c r="Z13" s="90"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="89"/>
+      <c r="AC13" s="87"/>
+      <c r="AD13" s="90"/>
+      <c r="AE13" s="87"/>
+      <c r="AF13" s="90"/>
+      <c r="AG13" s="87"/>
+      <c r="AH13" s="90"/>
+      <c r="AI13" s="87"/>
+      <c r="AJ13" s="90"/>
+      <c r="AK13" s="88"/>
+      <c r="AL13" s="89"/>
+      <c r="AM13" s="87"/>
+      <c r="AN13" s="90"/>
+      <c r="AO13" s="87"/>
+      <c r="AP13" s="90"/>
+      <c r="AQ13" s="87"/>
+      <c r="AR13" s="90"/>
+      <c r="AS13" s="87"/>
+      <c r="AT13" s="90"/>
+      <c r="AU13" s="88"/>
+      <c r="AV13" s="89"/>
+      <c r="AW13" s="87"/>
+    </row>
+    <row r="14" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="213"/>
+      <c r="D14" s="213"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="94"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="94"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="93"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="94"/>
+      <c r="Y14" s="91"/>
+      <c r="Z14" s="94"/>
+      <c r="AA14" s="92"/>
+      <c r="AB14" s="93"/>
+      <c r="AC14" s="91"/>
+      <c r="AD14" s="94"/>
+      <c r="AE14" s="91"/>
+      <c r="AF14" s="94"/>
+      <c r="AG14" s="91"/>
+      <c r="AH14" s="94"/>
+      <c r="AI14" s="91"/>
+      <c r="AJ14" s="94"/>
+      <c r="AK14" s="92"/>
+      <c r="AL14" s="93"/>
+      <c r="AM14" s="91"/>
+      <c r="AN14" s="94"/>
+      <c r="AO14" s="91"/>
+      <c r="AP14" s="94"/>
+      <c r="AQ14" s="91"/>
+      <c r="AR14" s="94"/>
+      <c r="AS14" s="91"/>
+      <c r="AT14" s="94"/>
+      <c r="AU14" s="92"/>
+      <c r="AV14" s="93"/>
+      <c r="AW14" s="91"/>
+    </row>
+    <row r="15" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f>B13+$A$11</f>
         <v>40</v>
       </c>
-      <c r="C12" s="183" t="str">
-        <f>CONCATENATE(B12,"°")</f>
+      <c r="C15" s="213" t="str">
+        <f>CONCATENATE(B15,"°")</f>
         <v>40°</v>
       </c>
-      <c r="D12" s="183"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="197"/>
-      <c r="G12" s="198"/>
-      <c r="H12" s="199"/>
-      <c r="I12" s="198"/>
-      <c r="J12" s="200"/>
-      <c r="K12" s="197"/>
-      <c r="L12" s="200"/>
-      <c r="M12" s="197"/>
-      <c r="N12" s="200"/>
-      <c r="O12" s="197"/>
-      <c r="P12" s="200"/>
-      <c r="Q12" s="198"/>
-      <c r="R12" s="199"/>
-      <c r="S12" s="197"/>
-      <c r="T12" s="200"/>
-      <c r="U12" s="197"/>
-      <c r="V12" s="200"/>
-      <c r="W12" s="197"/>
-      <c r="X12" s="200"/>
-      <c r="Y12" s="197"/>
-      <c r="Z12" s="200"/>
-      <c r="AA12" s="198"/>
-      <c r="AB12" s="199"/>
-      <c r="AC12" s="197"/>
-      <c r="AD12" s="200"/>
-      <c r="AE12" s="197"/>
-      <c r="AF12" s="200"/>
-      <c r="AG12" s="197"/>
-      <c r="AH12" s="200"/>
-      <c r="AI12" s="197"/>
-      <c r="AJ12" s="200"/>
-      <c r="AK12" s="198"/>
-      <c r="AL12" s="199"/>
-      <c r="AM12" s="197"/>
-      <c r="AN12" s="200"/>
-      <c r="AO12" s="197"/>
-      <c r="AP12" s="200"/>
-      <c r="AQ12" s="197"/>
-      <c r="AR12" s="200"/>
-      <c r="AS12" s="197"/>
-      <c r="AT12" s="200"/>
-      <c r="AU12" s="198"/>
-      <c r="AV12" s="199"/>
-      <c r="AW12" s="197"/>
-    </row>
-    <row r="13" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="183"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="184"/>
-      <c r="F13" s="201"/>
-      <c r="G13" s="202"/>
-      <c r="H13" s="203"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="204"/>
-      <c r="K13" s="201"/>
-      <c r="L13" s="204"/>
-      <c r="M13" s="201"/>
-      <c r="N13" s="204"/>
-      <c r="O13" s="201"/>
-      <c r="P13" s="204"/>
-      <c r="Q13" s="202"/>
-      <c r="R13" s="203"/>
-      <c r="S13" s="201"/>
-      <c r="T13" s="204"/>
-      <c r="U13" s="201"/>
-      <c r="V13" s="204"/>
-      <c r="W13" s="201"/>
-      <c r="X13" s="204"/>
-      <c r="Y13" s="201"/>
-      <c r="Z13" s="204"/>
-      <c r="AA13" s="202"/>
-      <c r="AB13" s="203"/>
-      <c r="AC13" s="201"/>
-      <c r="AD13" s="204"/>
-      <c r="AE13" s="201"/>
-      <c r="AF13" s="204"/>
-      <c r="AG13" s="201"/>
-      <c r="AH13" s="204"/>
-      <c r="AI13" s="201"/>
-      <c r="AJ13" s="204"/>
-      <c r="AK13" s="202"/>
-      <c r="AL13" s="203"/>
-      <c r="AM13" s="201"/>
-      <c r="AN13" s="204"/>
-      <c r="AO13" s="201"/>
-      <c r="AP13" s="204"/>
-      <c r="AQ13" s="201"/>
-      <c r="AR13" s="204"/>
-      <c r="AS13" s="201"/>
-      <c r="AT13" s="204"/>
-      <c r="AU13" s="202"/>
-      <c r="AV13" s="203"/>
-      <c r="AW13" s="201"/>
-    </row>
-    <row r="14" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <f>B12+$A$8</f>
+      <c r="D15" s="213"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="97"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="95"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="98"/>
+      <c r="O15" s="95"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="97"/>
+      <c r="S15" s="95"/>
+      <c r="T15" s="98"/>
+      <c r="U15" s="95"/>
+      <c r="V15" s="98"/>
+      <c r="W15" s="95"/>
+      <c r="X15" s="98"/>
+      <c r="Y15" s="95"/>
+      <c r="Z15" s="98"/>
+      <c r="AA15" s="96"/>
+      <c r="AB15" s="97"/>
+      <c r="AC15" s="95"/>
+      <c r="AD15" s="98"/>
+      <c r="AE15" s="95"/>
+      <c r="AF15" s="98"/>
+      <c r="AG15" s="95"/>
+      <c r="AH15" s="98"/>
+      <c r="AI15" s="95"/>
+      <c r="AJ15" s="98"/>
+      <c r="AK15" s="96"/>
+      <c r="AL15" s="97"/>
+      <c r="AM15" s="95"/>
+      <c r="AN15" s="98"/>
+      <c r="AO15" s="95"/>
+      <c r="AP15" s="98"/>
+      <c r="AQ15" s="95"/>
+      <c r="AR15" s="98"/>
+      <c r="AS15" s="95"/>
+      <c r="AT15" s="98"/>
+      <c r="AU15" s="96"/>
+      <c r="AV15" s="97"/>
+      <c r="AW15" s="95"/>
+    </row>
+    <row r="16" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="213"/>
+      <c r="D16" s="213"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="102"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="102"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="100"/>
+      <c r="R16" s="101"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="102"/>
+      <c r="U16" s="99"/>
+      <c r="V16" s="102"/>
+      <c r="W16" s="99"/>
+      <c r="X16" s="102"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="102"/>
+      <c r="AA16" s="100"/>
+      <c r="AB16" s="101"/>
+      <c r="AC16" s="99"/>
+      <c r="AD16" s="102"/>
+      <c r="AE16" s="99"/>
+      <c r="AF16" s="102"/>
+      <c r="AG16" s="99"/>
+      <c r="AH16" s="102"/>
+      <c r="AI16" s="99"/>
+      <c r="AJ16" s="102"/>
+      <c r="AK16" s="100"/>
+      <c r="AL16" s="101"/>
+      <c r="AM16" s="99"/>
+      <c r="AN16" s="102"/>
+      <c r="AO16" s="99"/>
+      <c r="AP16" s="102"/>
+      <c r="AQ16" s="99"/>
+      <c r="AR16" s="102"/>
+      <c r="AS16" s="99"/>
+      <c r="AT16" s="102"/>
+      <c r="AU16" s="100"/>
+      <c r="AV16" s="101"/>
+      <c r="AW16" s="99"/>
+    </row>
+    <row r="17" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f>B15+$A$11</f>
         <v>60</v>
       </c>
-      <c r="C14" s="183" t="str">
-        <f>CONCATENATE(B14,"°")</f>
+      <c r="C17" s="213" t="str">
+        <f>CONCATENATE(B17,"°")</f>
         <v>60°</v>
       </c>
-      <c r="D14" s="183"/>
-      <c r="E14" s="184"/>
-      <c r="F14" s="189"/>
-      <c r="G14" s="190"/>
-      <c r="H14" s="191"/>
-      <c r="I14" s="190"/>
-      <c r="J14" s="192"/>
-      <c r="K14" s="189"/>
-      <c r="L14" s="192"/>
-      <c r="M14" s="189"/>
-      <c r="N14" s="192"/>
-      <c r="O14" s="189"/>
-      <c r="P14" s="192"/>
-      <c r="Q14" s="190"/>
-      <c r="R14" s="191"/>
-      <c r="S14" s="189"/>
-      <c r="T14" s="192"/>
-      <c r="U14" s="189"/>
-      <c r="V14" s="192"/>
-      <c r="W14" s="189"/>
-      <c r="X14" s="192"/>
-      <c r="Y14" s="189"/>
-      <c r="Z14" s="192"/>
-      <c r="AA14" s="190"/>
-      <c r="AB14" s="191"/>
-      <c r="AC14" s="189"/>
-      <c r="AD14" s="192"/>
-      <c r="AE14" s="189"/>
-      <c r="AF14" s="192"/>
-      <c r="AG14" s="189"/>
-      <c r="AH14" s="192"/>
-      <c r="AI14" s="189"/>
-      <c r="AJ14" s="192"/>
-      <c r="AK14" s="190"/>
-      <c r="AL14" s="191"/>
-      <c r="AM14" s="189"/>
-      <c r="AN14" s="192"/>
-      <c r="AO14" s="189"/>
-      <c r="AP14" s="192"/>
-      <c r="AQ14" s="189"/>
-      <c r="AR14" s="192"/>
-      <c r="AS14" s="189"/>
-      <c r="AT14" s="192"/>
-      <c r="AU14" s="190"/>
-      <c r="AV14" s="191"/>
-      <c r="AW14" s="189"/>
-    </row>
-    <row r="15" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="183"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="184"/>
-      <c r="F15" s="193"/>
-      <c r="G15" s="194"/>
-      <c r="H15" s="195"/>
-      <c r="I15" s="194"/>
-      <c r="J15" s="196"/>
-      <c r="K15" s="193"/>
-      <c r="L15" s="196"/>
-      <c r="M15" s="193"/>
-      <c r="N15" s="196"/>
-      <c r="O15" s="193"/>
-      <c r="P15" s="196"/>
-      <c r="Q15" s="194"/>
-      <c r="R15" s="195"/>
-      <c r="S15" s="193"/>
-      <c r="T15" s="196"/>
-      <c r="U15" s="193"/>
-      <c r="V15" s="196"/>
-      <c r="W15" s="193"/>
-      <c r="X15" s="196"/>
-      <c r="Y15" s="193"/>
-      <c r="Z15" s="196"/>
-      <c r="AA15" s="194"/>
-      <c r="AB15" s="195"/>
-      <c r="AC15" s="193"/>
-      <c r="AD15" s="196"/>
-      <c r="AE15" s="193"/>
-      <c r="AF15" s="196"/>
-      <c r="AG15" s="193"/>
-      <c r="AH15" s="196"/>
-      <c r="AI15" s="193"/>
-      <c r="AJ15" s="196"/>
-      <c r="AK15" s="194"/>
-      <c r="AL15" s="195"/>
-      <c r="AM15" s="193"/>
-      <c r="AN15" s="196"/>
-      <c r="AO15" s="193"/>
-      <c r="AP15" s="196"/>
-      <c r="AQ15" s="193"/>
-      <c r="AR15" s="196"/>
-      <c r="AS15" s="193"/>
-      <c r="AT15" s="196"/>
-      <c r="AU15" s="194"/>
-      <c r="AV15" s="195"/>
-      <c r="AW15" s="193"/>
-    </row>
-    <row r="16" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <f>B14+$A$8</f>
+      <c r="D17" s="213"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="87"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="87"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="88"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="87"/>
+      <c r="T17" s="90"/>
+      <c r="U17" s="87"/>
+      <c r="V17" s="90"/>
+      <c r="W17" s="87"/>
+      <c r="X17" s="90"/>
+      <c r="Y17" s="87"/>
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="90"/>
+      <c r="AE17" s="87"/>
+      <c r="AF17" s="90"/>
+      <c r="AG17" s="87"/>
+      <c r="AH17" s="90"/>
+      <c r="AI17" s="87"/>
+      <c r="AJ17" s="90"/>
+      <c r="AK17" s="88"/>
+      <c r="AL17" s="89"/>
+      <c r="AM17" s="87"/>
+      <c r="AN17" s="90"/>
+      <c r="AO17" s="87"/>
+      <c r="AP17" s="90"/>
+      <c r="AQ17" s="87"/>
+      <c r="AR17" s="90"/>
+      <c r="AS17" s="87"/>
+      <c r="AT17" s="90"/>
+      <c r="AU17" s="88"/>
+      <c r="AV17" s="89"/>
+      <c r="AW17" s="87"/>
+    </row>
+    <row r="18" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="213"/>
+      <c r="D18" s="213"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="93"/>
+      <c r="S18" s="91"/>
+      <c r="T18" s="94"/>
+      <c r="U18" s="91"/>
+      <c r="V18" s="94"/>
+      <c r="W18" s="91"/>
+      <c r="X18" s="94"/>
+      <c r="Y18" s="91"/>
+      <c r="Z18" s="94"/>
+      <c r="AA18" s="92"/>
+      <c r="AB18" s="93"/>
+      <c r="AC18" s="91"/>
+      <c r="AD18" s="94"/>
+      <c r="AE18" s="91"/>
+      <c r="AF18" s="94"/>
+      <c r="AG18" s="91"/>
+      <c r="AH18" s="94"/>
+      <c r="AI18" s="91"/>
+      <c r="AJ18" s="94"/>
+      <c r="AK18" s="92"/>
+      <c r="AL18" s="93"/>
+      <c r="AM18" s="91"/>
+      <c r="AN18" s="94"/>
+      <c r="AO18" s="91"/>
+      <c r="AP18" s="94"/>
+      <c r="AQ18" s="91"/>
+      <c r="AR18" s="94"/>
+      <c r="AS18" s="91"/>
+      <c r="AT18" s="94"/>
+      <c r="AU18" s="92"/>
+      <c r="AV18" s="93"/>
+      <c r="AW18" s="91"/>
+    </row>
+    <row r="19" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f>B17+$A$11</f>
         <v>80</v>
       </c>
-      <c r="C16" s="183" t="str">
-        <f>CONCATENATE(B16,"°")</f>
+      <c r="C19" s="213" t="str">
+        <f>CONCATENATE(B19,"°")</f>
         <v>80°</v>
       </c>
-      <c r="D16" s="183"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="205"/>
-      <c r="G16" s="206"/>
-      <c r="H16" s="207"/>
-      <c r="I16" s="206"/>
-      <c r="J16" s="208"/>
-      <c r="K16" s="205"/>
-      <c r="L16" s="208"/>
-      <c r="M16" s="205"/>
-      <c r="N16" s="208"/>
-      <c r="O16" s="205"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="206"/>
-      <c r="R16" s="207"/>
-      <c r="S16" s="205"/>
-      <c r="T16" s="208"/>
-      <c r="U16" s="205"/>
-      <c r="V16" s="208"/>
-      <c r="W16" s="205"/>
-      <c r="X16" s="208"/>
-      <c r="Y16" s="205"/>
-      <c r="Z16" s="208"/>
-      <c r="AA16" s="206"/>
-      <c r="AB16" s="207"/>
-      <c r="AC16" s="205"/>
-      <c r="AD16" s="208"/>
-      <c r="AE16" s="205"/>
-      <c r="AF16" s="208"/>
-      <c r="AG16" s="205"/>
-      <c r="AH16" s="208"/>
-      <c r="AI16" s="205"/>
-      <c r="AJ16" s="208"/>
-      <c r="AK16" s="206"/>
-      <c r="AL16" s="207"/>
-      <c r="AM16" s="205"/>
-      <c r="AN16" s="208"/>
-      <c r="AO16" s="205"/>
-      <c r="AP16" s="208"/>
-      <c r="AQ16" s="205"/>
-      <c r="AR16" s="208"/>
-      <c r="AS16" s="205"/>
-      <c r="AT16" s="208"/>
-      <c r="AU16" s="206"/>
-      <c r="AV16" s="207"/>
-      <c r="AW16" s="205"/>
-    </row>
-    <row r="17" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="183"/>
-      <c r="D17" s="183"/>
-      <c r="E17" s="184"/>
-      <c r="F17" s="209"/>
-      <c r="G17" s="210"/>
-      <c r="H17" s="211"/>
-      <c r="I17" s="210"/>
-      <c r="J17" s="212"/>
-      <c r="K17" s="209"/>
-      <c r="L17" s="212"/>
-      <c r="M17" s="209"/>
-      <c r="N17" s="212"/>
-      <c r="O17" s="209"/>
-      <c r="P17" s="212"/>
-      <c r="Q17" s="210"/>
-      <c r="R17" s="211"/>
-      <c r="S17" s="209"/>
-      <c r="T17" s="212"/>
-      <c r="U17" s="209"/>
-      <c r="V17" s="212"/>
-      <c r="W17" s="209"/>
-      <c r="X17" s="212"/>
-      <c r="Y17" s="209"/>
-      <c r="Z17" s="212"/>
-      <c r="AA17" s="210"/>
-      <c r="AB17" s="211"/>
-      <c r="AC17" s="209"/>
-      <c r="AD17" s="212"/>
-      <c r="AE17" s="209"/>
-      <c r="AF17" s="212"/>
-      <c r="AG17" s="209"/>
-      <c r="AH17" s="212"/>
-      <c r="AI17" s="209"/>
-      <c r="AJ17" s="212"/>
-      <c r="AK17" s="210"/>
-      <c r="AL17" s="211"/>
-      <c r="AM17" s="209"/>
-      <c r="AN17" s="212"/>
-      <c r="AO17" s="209"/>
-      <c r="AP17" s="212"/>
-      <c r="AQ17" s="209"/>
-      <c r="AR17" s="212"/>
-      <c r="AS17" s="209"/>
-      <c r="AT17" s="212"/>
-      <c r="AU17" s="210"/>
-      <c r="AV17" s="211"/>
-      <c r="AW17" s="209"/>
-    </row>
-    <row r="18" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18">
-        <f>B16+$A$8</f>
+      <c r="D19" s="213"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="103"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="106"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="104"/>
+      <c r="R19" s="105"/>
+      <c r="S19" s="103"/>
+      <c r="T19" s="106"/>
+      <c r="U19" s="103"/>
+      <c r="V19" s="106"/>
+      <c r="W19" s="103"/>
+      <c r="X19" s="106"/>
+      <c r="Y19" s="103"/>
+      <c r="Z19" s="106"/>
+      <c r="AA19" s="104"/>
+      <c r="AB19" s="105"/>
+      <c r="AC19" s="103"/>
+      <c r="AD19" s="106"/>
+      <c r="AE19" s="103"/>
+      <c r="AF19" s="106"/>
+      <c r="AG19" s="103"/>
+      <c r="AH19" s="106"/>
+      <c r="AI19" s="103"/>
+      <c r="AJ19" s="106"/>
+      <c r="AK19" s="104"/>
+      <c r="AL19" s="105"/>
+      <c r="AM19" s="103"/>
+      <c r="AN19" s="106"/>
+      <c r="AO19" s="103"/>
+      <c r="AP19" s="106"/>
+      <c r="AQ19" s="103"/>
+      <c r="AR19" s="106"/>
+      <c r="AS19" s="103"/>
+      <c r="AT19" s="106"/>
+      <c r="AU19" s="104"/>
+      <c r="AV19" s="105"/>
+      <c r="AW19" s="103"/>
+    </row>
+    <row r="20" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="213"/>
+      <c r="D20" s="213"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="110"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="108"/>
+      <c r="R20" s="109"/>
+      <c r="S20" s="107"/>
+      <c r="T20" s="110"/>
+      <c r="U20" s="107"/>
+      <c r="V20" s="110"/>
+      <c r="W20" s="107"/>
+      <c r="X20" s="110"/>
+      <c r="Y20" s="107"/>
+      <c r="Z20" s="110"/>
+      <c r="AA20" s="108"/>
+      <c r="AB20" s="109"/>
+      <c r="AC20" s="107"/>
+      <c r="AD20" s="110"/>
+      <c r="AE20" s="107"/>
+      <c r="AF20" s="110"/>
+      <c r="AG20" s="107"/>
+      <c r="AH20" s="110"/>
+      <c r="AI20" s="107"/>
+      <c r="AJ20" s="110"/>
+      <c r="AK20" s="108"/>
+      <c r="AL20" s="109"/>
+      <c r="AM20" s="107"/>
+      <c r="AN20" s="110"/>
+      <c r="AO20" s="107"/>
+      <c r="AP20" s="110"/>
+      <c r="AQ20" s="107"/>
+      <c r="AR20" s="110"/>
+      <c r="AS20" s="107"/>
+      <c r="AT20" s="110"/>
+      <c r="AU20" s="108"/>
+      <c r="AV20" s="109"/>
+      <c r="AW20" s="107"/>
+    </row>
+    <row r="21" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f>B19+$A$11</f>
         <v>100</v>
       </c>
-      <c r="C18" s="183" t="str">
-        <f>CONCATENATE(B18,"°")</f>
+      <c r="C21" s="213" t="str">
+        <f>CONCATENATE(B21,"°")</f>
         <v>100°</v>
       </c>
-      <c r="D18" s="183"/>
-      <c r="E18" s="184"/>
-      <c r="F18" s="213"/>
-      <c r="G18" s="214"/>
-      <c r="H18" s="215"/>
-      <c r="I18" s="214"/>
-      <c r="J18" s="216"/>
-      <c r="K18" s="213"/>
-      <c r="L18" s="216"/>
-      <c r="M18" s="213"/>
-      <c r="N18" s="216"/>
-      <c r="O18" s="213"/>
-      <c r="P18" s="216"/>
-      <c r="Q18" s="214"/>
-      <c r="R18" s="215"/>
-      <c r="S18" s="213"/>
-      <c r="T18" s="216"/>
-      <c r="U18" s="213"/>
-      <c r="V18" s="216"/>
-      <c r="W18" s="213"/>
-      <c r="X18" s="216"/>
-      <c r="Y18" s="213"/>
-      <c r="Z18" s="216"/>
-      <c r="AA18" s="214"/>
-      <c r="AB18" s="215"/>
-      <c r="AC18" s="213"/>
-      <c r="AD18" s="216"/>
-      <c r="AE18" s="213"/>
-      <c r="AF18" s="216"/>
-      <c r="AG18" s="213"/>
-      <c r="AH18" s="216"/>
-      <c r="AI18" s="213"/>
-      <c r="AJ18" s="216"/>
-      <c r="AK18" s="214"/>
-      <c r="AL18" s="215"/>
-      <c r="AM18" s="213"/>
-      <c r="AN18" s="216"/>
-      <c r="AO18" s="213"/>
-      <c r="AP18" s="216"/>
-      <c r="AQ18" s="213"/>
-      <c r="AR18" s="216"/>
-      <c r="AS18" s="213"/>
-      <c r="AT18" s="216"/>
-      <c r="AU18" s="214"/>
-      <c r="AV18" s="215"/>
-      <c r="AW18" s="213"/>
-    </row>
-    <row r="19" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="183"/>
-      <c r="D19" s="183"/>
-      <c r="E19" s="184"/>
-      <c r="F19" s="193"/>
-      <c r="G19" s="194"/>
-      <c r="H19" s="195"/>
-      <c r="I19" s="194"/>
-      <c r="J19" s="196"/>
-      <c r="K19" s="193"/>
-      <c r="L19" s="196"/>
-      <c r="M19" s="193"/>
-      <c r="N19" s="196"/>
-      <c r="O19" s="193"/>
-      <c r="P19" s="196"/>
-      <c r="Q19" s="194"/>
-      <c r="R19" s="195"/>
-      <c r="S19" s="193"/>
-      <c r="T19" s="196"/>
-      <c r="U19" s="193"/>
-      <c r="V19" s="196"/>
-      <c r="W19" s="193"/>
-      <c r="X19" s="196"/>
-      <c r="Y19" s="193"/>
-      <c r="Z19" s="196"/>
-      <c r="AA19" s="194"/>
-      <c r="AB19" s="195"/>
-      <c r="AC19" s="193"/>
-      <c r="AD19" s="196"/>
-      <c r="AE19" s="193"/>
-      <c r="AF19" s="196"/>
-      <c r="AG19" s="193"/>
-      <c r="AH19" s="196"/>
-      <c r="AI19" s="193"/>
-      <c r="AJ19" s="196"/>
-      <c r="AK19" s="194"/>
-      <c r="AL19" s="195"/>
-      <c r="AM19" s="193"/>
-      <c r="AN19" s="196"/>
-      <c r="AO19" s="193"/>
-      <c r="AP19" s="196"/>
-      <c r="AQ19" s="193"/>
-      <c r="AR19" s="196"/>
-      <c r="AS19" s="193"/>
-      <c r="AT19" s="196"/>
-      <c r="AU19" s="194"/>
-      <c r="AV19" s="195"/>
-      <c r="AW19" s="193"/>
-    </row>
-    <row r="20" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20">
-        <f>B18+$A$8</f>
+      <c r="D21" s="213"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="114"/>
+      <c r="M21" s="111"/>
+      <c r="N21" s="114"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="114"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="111"/>
+      <c r="T21" s="114"/>
+      <c r="U21" s="111"/>
+      <c r="V21" s="114"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="114"/>
+      <c r="Y21" s="111"/>
+      <c r="Z21" s="114"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="113"/>
+      <c r="AC21" s="111"/>
+      <c r="AD21" s="114"/>
+      <c r="AE21" s="111"/>
+      <c r="AF21" s="114"/>
+      <c r="AG21" s="111"/>
+      <c r="AH21" s="114"/>
+      <c r="AI21" s="111"/>
+      <c r="AJ21" s="114"/>
+      <c r="AK21" s="112"/>
+      <c r="AL21" s="113"/>
+      <c r="AM21" s="111"/>
+      <c r="AN21" s="114"/>
+      <c r="AO21" s="111"/>
+      <c r="AP21" s="114"/>
+      <c r="AQ21" s="111"/>
+      <c r="AR21" s="114"/>
+      <c r="AS21" s="111"/>
+      <c r="AT21" s="114"/>
+      <c r="AU21" s="112"/>
+      <c r="AV21" s="113"/>
+      <c r="AW21" s="111"/>
+    </row>
+    <row r="22" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="213"/>
+      <c r="D22" s="213"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="93"/>
+      <c r="S22" s="91"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="91"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="91"/>
+      <c r="X22" s="94"/>
+      <c r="Y22" s="91"/>
+      <c r="Z22" s="94"/>
+      <c r="AA22" s="92"/>
+      <c r="AB22" s="93"/>
+      <c r="AC22" s="91"/>
+      <c r="AD22" s="94"/>
+      <c r="AE22" s="91"/>
+      <c r="AF22" s="94"/>
+      <c r="AG22" s="91"/>
+      <c r="AH22" s="94"/>
+      <c r="AI22" s="91"/>
+      <c r="AJ22" s="94"/>
+      <c r="AK22" s="92"/>
+      <c r="AL22" s="93"/>
+      <c r="AM22" s="91"/>
+      <c r="AN22" s="94"/>
+      <c r="AO22" s="91"/>
+      <c r="AP22" s="94"/>
+      <c r="AQ22" s="91"/>
+      <c r="AR22" s="94"/>
+      <c r="AS22" s="91"/>
+      <c r="AT22" s="94"/>
+      <c r="AU22" s="92"/>
+      <c r="AV22" s="93"/>
+      <c r="AW22" s="91"/>
+    </row>
+    <row r="23" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f>B21+$A$11</f>
         <v>120</v>
       </c>
-      <c r="C20" s="183" t="str">
-        <f>CONCATENATE(B20,"°")</f>
+      <c r="C23" s="213" t="str">
+        <f>CONCATENATE(B23,"°")</f>
         <v>120°</v>
       </c>
-      <c r="D20" s="183"/>
-      <c r="E20" s="184"/>
-      <c r="F20" s="205"/>
-      <c r="G20" s="206"/>
-      <c r="H20" s="207"/>
-      <c r="I20" s="206"/>
-      <c r="J20" s="208"/>
-      <c r="K20" s="205"/>
-      <c r="L20" s="208"/>
-      <c r="M20" s="205"/>
-      <c r="N20" s="208"/>
-      <c r="O20" s="205"/>
-      <c r="P20" s="208"/>
-      <c r="Q20" s="206"/>
-      <c r="R20" s="207"/>
-      <c r="S20" s="205"/>
-      <c r="T20" s="208"/>
-      <c r="U20" s="205"/>
-      <c r="V20" s="208"/>
-      <c r="W20" s="205"/>
-      <c r="X20" s="208"/>
-      <c r="Y20" s="205"/>
-      <c r="Z20" s="208"/>
-      <c r="AA20" s="206"/>
-      <c r="AB20" s="207"/>
-      <c r="AC20" s="205"/>
-      <c r="AD20" s="208"/>
-      <c r="AE20" s="205"/>
-      <c r="AF20" s="208"/>
-      <c r="AG20" s="205"/>
-      <c r="AH20" s="208"/>
-      <c r="AI20" s="205"/>
-      <c r="AJ20" s="208"/>
-      <c r="AK20" s="206"/>
-      <c r="AL20" s="207"/>
-      <c r="AM20" s="205"/>
-      <c r="AN20" s="208"/>
-      <c r="AO20" s="205"/>
-      <c r="AP20" s="208"/>
-      <c r="AQ20" s="205"/>
-      <c r="AR20" s="208"/>
-      <c r="AS20" s="205"/>
-      <c r="AT20" s="208"/>
-      <c r="AU20" s="206"/>
-      <c r="AV20" s="207"/>
-      <c r="AW20" s="205"/>
-    </row>
-    <row r="21" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="183"/>
-      <c r="D21" s="183"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="201"/>
-      <c r="G21" s="202"/>
-      <c r="H21" s="203"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="204"/>
-      <c r="K21" s="201"/>
-      <c r="L21" s="204"/>
-      <c r="M21" s="201"/>
-      <c r="N21" s="204"/>
-      <c r="O21" s="201"/>
-      <c r="P21" s="204"/>
-      <c r="Q21" s="202"/>
-      <c r="R21" s="203"/>
-      <c r="S21" s="201"/>
-      <c r="T21" s="204"/>
-      <c r="U21" s="201"/>
-      <c r="V21" s="204"/>
-      <c r="W21" s="201"/>
-      <c r="X21" s="204"/>
-      <c r="Y21" s="201"/>
-      <c r="Z21" s="204"/>
-      <c r="AA21" s="202"/>
-      <c r="AB21" s="203"/>
-      <c r="AC21" s="201"/>
-      <c r="AD21" s="204"/>
-      <c r="AE21" s="201"/>
-      <c r="AF21" s="204"/>
-      <c r="AG21" s="201"/>
-      <c r="AH21" s="204"/>
-      <c r="AI21" s="201"/>
-      <c r="AJ21" s="204"/>
-      <c r="AK21" s="202"/>
-      <c r="AL21" s="203"/>
-      <c r="AM21" s="201"/>
-      <c r="AN21" s="204"/>
-      <c r="AO21" s="201"/>
-      <c r="AP21" s="204"/>
-      <c r="AQ21" s="201"/>
-      <c r="AR21" s="204"/>
-      <c r="AS21" s="201"/>
-      <c r="AT21" s="204"/>
-      <c r="AU21" s="202"/>
-      <c r="AV21" s="203"/>
-      <c r="AW21" s="201"/>
-    </row>
-    <row r="22" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <f>B20+$A$8</f>
+      <c r="D23" s="213"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="103"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="106"/>
+      <c r="O23" s="103"/>
+      <c r="P23" s="106"/>
+      <c r="Q23" s="104"/>
+      <c r="R23" s="105"/>
+      <c r="S23" s="103"/>
+      <c r="T23" s="106"/>
+      <c r="U23" s="103"/>
+      <c r="V23" s="106"/>
+      <c r="W23" s="103"/>
+      <c r="X23" s="106"/>
+      <c r="Y23" s="103"/>
+      <c r="Z23" s="106"/>
+      <c r="AA23" s="104"/>
+      <c r="AB23" s="105"/>
+      <c r="AC23" s="103"/>
+      <c r="AD23" s="106"/>
+      <c r="AE23" s="103"/>
+      <c r="AF23" s="106"/>
+      <c r="AG23" s="103"/>
+      <c r="AH23" s="106"/>
+      <c r="AI23" s="103"/>
+      <c r="AJ23" s="106"/>
+      <c r="AK23" s="104"/>
+      <c r="AL23" s="105"/>
+      <c r="AM23" s="103"/>
+      <c r="AN23" s="106"/>
+      <c r="AO23" s="103"/>
+      <c r="AP23" s="106"/>
+      <c r="AQ23" s="103"/>
+      <c r="AR23" s="106"/>
+      <c r="AS23" s="103"/>
+      <c r="AT23" s="106"/>
+      <c r="AU23" s="104"/>
+      <c r="AV23" s="105"/>
+      <c r="AW23" s="103"/>
+    </row>
+    <row r="24" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="213"/>
+      <c r="D24" s="213"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="99"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="99"/>
+      <c r="N24" s="102"/>
+      <c r="O24" s="99"/>
+      <c r="P24" s="102"/>
+      <c r="Q24" s="100"/>
+      <c r="R24" s="101"/>
+      <c r="S24" s="99"/>
+      <c r="T24" s="102"/>
+      <c r="U24" s="99"/>
+      <c r="V24" s="102"/>
+      <c r="W24" s="99"/>
+      <c r="X24" s="102"/>
+      <c r="Y24" s="99"/>
+      <c r="Z24" s="102"/>
+      <c r="AA24" s="100"/>
+      <c r="AB24" s="101"/>
+      <c r="AC24" s="99"/>
+      <c r="AD24" s="102"/>
+      <c r="AE24" s="99"/>
+      <c r="AF24" s="102"/>
+      <c r="AG24" s="99"/>
+      <c r="AH24" s="102"/>
+      <c r="AI24" s="99"/>
+      <c r="AJ24" s="102"/>
+      <c r="AK24" s="100"/>
+      <c r="AL24" s="101"/>
+      <c r="AM24" s="99"/>
+      <c r="AN24" s="102"/>
+      <c r="AO24" s="99"/>
+      <c r="AP24" s="102"/>
+      <c r="AQ24" s="99"/>
+      <c r="AR24" s="102"/>
+      <c r="AS24" s="99"/>
+      <c r="AT24" s="102"/>
+      <c r="AU24" s="100"/>
+      <c r="AV24" s="101"/>
+      <c r="AW24" s="99"/>
+    </row>
+    <row r="25" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <f>B23+$A$11</f>
         <v>140</v>
       </c>
-      <c r="C22" s="183" t="str">
-        <f>CONCATENATE(B22,"°")</f>
+      <c r="C25" s="213" t="str">
+        <f>CONCATENATE(B25,"°")</f>
         <v>140°</v>
       </c>
-      <c r="D22" s="183"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="189"/>
-      <c r="G22" s="190"/>
-      <c r="H22" s="191"/>
-      <c r="I22" s="190"/>
-      <c r="J22" s="192"/>
-      <c r="K22" s="189"/>
-      <c r="L22" s="192"/>
-      <c r="M22" s="189"/>
-      <c r="N22" s="192"/>
-      <c r="O22" s="189"/>
-      <c r="P22" s="192"/>
-      <c r="Q22" s="190"/>
-      <c r="R22" s="191"/>
-      <c r="S22" s="189"/>
-      <c r="T22" s="192"/>
-      <c r="U22" s="189"/>
-      <c r="V22" s="192"/>
-      <c r="W22" s="189"/>
-      <c r="X22" s="192"/>
-      <c r="Y22" s="189"/>
-      <c r="Z22" s="192"/>
-      <c r="AA22" s="190"/>
-      <c r="AB22" s="191"/>
-      <c r="AC22" s="189"/>
-      <c r="AD22" s="192"/>
-      <c r="AE22" s="189"/>
-      <c r="AF22" s="192"/>
-      <c r="AG22" s="189"/>
-      <c r="AH22" s="192"/>
-      <c r="AI22" s="189"/>
-      <c r="AJ22" s="192"/>
-      <c r="AK22" s="190"/>
-      <c r="AL22" s="191"/>
-      <c r="AM22" s="189"/>
-      <c r="AN22" s="192"/>
-      <c r="AO22" s="189"/>
-      <c r="AP22" s="192"/>
-      <c r="AQ22" s="189"/>
-      <c r="AR22" s="192"/>
-      <c r="AS22" s="189"/>
-      <c r="AT22" s="192"/>
-      <c r="AU22" s="190"/>
-      <c r="AV22" s="191"/>
-      <c r="AW22" s="189"/>
-    </row>
-    <row r="23" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="183"/>
-      <c r="D23" s="183"/>
-      <c r="E23" s="184"/>
-      <c r="F23" s="205"/>
-      <c r="G23" s="206"/>
-      <c r="H23" s="207"/>
-      <c r="I23" s="206"/>
-      <c r="J23" s="208"/>
-      <c r="K23" s="205"/>
-      <c r="L23" s="208"/>
-      <c r="M23" s="205"/>
-      <c r="N23" s="208"/>
-      <c r="O23" s="205"/>
-      <c r="P23" s="208"/>
-      <c r="Q23" s="206"/>
-      <c r="R23" s="207"/>
-      <c r="S23" s="205"/>
-      <c r="T23" s="208"/>
-      <c r="U23" s="205"/>
-      <c r="V23" s="208"/>
-      <c r="W23" s="205"/>
-      <c r="X23" s="208"/>
-      <c r="Y23" s="205"/>
-      <c r="Z23" s="208"/>
-      <c r="AA23" s="206"/>
-      <c r="AB23" s="207"/>
-      <c r="AC23" s="205"/>
-      <c r="AD23" s="208"/>
-      <c r="AE23" s="205"/>
-      <c r="AF23" s="208"/>
-      <c r="AG23" s="205"/>
-      <c r="AH23" s="208"/>
-      <c r="AI23" s="205"/>
-      <c r="AJ23" s="208"/>
-      <c r="AK23" s="206"/>
-      <c r="AL23" s="207"/>
-      <c r="AM23" s="205"/>
-      <c r="AN23" s="208"/>
-      <c r="AO23" s="205"/>
-      <c r="AP23" s="208"/>
-      <c r="AQ23" s="205"/>
-      <c r="AR23" s="208"/>
-      <c r="AS23" s="205"/>
-      <c r="AT23" s="208"/>
-      <c r="AU23" s="206"/>
-      <c r="AV23" s="207"/>
-      <c r="AW23" s="205"/>
-    </row>
-    <row r="24" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <f>B22+$A$8</f>
+      <c r="D25" s="213"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="87"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="87"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="87"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="90"/>
+      <c r="U25" s="87"/>
+      <c r="V25" s="90"/>
+      <c r="W25" s="87"/>
+      <c r="X25" s="90"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="90"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="89"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="90"/>
+      <c r="AE25" s="87"/>
+      <c r="AF25" s="90"/>
+      <c r="AG25" s="87"/>
+      <c r="AH25" s="90"/>
+      <c r="AI25" s="87"/>
+      <c r="AJ25" s="90"/>
+      <c r="AK25" s="88"/>
+      <c r="AL25" s="89"/>
+      <c r="AM25" s="87"/>
+      <c r="AN25" s="90"/>
+      <c r="AO25" s="87"/>
+      <c r="AP25" s="90"/>
+      <c r="AQ25" s="87"/>
+      <c r="AR25" s="90"/>
+      <c r="AS25" s="87"/>
+      <c r="AT25" s="90"/>
+      <c r="AU25" s="88"/>
+      <c r="AV25" s="89"/>
+      <c r="AW25" s="87"/>
+    </row>
+    <row r="26" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="213"/>
+      <c r="D26" s="213"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="106"/>
+      <c r="O26" s="103"/>
+      <c r="P26" s="106"/>
+      <c r="Q26" s="104"/>
+      <c r="R26" s="105"/>
+      <c r="S26" s="103"/>
+      <c r="T26" s="106"/>
+      <c r="U26" s="103"/>
+      <c r="V26" s="106"/>
+      <c r="W26" s="103"/>
+      <c r="X26" s="106"/>
+      <c r="Y26" s="103"/>
+      <c r="Z26" s="106"/>
+      <c r="AA26" s="104"/>
+      <c r="AB26" s="105"/>
+      <c r="AC26" s="103"/>
+      <c r="AD26" s="106"/>
+      <c r="AE26" s="103"/>
+      <c r="AF26" s="106"/>
+      <c r="AG26" s="103"/>
+      <c r="AH26" s="106"/>
+      <c r="AI26" s="103"/>
+      <c r="AJ26" s="106"/>
+      <c r="AK26" s="104"/>
+      <c r="AL26" s="105"/>
+      <c r="AM26" s="103"/>
+      <c r="AN26" s="106"/>
+      <c r="AO26" s="103"/>
+      <c r="AP26" s="106"/>
+      <c r="AQ26" s="103"/>
+      <c r="AR26" s="106"/>
+      <c r="AS26" s="103"/>
+      <c r="AT26" s="106"/>
+      <c r="AU26" s="104"/>
+      <c r="AV26" s="105"/>
+      <c r="AW26" s="103"/>
+    </row>
+    <row r="27" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <f>B25+$A$11</f>
         <v>160</v>
       </c>
-      <c r="C24" s="183" t="str">
-        <f>CONCATENATE(B24,"°")</f>
+      <c r="C27" s="213" t="str">
+        <f>CONCATENATE(B27,"°")</f>
         <v>160°</v>
       </c>
-      <c r="D24" s="183"/>
-      <c r="E24" s="184"/>
-      <c r="F24" s="205"/>
-      <c r="G24" s="206"/>
-      <c r="H24" s="207"/>
-      <c r="I24" s="206"/>
-      <c r="J24" s="208"/>
-      <c r="K24" s="205"/>
-      <c r="L24" s="208"/>
-      <c r="M24" s="205"/>
-      <c r="N24" s="208"/>
-      <c r="O24" s="205"/>
-      <c r="P24" s="208"/>
-      <c r="Q24" s="206"/>
-      <c r="R24" s="207"/>
-      <c r="S24" s="205"/>
-      <c r="T24" s="208"/>
-      <c r="U24" s="205"/>
-      <c r="V24" s="208"/>
-      <c r="W24" s="205"/>
-      <c r="X24" s="208"/>
-      <c r="Y24" s="205"/>
-      <c r="Z24" s="208"/>
-      <c r="AA24" s="206"/>
-      <c r="AB24" s="207"/>
-      <c r="AC24" s="205"/>
-      <c r="AD24" s="208"/>
-      <c r="AE24" s="205"/>
-      <c r="AF24" s="208"/>
-      <c r="AG24" s="205"/>
-      <c r="AH24" s="208"/>
-      <c r="AI24" s="205"/>
-      <c r="AJ24" s="208"/>
-      <c r="AK24" s="206"/>
-      <c r="AL24" s="207"/>
-      <c r="AM24" s="205"/>
-      <c r="AN24" s="208"/>
-      <c r="AO24" s="205"/>
-      <c r="AP24" s="208"/>
-      <c r="AQ24" s="205"/>
-      <c r="AR24" s="208"/>
-      <c r="AS24" s="205"/>
-      <c r="AT24" s="208"/>
-      <c r="AU24" s="206"/>
-      <c r="AV24" s="207"/>
-      <c r="AW24" s="205"/>
-    </row>
-    <row r="25" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="183"/>
-      <c r="D25" s="183"/>
-      <c r="E25" s="184"/>
-      <c r="F25" s="201"/>
-      <c r="G25" s="202"/>
-      <c r="H25" s="203"/>
-      <c r="I25" s="202"/>
-      <c r="J25" s="204"/>
-      <c r="K25" s="201"/>
-      <c r="L25" s="204"/>
-      <c r="M25" s="201"/>
-      <c r="N25" s="204"/>
-      <c r="O25" s="201"/>
-      <c r="P25" s="204"/>
-      <c r="Q25" s="202"/>
-      <c r="R25" s="203"/>
-      <c r="S25" s="201"/>
-      <c r="T25" s="204"/>
-      <c r="U25" s="201"/>
-      <c r="V25" s="204"/>
-      <c r="W25" s="201"/>
-      <c r="X25" s="204"/>
-      <c r="Y25" s="201"/>
-      <c r="Z25" s="204"/>
-      <c r="AA25" s="202"/>
-      <c r="AB25" s="203"/>
-      <c r="AC25" s="201"/>
-      <c r="AD25" s="204"/>
-      <c r="AE25" s="201"/>
-      <c r="AF25" s="204"/>
-      <c r="AG25" s="201"/>
-      <c r="AH25" s="204"/>
-      <c r="AI25" s="201"/>
-      <c r="AJ25" s="204"/>
-      <c r="AK25" s="202"/>
-      <c r="AL25" s="203"/>
-      <c r="AM25" s="201"/>
-      <c r="AN25" s="204"/>
-      <c r="AO25" s="201"/>
-      <c r="AP25" s="204"/>
-      <c r="AQ25" s="201"/>
-      <c r="AR25" s="204"/>
-      <c r="AS25" s="201"/>
-      <c r="AT25" s="204"/>
-      <c r="AU25" s="202"/>
-      <c r="AV25" s="203"/>
-      <c r="AW25" s="201"/>
-    </row>
-    <row r="26" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26">
-        <f>B24+$A$8</f>
+      <c r="D27" s="213"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="106"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="103"/>
+      <c r="P27" s="106"/>
+      <c r="Q27" s="104"/>
+      <c r="R27" s="105"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="106"/>
+      <c r="U27" s="103"/>
+      <c r="V27" s="106"/>
+      <c r="W27" s="103"/>
+      <c r="X27" s="106"/>
+      <c r="Y27" s="103"/>
+      <c r="Z27" s="106"/>
+      <c r="AA27" s="104"/>
+      <c r="AB27" s="105"/>
+      <c r="AC27" s="103"/>
+      <c r="AD27" s="106"/>
+      <c r="AE27" s="103"/>
+      <c r="AF27" s="106"/>
+      <c r="AG27" s="103"/>
+      <c r="AH27" s="106"/>
+      <c r="AI27" s="103"/>
+      <c r="AJ27" s="106"/>
+      <c r="AK27" s="104"/>
+      <c r="AL27" s="105"/>
+      <c r="AM27" s="103"/>
+      <c r="AN27" s="106"/>
+      <c r="AO27" s="103"/>
+      <c r="AP27" s="106"/>
+      <c r="AQ27" s="103"/>
+      <c r="AR27" s="106"/>
+      <c r="AS27" s="103"/>
+      <c r="AT27" s="106"/>
+      <c r="AU27" s="104"/>
+      <c r="AV27" s="105"/>
+      <c r="AW27" s="103"/>
+    </row>
+    <row r="28" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="213"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="100"/>
+      <c r="H28" s="101"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="99"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="99"/>
+      <c r="N28" s="102"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="102"/>
+      <c r="Q28" s="100"/>
+      <c r="R28" s="101"/>
+      <c r="S28" s="99"/>
+      <c r="T28" s="102"/>
+      <c r="U28" s="99"/>
+      <c r="V28" s="102"/>
+      <c r="W28" s="99"/>
+      <c r="X28" s="102"/>
+      <c r="Y28" s="99"/>
+      <c r="Z28" s="102"/>
+      <c r="AA28" s="100"/>
+      <c r="AB28" s="101"/>
+      <c r="AC28" s="99"/>
+      <c r="AD28" s="102"/>
+      <c r="AE28" s="99"/>
+      <c r="AF28" s="102"/>
+      <c r="AG28" s="99"/>
+      <c r="AH28" s="102"/>
+      <c r="AI28" s="99"/>
+      <c r="AJ28" s="102"/>
+      <c r="AK28" s="100"/>
+      <c r="AL28" s="101"/>
+      <c r="AM28" s="99"/>
+      <c r="AN28" s="102"/>
+      <c r="AO28" s="99"/>
+      <c r="AP28" s="102"/>
+      <c r="AQ28" s="99"/>
+      <c r="AR28" s="102"/>
+      <c r="AS28" s="99"/>
+      <c r="AT28" s="102"/>
+      <c r="AU28" s="100"/>
+      <c r="AV28" s="101"/>
+      <c r="AW28" s="99"/>
+    </row>
+    <row r="29" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <f>B27+$A$11</f>
         <v>180</v>
       </c>
-      <c r="C26" s="183" t="str">
-        <f>CONCATENATE(B26,"°")</f>
+      <c r="C29" s="213" t="str">
+        <f>CONCATENATE(B29,"°")</f>
         <v>180°</v>
       </c>
-      <c r="D26" s="183"/>
-      <c r="E26" s="184"/>
-      <c r="F26" s="197"/>
-      <c r="G26" s="198"/>
-      <c r="H26" s="199"/>
-      <c r="I26" s="198"/>
-      <c r="J26" s="200"/>
-      <c r="K26" s="197"/>
-      <c r="L26" s="200"/>
-      <c r="M26" s="197"/>
-      <c r="N26" s="200"/>
-      <c r="O26" s="197"/>
-      <c r="P26" s="200"/>
-      <c r="Q26" s="198"/>
-      <c r="R26" s="199"/>
-      <c r="S26" s="197"/>
-      <c r="T26" s="200"/>
-      <c r="U26" s="197"/>
-      <c r="V26" s="200"/>
-      <c r="W26" s="197"/>
-      <c r="X26" s="200"/>
-      <c r="Y26" s="197"/>
-      <c r="Z26" s="200"/>
-      <c r="AA26" s="198"/>
-      <c r="AB26" s="199"/>
-      <c r="AC26" s="197"/>
-      <c r="AD26" s="200"/>
-      <c r="AE26" s="197"/>
-      <c r="AF26" s="200"/>
-      <c r="AG26" s="197"/>
-      <c r="AH26" s="200"/>
-      <c r="AI26" s="197"/>
-      <c r="AJ26" s="200"/>
-      <c r="AK26" s="198"/>
-      <c r="AL26" s="199"/>
-      <c r="AM26" s="197"/>
-      <c r="AN26" s="200"/>
-      <c r="AO26" s="197"/>
-      <c r="AP26" s="200"/>
-      <c r="AQ26" s="197"/>
-      <c r="AR26" s="200"/>
-      <c r="AS26" s="197"/>
-      <c r="AT26" s="200"/>
-      <c r="AU26" s="198"/>
-      <c r="AV26" s="199"/>
-      <c r="AW26" s="197"/>
-    </row>
-    <row r="27" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="183"/>
-      <c r="D27" s="183"/>
-      <c r="E27" s="184"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="186"/>
-      <c r="H27" s="187"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="188"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="188"/>
-      <c r="M27" s="185"/>
-      <c r="N27" s="188"/>
-      <c r="O27" s="185"/>
-      <c r="P27" s="188"/>
-      <c r="Q27" s="186"/>
-      <c r="R27" s="187"/>
-      <c r="S27" s="185"/>
-      <c r="T27" s="188"/>
-      <c r="U27" s="185"/>
-      <c r="V27" s="188"/>
-      <c r="W27" s="185"/>
-      <c r="X27" s="188"/>
-      <c r="Y27" s="185"/>
-      <c r="Z27" s="188"/>
-      <c r="AA27" s="186"/>
-      <c r="AB27" s="187"/>
-      <c r="AC27" s="185"/>
-      <c r="AD27" s="188"/>
-      <c r="AE27" s="185"/>
-      <c r="AF27" s="188"/>
-      <c r="AG27" s="185"/>
-      <c r="AH27" s="188"/>
-      <c r="AI27" s="185"/>
-      <c r="AJ27" s="188"/>
-      <c r="AK27" s="186"/>
-      <c r="AL27" s="187"/>
-      <c r="AM27" s="185"/>
-      <c r="AN27" s="188"/>
-      <c r="AO27" s="185"/>
-      <c r="AP27" s="188"/>
-      <c r="AQ27" s="185"/>
-      <c r="AR27" s="188"/>
-      <c r="AS27" s="185"/>
-      <c r="AT27" s="188"/>
-      <c r="AU27" s="186"/>
-      <c r="AV27" s="187"/>
-      <c r="AW27" s="185"/>
-    </row>
-    <row r="28" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28">
-        <f>B26+$A$8</f>
+      <c r="D29" s="213"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="97"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="95"/>
+      <c r="N29" s="98"/>
+      <c r="O29" s="95"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="97"/>
+      <c r="S29" s="95"/>
+      <c r="T29" s="98"/>
+      <c r="U29" s="95"/>
+      <c r="V29" s="98"/>
+      <c r="W29" s="95"/>
+      <c r="X29" s="98"/>
+      <c r="Y29" s="95"/>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="96"/>
+      <c r="AB29" s="97"/>
+      <c r="AC29" s="95"/>
+      <c r="AD29" s="98"/>
+      <c r="AE29" s="95"/>
+      <c r="AF29" s="98"/>
+      <c r="AG29" s="95"/>
+      <c r="AH29" s="98"/>
+      <c r="AI29" s="95"/>
+      <c r="AJ29" s="98"/>
+      <c r="AK29" s="96"/>
+      <c r="AL29" s="97"/>
+      <c r="AM29" s="95"/>
+      <c r="AN29" s="98"/>
+      <c r="AO29" s="95"/>
+      <c r="AP29" s="98"/>
+      <c r="AQ29" s="95"/>
+      <c r="AR29" s="98"/>
+      <c r="AS29" s="95"/>
+      <c r="AT29" s="98"/>
+      <c r="AU29" s="96"/>
+      <c r="AV29" s="97"/>
+      <c r="AW29" s="95"/>
+    </row>
+    <row r="30" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="213"/>
+      <c r="D30" s="213"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="85"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="83"/>
+      <c r="L30" s="86"/>
+      <c r="M30" s="83"/>
+      <c r="N30" s="86"/>
+      <c r="O30" s="83"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="84"/>
+      <c r="R30" s="85"/>
+      <c r="S30" s="83"/>
+      <c r="T30" s="86"/>
+      <c r="U30" s="83"/>
+      <c r="V30" s="86"/>
+      <c r="W30" s="83"/>
+      <c r="X30" s="86"/>
+      <c r="Y30" s="83"/>
+      <c r="Z30" s="86"/>
+      <c r="AA30" s="84"/>
+      <c r="AB30" s="85"/>
+      <c r="AC30" s="83"/>
+      <c r="AD30" s="86"/>
+      <c r="AE30" s="83"/>
+      <c r="AF30" s="86"/>
+      <c r="AG30" s="83"/>
+      <c r="AH30" s="86"/>
+      <c r="AI30" s="83"/>
+      <c r="AJ30" s="86"/>
+      <c r="AK30" s="84"/>
+      <c r="AL30" s="85"/>
+      <c r="AM30" s="83"/>
+      <c r="AN30" s="86"/>
+      <c r="AO30" s="83"/>
+      <c r="AP30" s="86"/>
+      <c r="AQ30" s="83"/>
+      <c r="AR30" s="86"/>
+      <c r="AS30" s="83"/>
+      <c r="AT30" s="86"/>
+      <c r="AU30" s="84"/>
+      <c r="AV30" s="85"/>
+      <c r="AW30" s="83"/>
+    </row>
+    <row r="31" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <f>B29+$A$11</f>
         <v>200</v>
       </c>
-      <c r="C28" s="183" t="str">
-        <f>CONCATENATE(B28,"°")</f>
+      <c r="C31" s="213" t="str">
+        <f>CONCATENATE(B31,"°")</f>
         <v>200°</v>
       </c>
-      <c r="D28" s="183"/>
-      <c r="E28" s="184"/>
-      <c r="F28" s="205"/>
-      <c r="G28" s="206"/>
-      <c r="H28" s="207"/>
-      <c r="I28" s="206"/>
-      <c r="J28" s="208"/>
-      <c r="K28" s="205"/>
-      <c r="L28" s="208"/>
-      <c r="M28" s="205"/>
-      <c r="N28" s="208"/>
-      <c r="O28" s="205"/>
-      <c r="P28" s="208"/>
-      <c r="Q28" s="206"/>
-      <c r="R28" s="207"/>
-      <c r="S28" s="205"/>
-      <c r="T28" s="208"/>
-      <c r="U28" s="205"/>
-      <c r="V28" s="208"/>
-      <c r="W28" s="205"/>
-      <c r="X28" s="208"/>
-      <c r="Y28" s="205"/>
-      <c r="Z28" s="208"/>
-      <c r="AA28" s="206"/>
-      <c r="AB28" s="207"/>
-      <c r="AC28" s="205"/>
-      <c r="AD28" s="208"/>
-      <c r="AE28" s="205"/>
-      <c r="AF28" s="208"/>
-      <c r="AG28" s="205"/>
-      <c r="AH28" s="208"/>
-      <c r="AI28" s="205"/>
-      <c r="AJ28" s="208"/>
-      <c r="AK28" s="206"/>
-      <c r="AL28" s="207"/>
-      <c r="AM28" s="205"/>
-      <c r="AN28" s="208"/>
-      <c r="AO28" s="205"/>
-      <c r="AP28" s="208"/>
-      <c r="AQ28" s="205"/>
-      <c r="AR28" s="208"/>
-      <c r="AS28" s="205"/>
-      <c r="AT28" s="208"/>
-      <c r="AU28" s="206"/>
-      <c r="AV28" s="207"/>
-      <c r="AW28" s="205"/>
-    </row>
-    <row r="29" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="183"/>
-      <c r="D29" s="183"/>
-      <c r="E29" s="184"/>
-      <c r="F29" s="201"/>
-      <c r="G29" s="202"/>
-      <c r="H29" s="203"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="204"/>
-      <c r="K29" s="201"/>
-      <c r="L29" s="204"/>
-      <c r="M29" s="201"/>
-      <c r="N29" s="204"/>
-      <c r="O29" s="201"/>
-      <c r="P29" s="204"/>
-      <c r="Q29" s="202"/>
-      <c r="R29" s="203"/>
-      <c r="S29" s="201"/>
-      <c r="T29" s="204"/>
-      <c r="U29" s="201"/>
-      <c r="V29" s="204"/>
-      <c r="W29" s="201"/>
-      <c r="X29" s="204"/>
-      <c r="Y29" s="201"/>
-      <c r="Z29" s="204"/>
-      <c r="AA29" s="202"/>
-      <c r="AB29" s="203"/>
-      <c r="AC29" s="201"/>
-      <c r="AD29" s="204"/>
-      <c r="AE29" s="201"/>
-      <c r="AF29" s="204"/>
-      <c r="AG29" s="201"/>
-      <c r="AH29" s="204"/>
-      <c r="AI29" s="201"/>
-      <c r="AJ29" s="204"/>
-      <c r="AK29" s="202"/>
-      <c r="AL29" s="203"/>
-      <c r="AM29" s="201"/>
-      <c r="AN29" s="204"/>
-      <c r="AO29" s="201"/>
-      <c r="AP29" s="204"/>
-      <c r="AQ29" s="201"/>
-      <c r="AR29" s="204"/>
-      <c r="AS29" s="201"/>
-      <c r="AT29" s="204"/>
-      <c r="AU29" s="202"/>
-      <c r="AV29" s="203"/>
-      <c r="AW29" s="201"/>
-    </row>
-    <row r="30" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30">
-        <f>B28+$A$8</f>
+      <c r="D31" s="213"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="103"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="103"/>
+      <c r="L31" s="106"/>
+      <c r="M31" s="103"/>
+      <c r="N31" s="106"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="106"/>
+      <c r="Q31" s="104"/>
+      <c r="R31" s="105"/>
+      <c r="S31" s="103"/>
+      <c r="T31" s="106"/>
+      <c r="U31" s="103"/>
+      <c r="V31" s="106"/>
+      <c r="W31" s="103"/>
+      <c r="X31" s="106"/>
+      <c r="Y31" s="103"/>
+      <c r="Z31" s="106"/>
+      <c r="AA31" s="104"/>
+      <c r="AB31" s="105"/>
+      <c r="AC31" s="103"/>
+      <c r="AD31" s="106"/>
+      <c r="AE31" s="103"/>
+      <c r="AF31" s="106"/>
+      <c r="AG31" s="103"/>
+      <c r="AH31" s="106"/>
+      <c r="AI31" s="103"/>
+      <c r="AJ31" s="106"/>
+      <c r="AK31" s="104"/>
+      <c r="AL31" s="105"/>
+      <c r="AM31" s="103"/>
+      <c r="AN31" s="106"/>
+      <c r="AO31" s="103"/>
+      <c r="AP31" s="106"/>
+      <c r="AQ31" s="103"/>
+      <c r="AR31" s="106"/>
+      <c r="AS31" s="103"/>
+      <c r="AT31" s="106"/>
+      <c r="AU31" s="104"/>
+      <c r="AV31" s="105"/>
+      <c r="AW31" s="103"/>
+    </row>
+    <row r="32" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="100"/>
+      <c r="H32" s="101"/>
+      <c r="I32" s="100"/>
+      <c r="J32" s="102"/>
+      <c r="K32" s="99"/>
+      <c r="L32" s="102"/>
+      <c r="M32" s="99"/>
+      <c r="N32" s="102"/>
+      <c r="O32" s="99"/>
+      <c r="P32" s="102"/>
+      <c r="Q32" s="100"/>
+      <c r="R32" s="101"/>
+      <c r="S32" s="99"/>
+      <c r="T32" s="102"/>
+      <c r="U32" s="99"/>
+      <c r="V32" s="102"/>
+      <c r="W32" s="99"/>
+      <c r="X32" s="102"/>
+      <c r="Y32" s="99"/>
+      <c r="Z32" s="102"/>
+      <c r="AA32" s="100"/>
+      <c r="AB32" s="101"/>
+      <c r="AC32" s="99"/>
+      <c r="AD32" s="102"/>
+      <c r="AE32" s="99"/>
+      <c r="AF32" s="102"/>
+      <c r="AG32" s="99"/>
+      <c r="AH32" s="102"/>
+      <c r="AI32" s="99"/>
+      <c r="AJ32" s="102"/>
+      <c r="AK32" s="100"/>
+      <c r="AL32" s="101"/>
+      <c r="AM32" s="99"/>
+      <c r="AN32" s="102"/>
+      <c r="AO32" s="99"/>
+      <c r="AP32" s="102"/>
+      <c r="AQ32" s="99"/>
+      <c r="AR32" s="102"/>
+      <c r="AS32" s="99"/>
+      <c r="AT32" s="102"/>
+      <c r="AU32" s="100"/>
+      <c r="AV32" s="101"/>
+      <c r="AW32" s="99"/>
+    </row>
+    <row r="33" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <f>B31+$A$11</f>
         <v>220</v>
       </c>
-      <c r="C30" s="183" t="str">
-        <f>CONCATENATE(B30,"°")</f>
+      <c r="C33" s="213" t="str">
+        <f>CONCATENATE(B33,"°")</f>
         <v>220°</v>
       </c>
-      <c r="D30" s="183"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="189"/>
-      <c r="G30" s="190"/>
-      <c r="H30" s="191"/>
-      <c r="I30" s="190"/>
-      <c r="J30" s="192"/>
-      <c r="K30" s="189"/>
-      <c r="L30" s="192"/>
-      <c r="M30" s="189"/>
-      <c r="N30" s="192"/>
-      <c r="O30" s="189"/>
-      <c r="P30" s="192"/>
-      <c r="Q30" s="190"/>
-      <c r="R30" s="191"/>
-      <c r="S30" s="189"/>
-      <c r="T30" s="192"/>
-      <c r="U30" s="189"/>
-      <c r="V30" s="192"/>
-      <c r="W30" s="189"/>
-      <c r="X30" s="192"/>
-      <c r="Y30" s="189"/>
-      <c r="Z30" s="192"/>
-      <c r="AA30" s="190"/>
-      <c r="AB30" s="191"/>
-      <c r="AC30" s="189"/>
-      <c r="AD30" s="192"/>
-      <c r="AE30" s="189"/>
-      <c r="AF30" s="192"/>
-      <c r="AG30" s="189"/>
-      <c r="AH30" s="192"/>
-      <c r="AI30" s="189"/>
-      <c r="AJ30" s="192"/>
-      <c r="AK30" s="190"/>
-      <c r="AL30" s="191"/>
-      <c r="AM30" s="189"/>
-      <c r="AN30" s="192"/>
-      <c r="AO30" s="189"/>
-      <c r="AP30" s="192"/>
-      <c r="AQ30" s="189"/>
-      <c r="AR30" s="192"/>
-      <c r="AS30" s="189"/>
-      <c r="AT30" s="192"/>
-      <c r="AU30" s="190"/>
-      <c r="AV30" s="191"/>
-      <c r="AW30" s="189"/>
-    </row>
-    <row r="31" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="183"/>
-      <c r="D31" s="183"/>
-      <c r="E31" s="184"/>
-      <c r="F31" s="205"/>
-      <c r="G31" s="206"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="206"/>
-      <c r="J31" s="208"/>
-      <c r="K31" s="205"/>
-      <c r="L31" s="208"/>
-      <c r="M31" s="205"/>
-      <c r="N31" s="208"/>
-      <c r="O31" s="205"/>
-      <c r="P31" s="208"/>
-      <c r="Q31" s="206"/>
-      <c r="R31" s="207"/>
-      <c r="S31" s="205"/>
-      <c r="T31" s="208"/>
-      <c r="U31" s="205"/>
-      <c r="V31" s="208"/>
-      <c r="W31" s="205"/>
-      <c r="X31" s="208"/>
-      <c r="Y31" s="205"/>
-      <c r="Z31" s="208"/>
-      <c r="AA31" s="206"/>
-      <c r="AB31" s="207"/>
-      <c r="AC31" s="205"/>
-      <c r="AD31" s="208"/>
-      <c r="AE31" s="205"/>
-      <c r="AF31" s="208"/>
-      <c r="AG31" s="205"/>
-      <c r="AH31" s="208"/>
-      <c r="AI31" s="205"/>
-      <c r="AJ31" s="208"/>
-      <c r="AK31" s="206"/>
-      <c r="AL31" s="207"/>
-      <c r="AM31" s="205"/>
-      <c r="AN31" s="208"/>
-      <c r="AO31" s="205"/>
-      <c r="AP31" s="208"/>
-      <c r="AQ31" s="205"/>
-      <c r="AR31" s="208"/>
-      <c r="AS31" s="205"/>
-      <c r="AT31" s="208"/>
-      <c r="AU31" s="206"/>
-      <c r="AV31" s="207"/>
-      <c r="AW31" s="205"/>
-    </row>
-    <row r="32" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32">
-        <f>B30+$A$8</f>
+      <c r="D33" s="213"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="87"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="87"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="87"/>
+      <c r="P33" s="90"/>
+      <c r="Q33" s="88"/>
+      <c r="R33" s="89"/>
+      <c r="S33" s="87"/>
+      <c r="T33" s="90"/>
+      <c r="U33" s="87"/>
+      <c r="V33" s="90"/>
+      <c r="W33" s="87"/>
+      <c r="X33" s="90"/>
+      <c r="Y33" s="87"/>
+      <c r="Z33" s="90"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="89"/>
+      <c r="AC33" s="87"/>
+      <c r="AD33" s="90"/>
+      <c r="AE33" s="87"/>
+      <c r="AF33" s="90"/>
+      <c r="AG33" s="87"/>
+      <c r="AH33" s="90"/>
+      <c r="AI33" s="87"/>
+      <c r="AJ33" s="90"/>
+      <c r="AK33" s="88"/>
+      <c r="AL33" s="89"/>
+      <c r="AM33" s="87"/>
+      <c r="AN33" s="90"/>
+      <c r="AO33" s="87"/>
+      <c r="AP33" s="90"/>
+      <c r="AQ33" s="87"/>
+      <c r="AR33" s="90"/>
+      <c r="AS33" s="87"/>
+      <c r="AT33" s="90"/>
+      <c r="AU33" s="88"/>
+      <c r="AV33" s="89"/>
+      <c r="AW33" s="87"/>
+    </row>
+    <row r="34" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="213"/>
+      <c r="D34" s="213"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="103"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="106"/>
+      <c r="O34" s="103"/>
+      <c r="P34" s="106"/>
+      <c r="Q34" s="104"/>
+      <c r="R34" s="105"/>
+      <c r="S34" s="103"/>
+      <c r="T34" s="106"/>
+      <c r="U34" s="103"/>
+      <c r="V34" s="106"/>
+      <c r="W34" s="103"/>
+      <c r="X34" s="106"/>
+      <c r="Y34" s="103"/>
+      <c r="Z34" s="106"/>
+      <c r="AA34" s="104"/>
+      <c r="AB34" s="105"/>
+      <c r="AC34" s="103"/>
+      <c r="AD34" s="106"/>
+      <c r="AE34" s="103"/>
+      <c r="AF34" s="106"/>
+      <c r="AG34" s="103"/>
+      <c r="AH34" s="106"/>
+      <c r="AI34" s="103"/>
+      <c r="AJ34" s="106"/>
+      <c r="AK34" s="104"/>
+      <c r="AL34" s="105"/>
+      <c r="AM34" s="103"/>
+      <c r="AN34" s="106"/>
+      <c r="AO34" s="103"/>
+      <c r="AP34" s="106"/>
+      <c r="AQ34" s="103"/>
+      <c r="AR34" s="106"/>
+      <c r="AS34" s="103"/>
+      <c r="AT34" s="106"/>
+      <c r="AU34" s="104"/>
+      <c r="AV34" s="105"/>
+      <c r="AW34" s="103"/>
+    </row>
+    <row r="35" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <f>B33+$A$11</f>
         <v>240</v>
       </c>
-      <c r="C32" s="183" t="str">
-        <f>CONCATENATE(B32,"°")</f>
+      <c r="C35" s="213" t="str">
+        <f>CONCATENATE(B35,"°")</f>
         <v>240°</v>
       </c>
-      <c r="D32" s="183"/>
-      <c r="E32" s="184"/>
-      <c r="F32" s="205"/>
-      <c r="G32" s="206"/>
-      <c r="H32" s="207"/>
-      <c r="I32" s="206"/>
-      <c r="J32" s="208"/>
-      <c r="K32" s="205"/>
-      <c r="L32" s="208"/>
-      <c r="M32" s="205"/>
-      <c r="N32" s="208"/>
-      <c r="O32" s="205"/>
-      <c r="P32" s="208"/>
-      <c r="Q32" s="206"/>
-      <c r="R32" s="207"/>
-      <c r="S32" s="205"/>
-      <c r="T32" s="208"/>
-      <c r="U32" s="205"/>
-      <c r="V32" s="208"/>
-      <c r="W32" s="205"/>
-      <c r="X32" s="208"/>
-      <c r="Y32" s="205"/>
-      <c r="Z32" s="208"/>
-      <c r="AA32" s="206"/>
-      <c r="AB32" s="207"/>
-      <c r="AC32" s="205"/>
-      <c r="AD32" s="208"/>
-      <c r="AE32" s="205"/>
-      <c r="AF32" s="208"/>
-      <c r="AG32" s="205"/>
-      <c r="AH32" s="208"/>
-      <c r="AI32" s="205"/>
-      <c r="AJ32" s="208"/>
-      <c r="AK32" s="206"/>
-      <c r="AL32" s="207"/>
-      <c r="AM32" s="205"/>
-      <c r="AN32" s="208"/>
-      <c r="AO32" s="205"/>
-      <c r="AP32" s="208"/>
-      <c r="AQ32" s="205"/>
-      <c r="AR32" s="208"/>
-      <c r="AS32" s="205"/>
-      <c r="AT32" s="208"/>
-      <c r="AU32" s="206"/>
-      <c r="AV32" s="207"/>
-      <c r="AW32" s="205"/>
-    </row>
-    <row r="33" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="183"/>
-      <c r="D33" s="183"/>
-      <c r="E33" s="184"/>
-      <c r="F33" s="201"/>
-      <c r="G33" s="202"/>
-      <c r="H33" s="203"/>
-      <c r="I33" s="202"/>
-      <c r="J33" s="204"/>
-      <c r="K33" s="201"/>
-      <c r="L33" s="204"/>
-      <c r="M33" s="201"/>
-      <c r="N33" s="204"/>
-      <c r="O33" s="201"/>
-      <c r="P33" s="204"/>
-      <c r="Q33" s="202"/>
-      <c r="R33" s="203"/>
-      <c r="S33" s="201"/>
-      <c r="T33" s="204"/>
-      <c r="U33" s="201"/>
-      <c r="V33" s="204"/>
-      <c r="W33" s="201"/>
-      <c r="X33" s="204"/>
-      <c r="Y33" s="201"/>
-      <c r="Z33" s="204"/>
-      <c r="AA33" s="202"/>
-      <c r="AB33" s="203"/>
-      <c r="AC33" s="201"/>
-      <c r="AD33" s="204"/>
-      <c r="AE33" s="201"/>
-      <c r="AF33" s="204"/>
-      <c r="AG33" s="201"/>
-      <c r="AH33" s="204"/>
-      <c r="AI33" s="201"/>
-      <c r="AJ33" s="204"/>
-      <c r="AK33" s="202"/>
-      <c r="AL33" s="203"/>
-      <c r="AM33" s="201"/>
-      <c r="AN33" s="204"/>
-      <c r="AO33" s="201"/>
-      <c r="AP33" s="204"/>
-      <c r="AQ33" s="201"/>
-      <c r="AR33" s="204"/>
-      <c r="AS33" s="201"/>
-      <c r="AT33" s="204"/>
-      <c r="AU33" s="202"/>
-      <c r="AV33" s="203"/>
-      <c r="AW33" s="201"/>
-    </row>
-    <row r="34" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34">
-        <f>B32+$A$8</f>
+      <c r="D35" s="213"/>
+      <c r="E35" s="82"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="106"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="106"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="106"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="106"/>
+      <c r="Q35" s="104"/>
+      <c r="R35" s="105"/>
+      <c r="S35" s="103"/>
+      <c r="T35" s="106"/>
+      <c r="U35" s="103"/>
+      <c r="V35" s="106"/>
+      <c r="W35" s="103"/>
+      <c r="X35" s="106"/>
+      <c r="Y35" s="103"/>
+      <c r="Z35" s="106"/>
+      <c r="AA35" s="104"/>
+      <c r="AB35" s="105"/>
+      <c r="AC35" s="103"/>
+      <c r="AD35" s="106"/>
+      <c r="AE35" s="103"/>
+      <c r="AF35" s="106"/>
+      <c r="AG35" s="103"/>
+      <c r="AH35" s="106"/>
+      <c r="AI35" s="103"/>
+      <c r="AJ35" s="106"/>
+      <c r="AK35" s="104"/>
+      <c r="AL35" s="105"/>
+      <c r="AM35" s="103"/>
+      <c r="AN35" s="106"/>
+      <c r="AO35" s="103"/>
+      <c r="AP35" s="106"/>
+      <c r="AQ35" s="103"/>
+      <c r="AR35" s="106"/>
+      <c r="AS35" s="103"/>
+      <c r="AT35" s="106"/>
+      <c r="AU35" s="104"/>
+      <c r="AV35" s="105"/>
+      <c r="AW35" s="103"/>
+    </row>
+    <row r="36" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="213"/>
+      <c r="D36" s="213"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="99"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="100"/>
+      <c r="J36" s="102"/>
+      <c r="K36" s="99"/>
+      <c r="L36" s="102"/>
+      <c r="M36" s="99"/>
+      <c r="N36" s="102"/>
+      <c r="O36" s="99"/>
+      <c r="P36" s="102"/>
+      <c r="Q36" s="100"/>
+      <c r="R36" s="101"/>
+      <c r="S36" s="99"/>
+      <c r="T36" s="102"/>
+      <c r="U36" s="99"/>
+      <c r="V36" s="102"/>
+      <c r="W36" s="99"/>
+      <c r="X36" s="102"/>
+      <c r="Y36" s="99"/>
+      <c r="Z36" s="102"/>
+      <c r="AA36" s="100"/>
+      <c r="AB36" s="101"/>
+      <c r="AC36" s="99"/>
+      <c r="AD36" s="102"/>
+      <c r="AE36" s="99"/>
+      <c r="AF36" s="102"/>
+      <c r="AG36" s="99"/>
+      <c r="AH36" s="102"/>
+      <c r="AI36" s="99"/>
+      <c r="AJ36" s="102"/>
+      <c r="AK36" s="100"/>
+      <c r="AL36" s="101"/>
+      <c r="AM36" s="99"/>
+      <c r="AN36" s="102"/>
+      <c r="AO36" s="99"/>
+      <c r="AP36" s="102"/>
+      <c r="AQ36" s="99"/>
+      <c r="AR36" s="102"/>
+      <c r="AS36" s="99"/>
+      <c r="AT36" s="102"/>
+      <c r="AU36" s="100"/>
+      <c r="AV36" s="101"/>
+      <c r="AW36" s="99"/>
+    </row>
+    <row r="37" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <f>B35+$A$11</f>
         <v>260</v>
       </c>
-      <c r="C34" s="183" t="str">
-        <f>CONCATENATE(B34,"°")</f>
+      <c r="C37" s="213" t="str">
+        <f>CONCATENATE(B37,"°")</f>
         <v>260°</v>
       </c>
-      <c r="D34" s="183"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="189"/>
-      <c r="G34" s="190"/>
-      <c r="H34" s="191"/>
-      <c r="I34" s="190"/>
-      <c r="J34" s="192"/>
-      <c r="K34" s="189"/>
-      <c r="L34" s="192"/>
-      <c r="M34" s="189"/>
-      <c r="N34" s="192"/>
-      <c r="O34" s="189"/>
-      <c r="P34" s="192"/>
-      <c r="Q34" s="190"/>
-      <c r="R34" s="191"/>
-      <c r="S34" s="189"/>
-      <c r="T34" s="192"/>
-      <c r="U34" s="189"/>
-      <c r="V34" s="192"/>
-      <c r="W34" s="189"/>
-      <c r="X34" s="192"/>
-      <c r="Y34" s="189"/>
-      <c r="Z34" s="192"/>
-      <c r="AA34" s="190"/>
-      <c r="AB34" s="191"/>
-      <c r="AC34" s="189"/>
-      <c r="AD34" s="192"/>
-      <c r="AE34" s="189"/>
-      <c r="AF34" s="192"/>
-      <c r="AG34" s="189"/>
-      <c r="AH34" s="192"/>
-      <c r="AI34" s="189"/>
-      <c r="AJ34" s="192"/>
-      <c r="AK34" s="190"/>
-      <c r="AL34" s="191"/>
-      <c r="AM34" s="189"/>
-      <c r="AN34" s="192"/>
-      <c r="AO34" s="189"/>
-      <c r="AP34" s="192"/>
-      <c r="AQ34" s="189"/>
-      <c r="AR34" s="192"/>
-      <c r="AS34" s="189"/>
-      <c r="AT34" s="192"/>
-      <c r="AU34" s="190"/>
-      <c r="AV34" s="191"/>
-      <c r="AW34" s="189"/>
-    </row>
-    <row r="35" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="183"/>
-      <c r="D35" s="183"/>
-      <c r="E35" s="184"/>
-      <c r="F35" s="197"/>
-      <c r="G35" s="198"/>
-      <c r="H35" s="199"/>
-      <c r="I35" s="198"/>
-      <c r="J35" s="200"/>
-      <c r="K35" s="197"/>
-      <c r="L35" s="200"/>
-      <c r="M35" s="197"/>
-      <c r="N35" s="200"/>
-      <c r="O35" s="197"/>
-      <c r="P35" s="200"/>
-      <c r="Q35" s="198"/>
-      <c r="R35" s="199"/>
-      <c r="S35" s="197"/>
-      <c r="T35" s="200"/>
-      <c r="U35" s="197"/>
-      <c r="V35" s="200"/>
-      <c r="W35" s="197"/>
-      <c r="X35" s="200"/>
-      <c r="Y35" s="197"/>
-      <c r="Z35" s="200"/>
-      <c r="AA35" s="198"/>
-      <c r="AB35" s="199"/>
-      <c r="AC35" s="197"/>
-      <c r="AD35" s="200"/>
-      <c r="AE35" s="197"/>
-      <c r="AF35" s="200"/>
-      <c r="AG35" s="197"/>
-      <c r="AH35" s="200"/>
-      <c r="AI35" s="197"/>
-      <c r="AJ35" s="200"/>
-      <c r="AK35" s="198"/>
-      <c r="AL35" s="199"/>
-      <c r="AM35" s="197"/>
-      <c r="AN35" s="200"/>
-      <c r="AO35" s="197"/>
-      <c r="AP35" s="200"/>
-      <c r="AQ35" s="197"/>
-      <c r="AR35" s="200"/>
-      <c r="AS35" s="197"/>
-      <c r="AT35" s="200"/>
-      <c r="AU35" s="198"/>
-      <c r="AV35" s="199"/>
-      <c r="AW35" s="197"/>
-    </row>
-    <row r="36" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36">
-        <f>B34+$A$8</f>
+      <c r="D37" s="213"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="90"/>
+      <c r="K37" s="87"/>
+      <c r="L37" s="90"/>
+      <c r="M37" s="87"/>
+      <c r="N37" s="90"/>
+      <c r="O37" s="87"/>
+      <c r="P37" s="90"/>
+      <c r="Q37" s="88"/>
+      <c r="R37" s="89"/>
+      <c r="S37" s="87"/>
+      <c r="T37" s="90"/>
+      <c r="U37" s="87"/>
+      <c r="V37" s="90"/>
+      <c r="W37" s="87"/>
+      <c r="X37" s="90"/>
+      <c r="Y37" s="87"/>
+      <c r="Z37" s="90"/>
+      <c r="AA37" s="88"/>
+      <c r="AB37" s="89"/>
+      <c r="AC37" s="87"/>
+      <c r="AD37" s="90"/>
+      <c r="AE37" s="87"/>
+      <c r="AF37" s="90"/>
+      <c r="AG37" s="87"/>
+      <c r="AH37" s="90"/>
+      <c r="AI37" s="87"/>
+      <c r="AJ37" s="90"/>
+      <c r="AK37" s="88"/>
+      <c r="AL37" s="89"/>
+      <c r="AM37" s="87"/>
+      <c r="AN37" s="90"/>
+      <c r="AO37" s="87"/>
+      <c r="AP37" s="90"/>
+      <c r="AQ37" s="87"/>
+      <c r="AR37" s="90"/>
+      <c r="AS37" s="87"/>
+      <c r="AT37" s="90"/>
+      <c r="AU37" s="88"/>
+      <c r="AV37" s="89"/>
+      <c r="AW37" s="87"/>
+    </row>
+    <row r="38" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="213"/>
+      <c r="D38" s="213"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="96"/>
+      <c r="H38" s="97"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="98"/>
+      <c r="K38" s="95"/>
+      <c r="L38" s="98"/>
+      <c r="M38" s="95"/>
+      <c r="N38" s="98"/>
+      <c r="O38" s="95"/>
+      <c r="P38" s="98"/>
+      <c r="Q38" s="96"/>
+      <c r="R38" s="97"/>
+      <c r="S38" s="95"/>
+      <c r="T38" s="98"/>
+      <c r="U38" s="95"/>
+      <c r="V38" s="98"/>
+      <c r="W38" s="95"/>
+      <c r="X38" s="98"/>
+      <c r="Y38" s="95"/>
+      <c r="Z38" s="98"/>
+      <c r="AA38" s="96"/>
+      <c r="AB38" s="97"/>
+      <c r="AC38" s="95"/>
+      <c r="AD38" s="98"/>
+      <c r="AE38" s="95"/>
+      <c r="AF38" s="98"/>
+      <c r="AG38" s="95"/>
+      <c r="AH38" s="98"/>
+      <c r="AI38" s="95"/>
+      <c r="AJ38" s="98"/>
+      <c r="AK38" s="96"/>
+      <c r="AL38" s="97"/>
+      <c r="AM38" s="95"/>
+      <c r="AN38" s="98"/>
+      <c r="AO38" s="95"/>
+      <c r="AP38" s="98"/>
+      <c r="AQ38" s="95"/>
+      <c r="AR38" s="98"/>
+      <c r="AS38" s="95"/>
+      <c r="AT38" s="98"/>
+      <c r="AU38" s="96"/>
+      <c r="AV38" s="97"/>
+      <c r="AW38" s="95"/>
+    </row>
+    <row r="39" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <f>B37+$A$11</f>
         <v>280</v>
       </c>
-      <c r="C36" s="183" t="str">
-        <f>CONCATENATE(B36,"°")</f>
+      <c r="C39" s="213" t="str">
+        <f>CONCATENATE(B39,"°")</f>
         <v>280°</v>
       </c>
-      <c r="D36" s="183"/>
-      <c r="E36" s="184"/>
-      <c r="F36" s="185"/>
-      <c r="G36" s="186"/>
-      <c r="H36" s="187"/>
-      <c r="I36" s="186"/>
-      <c r="J36" s="188"/>
-      <c r="K36" s="185"/>
-      <c r="L36" s="188"/>
-      <c r="M36" s="185"/>
-      <c r="N36" s="188"/>
-      <c r="O36" s="185"/>
-      <c r="P36" s="188"/>
-      <c r="Q36" s="186"/>
-      <c r="R36" s="187"/>
-      <c r="S36" s="185"/>
-      <c r="T36" s="188"/>
-      <c r="U36" s="185"/>
-      <c r="V36" s="188"/>
-      <c r="W36" s="185"/>
-      <c r="X36" s="188"/>
-      <c r="Y36" s="185"/>
-      <c r="Z36" s="188"/>
-      <c r="AA36" s="186"/>
-      <c r="AB36" s="187"/>
-      <c r="AC36" s="185"/>
-      <c r="AD36" s="188"/>
-      <c r="AE36" s="185"/>
-      <c r="AF36" s="188"/>
-      <c r="AG36" s="185"/>
-      <c r="AH36" s="188"/>
-      <c r="AI36" s="185"/>
-      <c r="AJ36" s="188"/>
-      <c r="AK36" s="186"/>
-      <c r="AL36" s="187"/>
-      <c r="AM36" s="185"/>
-      <c r="AN36" s="188"/>
-      <c r="AO36" s="185"/>
-      <c r="AP36" s="188"/>
-      <c r="AQ36" s="185"/>
-      <c r="AR36" s="188"/>
-      <c r="AS36" s="185"/>
-      <c r="AT36" s="188"/>
-      <c r="AU36" s="186"/>
-      <c r="AV36" s="187"/>
-      <c r="AW36" s="185"/>
-    </row>
-    <row r="37" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="183"/>
-      <c r="D37" s="183"/>
-      <c r="E37" s="184"/>
-      <c r="F37" s="201"/>
-      <c r="G37" s="202"/>
-      <c r="H37" s="203"/>
-      <c r="I37" s="202"/>
-      <c r="J37" s="204"/>
-      <c r="K37" s="201"/>
-      <c r="L37" s="204"/>
-      <c r="M37" s="201"/>
-      <c r="N37" s="204"/>
-      <c r="O37" s="201"/>
-      <c r="P37" s="204"/>
-      <c r="Q37" s="202"/>
-      <c r="R37" s="203"/>
-      <c r="S37" s="201"/>
-      <c r="T37" s="204"/>
-      <c r="U37" s="201"/>
-      <c r="V37" s="204"/>
-      <c r="W37" s="201"/>
-      <c r="X37" s="204"/>
-      <c r="Y37" s="201"/>
-      <c r="Z37" s="204"/>
-      <c r="AA37" s="202"/>
-      <c r="AB37" s="203"/>
-      <c r="AC37" s="201"/>
-      <c r="AD37" s="204"/>
-      <c r="AE37" s="201"/>
-      <c r="AF37" s="204"/>
-      <c r="AG37" s="201"/>
-      <c r="AH37" s="204"/>
-      <c r="AI37" s="201"/>
-      <c r="AJ37" s="204"/>
-      <c r="AK37" s="202"/>
-      <c r="AL37" s="203"/>
-      <c r="AM37" s="201"/>
-      <c r="AN37" s="204"/>
-      <c r="AO37" s="201"/>
-      <c r="AP37" s="204"/>
-      <c r="AQ37" s="201"/>
-      <c r="AR37" s="204"/>
-      <c r="AS37" s="201"/>
-      <c r="AT37" s="204"/>
-      <c r="AU37" s="202"/>
-      <c r="AV37" s="203"/>
-      <c r="AW37" s="201"/>
-    </row>
-    <row r="38" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38">
-        <f>B36+$A$8</f>
+      <c r="D39" s="213"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="83"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="86"/>
+      <c r="K39" s="83"/>
+      <c r="L39" s="86"/>
+      <c r="M39" s="83"/>
+      <c r="N39" s="86"/>
+      <c r="O39" s="83"/>
+      <c r="P39" s="86"/>
+      <c r="Q39" s="84"/>
+      <c r="R39" s="85"/>
+      <c r="S39" s="83"/>
+      <c r="T39" s="86"/>
+      <c r="U39" s="83"/>
+      <c r="V39" s="86"/>
+      <c r="W39" s="83"/>
+      <c r="X39" s="86"/>
+      <c r="Y39" s="83"/>
+      <c r="Z39" s="86"/>
+      <c r="AA39" s="84"/>
+      <c r="AB39" s="85"/>
+      <c r="AC39" s="83"/>
+      <c r="AD39" s="86"/>
+      <c r="AE39" s="83"/>
+      <c r="AF39" s="86"/>
+      <c r="AG39" s="83"/>
+      <c r="AH39" s="86"/>
+      <c r="AI39" s="83"/>
+      <c r="AJ39" s="86"/>
+      <c r="AK39" s="84"/>
+      <c r="AL39" s="85"/>
+      <c r="AM39" s="83"/>
+      <c r="AN39" s="86"/>
+      <c r="AO39" s="83"/>
+      <c r="AP39" s="86"/>
+      <c r="AQ39" s="83"/>
+      <c r="AR39" s="86"/>
+      <c r="AS39" s="83"/>
+      <c r="AT39" s="86"/>
+      <c r="AU39" s="84"/>
+      <c r="AV39" s="85"/>
+      <c r="AW39" s="83"/>
+    </row>
+    <row r="40" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="213"/>
+      <c r="D40" s="213"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="100"/>
+      <c r="H40" s="101"/>
+      <c r="I40" s="100"/>
+      <c r="J40" s="102"/>
+      <c r="K40" s="99"/>
+      <c r="L40" s="102"/>
+      <c r="M40" s="99"/>
+      <c r="N40" s="102"/>
+      <c r="O40" s="99"/>
+      <c r="P40" s="102"/>
+      <c r="Q40" s="100"/>
+      <c r="R40" s="101"/>
+      <c r="S40" s="99"/>
+      <c r="T40" s="102"/>
+      <c r="U40" s="99"/>
+      <c r="V40" s="102"/>
+      <c r="W40" s="99"/>
+      <c r="X40" s="102"/>
+      <c r="Y40" s="99"/>
+      <c r="Z40" s="102"/>
+      <c r="AA40" s="100"/>
+      <c r="AB40" s="101"/>
+      <c r="AC40" s="99"/>
+      <c r="AD40" s="102"/>
+      <c r="AE40" s="99"/>
+      <c r="AF40" s="102"/>
+      <c r="AG40" s="99"/>
+      <c r="AH40" s="102"/>
+      <c r="AI40" s="99"/>
+      <c r="AJ40" s="102"/>
+      <c r="AK40" s="100"/>
+      <c r="AL40" s="101"/>
+      <c r="AM40" s="99"/>
+      <c r="AN40" s="102"/>
+      <c r="AO40" s="99"/>
+      <c r="AP40" s="102"/>
+      <c r="AQ40" s="99"/>
+      <c r="AR40" s="102"/>
+      <c r="AS40" s="99"/>
+      <c r="AT40" s="102"/>
+      <c r="AU40" s="100"/>
+      <c r="AV40" s="101"/>
+      <c r="AW40" s="99"/>
+    </row>
+    <row r="41" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <f>B39+$A$11</f>
         <v>300</v>
       </c>
-      <c r="C38" s="183" t="str">
-        <f>CONCATENATE(B38,"°")</f>
+      <c r="C41" s="213" t="str">
+        <f>CONCATENATE(B41,"°")</f>
         <v>300°</v>
       </c>
-      <c r="D38" s="183"/>
-      <c r="E38" s="184"/>
-      <c r="F38" s="189"/>
-      <c r="G38" s="190"/>
-      <c r="H38" s="191"/>
-      <c r="I38" s="190"/>
-      <c r="J38" s="192"/>
-      <c r="K38" s="189"/>
-      <c r="L38" s="192"/>
-      <c r="M38" s="189"/>
-      <c r="N38" s="192"/>
-      <c r="O38" s="189"/>
-      <c r="P38" s="192"/>
-      <c r="Q38" s="190"/>
-      <c r="R38" s="191"/>
-      <c r="S38" s="189"/>
-      <c r="T38" s="192"/>
-      <c r="U38" s="189"/>
-      <c r="V38" s="192"/>
-      <c r="W38" s="189"/>
-      <c r="X38" s="192"/>
-      <c r="Y38" s="189"/>
-      <c r="Z38" s="192"/>
-      <c r="AA38" s="190"/>
-      <c r="AB38" s="191"/>
-      <c r="AC38" s="189"/>
-      <c r="AD38" s="192"/>
-      <c r="AE38" s="189"/>
-      <c r="AF38" s="192"/>
-      <c r="AG38" s="189"/>
-      <c r="AH38" s="192"/>
-      <c r="AI38" s="189"/>
-      <c r="AJ38" s="192"/>
-      <c r="AK38" s="190"/>
-      <c r="AL38" s="191"/>
-      <c r="AM38" s="189"/>
-      <c r="AN38" s="192"/>
-      <c r="AO38" s="189"/>
-      <c r="AP38" s="192"/>
-      <c r="AQ38" s="189"/>
-      <c r="AR38" s="192"/>
-      <c r="AS38" s="189"/>
-      <c r="AT38" s="192"/>
-      <c r="AU38" s="190"/>
-      <c r="AV38" s="191"/>
-      <c r="AW38" s="189"/>
-    </row>
-    <row r="39" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="183"/>
-      <c r="D39" s="183"/>
-      <c r="E39" s="184"/>
-      <c r="F39" s="205"/>
-      <c r="G39" s="206"/>
-      <c r="H39" s="207"/>
-      <c r="I39" s="206"/>
-      <c r="J39" s="208"/>
-      <c r="K39" s="205"/>
-      <c r="L39" s="208"/>
-      <c r="M39" s="205"/>
-      <c r="N39" s="208"/>
-      <c r="O39" s="205"/>
-      <c r="P39" s="208"/>
-      <c r="Q39" s="206"/>
-      <c r="R39" s="207"/>
-      <c r="S39" s="205"/>
-      <c r="T39" s="208"/>
-      <c r="U39" s="205"/>
-      <c r="V39" s="208"/>
-      <c r="W39" s="205"/>
-      <c r="X39" s="208"/>
-      <c r="Y39" s="205"/>
-      <c r="Z39" s="208"/>
-      <c r="AA39" s="206"/>
-      <c r="AB39" s="207"/>
-      <c r="AC39" s="205"/>
-      <c r="AD39" s="208"/>
-      <c r="AE39" s="205"/>
-      <c r="AF39" s="208"/>
-      <c r="AG39" s="205"/>
-      <c r="AH39" s="208"/>
-      <c r="AI39" s="205"/>
-      <c r="AJ39" s="208"/>
-      <c r="AK39" s="206"/>
-      <c r="AL39" s="207"/>
-      <c r="AM39" s="205"/>
-      <c r="AN39" s="208"/>
-      <c r="AO39" s="205"/>
-      <c r="AP39" s="208"/>
-      <c r="AQ39" s="205"/>
-      <c r="AR39" s="208"/>
-      <c r="AS39" s="205"/>
-      <c r="AT39" s="208"/>
-      <c r="AU39" s="206"/>
-      <c r="AV39" s="207"/>
-      <c r="AW39" s="205"/>
-    </row>
-    <row r="40" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40">
-        <f>B38+$A$8</f>
+      <c r="D41" s="213"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="87"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="87"/>
+      <c r="P41" s="90"/>
+      <c r="Q41" s="88"/>
+      <c r="R41" s="89"/>
+      <c r="S41" s="87"/>
+      <c r="T41" s="90"/>
+      <c r="U41" s="87"/>
+      <c r="V41" s="90"/>
+      <c r="W41" s="87"/>
+      <c r="X41" s="90"/>
+      <c r="Y41" s="87"/>
+      <c r="Z41" s="90"/>
+      <c r="AA41" s="88"/>
+      <c r="AB41" s="89"/>
+      <c r="AC41" s="87"/>
+      <c r="AD41" s="90"/>
+      <c r="AE41" s="87"/>
+      <c r="AF41" s="90"/>
+      <c r="AG41" s="87"/>
+      <c r="AH41" s="90"/>
+      <c r="AI41" s="87"/>
+      <c r="AJ41" s="90"/>
+      <c r="AK41" s="88"/>
+      <c r="AL41" s="89"/>
+      <c r="AM41" s="87"/>
+      <c r="AN41" s="90"/>
+      <c r="AO41" s="87"/>
+      <c r="AP41" s="90"/>
+      <c r="AQ41" s="87"/>
+      <c r="AR41" s="90"/>
+      <c r="AS41" s="87"/>
+      <c r="AT41" s="90"/>
+      <c r="AU41" s="88"/>
+      <c r="AV41" s="89"/>
+      <c r="AW41" s="87"/>
+    </row>
+    <row r="42" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="213"/>
+      <c r="D42" s="213"/>
+      <c r="E42" s="82"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="106"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="106"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="106"/>
+      <c r="O42" s="103"/>
+      <c r="P42" s="106"/>
+      <c r="Q42" s="104"/>
+      <c r="R42" s="105"/>
+      <c r="S42" s="103"/>
+      <c r="T42" s="106"/>
+      <c r="U42" s="103"/>
+      <c r="V42" s="106"/>
+      <c r="W42" s="103"/>
+      <c r="X42" s="106"/>
+      <c r="Y42" s="103"/>
+      <c r="Z42" s="106"/>
+      <c r="AA42" s="104"/>
+      <c r="AB42" s="105"/>
+      <c r="AC42" s="103"/>
+      <c r="AD42" s="106"/>
+      <c r="AE42" s="103"/>
+      <c r="AF42" s="106"/>
+      <c r="AG42" s="103"/>
+      <c r="AH42" s="106"/>
+      <c r="AI42" s="103"/>
+      <c r="AJ42" s="106"/>
+      <c r="AK42" s="104"/>
+      <c r="AL42" s="105"/>
+      <c r="AM42" s="103"/>
+      <c r="AN42" s="106"/>
+      <c r="AO42" s="103"/>
+      <c r="AP42" s="106"/>
+      <c r="AQ42" s="103"/>
+      <c r="AR42" s="106"/>
+      <c r="AS42" s="103"/>
+      <c r="AT42" s="106"/>
+      <c r="AU42" s="104"/>
+      <c r="AV42" s="105"/>
+      <c r="AW42" s="103"/>
+    </row>
+    <row r="43" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <f>B41+$A$11</f>
         <v>320</v>
       </c>
-      <c r="C40" s="183" t="str">
-        <f>CONCATENATE(B40,"°")</f>
+      <c r="C43" s="213" t="str">
+        <f>CONCATENATE(B43,"°")</f>
         <v>320°</v>
       </c>
-      <c r="D40" s="183"/>
-      <c r="E40" s="184"/>
-      <c r="F40" s="205"/>
-      <c r="G40" s="206"/>
-      <c r="H40" s="207"/>
-      <c r="I40" s="206"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="205"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="205"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="205"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="206"/>
-      <c r="R40" s="207"/>
-      <c r="S40" s="205"/>
-      <c r="T40" s="208"/>
-      <c r="U40" s="205"/>
-      <c r="V40" s="208"/>
-      <c r="W40" s="205"/>
-      <c r="X40" s="208"/>
-      <c r="Y40" s="205"/>
-      <c r="Z40" s="208"/>
-      <c r="AA40" s="206"/>
-      <c r="AB40" s="207"/>
-      <c r="AC40" s="205"/>
-      <c r="AD40" s="208"/>
-      <c r="AE40" s="205"/>
-      <c r="AF40" s="208"/>
-      <c r="AG40" s="205"/>
-      <c r="AH40" s="208"/>
-      <c r="AI40" s="205"/>
-      <c r="AJ40" s="208"/>
-      <c r="AK40" s="206"/>
-      <c r="AL40" s="207"/>
-      <c r="AM40" s="205"/>
-      <c r="AN40" s="208"/>
-      <c r="AO40" s="205"/>
-      <c r="AP40" s="208"/>
-      <c r="AQ40" s="205"/>
-      <c r="AR40" s="208"/>
-      <c r="AS40" s="205"/>
-      <c r="AT40" s="208"/>
-      <c r="AU40" s="206"/>
-      <c r="AV40" s="207"/>
-      <c r="AW40" s="205"/>
-    </row>
-    <row r="41" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="183"/>
-      <c r="D41" s="183"/>
-      <c r="E41" s="184"/>
-      <c r="F41" s="201"/>
-      <c r="G41" s="202"/>
-      <c r="H41" s="203"/>
-      <c r="I41" s="202"/>
-      <c r="J41" s="204"/>
-      <c r="K41" s="201"/>
-      <c r="L41" s="204"/>
-      <c r="M41" s="201"/>
-      <c r="N41" s="204"/>
-      <c r="O41" s="201"/>
-      <c r="P41" s="204"/>
-      <c r="Q41" s="202"/>
-      <c r="R41" s="203"/>
-      <c r="S41" s="201"/>
-      <c r="T41" s="204"/>
-      <c r="U41" s="201"/>
-      <c r="V41" s="204"/>
-      <c r="W41" s="201"/>
-      <c r="X41" s="204"/>
-      <c r="Y41" s="201"/>
-      <c r="Z41" s="204"/>
-      <c r="AA41" s="202"/>
-      <c r="AB41" s="203"/>
-      <c r="AC41" s="201"/>
-      <c r="AD41" s="204"/>
-      <c r="AE41" s="201"/>
-      <c r="AF41" s="204"/>
-      <c r="AG41" s="201"/>
-      <c r="AH41" s="204"/>
-      <c r="AI41" s="201"/>
-      <c r="AJ41" s="204"/>
-      <c r="AK41" s="202"/>
-      <c r="AL41" s="203"/>
-      <c r="AM41" s="201"/>
-      <c r="AN41" s="204"/>
-      <c r="AO41" s="201"/>
-      <c r="AP41" s="204"/>
-      <c r="AQ41" s="201"/>
-      <c r="AR41" s="204"/>
-      <c r="AS41" s="201"/>
-      <c r="AT41" s="204"/>
-      <c r="AU41" s="202"/>
-      <c r="AV41" s="203"/>
-      <c r="AW41" s="201"/>
-    </row>
-    <row r="42" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42">
-        <f>B40+$A$8</f>
+      <c r="D43" s="213"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="106"/>
+      <c r="K43" s="103"/>
+      <c r="L43" s="106"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="106"/>
+      <c r="O43" s="103"/>
+      <c r="P43" s="106"/>
+      <c r="Q43" s="104"/>
+      <c r="R43" s="105"/>
+      <c r="S43" s="103"/>
+      <c r="T43" s="106"/>
+      <c r="U43" s="103"/>
+      <c r="V43" s="106"/>
+      <c r="W43" s="103"/>
+      <c r="X43" s="106"/>
+      <c r="Y43" s="103"/>
+      <c r="Z43" s="106"/>
+      <c r="AA43" s="104"/>
+      <c r="AB43" s="105"/>
+      <c r="AC43" s="103"/>
+      <c r="AD43" s="106"/>
+      <c r="AE43" s="103"/>
+      <c r="AF43" s="106"/>
+      <c r="AG43" s="103"/>
+      <c r="AH43" s="106"/>
+      <c r="AI43" s="103"/>
+      <c r="AJ43" s="106"/>
+      <c r="AK43" s="104"/>
+      <c r="AL43" s="105"/>
+      <c r="AM43" s="103"/>
+      <c r="AN43" s="106"/>
+      <c r="AO43" s="103"/>
+      <c r="AP43" s="106"/>
+      <c r="AQ43" s="103"/>
+      <c r="AR43" s="106"/>
+      <c r="AS43" s="103"/>
+      <c r="AT43" s="106"/>
+      <c r="AU43" s="104"/>
+      <c r="AV43" s="105"/>
+      <c r="AW43" s="103"/>
+    </row>
+    <row r="44" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="213"/>
+      <c r="D44" s="213"/>
+      <c r="E44" s="82"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="101"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="102"/>
+      <c r="K44" s="99"/>
+      <c r="L44" s="102"/>
+      <c r="M44" s="99"/>
+      <c r="N44" s="102"/>
+      <c r="O44" s="99"/>
+      <c r="P44" s="102"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="101"/>
+      <c r="S44" s="99"/>
+      <c r="T44" s="102"/>
+      <c r="U44" s="99"/>
+      <c r="V44" s="102"/>
+      <c r="W44" s="99"/>
+      <c r="X44" s="102"/>
+      <c r="Y44" s="99"/>
+      <c r="Z44" s="102"/>
+      <c r="AA44" s="100"/>
+      <c r="AB44" s="101"/>
+      <c r="AC44" s="99"/>
+      <c r="AD44" s="102"/>
+      <c r="AE44" s="99"/>
+      <c r="AF44" s="102"/>
+      <c r="AG44" s="99"/>
+      <c r="AH44" s="102"/>
+      <c r="AI44" s="99"/>
+      <c r="AJ44" s="102"/>
+      <c r="AK44" s="100"/>
+      <c r="AL44" s="101"/>
+      <c r="AM44" s="99"/>
+      <c r="AN44" s="102"/>
+      <c r="AO44" s="99"/>
+      <c r="AP44" s="102"/>
+      <c r="AQ44" s="99"/>
+      <c r="AR44" s="102"/>
+      <c r="AS44" s="99"/>
+      <c r="AT44" s="102"/>
+      <c r="AU44" s="100"/>
+      <c r="AV44" s="101"/>
+      <c r="AW44" s="99"/>
+    </row>
+    <row r="45" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <f>B43+$A$11</f>
         <v>340</v>
       </c>
-      <c r="C42" s="183" t="str">
-        <f>CONCATENATE(B42,"°")</f>
+      <c r="C45" s="213" t="str">
+        <f>CONCATENATE(B45,"°")</f>
         <v>340°</v>
       </c>
-      <c r="D42" s="183"/>
-      <c r="E42" s="184"/>
-      <c r="F42" s="189"/>
-      <c r="G42" s="190"/>
-      <c r="H42" s="191"/>
-      <c r="I42" s="190"/>
-      <c r="J42" s="192"/>
-      <c r="K42" s="189"/>
-      <c r="L42" s="192"/>
-      <c r="M42" s="189"/>
-      <c r="N42" s="192"/>
-      <c r="O42" s="189"/>
-      <c r="P42" s="192"/>
-      <c r="Q42" s="190"/>
-      <c r="R42" s="191"/>
-      <c r="S42" s="189"/>
-      <c r="T42" s="192"/>
-      <c r="U42" s="189"/>
-      <c r="V42" s="192"/>
-      <c r="W42" s="189"/>
-      <c r="X42" s="192"/>
-      <c r="Y42" s="189"/>
-      <c r="Z42" s="192"/>
-      <c r="AA42" s="190"/>
-      <c r="AB42" s="191"/>
-      <c r="AC42" s="189"/>
-      <c r="AD42" s="192"/>
-      <c r="AE42" s="189"/>
-      <c r="AF42" s="192"/>
-      <c r="AG42" s="189"/>
-      <c r="AH42" s="192"/>
-      <c r="AI42" s="189"/>
-      <c r="AJ42" s="192"/>
-      <c r="AK42" s="190"/>
-      <c r="AL42" s="191"/>
-      <c r="AM42" s="189"/>
-      <c r="AN42" s="192"/>
-      <c r="AO42" s="189"/>
-      <c r="AP42" s="192"/>
-      <c r="AQ42" s="189"/>
-      <c r="AR42" s="192"/>
-      <c r="AS42" s="189"/>
-      <c r="AT42" s="192"/>
-      <c r="AU42" s="190"/>
-      <c r="AV42" s="191"/>
-      <c r="AW42" s="189"/>
-    </row>
-    <row r="43" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="183"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="184"/>
-      <c r="F43" s="205"/>
-      <c r="G43" s="206"/>
-      <c r="H43" s="207"/>
-      <c r="I43" s="206"/>
-      <c r="J43" s="208"/>
-      <c r="K43" s="205"/>
-      <c r="L43" s="208"/>
-      <c r="M43" s="205"/>
-      <c r="N43" s="208"/>
-      <c r="O43" s="205"/>
-      <c r="P43" s="208"/>
-      <c r="Q43" s="206"/>
-      <c r="R43" s="207"/>
-      <c r="S43" s="205"/>
-      <c r="T43" s="208"/>
-      <c r="U43" s="205"/>
-      <c r="V43" s="208"/>
-      <c r="W43" s="205"/>
-      <c r="X43" s="208"/>
-      <c r="Y43" s="205"/>
-      <c r="Z43" s="208"/>
-      <c r="AA43" s="206"/>
-      <c r="AB43" s="207"/>
-      <c r="AC43" s="205"/>
-      <c r="AD43" s="208"/>
-      <c r="AE43" s="205"/>
-      <c r="AF43" s="208"/>
-      <c r="AG43" s="205"/>
-      <c r="AH43" s="208"/>
-      <c r="AI43" s="205"/>
-      <c r="AJ43" s="208"/>
-      <c r="AK43" s="206"/>
-      <c r="AL43" s="207"/>
-      <c r="AM43" s="205"/>
-      <c r="AN43" s="208"/>
-      <c r="AO43" s="205"/>
-      <c r="AP43" s="208"/>
-      <c r="AQ43" s="205"/>
-      <c r="AR43" s="208"/>
-      <c r="AS43" s="205"/>
-      <c r="AT43" s="208"/>
-      <c r="AU43" s="206"/>
-      <c r="AV43" s="207"/>
-      <c r="AW43" s="205"/>
-    </row>
-    <row r="44" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44">
+      <c r="D45" s="213"/>
+      <c r="E45" s="82"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="88"/>
+      <c r="H45" s="89"/>
+      <c r="I45" s="88"/>
+      <c r="J45" s="90"/>
+      <c r="K45" s="87"/>
+      <c r="L45" s="90"/>
+      <c r="M45" s="87"/>
+      <c r="N45" s="90"/>
+      <c r="O45" s="87"/>
+      <c r="P45" s="90"/>
+      <c r="Q45" s="88"/>
+      <c r="R45" s="89"/>
+      <c r="S45" s="87"/>
+      <c r="T45" s="90"/>
+      <c r="U45" s="87"/>
+      <c r="V45" s="90"/>
+      <c r="W45" s="87"/>
+      <c r="X45" s="90"/>
+      <c r="Y45" s="87"/>
+      <c r="Z45" s="90"/>
+      <c r="AA45" s="88"/>
+      <c r="AB45" s="89"/>
+      <c r="AC45" s="87"/>
+      <c r="AD45" s="90"/>
+      <c r="AE45" s="87"/>
+      <c r="AF45" s="90"/>
+      <c r="AG45" s="87"/>
+      <c r="AH45" s="90"/>
+      <c r="AI45" s="87"/>
+      <c r="AJ45" s="90"/>
+      <c r="AK45" s="88"/>
+      <c r="AL45" s="89"/>
+      <c r="AM45" s="87"/>
+      <c r="AN45" s="90"/>
+      <c r="AO45" s="87"/>
+      <c r="AP45" s="90"/>
+      <c r="AQ45" s="87"/>
+      <c r="AR45" s="90"/>
+      <c r="AS45" s="87"/>
+      <c r="AT45" s="90"/>
+      <c r="AU45" s="88"/>
+      <c r="AV45" s="89"/>
+      <c r="AW45" s="87"/>
+    </row>
+    <row r="46" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="213"/>
+      <c r="D46" s="213"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="106"/>
+      <c r="K46" s="103"/>
+      <c r="L46" s="106"/>
+      <c r="M46" s="103"/>
+      <c r="N46" s="106"/>
+      <c r="O46" s="103"/>
+      <c r="P46" s="106"/>
+      <c r="Q46" s="104"/>
+      <c r="R46" s="105"/>
+      <c r="S46" s="103"/>
+      <c r="T46" s="106"/>
+      <c r="U46" s="103"/>
+      <c r="V46" s="106"/>
+      <c r="W46" s="103"/>
+      <c r="X46" s="106"/>
+      <c r="Y46" s="103"/>
+      <c r="Z46" s="106"/>
+      <c r="AA46" s="104"/>
+      <c r="AB46" s="105"/>
+      <c r="AC46" s="103"/>
+      <c r="AD46" s="106"/>
+      <c r="AE46" s="103"/>
+      <c r="AF46" s="106"/>
+      <c r="AG46" s="103"/>
+      <c r="AH46" s="106"/>
+      <c r="AI46" s="103"/>
+      <c r="AJ46" s="106"/>
+      <c r="AK46" s="104"/>
+      <c r="AL46" s="105"/>
+      <c r="AM46" s="103"/>
+      <c r="AN46" s="106"/>
+      <c r="AO46" s="103"/>
+      <c r="AP46" s="106"/>
+      <c r="AQ46" s="103"/>
+      <c r="AR46" s="106"/>
+      <c r="AS46" s="103"/>
+      <c r="AT46" s="106"/>
+      <c r="AU46" s="104"/>
+      <c r="AV46" s="105"/>
+      <c r="AW46" s="103"/>
+    </row>
+    <row r="47" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47">
         <v>0</v>
       </c>
-      <c r="C44" s="183" t="str">
-        <f>CONCATENATE(B44,"°")</f>
+      <c r="C47" s="213" t="str">
+        <f>CONCATENATE(B47,"°")</f>
         <v>0°</v>
       </c>
-      <c r="D44" s="183"/>
-      <c r="E44" s="184"/>
-      <c r="F44" s="197"/>
-      <c r="G44" s="198"/>
-      <c r="H44" s="199"/>
-      <c r="I44" s="198"/>
-      <c r="J44" s="217"/>
-      <c r="K44" s="197"/>
-      <c r="L44" s="217"/>
-      <c r="M44" s="197"/>
-      <c r="N44" s="217"/>
-      <c r="O44" s="197"/>
-      <c r="P44" s="217"/>
-      <c r="Q44" s="198"/>
-      <c r="R44" s="199"/>
-      <c r="S44" s="197"/>
-      <c r="T44" s="217"/>
-      <c r="U44" s="197"/>
-      <c r="V44" s="217"/>
-      <c r="W44" s="197"/>
-      <c r="X44" s="217"/>
-      <c r="Y44" s="197"/>
-      <c r="Z44" s="217"/>
-      <c r="AA44" s="198"/>
-      <c r="AB44" s="199"/>
-      <c r="AC44" s="197"/>
-      <c r="AD44" s="217"/>
-      <c r="AE44" s="197"/>
-      <c r="AF44" s="217"/>
-      <c r="AG44" s="197"/>
-      <c r="AH44" s="217"/>
-      <c r="AI44" s="197"/>
-      <c r="AJ44" s="217"/>
-      <c r="AK44" s="198"/>
-      <c r="AL44" s="199"/>
-      <c r="AM44" s="197"/>
-      <c r="AN44" s="217"/>
-      <c r="AO44" s="197"/>
-      <c r="AP44" s="217"/>
-      <c r="AQ44" s="197"/>
-      <c r="AR44" s="217"/>
-      <c r="AS44" s="197"/>
-      <c r="AT44" s="217"/>
-      <c r="AU44" s="198"/>
-      <c r="AV44" s="199"/>
-      <c r="AW44" s="197"/>
-    </row>
-    <row r="45" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="183"/>
-      <c r="D45" s="183"/>
-      <c r="E45" s="184"/>
-      <c r="F45" s="185"/>
-      <c r="G45" s="186"/>
-      <c r="H45" s="187"/>
-      <c r="I45" s="185"/>
-      <c r="J45" s="185"/>
-      <c r="K45" s="185"/>
-      <c r="L45" s="185"/>
-      <c r="M45" s="185"/>
-      <c r="N45" s="185"/>
-      <c r="O45" s="185"/>
-      <c r="P45" s="185"/>
-      <c r="Q45" s="186"/>
-      <c r="R45" s="187"/>
-      <c r="S45" s="185"/>
-      <c r="T45" s="185"/>
-      <c r="U45" s="185"/>
-      <c r="V45" s="185"/>
-      <c r="W45" s="185"/>
-      <c r="X45" s="185"/>
-      <c r="Y45" s="185"/>
-      <c r="Z45" s="185"/>
-      <c r="AA45" s="186"/>
-      <c r="AB45" s="187"/>
-      <c r="AC45" s="185"/>
-      <c r="AD45" s="185"/>
-      <c r="AE45" s="185"/>
-      <c r="AF45" s="185"/>
-      <c r="AG45" s="185"/>
-      <c r="AH45" s="185"/>
-      <c r="AI45" s="185"/>
-      <c r="AJ45" s="185"/>
-      <c r="AK45" s="186"/>
-      <c r="AL45" s="187"/>
-      <c r="AM45" s="185"/>
-      <c r="AN45" s="185"/>
-      <c r="AO45" s="185"/>
-      <c r="AP45" s="185"/>
-      <c r="AQ45" s="185"/>
-      <c r="AR45" s="185"/>
-      <c r="AS45" s="185"/>
-      <c r="AT45" s="185"/>
-      <c r="AU45" s="186"/>
-      <c r="AV45" s="187"/>
-      <c r="AW45" s="185"/>
-    </row>
-    <row r="46" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46">
-        <f>B44+$A$8</f>
+      <c r="D47" s="213"/>
+      <c r="E47" s="82"/>
+      <c r="F47" s="95"/>
+      <c r="G47" s="96"/>
+      <c r="H47" s="97"/>
+      <c r="I47" s="96"/>
+      <c r="J47" s="115"/>
+      <c r="K47" s="95"/>
+      <c r="L47" s="115"/>
+      <c r="M47" s="95"/>
+      <c r="N47" s="115"/>
+      <c r="O47" s="95"/>
+      <c r="P47" s="115"/>
+      <c r="Q47" s="96"/>
+      <c r="R47" s="97"/>
+      <c r="S47" s="95"/>
+      <c r="T47" s="115"/>
+      <c r="U47" s="95"/>
+      <c r="V47" s="115"/>
+      <c r="W47" s="95"/>
+      <c r="X47" s="115"/>
+      <c r="Y47" s="95"/>
+      <c r="Z47" s="115"/>
+      <c r="AA47" s="96"/>
+      <c r="AB47" s="97"/>
+      <c r="AC47" s="95"/>
+      <c r="AD47" s="115"/>
+      <c r="AE47" s="95"/>
+      <c r="AF47" s="115"/>
+      <c r="AG47" s="95"/>
+      <c r="AH47" s="115"/>
+      <c r="AI47" s="95"/>
+      <c r="AJ47" s="115"/>
+      <c r="AK47" s="96"/>
+      <c r="AL47" s="97"/>
+      <c r="AM47" s="95"/>
+      <c r="AN47" s="115"/>
+      <c r="AO47" s="95"/>
+      <c r="AP47" s="115"/>
+      <c r="AQ47" s="95"/>
+      <c r="AR47" s="115"/>
+      <c r="AS47" s="95"/>
+      <c r="AT47" s="115"/>
+      <c r="AU47" s="96"/>
+      <c r="AV47" s="97"/>
+      <c r="AW47" s="95"/>
+    </row>
+    <row r="48" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="213"/>
+      <c r="D48" s="213"/>
+      <c r="E48" s="82"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="85"/>
+      <c r="I48" s="83"/>
+      <c r="J48" s="83"/>
+      <c r="K48" s="83"/>
+      <c r="L48" s="83"/>
+      <c r="M48" s="83"/>
+      <c r="N48" s="83"/>
+      <c r="O48" s="83"/>
+      <c r="P48" s="83"/>
+      <c r="Q48" s="84"/>
+      <c r="R48" s="85"/>
+      <c r="S48" s="83"/>
+      <c r="T48" s="83"/>
+      <c r="U48" s="83"/>
+      <c r="V48" s="83"/>
+      <c r="W48" s="83"/>
+      <c r="X48" s="83"/>
+      <c r="Y48" s="83"/>
+      <c r="Z48" s="83"/>
+      <c r="AA48" s="84"/>
+      <c r="AB48" s="85"/>
+      <c r="AC48" s="83"/>
+      <c r="AD48" s="83"/>
+      <c r="AE48" s="83"/>
+      <c r="AF48" s="83"/>
+      <c r="AG48" s="83"/>
+      <c r="AH48" s="83"/>
+      <c r="AI48" s="83"/>
+      <c r="AJ48" s="83"/>
+      <c r="AK48" s="84"/>
+      <c r="AL48" s="85"/>
+      <c r="AM48" s="83"/>
+      <c r="AN48" s="83"/>
+      <c r="AO48" s="83"/>
+      <c r="AP48" s="83"/>
+      <c r="AQ48" s="83"/>
+      <c r="AR48" s="83"/>
+      <c r="AS48" s="83"/>
+      <c r="AT48" s="83"/>
+      <c r="AU48" s="84"/>
+      <c r="AV48" s="85"/>
+      <c r="AW48" s="83"/>
+    </row>
+    <row r="49" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <f>B47+$A$11</f>
         <v>20</v>
       </c>
-      <c r="C46" s="183" t="str">
-        <f>CONCATENATE(B46,"°")</f>
+      <c r="C49" s="213" t="str">
+        <f>CONCATENATE(B49,"°")</f>
         <v>20°</v>
       </c>
-      <c r="D46" s="183"/>
-      <c r="E46" s="184"/>
-      <c r="F46" s="218"/>
-      <c r="G46" s="219"/>
-      <c r="H46" s="220"/>
-      <c r="I46" s="218"/>
-      <c r="J46" s="218"/>
-      <c r="K46" s="218"/>
-      <c r="L46" s="218"/>
-      <c r="M46" s="218"/>
-      <c r="N46" s="218"/>
-      <c r="O46" s="218"/>
-      <c r="P46" s="218"/>
-      <c r="Q46" s="218"/>
-      <c r="R46" s="221"/>
-      <c r="S46" s="222"/>
-      <c r="T46" s="218"/>
-      <c r="U46" s="218"/>
-      <c r="V46" s="218"/>
-      <c r="W46" s="218"/>
-      <c r="X46" s="218"/>
-      <c r="Y46" s="218"/>
-      <c r="Z46" s="218"/>
-      <c r="AA46" s="218"/>
-      <c r="AB46" s="220"/>
-      <c r="AC46" s="218"/>
-      <c r="AD46" s="218"/>
-      <c r="AE46" s="218"/>
-      <c r="AF46" s="218"/>
-      <c r="AG46" s="218"/>
-      <c r="AH46" s="218"/>
-      <c r="AI46" s="218"/>
-      <c r="AJ46" s="218"/>
-      <c r="AK46" s="218"/>
-      <c r="AL46" s="220"/>
-      <c r="AM46" s="218"/>
-      <c r="AN46" s="218"/>
-      <c r="AO46" s="218"/>
-      <c r="AP46" s="218"/>
-      <c r="AQ46" s="218"/>
-      <c r="AR46" s="218"/>
-      <c r="AS46" s="218"/>
-      <c r="AT46" s="218"/>
-      <c r="AU46" s="218"/>
-      <c r="AV46" s="220"/>
-      <c r="AW46" s="218"/>
-    </row>
-    <row r="47" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="183"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="184"/>
-      <c r="F47" s="184"/>
-      <c r="G47" s="184"/>
-    </row>
-    <row r="48" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48">
-        <f>B46+$A$8</f>
+      <c r="D49" s="213"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="116"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="118"/>
+      <c r="I49" s="116"/>
+      <c r="J49" s="116"/>
+      <c r="K49" s="116"/>
+      <c r="L49" s="116"/>
+      <c r="M49" s="116"/>
+      <c r="N49" s="116"/>
+      <c r="O49" s="116"/>
+      <c r="P49" s="116"/>
+      <c r="Q49" s="116"/>
+      <c r="R49" s="119"/>
+      <c r="S49" s="120"/>
+      <c r="T49" s="116"/>
+      <c r="U49" s="116"/>
+      <c r="V49" s="116"/>
+      <c r="W49" s="116"/>
+      <c r="X49" s="116"/>
+      <c r="Y49" s="116"/>
+      <c r="Z49" s="116"/>
+      <c r="AA49" s="116"/>
+      <c r="AB49" s="118"/>
+      <c r="AC49" s="116"/>
+      <c r="AD49" s="116"/>
+      <c r="AE49" s="116"/>
+      <c r="AF49" s="116"/>
+      <c r="AG49" s="116"/>
+      <c r="AH49" s="116"/>
+      <c r="AI49" s="116"/>
+      <c r="AJ49" s="116"/>
+      <c r="AK49" s="116"/>
+      <c r="AL49" s="118"/>
+      <c r="AM49" s="116"/>
+      <c r="AN49" s="116"/>
+      <c r="AO49" s="116"/>
+      <c r="AP49" s="116"/>
+      <c r="AQ49" s="116"/>
+      <c r="AR49" s="116"/>
+      <c r="AS49" s="116"/>
+      <c r="AT49" s="116"/>
+      <c r="AU49" s="116"/>
+      <c r="AV49" s="118"/>
+      <c r="AW49" s="116"/>
+    </row>
+    <row r="50" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="213"/>
+      <c r="D50" s="213"/>
+      <c r="E50" s="82"/>
+      <c r="F50" s="82"/>
+      <c r="G50" s="82"/>
+    </row>
+    <row r="51" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <f>B49+$A$11</f>
         <v>40</v>
       </c>
-      <c r="C48" s="183" t="str">
-        <f>CONCATENATE(B48,"°")</f>
+      <c r="C51" s="213" t="str">
+        <f>CONCATENATE(B51,"°")</f>
         <v>40°</v>
       </c>
-      <c r="D48" s="223"/>
-      <c r="E48" s="184"/>
-      <c r="F48" s="184"/>
-      <c r="G48" s="184"/>
-    </row>
-    <row r="49" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="183"/>
-      <c r="D49" s="223"/>
-      <c r="E49" s="184"/>
-      <c r="F49" s="184"/>
-      <c r="G49" s="184"/>
-    </row>
-    <row r="50" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50">
-        <f>B48+$A$8</f>
+      <c r="D51" s="214"/>
+      <c r="E51" s="82"/>
+      <c r="F51" s="82"/>
+      <c r="G51" s="82"/>
+    </row>
+    <row r="52" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="213"/>
+      <c r="D52" s="214"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
+    </row>
+    <row r="53" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <f>B51+$A$11</f>
         <v>60</v>
       </c>
-      <c r="C50" s="183" t="str">
-        <f>CONCATENATE(B50,"°")</f>
+      <c r="C53" s="213" t="str">
+        <f>CONCATENATE(B53,"°")</f>
         <v>60°</v>
       </c>
-      <c r="D50" s="223"/>
-      <c r="E50" s="184"/>
-      <c r="F50" s="184"/>
-      <c r="G50" s="184"/>
-    </row>
-    <row r="51" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="183"/>
-      <c r="D51" s="223"/>
-      <c r="E51" s="184"/>
-      <c r="F51" s="184"/>
-      <c r="G51" s="184"/>
-    </row>
-    <row r="52" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52">
-        <f>B50+$A$8</f>
+      <c r="D53" s="214"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="82"/>
+      <c r="G53" s="82"/>
+    </row>
+    <row r="54" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="213"/>
+      <c r="D54" s="214"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+    </row>
+    <row r="55" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <f>B53+$A$11</f>
         <v>80</v>
       </c>
-      <c r="C52" s="183" t="str">
-        <f>CONCATENATE(B52,"°")</f>
+      <c r="C55" s="213" t="str">
+        <f>CONCATENATE(B55,"°")</f>
         <v>80°</v>
       </c>
-      <c r="D52" s="223"/>
-      <c r="E52" s="184"/>
-      <c r="F52" s="184"/>
-      <c r="G52" s="184"/>
-    </row>
-    <row r="53" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="183"/>
-      <c r="D53" s="223"/>
-      <c r="E53" s="184"/>
-      <c r="F53" s="184"/>
-      <c r="G53" s="184"/>
-    </row>
-    <row r="54" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54">
-        <f>B52+$A$8</f>
+      <c r="D55" s="214"/>
+      <c r="E55" s="82"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="82"/>
+    </row>
+    <row r="56" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="213"/>
+      <c r="D56" s="214"/>
+      <c r="E56" s="82"/>
+      <c r="F56" s="82"/>
+      <c r="G56" s="82"/>
+    </row>
+    <row r="57" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <f>B55+$A$11</f>
         <v>100</v>
       </c>
-      <c r="C54" s="183" t="str">
-        <f>CONCATENATE(B54,"°")</f>
+      <c r="C57" s="213" t="str">
+        <f>CONCATENATE(B57,"°")</f>
         <v>100°</v>
       </c>
-      <c r="D54" s="223"/>
-      <c r="E54" s="184"/>
-      <c r="F54" s="184"/>
-      <c r="G54" s="184"/>
-    </row>
-    <row r="55" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="183"/>
-      <c r="D55" s="223"/>
-      <c r="E55" s="184"/>
-      <c r="F55" s="184"/>
-      <c r="G55" s="184"/>
-    </row>
-    <row r="56" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56">
-        <f>B54+$A$8</f>
+      <c r="D57" s="214"/>
+      <c r="E57" s="82"/>
+      <c r="F57" s="82"/>
+      <c r="G57" s="82"/>
+    </row>
+    <row r="58" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="213"/>
+      <c r="D58" s="214"/>
+      <c r="E58" s="82"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
+    </row>
+    <row r="59" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <f>B57+$A$11</f>
         <v>120</v>
       </c>
-      <c r="C56" s="183" t="str">
-        <f>CONCATENATE(B56,"°")</f>
+      <c r="C59" s="213" t="str">
+        <f>CONCATENATE(B59,"°")</f>
         <v>120°</v>
       </c>
-      <c r="D56" s="223"/>
-      <c r="E56" s="184"/>
-      <c r="F56" s="184"/>
-      <c r="G56" s="184"/>
-    </row>
-    <row r="57" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="183"/>
-      <c r="D57" s="223"/>
-      <c r="E57" s="184"/>
-      <c r="F57" s="184"/>
-      <c r="G57" s="184"/>
-    </row>
-    <row r="58" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58">
-        <f>B56+$A$8</f>
+      <c r="D59" s="214"/>
+      <c r="E59" s="82"/>
+      <c r="F59" s="82"/>
+      <c r="G59" s="82"/>
+    </row>
+    <row r="60" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="213"/>
+      <c r="D60" s="214"/>
+      <c r="E60" s="82"/>
+      <c r="F60" s="82"/>
+      <c r="G60" s="82"/>
+    </row>
+    <row r="61" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <f>B59+$A$11</f>
         <v>140</v>
       </c>
-      <c r="C58" s="183" t="str">
-        <f>CONCATENATE(B58,"°")</f>
+      <c r="C61" s="213" t="str">
+        <f>CONCATENATE(B61,"°")</f>
         <v>140°</v>
       </c>
-      <c r="D58" s="223"/>
-      <c r="E58" s="184"/>
-      <c r="F58" s="184"/>
-      <c r="G58" s="184"/>
-    </row>
-    <row r="59" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="183"/>
-      <c r="D59" s="223"/>
-      <c r="E59" s="184"/>
-      <c r="F59" s="184"/>
-      <c r="G59" s="184"/>
-    </row>
-    <row r="60" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60">
-        <f>B58+$A$8</f>
+      <c r="D61" s="214"/>
+      <c r="E61" s="82"/>
+      <c r="F61" s="82"/>
+      <c r="G61" s="82"/>
+    </row>
+    <row r="62" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="213"/>
+      <c r="D62" s="214"/>
+      <c r="E62" s="82"/>
+      <c r="F62" s="82"/>
+      <c r="G62" s="82"/>
+    </row>
+    <row r="63" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <f>B61+$A$11</f>
         <v>160</v>
       </c>
-      <c r="C60" s="183" t="str">
-        <f>CONCATENATE(B60,"°")</f>
+      <c r="C63" s="213" t="str">
+        <f>CONCATENATE(B63,"°")</f>
         <v>160°</v>
       </c>
-      <c r="D60" s="223"/>
-      <c r="E60" s="184"/>
-      <c r="F60" s="184"/>
-      <c r="G60" s="184"/>
-    </row>
-    <row r="61" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="183"/>
-      <c r="D61" s="223"/>
-      <c r="E61" s="184"/>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-    </row>
-    <row r="62" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62">
-        <f>B60+$A$8</f>
+      <c r="D63" s="214"/>
+      <c r="E63" s="82"/>
+      <c r="F63" s="82"/>
+      <c r="G63" s="82"/>
+    </row>
+    <row r="64" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="213"/>
+      <c r="D64" s="214"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="82"/>
+    </row>
+    <row r="65" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <f>B63+$A$11</f>
         <v>180</v>
       </c>
-      <c r="C62" s="183" t="str">
-        <f>CONCATENATE(B62,"°")</f>
+      <c r="C65" s="213" t="str">
+        <f>CONCATENATE(B65,"°")</f>
         <v>180°</v>
       </c>
-      <c r="D62" s="223"/>
-      <c r="E62" s="184"/>
-      <c r="F62" s="184"/>
-      <c r="G62" s="184"/>
-    </row>
-    <row r="63" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="183"/>
-      <c r="D63" s="223"/>
-      <c r="E63" s="184"/>
-      <c r="F63" s="184"/>
-      <c r="G63" s="184"/>
-    </row>
-    <row r="64" spans="2:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64">
-        <f>B62+$A$8</f>
+      <c r="D65" s="214"/>
+      <c r="E65" s="82"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="82"/>
+    </row>
+    <row r="66" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="213"/>
+      <c r="D66" s="214"/>
+      <c r="E66" s="82"/>
+      <c r="F66" s="82"/>
+      <c r="G66" s="82"/>
+    </row>
+    <row r="67" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <f>B65+$A$11</f>
         <v>200</v>
       </c>
-      <c r="C64" s="183" t="str">
-        <f>CONCATENATE(B64,"°")</f>
+      <c r="C67" s="213" t="str">
+        <f>CONCATENATE(B67,"°")</f>
         <v>200°</v>
       </c>
-      <c r="D64" s="223"/>
-      <c r="E64" s="184"/>
-      <c r="F64" s="184"/>
-      <c r="G64" s="184"/>
-    </row>
-    <row r="65" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="183"/>
-      <c r="D65" s="223"/>
-      <c r="E65" s="184"/>
-      <c r="F65" s="184"/>
-      <c r="G65" s="184"/>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A68" s="169" t="s">
+      <c r="D67" s="214"/>
+      <c r="E67" s="82"/>
+      <c r="F67" s="82"/>
+      <c r="G67" s="82"/>
+    </row>
+    <row r="68" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="213"/>
+      <c r="D68" s="214"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A71" s="215" t="s">
         <v>143</v>
       </c>
-      <c r="B68" s="169"/>
-      <c r="C68" s="169"/>
-      <c r="D68" s="169"/>
-      <c r="E68" s="169"/>
-      <c r="F68" s="169"/>
-      <c r="G68" s="169"/>
-      <c r="H68" s="169"/>
-      <c r="I68" s="169"/>
-      <c r="J68" s="169"/>
-      <c r="K68" s="169"/>
-      <c r="L68" s="169"/>
-      <c r="M68" s="169"/>
-      <c r="N68" s="169"/>
-      <c r="O68" s="169"/>
-      <c r="P68" s="169"/>
-      <c r="Q68" s="169"/>
-      <c r="R68" s="169"/>
-      <c r="S68" s="169"/>
-      <c r="T68" s="169"/>
-      <c r="U68" s="169"/>
-      <c r="V68" s="169"/>
-      <c r="W68" s="169"/>
-      <c r="X68" s="169"/>
-      <c r="Y68" s="169"/>
-      <c r="Z68" s="169"/>
-      <c r="AA68" s="169"/>
-      <c r="AB68" s="169"/>
-      <c r="AC68" s="169"/>
-      <c r="AD68" s="169"/>
-      <c r="AE68" s="169"/>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A69" s="169"/>
-      <c r="B69" s="169"/>
-      <c r="C69" s="169"/>
-      <c r="D69" s="169"/>
-      <c r="E69" s="169"/>
-      <c r="F69" s="169"/>
-      <c r="G69" s="169"/>
-      <c r="H69" s="169"/>
-      <c r="I69" s="169"/>
-      <c r="J69" s="169"/>
-      <c r="K69" s="169"/>
-      <c r="L69" s="169"/>
-      <c r="M69" s="169"/>
-      <c r="N69" s="169"/>
-      <c r="O69" s="169"/>
-      <c r="P69" s="169"/>
-      <c r="Q69" s="169"/>
-      <c r="R69" s="169"/>
-      <c r="S69" s="169"/>
-      <c r="T69" s="169"/>
-      <c r="U69" s="169"/>
-      <c r="V69" s="169"/>
-      <c r="W69" s="169"/>
-      <c r="X69" s="169"/>
-      <c r="Y69" s="169"/>
-      <c r="Z69" s="169"/>
-      <c r="AA69" s="169"/>
-      <c r="AB69" s="169"/>
-      <c r="AC69" s="169"/>
-      <c r="AD69" s="169"/>
-      <c r="AE69" s="169"/>
-    </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
+      <c r="B71" s="215"/>
+      <c r="C71" s="215"/>
+      <c r="D71" s="215"/>
+      <c r="E71" s="215"/>
+      <c r="F71" s="215"/>
+      <c r="G71" s="215"/>
+      <c r="H71" s="215"/>
+      <c r="I71" s="215"/>
+      <c r="J71" s="215"/>
+      <c r="K71" s="215"/>
+      <c r="L71" s="215"/>
+      <c r="M71" s="215"/>
+      <c r="N71" s="215"/>
+      <c r="O71" s="215"/>
+      <c r="P71" s="215"/>
+      <c r="Q71" s="215"/>
+      <c r="R71" s="215"/>
+      <c r="S71" s="215"/>
+      <c r="T71" s="215"/>
+      <c r="U71" s="215"/>
+      <c r="V71" s="215"/>
+      <c r="W71" s="215"/>
+      <c r="X71" s="215"/>
+      <c r="Y71" s="215"/>
+      <c r="Z71" s="215"/>
+      <c r="AA71" s="215"/>
+      <c r="AB71" s="215"/>
+      <c r="AC71" s="215"/>
+      <c r="AD71" s="215"/>
+      <c r="AE71" s="215"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A72" s="215"/>
+      <c r="B72" s="215"/>
+      <c r="C72" s="215"/>
+      <c r="D72" s="215"/>
+      <c r="E72" s="215"/>
+      <c r="F72" s="215"/>
+      <c r="G72" s="215"/>
+      <c r="H72" s="215"/>
+      <c r="I72" s="215"/>
+      <c r="J72" s="215"/>
+      <c r="K72" s="215"/>
+      <c r="L72" s="215"/>
+      <c r="M72" s="215"/>
+      <c r="N72" s="215"/>
+      <c r="O72" s="215"/>
+      <c r="P72" s="215"/>
+      <c r="Q72" s="215"/>
+      <c r="R72" s="215"/>
+      <c r="S72" s="215"/>
+      <c r="T72" s="215"/>
+      <c r="U72" s="215"/>
+      <c r="V72" s="215"/>
+      <c r="W72" s="215"/>
+      <c r="X72" s="215"/>
+      <c r="Y72" s="215"/>
+      <c r="Z72" s="215"/>
+      <c r="AA72" s="215"/>
+      <c r="AB72" s="215"/>
+      <c r="AC72" s="215"/>
+      <c r="AD72" s="215"/>
+      <c r="AE72" s="215"/>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="C72" s="224" t="s">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C75" s="121" t="s">
         <v>145</v>
       </c>
-      <c r="D72" s="224"/>
-      <c r="E72" s="224"/>
-      <c r="F72" s="224"/>
-      <c r="G72" s="224"/>
-      <c r="H72" s="224"/>
-      <c r="I72" s="224"/>
-      <c r="J72" s="224"/>
-    </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="D73" t="s">
+      <c r="D75" s="121"/>
+      <c r="E75" s="121"/>
+      <c r="F75" s="121"/>
+      <c r="G75" s="121"/>
+      <c r="H75" s="121"/>
+      <c r="I75" s="121"/>
+      <c r="J75" s="121"/>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="D74" t="s">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="D75" t="s">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="D76" s="225" t="s">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="D79" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="E76" s="225"/>
-      <c r="F76" s="225"/>
-      <c r="G76" s="225"/>
-      <c r="H76" s="226"/>
-      <c r="I76" s="226"/>
-      <c r="J76" s="226"/>
-    </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="C78" s="224" t="s">
+      <c r="E79" s="122"/>
+      <c r="F79" s="122"/>
+      <c r="G79" s="122"/>
+      <c r="H79" s="123"/>
+      <c r="I79" s="123"/>
+      <c r="J79" s="123"/>
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C81" s="121" t="s">
         <v>150</v>
       </c>
-      <c r="D78" s="224"/>
-      <c r="E78" s="224"/>
-      <c r="F78" s="224"/>
-      <c r="G78" s="224"/>
-      <c r="H78" s="224"/>
-      <c r="I78" s="224"/>
-      <c r="J78" s="224"/>
-    </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="D79" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C81" s="224" t="s">
-        <v>152</v>
-      </c>
-      <c r="D81" s="224"/>
-      <c r="E81" s="224"/>
-      <c r="F81" s="224"/>
-      <c r="G81" s="224"/>
-      <c r="H81" s="224"/>
-      <c r="I81" s="224"/>
-      <c r="J81" s="224"/>
+      <c r="D81" s="121"/>
+      <c r="E81" s="121"/>
+      <c r="F81" s="121"/>
+      <c r="G81" s="121"/>
+      <c r="H81" s="121"/>
+      <c r="I81" s="121"/>
+      <c r="J81" s="121"/>
     </row>
     <row r="82" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D82" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C84" t="s">
-        <v>154</v>
-      </c>
+      <c r="C84" s="121" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84" s="121"/>
+      <c r="E84" s="121"/>
+      <c r="F84" s="121"/>
+      <c r="G84" s="121"/>
+      <c r="H84" s="121"/>
+      <c r="I84" s="121"/>
+      <c r="J84" s="121"/>
     </row>
     <row r="85" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D85" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="D86" t="s">
+    <row r="89" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
         <v>156</v>
       </c>
-      <c r="I86" t="s">
+      <c r="I89" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="I87" t="s">
+    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="I90" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="89" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="C60:D61"/>
-    <mergeCell ref="C62:D63"/>
-    <mergeCell ref="C64:D65"/>
-    <mergeCell ref="A68:AE69"/>
-    <mergeCell ref="C48:D49"/>
-    <mergeCell ref="C50:D51"/>
-    <mergeCell ref="C52:D53"/>
-    <mergeCell ref="C54:D55"/>
-    <mergeCell ref="C56:D57"/>
-    <mergeCell ref="C58:D59"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="C42:D43"/>
-    <mergeCell ref="C44:D45"/>
-    <mergeCell ref="C46:D47"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="AP7:AQ8"/>
-    <mergeCell ref="AR7:AS8"/>
-    <mergeCell ref="AT7:AU8"/>
-    <mergeCell ref="AV7:AW8"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="AD7:AE8"/>
-    <mergeCell ref="AF7:AG8"/>
-    <mergeCell ref="AH7:AI8"/>
-    <mergeCell ref="AJ7:AK8"/>
-    <mergeCell ref="AL7:AM8"/>
-    <mergeCell ref="AN7:AO8"/>
-    <mergeCell ref="R7:S8"/>
-    <mergeCell ref="T7:U8"/>
-    <mergeCell ref="V7:W8"/>
-    <mergeCell ref="X7:Y8"/>
-    <mergeCell ref="Z7:AA8"/>
-    <mergeCell ref="AB7:AC8"/>
-    <mergeCell ref="AO6:AP6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="AS6:AT6"/>
-    <mergeCell ref="AW6:AX6"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="H7:I8"/>
-    <mergeCell ref="J7:K8"/>
-    <mergeCell ref="L7:M8"/>
-    <mergeCell ref="N7:O8"/>
-    <mergeCell ref="P7:Q8"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AG6:AH6"/>
-    <mergeCell ref="AI6:AJ6"/>
-    <mergeCell ref="AM6:AN6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="C1:AX2"/>
-    <mergeCell ref="G5:H6"/>
-    <mergeCell ref="Q5:R6"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="AA5:AB6"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="AK5:AL6"/>
-    <mergeCell ref="AU5:AV6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:X9"/>
+    <mergeCell ref="C4:AX5"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="Q8:R9"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="AA8:AB9"/>
+    <mergeCell ref="AE8:AF8"/>
+    <mergeCell ref="AK8:AL9"/>
+    <mergeCell ref="AU8:AV9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="AS9:AT9"/>
+    <mergeCell ref="AW9:AX9"/>
+    <mergeCell ref="F10:G11"/>
+    <mergeCell ref="H10:I11"/>
+    <mergeCell ref="J10:K11"/>
+    <mergeCell ref="L10:M11"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="AG9:AH9"/>
+    <mergeCell ref="AI9:AJ9"/>
+    <mergeCell ref="AM9:AN9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="X10:Y11"/>
+    <mergeCell ref="Z10:AA11"/>
+    <mergeCell ref="AB10:AC11"/>
+    <mergeCell ref="AO9:AP9"/>
+    <mergeCell ref="AQ9:AR9"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="AP10:AQ11"/>
+    <mergeCell ref="AR10:AS11"/>
+    <mergeCell ref="AT10:AU11"/>
+    <mergeCell ref="AV10:AW11"/>
+    <mergeCell ref="C11:D12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="AD10:AE11"/>
+    <mergeCell ref="AF10:AG11"/>
+    <mergeCell ref="AH10:AI11"/>
+    <mergeCell ref="AJ10:AK11"/>
+    <mergeCell ref="AL10:AM11"/>
+    <mergeCell ref="AN10:AO11"/>
+    <mergeCell ref="R10:S11"/>
+    <mergeCell ref="T10:U11"/>
+    <mergeCell ref="V10:W11"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="C47:D48"/>
+    <mergeCell ref="C63:D64"/>
+    <mergeCell ref="C65:D66"/>
+    <mergeCell ref="C67:D68"/>
+    <mergeCell ref="A71:AE72"/>
+    <mergeCell ref="C51:D52"/>
+    <mergeCell ref="C53:D54"/>
+    <mergeCell ref="C55:D56"/>
+    <mergeCell ref="C57:D58"/>
+    <mergeCell ref="C59:D60"/>
+    <mergeCell ref="C61:D62"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ProjetXLS/JournalDeBord/JournalDeBord.xlsx
+++ b/ProjetXLS/JournalDeBord/JournalDeBord.xlsx
@@ -1,42 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\data\git\bateau\NavigationBateau\ProjetXLS\JournalDeBord\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpaces\WS\GitHub\Navigation\NavigationBateau\ProjetXLS\JournalDeBord\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C7110-5BFD-4323-B01B-C3FFABD671A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CFE188-F54E-4385-8DA2-CA7DDFD73245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="240" windowWidth="25230" windowHeight="15060" activeTab="4" xr2:uid="{E20D9DF7-46DF-4441-A87B-8D054A4C81F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" activeTab="5" xr2:uid="{E20D9DF7-46DF-4441-A87B-8D054A4C81F1}"/>
   </bookViews>
   <sheets>
     <sheet name="premiere page" sheetId="6" r:id="rId1"/>
     <sheet name="inverse pour impression" sheetId="1" r:id="rId2"/>
     <sheet name="Page prise meteo" sheetId="3" r:id="rId3"/>
     <sheet name="GrilleCompas" sheetId="8" r:id="rId4"/>
-    <sheet name="VoileVent (2)" sheetId="10" r:id="rId5"/>
+    <sheet name="AvantPage1" sheetId="11" r:id="rId5"/>
+    <sheet name="VoileVent (2)" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">AvantPage1!$B$2:$P$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">GrilleCompas!$C$1:$AX$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'inverse pour impression'!$B$2:$AA$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Page prise meteo'!$B$2:$Q$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'premiere page'!$B$2:$AA$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'VoileVent (2)'!$B$2:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'VoileVent (2)'!$B$2:$N$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="204">
   <si>
     <t xml:space="preserve">Date: </t>
   </si>
@@ -602,9 +613,6 @@
     <t>Date de mise jour:</t>
   </si>
   <si>
-    <t xml:space="preserve">Vent </t>
-  </si>
-  <si>
     <t>Prés</t>
   </si>
   <si>
@@ -614,9 +622,6 @@
     <t>Gd Large</t>
   </si>
   <si>
-    <t>Vent Arriere</t>
-  </si>
-  <si>
     <t>Bon plein</t>
   </si>
   <si>
@@ -656,21 +661,6 @@
     <t>F12</t>
   </si>
   <si>
-    <t>GV 1</t>
-  </si>
-  <si>
-    <t>trinquette</t>
-  </si>
-  <si>
-    <t>Clinfoc</t>
-  </si>
-  <si>
-    <t>foc en hauteur</t>
-  </si>
-  <si>
-    <t>foc le plus pres du mat</t>
-  </si>
-  <si>
     <t>15°</t>
   </si>
   <si>
@@ -683,9 +673,6 @@
     <t>0°</t>
   </si>
   <si>
-    <t>Dérive</t>
-  </si>
-  <si>
     <t>1 - 3</t>
   </si>
   <si>
@@ -725,32 +712,44 @@
     <t>F0</t>
   </si>
   <si>
-    <t>Spi</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GV  </t>
-  </si>
-  <si>
-    <t>GV</t>
-  </si>
-  <si>
-    <t>Fuite - Tourmentin</t>
-  </si>
-  <si>
-    <t>GV 3 + Tourmentin</t>
-  </si>
-  <si>
-    <t>GV 2</t>
+    <t>Derive</t>
+  </si>
+  <si>
+    <t>Pres</t>
+  </si>
+  <si>
+    <t>Vent arriere</t>
+  </si>
+  <si>
+    <t>petit largue</t>
+  </si>
+  <si>
+    <t>Fuite / tourmentin / a sec</t>
+  </si>
+  <si>
+    <t>Suedoise + tourmentin</t>
+  </si>
+  <si>
+    <t>GV3 + tourmentin</t>
+  </si>
+  <si>
+    <t>Gd Largue</t>
+  </si>
+  <si>
+    <t>Vent Arrière</t>
+  </si>
+  <si>
+    <t>Moyen</t>
+  </si>
+  <si>
+    <t>Fort</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -895,17 +894,72 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
-      <name val="Roboto"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF7030A0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -943,18 +997,39 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC775"/>
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE7EA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC9C9"/>
+        <fgColor rgb="FFFFF9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF9EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="168">
+  <borders count="170">
     <border>
       <left/>
       <right/>
@@ -2931,86 +3006,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -3020,155 +3015,240 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0070C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0070C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0070C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0070C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right style="thin">
+        <color rgb="FF0070C0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0070C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0070C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </diagonal>
+    </border>
+    <border diagonalDown="1">
+      <left/>
+      <right style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal style="thin">
+        <color theme="8" tint="-0.24994659260841701"/>
+      </diagonal>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="153" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3357,87 +3437,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="151" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="152" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="160" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="150" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="20" fillId="0" borderId="149" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="162" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="149" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="149" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="149" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="165" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="161" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="149" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="162" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="163" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="157" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="158" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3747,48 +3746,139 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="151" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="153" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="149" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="149" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="149" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="151" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="154" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="156" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="155" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="152" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="101" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="102" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="150" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="103" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="104" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="100" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="149" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="16" fontId="24" fillId="12" borderId="149" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="149" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="149" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="157" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="158" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="159" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="160" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="161" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="152" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="153" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="154" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="166" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="167" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="168" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="169" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Satisfaisant" xfId="1" builtinId="26"/>
+    <cellStyle name="Output" xfId="4" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFEBF9EE"/>
+      <color rgb="FFFFF9E1"/>
+      <color rgb="FFFFE7EA"/>
       <color rgb="FFFFC9C9"/>
       <color rgb="FFFF7171"/>
       <color rgb="FFFFC775"/>
@@ -4522,7 +4612,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4822,7 +4912,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="11.42578125" style="1"/>
     <col min="5" max="6" width="12.140625" style="1" customWidth="1"/>
@@ -4839,7 +4929,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
         <f t="shared" ref="B1:N1" si="0">A1+1</f>
         <v>1</v>
@@ -4944,7 +5034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="22.5" customHeight="1">
+    <row r="2" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
@@ -4958,23 +5048,23 @@
       <c r="L2"/>
       <c r="M2"/>
       <c r="N2"/>
-      <c r="O2" s="151" t="s">
+      <c r="O2" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="152"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="153"/>
-    </row>
-    <row r="3" spans="2:27" ht="22.5" customHeight="1">
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="126"/>
+    </row>
+    <row r="3" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
@@ -4988,21 +5078,21 @@
       <c r="L3"/>
       <c r="M3"/>
       <c r="N3"/>
-      <c r="O3" s="154"/>
-      <c r="P3" s="155"/>
-      <c r="Q3" s="155"/>
-      <c r="R3" s="155"/>
-      <c r="S3" s="155"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="155"/>
-      <c r="V3" s="155"/>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="155"/>
-      <c r="Z3" s="155"/>
-      <c r="AA3" s="156"/>
-    </row>
-    <row r="4" spans="2:27" ht="22.5" customHeight="1">
+      <c r="O3" s="127"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="129"/>
+    </row>
+    <row r="4" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
@@ -5016,25 +5106,25 @@
       <c r="L4"/>
       <c r="M4"/>
       <c r="N4"/>
-      <c r="O4" s="157" t="s">
+      <c r="O4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="158"/>
-      <c r="Q4" s="158"/>
-      <c r="R4" s="158"/>
-      <c r="S4" s="158"/>
-      <c r="T4" s="158"/>
-      <c r="U4" s="159"/>
-      <c r="V4" s="160" t="s">
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="131"/>
+      <c r="U4" s="132"/>
+      <c r="V4" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="158"/>
-      <c r="X4" s="158"/>
-      <c r="Y4" s="158"/>
-      <c r="Z4" s="158"/>
-      <c r="AA4" s="161"/>
-    </row>
-    <row r="5" spans="2:27" ht="22.5" customHeight="1">
+      <c r="W4" s="131"/>
+      <c r="X4" s="131"/>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="134"/>
+    </row>
+    <row r="5" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
@@ -5064,7 +5154,7 @@
       <c r="Z5" s="44"/>
       <c r="AA5" s="45"/>
     </row>
-    <row r="6" spans="2:27" ht="22.5" customHeight="1">
+    <row r="6" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
@@ -5092,7 +5182,7 @@
       <c r="Z6" s="47"/>
       <c r="AA6" s="48"/>
     </row>
-    <row r="7" spans="2:27" ht="22.5" customHeight="1">
+    <row r="7" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
@@ -5120,7 +5210,7 @@
       <c r="Z7" s="50"/>
       <c r="AA7" s="51"/>
     </row>
-    <row r="8" spans="2:27" ht="22.5" customHeight="1">
+    <row r="8" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -5134,23 +5224,23 @@
       <c r="L8"/>
       <c r="M8"/>
       <c r="N8"/>
-      <c r="O8" s="162" t="s">
+      <c r="O8" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="163"/>
-      <c r="Q8" s="163"/>
-      <c r="R8" s="163"/>
-      <c r="S8" s="163"/>
-      <c r="T8" s="163"/>
-      <c r="U8" s="163"/>
-      <c r="V8" s="163"/>
-      <c r="W8" s="163"/>
-      <c r="X8" s="163"/>
-      <c r="Y8" s="163"/>
-      <c r="Z8" s="163"/>
-      <c r="AA8" s="164"/>
-    </row>
-    <row r="9" spans="2:27" ht="22.5" customHeight="1">
+      <c r="P8" s="136"/>
+      <c r="Q8" s="136"/>
+      <c r="R8" s="136"/>
+      <c r="S8" s="136"/>
+      <c r="T8" s="136"/>
+      <c r="U8" s="136"/>
+      <c r="V8" s="136"/>
+      <c r="W8" s="136"/>
+      <c r="X8" s="136"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="136"/>
+      <c r="AA8" s="137"/>
+    </row>
+    <row r="9" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
@@ -5164,27 +5254,27 @@
       <c r="L9"/>
       <c r="M9"/>
       <c r="N9"/>
-      <c r="O9" s="171" t="s">
+      <c r="O9" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="172"/>
-      <c r="Q9" s="172"/>
-      <c r="R9" s="172"/>
-      <c r="S9" s="172"/>
-      <c r="T9" s="172" t="s">
+      <c r="P9" s="145"/>
+      <c r="Q9" s="145"/>
+      <c r="R9" s="145"/>
+      <c r="S9" s="145"/>
+      <c r="T9" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="172"/>
-      <c r="V9" s="172"/>
-      <c r="W9" s="172"/>
-      <c r="X9" s="172"/>
-      <c r="Y9" s="172" t="s">
+      <c r="U9" s="145"/>
+      <c r="V9" s="145"/>
+      <c r="W9" s="145"/>
+      <c r="X9" s="145"/>
+      <c r="Y9" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="Z9" s="172"/>
-      <c r="AA9" s="173"/>
-    </row>
-    <row r="10" spans="2:27" ht="22.5" customHeight="1">
+      <c r="Z9" s="145"/>
+      <c r="AA9" s="146"/>
+    </row>
+    <row r="10" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
@@ -5198,27 +5288,27 @@
       <c r="L10"/>
       <c r="M10"/>
       <c r="N10"/>
-      <c r="O10" s="165" t="s">
+      <c r="O10" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="166"/>
-      <c r="Q10" s="166"/>
-      <c r="R10" s="166"/>
-      <c r="S10" s="166"/>
-      <c r="T10" s="166" t="s">
+      <c r="P10" s="139"/>
+      <c r="Q10" s="139"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
+      <c r="T10" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="166"/>
-      <c r="V10" s="166"/>
-      <c r="W10" s="166"/>
-      <c r="X10" s="166"/>
-      <c r="Y10" s="166" t="s">
+      <c r="U10" s="139"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="139"/>
+      <c r="Y10" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="Z10" s="166"/>
-      <c r="AA10" s="167"/>
-    </row>
-    <row r="11" spans="2:27" ht="22.5" customHeight="1">
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="140"/>
+    </row>
+    <row r="11" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
@@ -5232,27 +5322,27 @@
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11"/>
-      <c r="O11" s="165" t="s">
+      <c r="O11" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="166"/>
-      <c r="Q11" s="166"/>
-      <c r="R11" s="166"/>
-      <c r="S11" s="166"/>
-      <c r="T11" s="166" t="s">
+      <c r="P11" s="139"/>
+      <c r="Q11" s="139"/>
+      <c r="R11" s="139"/>
+      <c r="S11" s="139"/>
+      <c r="T11" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="166"/>
-      <c r="V11" s="166"/>
-      <c r="W11" s="166"/>
-      <c r="X11" s="166"/>
-      <c r="Y11" s="166" t="s">
+      <c r="U11" s="139"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="139"/>
+      <c r="X11" s="139"/>
+      <c r="Y11" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="167"/>
-    </row>
-    <row r="12" spans="2:27" ht="22.5" customHeight="1">
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="140"/>
+    </row>
+    <row r="12" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
@@ -5266,23 +5356,23 @@
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12"/>
-      <c r="O12" s="168" t="s">
+      <c r="O12" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="169"/>
-      <c r="R12" s="169"/>
-      <c r="S12" s="169"/>
-      <c r="T12" s="169"/>
-      <c r="U12" s="169"/>
-      <c r="V12" s="169"/>
-      <c r="W12" s="169"/>
-      <c r="X12" s="169"/>
-      <c r="Y12" s="169"/>
-      <c r="Z12" s="169"/>
-      <c r="AA12" s="170"/>
-    </row>
-    <row r="13" spans="2:27" ht="22.5" customHeight="1">
+      <c r="P12" s="142"/>
+      <c r="Q12" s="142"/>
+      <c r="R12" s="142"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="142"/>
+      <c r="U12" s="142"/>
+      <c r="V12" s="142"/>
+      <c r="W12" s="142"/>
+      <c r="X12" s="142"/>
+      <c r="Y12" s="142"/>
+      <c r="Z12" s="142"/>
+      <c r="AA12" s="143"/>
+    </row>
+    <row r="13" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -5296,23 +5386,23 @@
       <c r="L13"/>
       <c r="M13"/>
       <c r="N13"/>
-      <c r="O13" s="162" t="s">
+      <c r="O13" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="163"/>
-      <c r="Q13" s="163"/>
-      <c r="R13" s="163"/>
-      <c r="S13" s="163"/>
-      <c r="T13" s="163"/>
-      <c r="U13" s="163"/>
-      <c r="V13" s="163"/>
-      <c r="W13" s="163"/>
-      <c r="X13" s="163"/>
-      <c r="Y13" s="163"/>
-      <c r="Z13" s="163"/>
-      <c r="AA13" s="164"/>
-    </row>
-    <row r="14" spans="2:27" ht="22.5" customHeight="1">
+      <c r="P13" s="136"/>
+      <c r="Q13" s="136"/>
+      <c r="R13" s="136"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="136"/>
+      <c r="U13" s="136"/>
+      <c r="V13" s="136"/>
+      <c r="W13" s="136"/>
+      <c r="X13" s="136"/>
+      <c r="Y13" s="136"/>
+      <c r="Z13" s="136"/>
+      <c r="AA13" s="137"/>
+    </row>
+    <row r="14" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -5326,27 +5416,27 @@
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
-      <c r="O14" s="171" t="s">
+      <c r="O14" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="172"/>
-      <c r="Q14" s="172"/>
-      <c r="R14" s="172"/>
-      <c r="S14" s="172"/>
-      <c r="T14" s="172" t="s">
+      <c r="P14" s="145"/>
+      <c r="Q14" s="145"/>
+      <c r="R14" s="145"/>
+      <c r="S14" s="145"/>
+      <c r="T14" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="U14" s="172"/>
-      <c r="V14" s="172"/>
-      <c r="W14" s="172"/>
-      <c r="X14" s="172"/>
-      <c r="Y14" s="172" t="s">
+      <c r="U14" s="145"/>
+      <c r="V14" s="145"/>
+      <c r="W14" s="145"/>
+      <c r="X14" s="145"/>
+      <c r="Y14" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="172"/>
-      <c r="AA14" s="173"/>
-    </row>
-    <row r="15" spans="2:27" ht="22.5" customHeight="1">
+      <c r="Z14" s="145"/>
+      <c r="AA14" s="146"/>
+    </row>
+    <row r="15" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -5360,27 +5450,27 @@
       <c r="L15"/>
       <c r="M15"/>
       <c r="N15"/>
-      <c r="O15" s="165" t="s">
+      <c r="O15" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="166"/>
-      <c r="Q15" s="166"/>
-      <c r="R15" s="166"/>
-      <c r="S15" s="166"/>
-      <c r="T15" s="166" t="s">
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="U15" s="166"/>
-      <c r="V15" s="166"/>
-      <c r="W15" s="166"/>
-      <c r="X15" s="166"/>
-      <c r="Y15" s="166" t="s">
+      <c r="U15" s="139"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
+      <c r="X15" s="139"/>
+      <c r="Y15" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="Z15" s="166"/>
-      <c r="AA15" s="167"/>
-    </row>
-    <row r="16" spans="2:27" ht="22.5" customHeight="1">
+      <c r="Z15" s="139"/>
+      <c r="AA15" s="140"/>
+    </row>
+    <row r="16" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -5394,27 +5484,27 @@
       <c r="L16"/>
       <c r="M16"/>
       <c r="N16"/>
-      <c r="O16" s="165" t="s">
+      <c r="O16" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="166"/>
-      <c r="Q16" s="166"/>
-      <c r="R16" s="166"/>
-      <c r="S16" s="166"/>
-      <c r="T16" s="166" t="s">
+      <c r="P16" s="139"/>
+      <c r="Q16" s="139"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
+      <c r="T16" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="166"/>
-      <c r="V16" s="166"/>
-      <c r="W16" s="166"/>
-      <c r="X16" s="166"/>
-      <c r="Y16" s="166" t="s">
+      <c r="U16" s="139"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="139"/>
+      <c r="X16" s="139"/>
+      <c r="Y16" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="166"/>
-      <c r="AA16" s="167"/>
-    </row>
-    <row r="17" spans="1:27" ht="22.5" customHeight="1">
+      <c r="Z16" s="139"/>
+      <c r="AA16" s="140"/>
+    </row>
+    <row r="17" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -5428,23 +5518,23 @@
       <c r="L17"/>
       <c r="M17"/>
       <c r="N17"/>
-      <c r="O17" s="168" t="s">
+      <c r="O17" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="169"/>
-      <c r="Q17" s="169"/>
-      <c r="R17" s="169"/>
-      <c r="S17" s="169"/>
-      <c r="T17" s="169"/>
-      <c r="U17" s="169"/>
-      <c r="V17" s="169"/>
-      <c r="W17" s="169"/>
-      <c r="X17" s="169"/>
-      <c r="Y17" s="169"/>
-      <c r="Z17" s="169"/>
-      <c r="AA17" s="170"/>
-    </row>
-    <row r="18" spans="1:27" ht="22.5" customHeight="1">
+      <c r="P17" s="142"/>
+      <c r="Q17" s="142"/>
+      <c r="R17" s="142"/>
+      <c r="S17" s="142"/>
+      <c r="T17" s="142"/>
+      <c r="U17" s="142"/>
+      <c r="V17" s="142"/>
+      <c r="W17" s="142"/>
+      <c r="X17" s="142"/>
+      <c r="Y17" s="142"/>
+      <c r="Z17" s="142"/>
+      <c r="AA17" s="143"/>
+    </row>
+    <row r="18" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -5458,23 +5548,23 @@
       <c r="L18"/>
       <c r="M18"/>
       <c r="N18"/>
-      <c r="O18" s="162" t="s">
+      <c r="O18" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="P18" s="163"/>
-      <c r="Q18" s="163"/>
-      <c r="R18" s="163"/>
-      <c r="S18" s="163"/>
-      <c r="T18" s="163"/>
-      <c r="U18" s="163"/>
-      <c r="V18" s="163"/>
-      <c r="W18" s="163"/>
-      <c r="X18" s="163"/>
-      <c r="Y18" s="163"/>
-      <c r="Z18" s="163"/>
-      <c r="AA18" s="164"/>
-    </row>
-    <row r="19" spans="1:27" ht="22.5" customHeight="1">
+      <c r="P18" s="136"/>
+      <c r="Q18" s="136"/>
+      <c r="R18" s="136"/>
+      <c r="S18" s="136"/>
+      <c r="T18" s="136"/>
+      <c r="U18" s="136"/>
+      <c r="V18" s="136"/>
+      <c r="W18" s="136"/>
+      <c r="X18" s="136"/>
+      <c r="Y18" s="136"/>
+      <c r="Z18" s="136"/>
+      <c r="AA18" s="137"/>
+    </row>
+    <row r="19" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -5488,27 +5578,27 @@
       <c r="L19"/>
       <c r="M19"/>
       <c r="N19"/>
-      <c r="O19" s="171" t="s">
+      <c r="O19" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="P19" s="172"/>
-      <c r="Q19" s="172"/>
-      <c r="R19" s="172"/>
-      <c r="S19" s="172"/>
-      <c r="T19" s="172" t="s">
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="U19" s="172"/>
-      <c r="V19" s="172"/>
-      <c r="W19" s="172"/>
-      <c r="X19" s="172"/>
-      <c r="Y19" s="172" t="s">
+      <c r="U19" s="145"/>
+      <c r="V19" s="145"/>
+      <c r="W19" s="145"/>
+      <c r="X19" s="145"/>
+      <c r="Y19" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="Z19" s="172"/>
-      <c r="AA19" s="173"/>
-    </row>
-    <row r="20" spans="1:27" ht="22.5" customHeight="1">
+      <c r="Z19" s="145"/>
+      <c r="AA19" s="146"/>
+    </row>
+    <row r="20" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -5522,27 +5612,27 @@
       <c r="L20"/>
       <c r="M20"/>
       <c r="N20"/>
-      <c r="O20" s="165" t="s">
+      <c r="O20" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="166"/>
-      <c r="Q20" s="166"/>
-      <c r="R20" s="166"/>
-      <c r="S20" s="166"/>
-      <c r="T20" s="166" t="s">
+      <c r="P20" s="139"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="139"/>
+      <c r="T20" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="U20" s="166"/>
-      <c r="V20" s="166"/>
-      <c r="W20" s="166"/>
-      <c r="X20" s="166"/>
-      <c r="Y20" s="166" t="s">
+      <c r="U20" s="139"/>
+      <c r="V20" s="139"/>
+      <c r="W20" s="139"/>
+      <c r="X20" s="139"/>
+      <c r="Y20" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="Z20" s="166"/>
-      <c r="AA20" s="167"/>
-    </row>
-    <row r="21" spans="1:27" ht="22.5" customHeight="1">
+      <c r="Z20" s="139"/>
+      <c r="AA20" s="140"/>
+    </row>
+    <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -5556,27 +5646,27 @@
       <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
-      <c r="O21" s="165" t="s">
+      <c r="O21" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="166"/>
-      <c r="Q21" s="166"/>
-      <c r="R21" s="166"/>
-      <c r="S21" s="166"/>
-      <c r="T21" s="166" t="s">
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="166"/>
-      <c r="V21" s="166"/>
-      <c r="W21" s="166"/>
-      <c r="X21" s="166"/>
-      <c r="Y21" s="166" t="s">
+      <c r="U21" s="139"/>
+      <c r="V21" s="139"/>
+      <c r="W21" s="139"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="166"/>
-      <c r="AA21" s="167"/>
-    </row>
-    <row r="22" spans="1:27" ht="22.5" customHeight="1">
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="140"/>
+    </row>
+    <row r="22" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
@@ -5590,23 +5680,23 @@
       <c r="L22"/>
       <c r="M22"/>
       <c r="N22"/>
-      <c r="O22" s="168" t="s">
+      <c r="O22" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="169"/>
-      <c r="Q22" s="169"/>
-      <c r="R22" s="169"/>
-      <c r="S22" s="169"/>
-      <c r="T22" s="169"/>
-      <c r="U22" s="169"/>
-      <c r="V22" s="169"/>
-      <c r="W22" s="169"/>
-      <c r="X22" s="169"/>
-      <c r="Y22" s="169"/>
-      <c r="Z22" s="169"/>
-      <c r="AA22" s="170"/>
-    </row>
-    <row r="23" spans="1:27" ht="28.5" customHeight="1">
+      <c r="P22" s="142"/>
+      <c r="Q22" s="142"/>
+      <c r="R22" s="142"/>
+      <c r="S22" s="142"/>
+      <c r="T22" s="142"/>
+      <c r="U22" s="142"/>
+      <c r="V22" s="142"/>
+      <c r="W22" s="142"/>
+      <c r="X22" s="142"/>
+      <c r="Y22" s="142"/>
+      <c r="Z22" s="142"/>
+      <c r="AA22" s="143"/>
+    </row>
+    <row r="23" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
@@ -5620,39 +5710,39 @@
       <c r="L23"/>
       <c r="M23"/>
       <c r="N23"/>
-      <c r="O23" s="174" t="s">
+      <c r="O23" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="P23" s="174" t="s">
+      <c r="P23" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="176" t="s">
+      <c r="Q23" s="149" t="s">
         <v>71</v>
       </c>
-      <c r="R23" s="177"/>
-      <c r="S23" s="186" t="s">
+      <c r="R23" s="150"/>
+      <c r="S23" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="177"/>
-      <c r="U23" s="186" t="s">
+      <c r="T23" s="150"/>
+      <c r="U23" s="159" t="s">
         <v>5</v>
       </c>
-      <c r="V23" s="177"/>
-      <c r="W23" s="187" t="s">
+      <c r="V23" s="150"/>
+      <c r="W23" s="160" t="s">
         <v>40</v>
       </c>
-      <c r="X23" s="186" t="s">
+      <c r="X23" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="177"/>
-      <c r="Z23" s="174" t="s">
+      <c r="Y23" s="150"/>
+      <c r="Z23" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="AA23" s="189" t="s">
+      <c r="AA23" s="162" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="22.5" customHeight="1">
+    <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
@@ -5666,8 +5756,8 @@
       <c r="L24"/>
       <c r="M24"/>
       <c r="N24"/>
-      <c r="O24" s="175"/>
-      <c r="P24" s="175"/>
+      <c r="O24" s="148"/>
+      <c r="P24" s="148"/>
       <c r="Q24" s="39" t="s">
         <v>13</v>
       </c>
@@ -5686,17 +5776,17 @@
       <c r="V24" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="188"/>
+      <c r="W24" s="161"/>
       <c r="X24" s="39" t="s">
         <v>11</v>
       </c>
       <c r="Y24" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="Z24" s="175"/>
-      <c r="AA24" s="189"/>
-    </row>
-    <row r="25" spans="1:27" ht="22.5" customHeight="1">
+      <c r="Z24" s="148"/>
+      <c r="AA24" s="162"/>
+    </row>
+    <row r="25" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -5727,7 +5817,7 @@
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
     </row>
-    <row r="26" spans="1:27" ht="22.5" customHeight="1">
+    <row r="26" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f>A25+1</f>
         <v>2</v>
@@ -5759,7 +5849,7 @@
       <c r="Z26" s="9"/>
       <c r="AA26" s="9"/>
     </row>
-    <row r="27" spans="1:27" ht="22.5" customHeight="1">
+    <row r="27" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" ref="A27:A54" si="2">A26+1</f>
         <v>3</v>
@@ -5791,7 +5881,7 @@
       <c r="Z27" s="9"/>
       <c r="AA27" s="9"/>
     </row>
-    <row r="28" spans="1:27" ht="22.5" customHeight="1">
+    <row r="28" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -5823,7 +5913,7 @@
       <c r="Z28" s="9"/>
       <c r="AA28" s="9"/>
     </row>
-    <row r="29" spans="1:27" ht="22.5" customHeight="1">
+    <row r="29" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -5855,7 +5945,7 @@
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
     </row>
-    <row r="30" spans="1:27" ht="22.5" customHeight="1">
+    <row r="30" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -5887,7 +5977,7 @@
       <c r="Z30" s="9"/>
       <c r="AA30" s="9"/>
     </row>
-    <row r="31" spans="1:27" ht="22.5" customHeight="1">
+    <row r="31" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -5919,7 +6009,7 @@
       <c r="Z31" s="9"/>
       <c r="AA31" s="9"/>
     </row>
-    <row r="32" spans="1:27" ht="22.5" customHeight="1">
+    <row r="32" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -5951,7 +6041,7 @@
       <c r="Z32" s="9"/>
       <c r="AA32" s="9"/>
     </row>
-    <row r="33" spans="1:27" ht="22.5" customHeight="1">
+    <row r="33" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -5983,7 +6073,7 @@
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
     </row>
-    <row r="34" spans="1:27" ht="22.5" customHeight="1">
+    <row r="34" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -6015,7 +6105,7 @@
       <c r="Z34" s="9"/>
       <c r="AA34" s="9"/>
     </row>
-    <row r="35" spans="1:27" ht="22.5" customHeight="1">
+    <row r="35" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -6047,7 +6137,7 @@
       <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
     </row>
-    <row r="36" spans="1:27" ht="22.5" customHeight="1">
+    <row r="36" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -6079,7 +6169,7 @@
       <c r="Z36" s="9"/>
       <c r="AA36" s="9"/>
     </row>
-    <row r="37" spans="1:27" ht="22.5" customHeight="1">
+    <row r="37" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -6111,7 +6201,7 @@
       <c r="Z37" s="9"/>
       <c r="AA37" s="9"/>
     </row>
-    <row r="38" spans="1:27" ht="22.5" customHeight="1">
+    <row r="38" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -6143,7 +6233,7 @@
       <c r="Z38" s="9"/>
       <c r="AA38" s="9"/>
     </row>
-    <row r="39" spans="1:27" ht="22.5" customHeight="1">
+    <row r="39" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -6175,7 +6265,7 @@
       <c r="Z39" s="9"/>
       <c r="AA39" s="9"/>
     </row>
-    <row r="40" spans="1:27" ht="22.5" customHeight="1">
+    <row r="40" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -6207,7 +6297,7 @@
       <c r="Z40" s="9"/>
       <c r="AA40" s="9"/>
     </row>
-    <row r="41" spans="1:27" ht="22.5" customHeight="1">
+    <row r="41" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -6239,7 +6329,7 @@
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
     </row>
-    <row r="42" spans="1:27" ht="22.5" customHeight="1">
+    <row r="42" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -6271,7 +6361,7 @@
       <c r="Z42" s="9"/>
       <c r="AA42" s="9"/>
     </row>
-    <row r="43" spans="1:27" ht="22.5" customHeight="1">
+    <row r="43" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -6303,7 +6393,7 @@
       <c r="Z43" s="9"/>
       <c r="AA43" s="9"/>
     </row>
-    <row r="44" spans="1:27" ht="22.5" customHeight="1">
+    <row r="44" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -6335,7 +6425,7 @@
       <c r="Z44" s="9"/>
       <c r="AA44" s="9"/>
     </row>
-    <row r="45" spans="1:27" ht="22.5" customHeight="1">
+    <row r="45" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -6367,7 +6457,7 @@
       <c r="Z45" s="9"/>
       <c r="AA45" s="9"/>
     </row>
-    <row r="46" spans="1:27" ht="22.5" customHeight="1">
+    <row r="46" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -6399,7 +6489,7 @@
       <c r="Z46" s="9"/>
       <c r="AA46" s="9"/>
     </row>
-    <row r="47" spans="1:27" ht="22.5" customHeight="1">
+    <row r="47" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -6431,7 +6521,7 @@
       <c r="Z47" s="9"/>
       <c r="AA47" s="9"/>
     </row>
-    <row r="48" spans="1:27" ht="22.5" customHeight="1">
+    <row r="48" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -6463,7 +6553,7 @@
       <c r="Z48" s="9"/>
       <c r="AA48" s="9"/>
     </row>
-    <row r="49" spans="1:27" ht="22.5" customHeight="1">
+    <row r="49" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -6495,7 +6585,7 @@
       <c r="Z49" s="9"/>
       <c r="AA49" s="9"/>
     </row>
-    <row r="50" spans="1:27" ht="22.5" customHeight="1">
+    <row r="50" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -6527,7 +6617,7 @@
       <c r="Z50" s="9"/>
       <c r="AA50" s="9"/>
     </row>
-    <row r="51" spans="1:27" ht="22.5" customHeight="1">
+    <row r="51" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -6559,7 +6649,7 @@
       <c r="Z51" s="9"/>
       <c r="AA51" s="9"/>
     </row>
-    <row r="52" spans="1:27" ht="22.5" customHeight="1">
+    <row r="52" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -6591,7 +6681,7 @@
       <c r="Z52" s="9"/>
       <c r="AA52" s="9"/>
     </row>
-    <row r="53" spans="1:27" ht="22.5" customHeight="1">
+    <row r="53" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -6623,7 +6713,7 @@
       <c r="Z53" s="9"/>
       <c r="AA53" s="9"/>
     </row>
-    <row r="54" spans="1:27" ht="22.5" customHeight="1">
+    <row r="54" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -6655,7 +6745,7 @@
       <c r="Z54" s="9"/>
       <c r="AA54" s="9"/>
     </row>
-    <row r="55" spans="1:27" ht="22.5" customHeight="1">
+    <row r="55" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55"/>
       <c r="C55"/>
       <c r="D55"/>
@@ -6669,25 +6759,25 @@
       <c r="L55"/>
       <c r="M55"/>
       <c r="N55"/>
-      <c r="O55" s="178" t="s">
+      <c r="O55" s="151" t="s">
         <v>57</v>
       </c>
-      <c r="P55" s="179"/>
-      <c r="Q55" s="179"/>
-      <c r="R55" s="179"/>
-      <c r="S55" s="179"/>
-      <c r="T55" s="179"/>
-      <c r="U55" s="180"/>
-      <c r="V55" s="178" t="s">
+      <c r="P55" s="152"/>
+      <c r="Q55" s="152"/>
+      <c r="R55" s="152"/>
+      <c r="S55" s="152"/>
+      <c r="T55" s="152"/>
+      <c r="U55" s="153"/>
+      <c r="V55" s="151" t="s">
         <v>60</v>
       </c>
-      <c r="W55" s="179"/>
-      <c r="X55" s="179"/>
-      <c r="Y55" s="179"/>
-      <c r="Z55" s="179"/>
-      <c r="AA55" s="180"/>
-    </row>
-    <row r="56" spans="1:27" ht="22.5" customHeight="1">
+      <c r="W55" s="152"/>
+      <c r="X55" s="152"/>
+      <c r="Y55" s="152"/>
+      <c r="Z55" s="152"/>
+      <c r="AA55" s="153"/>
+    </row>
+    <row r="56" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56"/>
       <c r="C56"/>
       <c r="D56"/>
@@ -6701,21 +6791,21 @@
       <c r="L56"/>
       <c r="M56"/>
       <c r="N56"/>
-      <c r="O56" s="181"/>
-      <c r="P56" s="182"/>
-      <c r="Q56" s="182"/>
-      <c r="R56" s="182"/>
-      <c r="S56" s="182"/>
-      <c r="T56" s="182"/>
-      <c r="U56" s="183"/>
-      <c r="V56" s="184"/>
-      <c r="W56" s="185"/>
-      <c r="X56" s="185"/>
-      <c r="Y56" s="185"/>
-      <c r="Z56" s="185"/>
-      <c r="AA56" s="185"/>
-    </row>
-    <row r="57" spans="1:27" ht="22.5" customHeight="1">
+      <c r="O56" s="154"/>
+      <c r="P56" s="155"/>
+      <c r="Q56" s="155"/>
+      <c r="R56" s="155"/>
+      <c r="S56" s="155"/>
+      <c r="T56" s="155"/>
+      <c r="U56" s="156"/>
+      <c r="V56" s="157"/>
+      <c r="W56" s="158"/>
+      <c r="X56" s="158"/>
+      <c r="Y56" s="158"/>
+      <c r="Z56" s="158"/>
+      <c r="AA56" s="158"/>
+    </row>
+    <row r="57" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57"/>
       <c r="C57"/>
       <c r="D57"/>
@@ -6729,21 +6819,21 @@
       <c r="L57"/>
       <c r="M57"/>
       <c r="N57"/>
-      <c r="O57" s="195"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="196"/>
-      <c r="T57" s="196"/>
-      <c r="U57" s="197"/>
-      <c r="V57" s="198"/>
-      <c r="W57" s="199"/>
-      <c r="X57" s="199"/>
-      <c r="Y57" s="199"/>
-      <c r="Z57" s="199"/>
-      <c r="AA57" s="199"/>
-    </row>
-    <row r="58" spans="1:27" ht="22.5" customHeight="1">
+      <c r="O57" s="168"/>
+      <c r="P57" s="169"/>
+      <c r="Q57" s="169"/>
+      <c r="R57" s="169"/>
+      <c r="S57" s="169"/>
+      <c r="T57" s="169"/>
+      <c r="U57" s="170"/>
+      <c r="V57" s="171"/>
+      <c r="W57" s="172"/>
+      <c r="X57" s="172"/>
+      <c r="Y57" s="172"/>
+      <c r="Z57" s="172"/>
+      <c r="AA57" s="172"/>
+    </row>
+    <row r="58" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58"/>
       <c r="C58"/>
       <c r="D58"/>
@@ -6757,21 +6847,21 @@
       <c r="L58"/>
       <c r="M58"/>
       <c r="N58"/>
-      <c r="O58" s="195"/>
-      <c r="P58" s="196"/>
-      <c r="Q58" s="196"/>
-      <c r="R58" s="196"/>
-      <c r="S58" s="196"/>
-      <c r="T58" s="196"/>
-      <c r="U58" s="197"/>
-      <c r="V58" s="198"/>
-      <c r="W58" s="199"/>
-      <c r="X58" s="199"/>
-      <c r="Y58" s="199"/>
-      <c r="Z58" s="199"/>
-      <c r="AA58" s="199"/>
-    </row>
-    <row r="59" spans="1:27" ht="22.5" customHeight="1">
+      <c r="O58" s="168"/>
+      <c r="P58" s="169"/>
+      <c r="Q58" s="169"/>
+      <c r="R58" s="169"/>
+      <c r="S58" s="169"/>
+      <c r="T58" s="169"/>
+      <c r="U58" s="170"/>
+      <c r="V58" s="171"/>
+      <c r="W58" s="172"/>
+      <c r="X58" s="172"/>
+      <c r="Y58" s="172"/>
+      <c r="Z58" s="172"/>
+      <c r="AA58" s="172"/>
+    </row>
+    <row r="59" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59"/>
       <c r="C59"/>
       <c r="D59"/>
@@ -6785,19 +6875,19 @@
       <c r="L59"/>
       <c r="M59"/>
       <c r="N59"/>
-      <c r="O59" s="190"/>
-      <c r="P59" s="191"/>
-      <c r="Q59" s="191"/>
-      <c r="R59" s="191"/>
-      <c r="S59" s="191"/>
-      <c r="T59" s="191"/>
-      <c r="U59" s="192"/>
-      <c r="V59" s="193"/>
-      <c r="W59" s="194"/>
-      <c r="X59" s="194"/>
-      <c r="Y59" s="194"/>
-      <c r="Z59" s="194"/>
-      <c r="AA59" s="194"/>
+      <c r="O59" s="163"/>
+      <c r="P59" s="164"/>
+      <c r="Q59" s="164"/>
+      <c r="R59" s="164"/>
+      <c r="S59" s="164"/>
+      <c r="T59" s="164"/>
+      <c r="U59" s="165"/>
+      <c r="V59" s="166"/>
+      <c r="W59" s="167"/>
+      <c r="X59" s="167"/>
+      <c r="Y59" s="167"/>
+      <c r="Z59" s="167"/>
+      <c r="AA59" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="55">
@@ -6859,7 +6949,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="66" fitToWidth="2" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" fitToWidth="2" orientation="portrait" r:id="rId1"/>
   <headerFooter differentOddEven="1"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="6" max="16383" man="1"/>
@@ -6880,7 +6970,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="11.42578125" style="1"/>
     <col min="5" max="6" width="12.140625" style="1" customWidth="1"/>
@@ -6897,7 +6987,7 @@
     <col min="28" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
         <f t="shared" ref="B1:N1" si="0">A1+1</f>
         <v>1</v>
@@ -7002,7 +7092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="22.5" customHeight="1">
+    <row r="2" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
         <v>65</v>
       </c>
@@ -7030,23 +7120,23 @@
         <v>63</v>
       </c>
       <c r="N2" s="38"/>
-      <c r="O2" s="151" t="s">
+      <c r="O2" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="152"/>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="153"/>
-    </row>
-    <row r="3" spans="2:27" ht="22.5" customHeight="1">
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="125"/>
+      <c r="Y2" s="125"/>
+      <c r="Z2" s="125"/>
+      <c r="AA2" s="126"/>
+    </row>
+    <row r="3" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="27" t="s">
         <v>29</v>
@@ -7075,21 +7165,21 @@
       <c r="N3" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="154"/>
-      <c r="P3" s="155"/>
-      <c r="Q3" s="155"/>
-      <c r="R3" s="155"/>
-      <c r="S3" s="155"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="155"/>
-      <c r="V3" s="155"/>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="155"/>
-      <c r="Z3" s="155"/>
-      <c r="AA3" s="156"/>
-    </row>
-    <row r="4" spans="2:27" ht="22.5" customHeight="1">
+      <c r="O3" s="127"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="129"/>
+    </row>
+    <row r="4" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="21" t="s">
         <v>30</v>
@@ -7107,25 +7197,25 @@
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
       <c r="N4" s="25"/>
-      <c r="O4" s="157" t="s">
+      <c r="O4" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="158"/>
-      <c r="Q4" s="158"/>
-      <c r="R4" s="158"/>
-      <c r="S4" s="158"/>
-      <c r="T4" s="158"/>
-      <c r="U4" s="159"/>
-      <c r="V4" s="160" t="s">
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="131"/>
+      <c r="U4" s="132"/>
+      <c r="V4" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="158"/>
-      <c r="X4" s="158"/>
-      <c r="Y4" s="158"/>
-      <c r="Z4" s="158"/>
-      <c r="AA4" s="161"/>
-    </row>
-    <row r="5" spans="2:27" ht="22.5" customHeight="1">
+      <c r="W4" s="131"/>
+      <c r="X4" s="131"/>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="134"/>
+    </row>
+    <row r="5" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="21" t="s">
         <v>29</v>
@@ -7159,7 +7249,7 @@
       <c r="Z5" s="44"/>
       <c r="AA5" s="45"/>
     </row>
-    <row r="6" spans="2:27" ht="22.5" customHeight="1">
+    <row r="6" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
       <c r="C6" s="21" t="s">
         <v>30</v>
@@ -7191,7 +7281,7 @@
       <c r="Z6" s="47"/>
       <c r="AA6" s="48"/>
     </row>
-    <row r="7" spans="2:27" ht="22.5" customHeight="1">
+    <row r="7" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="C7" s="22" t="s">
         <v>29</v>
@@ -7223,49 +7313,49 @@
       <c r="Z7" s="50"/>
       <c r="AA7" s="51"/>
     </row>
-    <row r="8" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B8" s="219" t="s">
+    <row r="8" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="192" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="220"/>
-      <c r="D8" s="220"/>
-      <c r="E8" s="220"/>
-      <c r="F8" s="220"/>
-      <c r="G8" s="221"/>
-      <c r="H8" s="219" t="s">
+      <c r="C8" s="193"/>
+      <c r="D8" s="193"/>
+      <c r="E8" s="193"/>
+      <c r="F8" s="193"/>
+      <c r="G8" s="194"/>
+      <c r="H8" s="192" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="220"/>
-      <c r="J8" s="221"/>
-      <c r="K8" s="233" t="s">
+      <c r="I8" s="193"/>
+      <c r="J8" s="194"/>
+      <c r="K8" s="206" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="235"/>
-      <c r="O8" s="162" t="s">
+      <c r="L8" s="207"/>
+      <c r="M8" s="207"/>
+      <c r="N8" s="208"/>
+      <c r="O8" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="163"/>
-      <c r="Q8" s="163"/>
-      <c r="R8" s="163"/>
-      <c r="S8" s="163"/>
-      <c r="T8" s="163"/>
-      <c r="U8" s="163"/>
-      <c r="V8" s="163"/>
-      <c r="W8" s="163"/>
-      <c r="X8" s="163"/>
-      <c r="Y8" s="163"/>
-      <c r="Z8" s="163"/>
-      <c r="AA8" s="164"/>
-    </row>
-    <row r="9" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B9" s="222"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="223"/>
-      <c r="E9" s="223"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="224"/>
+      <c r="P8" s="136"/>
+      <c r="Q8" s="136"/>
+      <c r="R8" s="136"/>
+      <c r="S8" s="136"/>
+      <c r="T8" s="136"/>
+      <c r="U8" s="136"/>
+      <c r="V8" s="136"/>
+      <c r="W8" s="136"/>
+      <c r="X8" s="136"/>
+      <c r="Y8" s="136"/>
+      <c r="Z8" s="136"/>
+      <c r="AA8" s="137"/>
+    </row>
+    <row r="9" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="195"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="196"/>
+      <c r="E9" s="196"/>
+      <c r="F9" s="196"/>
+      <c r="G9" s="197"/>
       <c r="H9" s="30" t="s">
         <v>15</v>
       </c>
@@ -7277,33 +7367,33 @@
       <c r="L9" s="53"/>
       <c r="M9" s="53"/>
       <c r="N9" s="54"/>
-      <c r="O9" s="171" t="s">
+      <c r="O9" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="172"/>
-      <c r="Q9" s="172"/>
-      <c r="R9" s="172"/>
-      <c r="S9" s="172"/>
-      <c r="T9" s="172" t="s">
+      <c r="P9" s="145"/>
+      <c r="Q9" s="145"/>
+      <c r="R9" s="145"/>
+      <c r="S9" s="145"/>
+      <c r="T9" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="U9" s="172"/>
-      <c r="V9" s="172"/>
-      <c r="W9" s="172"/>
-      <c r="X9" s="172"/>
-      <c r="Y9" s="172" t="s">
+      <c r="U9" s="145"/>
+      <c r="V9" s="145"/>
+      <c r="W9" s="145"/>
+      <c r="X9" s="145"/>
+      <c r="Y9" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="Z9" s="172"/>
-      <c r="AA9" s="173"/>
-    </row>
-    <row r="10" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B10" s="227"/>
-      <c r="C10" s="228"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="228"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="229"/>
+      <c r="Z9" s="145"/>
+      <c r="AA9" s="146"/>
+    </row>
+    <row r="10" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="200"/>
+      <c r="C10" s="201"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="201"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="202"/>
       <c r="H10" s="13" t="s">
         <v>16</v>
       </c>
@@ -7315,71 +7405,71 @@
       <c r="L10" s="56"/>
       <c r="M10" s="56"/>
       <c r="N10" s="57"/>
-      <c r="O10" s="165" t="s">
+      <c r="O10" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="166"/>
-      <c r="Q10" s="166"/>
-      <c r="R10" s="166"/>
-      <c r="S10" s="166"/>
-      <c r="T10" s="166" t="s">
+      <c r="P10" s="139"/>
+      <c r="Q10" s="139"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
+      <c r="T10" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="166"/>
-      <c r="V10" s="166"/>
-      <c r="W10" s="166"/>
-      <c r="X10" s="166"/>
-      <c r="Y10" s="166" t="s">
+      <c r="U10" s="139"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="139"/>
+      <c r="Y10" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="Z10" s="166"/>
-      <c r="AA10" s="167"/>
-    </row>
-    <row r="11" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B11" s="227"/>
-      <c r="C11" s="228"/>
-      <c r="D11" s="228"/>
-      <c r="E11" s="228"/>
-      <c r="F11" s="228"/>
-      <c r="G11" s="229"/>
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="140"/>
+    </row>
+    <row r="11" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="200"/>
+      <c r="C11" s="201"/>
+      <c r="D11" s="201"/>
+      <c r="E11" s="201"/>
+      <c r="F11" s="201"/>
+      <c r="G11" s="202"/>
       <c r="H11" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="225" t="s">
+      <c r="I11" s="198" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="226"/>
+      <c r="J11" s="199"/>
       <c r="K11" s="55"/>
       <c r="L11" s="56"/>
       <c r="M11" s="56"/>
       <c r="N11" s="57"/>
-      <c r="O11" s="165" t="s">
+      <c r="O11" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="166"/>
-      <c r="Q11" s="166"/>
-      <c r="R11" s="166"/>
-      <c r="S11" s="166"/>
-      <c r="T11" s="166" t="s">
+      <c r="P11" s="139"/>
+      <c r="Q11" s="139"/>
+      <c r="R11" s="139"/>
+      <c r="S11" s="139"/>
+      <c r="T11" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="166"/>
-      <c r="V11" s="166"/>
-      <c r="W11" s="166"/>
-      <c r="X11" s="166"/>
-      <c r="Y11" s="166" t="s">
+      <c r="U11" s="139"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="139"/>
+      <c r="X11" s="139"/>
+      <c r="Y11" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="167"/>
-    </row>
-    <row r="12" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B12" s="230"/>
-      <c r="C12" s="231"/>
-      <c r="D12" s="231"/>
-      <c r="E12" s="231"/>
-      <c r="F12" s="231"/>
-      <c r="G12" s="232"/>
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="140"/>
+    </row>
+    <row r="12" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="203"/>
+      <c r="C12" s="204"/>
+      <c r="D12" s="204"/>
+      <c r="E12" s="204"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="205"/>
       <c r="H12" s="13" t="s">
         <v>17</v>
       </c>
@@ -7391,31 +7481,31 @@
       <c r="L12" s="56"/>
       <c r="M12" s="56"/>
       <c r="N12" s="57"/>
-      <c r="O12" s="168" t="s">
+      <c r="O12" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="169"/>
-      <c r="R12" s="169"/>
-      <c r="S12" s="169"/>
-      <c r="T12" s="169"/>
-      <c r="U12" s="169"/>
-      <c r="V12" s="169"/>
-      <c r="W12" s="169"/>
-      <c r="X12" s="169"/>
-      <c r="Y12" s="169"/>
-      <c r="Z12" s="169"/>
-      <c r="AA12" s="170"/>
-    </row>
-    <row r="13" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B13" s="219" t="s">
+      <c r="P12" s="142"/>
+      <c r="Q12" s="142"/>
+      <c r="R12" s="142"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="142"/>
+      <c r="U12" s="142"/>
+      <c r="V12" s="142"/>
+      <c r="W12" s="142"/>
+      <c r="X12" s="142"/>
+      <c r="Y12" s="142"/>
+      <c r="Z12" s="142"/>
+      <c r="AA12" s="143"/>
+    </row>
+    <row r="13" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="192" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="220"/>
-      <c r="D13" s="220"/>
-      <c r="E13" s="220"/>
-      <c r="F13" s="220"/>
-      <c r="G13" s="221"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193"/>
+      <c r="G13" s="194"/>
       <c r="H13" s="13" t="s">
         <v>34</v>
       </c>
@@ -7427,100 +7517,100 @@
       <c r="L13" s="56"/>
       <c r="M13" s="56"/>
       <c r="N13" s="57"/>
-      <c r="O13" s="162" t="s">
+      <c r="O13" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="P13" s="163"/>
-      <c r="Q13" s="163"/>
-      <c r="R13" s="163"/>
-      <c r="S13" s="163"/>
-      <c r="T13" s="163"/>
-      <c r="U13" s="163"/>
-      <c r="V13" s="163"/>
-      <c r="W13" s="163"/>
-      <c r="X13" s="163"/>
-      <c r="Y13" s="163"/>
-      <c r="Z13" s="163"/>
-      <c r="AA13" s="164"/>
-    </row>
-    <row r="14" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B14" s="222"/>
-      <c r="C14" s="223"/>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="223"/>
-      <c r="G14" s="224"/>
+      <c r="P13" s="136"/>
+      <c r="Q13" s="136"/>
+      <c r="R13" s="136"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="136"/>
+      <c r="U13" s="136"/>
+      <c r="V13" s="136"/>
+      <c r="W13" s="136"/>
+      <c r="X13" s="136"/>
+      <c r="Y13" s="136"/>
+      <c r="Z13" s="136"/>
+      <c r="AA13" s="137"/>
+    </row>
+    <row r="14" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="195"/>
+      <c r="C14" s="196"/>
+      <c r="D14" s="196"/>
+      <c r="E14" s="196"/>
+      <c r="F14" s="196"/>
+      <c r="G14" s="197"/>
       <c r="H14" s="3"/>
       <c r="J14" s="4"/>
       <c r="K14" s="58"/>
       <c r="L14" s="59"/>
       <c r="M14" s="59"/>
       <c r="N14" s="60"/>
-      <c r="O14" s="171" t="s">
+      <c r="O14" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="172"/>
-      <c r="Q14" s="172"/>
-      <c r="R14" s="172"/>
-      <c r="S14" s="172"/>
-      <c r="T14" s="172" t="s">
+      <c r="P14" s="145"/>
+      <c r="Q14" s="145"/>
+      <c r="R14" s="145"/>
+      <c r="S14" s="145"/>
+      <c r="T14" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="U14" s="172"/>
-      <c r="V14" s="172"/>
-      <c r="W14" s="172"/>
-      <c r="X14" s="172"/>
-      <c r="Y14" s="172" t="s">
+      <c r="U14" s="145"/>
+      <c r="V14" s="145"/>
+      <c r="W14" s="145"/>
+      <c r="X14" s="145"/>
+      <c r="Y14" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="172"/>
-      <c r="AA14" s="173"/>
-    </row>
-    <row r="15" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B15" s="227"/>
-      <c r="C15" s="228"/>
-      <c r="D15" s="228"/>
-      <c r="E15" s="228"/>
-      <c r="F15" s="228"/>
-      <c r="G15" s="229"/>
-      <c r="H15" s="219" t="s">
+      <c r="Z14" s="145"/>
+      <c r="AA14" s="146"/>
+    </row>
+    <row r="15" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="200"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201"/>
+      <c r="E15" s="201"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="202"/>
+      <c r="H15" s="192" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="220"/>
-      <c r="J15" s="220"/>
-      <c r="K15" s="221"/>
-      <c r="L15" s="219" t="s">
+      <c r="I15" s="193"/>
+      <c r="J15" s="193"/>
+      <c r="K15" s="194"/>
+      <c r="L15" s="192" t="s">
         <v>75</v>
       </c>
-      <c r="M15" s="220"/>
-      <c r="N15" s="221"/>
-      <c r="O15" s="165" t="s">
+      <c r="M15" s="193"/>
+      <c r="N15" s="194"/>
+      <c r="O15" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="P15" s="166"/>
-      <c r="Q15" s="166"/>
-      <c r="R15" s="166"/>
-      <c r="S15" s="166"/>
-      <c r="T15" s="166" t="s">
+      <c r="P15" s="139"/>
+      <c r="Q15" s="139"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="U15" s="166"/>
-      <c r="V15" s="166"/>
-      <c r="W15" s="166"/>
-      <c r="X15" s="166"/>
-      <c r="Y15" s="166" t="s">
+      <c r="U15" s="139"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
+      <c r="X15" s="139"/>
+      <c r="Y15" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="Z15" s="166"/>
-      <c r="AA15" s="167"/>
-    </row>
-    <row r="16" spans="2:27" ht="22.5" customHeight="1">
-      <c r="B16" s="227"/>
-      <c r="C16" s="228"/>
-      <c r="D16" s="228"/>
-      <c r="E16" s="228"/>
-      <c r="F16" s="228"/>
-      <c r="G16" s="229"/>
+      <c r="Z15" s="139"/>
+      <c r="AA15" s="140"/>
+    </row>
+    <row r="16" spans="2:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="200"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
+      <c r="F16" s="201"/>
+      <c r="G16" s="202"/>
       <c r="H16" s="14"/>
       <c r="I16" s="18" t="s">
         <v>18</v>
@@ -7534,33 +7624,33 @@
       <c r="L16" s="61"/>
       <c r="M16" s="62"/>
       <c r="N16" s="63"/>
-      <c r="O16" s="165" t="s">
+      <c r="O16" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="P16" s="166"/>
-      <c r="Q16" s="166"/>
-      <c r="R16" s="166"/>
-      <c r="S16" s="166"/>
-      <c r="T16" s="166" t="s">
+      <c r="P16" s="139"/>
+      <c r="Q16" s="139"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
+      <c r="T16" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="166"/>
-      <c r="V16" s="166"/>
-      <c r="W16" s="166"/>
-      <c r="X16" s="166"/>
-      <c r="Y16" s="166" t="s">
+      <c r="U16" s="139"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="139"/>
+      <c r="X16" s="139"/>
+      <c r="Y16" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="Z16" s="166"/>
-      <c r="AA16" s="167"/>
-    </row>
-    <row r="17" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B17" s="227"/>
-      <c r="C17" s="228"/>
-      <c r="D17" s="228"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="228"/>
-      <c r="G17" s="229"/>
+      <c r="Z16" s="139"/>
+      <c r="AA16" s="140"/>
+    </row>
+    <row r="17" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="200"/>
+      <c r="C17" s="201"/>
+      <c r="D17" s="201"/>
+      <c r="E17" s="201"/>
+      <c r="F17" s="201"/>
+      <c r="G17" s="202"/>
       <c r="H17" s="10" t="s">
         <v>59</v>
       </c>
@@ -7570,29 +7660,29 @@
       <c r="L17" s="55"/>
       <c r="M17" s="56"/>
       <c r="N17" s="57"/>
-      <c r="O17" s="168" t="s">
+      <c r="O17" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="169"/>
-      <c r="Q17" s="169"/>
-      <c r="R17" s="169"/>
-      <c r="S17" s="169"/>
-      <c r="T17" s="169"/>
-      <c r="U17" s="169"/>
-      <c r="V17" s="169"/>
-      <c r="W17" s="169"/>
-      <c r="X17" s="169"/>
-      <c r="Y17" s="169"/>
-      <c r="Z17" s="169"/>
-      <c r="AA17" s="170"/>
-    </row>
-    <row r="18" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B18" s="227"/>
-      <c r="C18" s="228"/>
-      <c r="D18" s="228"/>
-      <c r="E18" s="228"/>
-      <c r="F18" s="228"/>
-      <c r="G18" s="229"/>
+      <c r="P17" s="142"/>
+      <c r="Q17" s="142"/>
+      <c r="R17" s="142"/>
+      <c r="S17" s="142"/>
+      <c r="T17" s="142"/>
+      <c r="U17" s="142"/>
+      <c r="V17" s="142"/>
+      <c r="W17" s="142"/>
+      <c r="X17" s="142"/>
+      <c r="Y17" s="142"/>
+      <c r="Z17" s="142"/>
+      <c r="AA17" s="143"/>
+    </row>
+    <row r="18" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="200"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="201"/>
+      <c r="E18" s="201"/>
+      <c r="F18" s="201"/>
+      <c r="G18" s="202"/>
       <c r="H18" s="10" t="s">
         <v>53</v>
       </c>
@@ -7602,29 +7692,29 @@
       <c r="L18" s="55"/>
       <c r="M18" s="56"/>
       <c r="N18" s="57"/>
-      <c r="O18" s="162" t="s">
+      <c r="O18" s="135" t="s">
         <v>49</v>
       </c>
-      <c r="P18" s="163"/>
-      <c r="Q18" s="163"/>
-      <c r="R18" s="163"/>
-      <c r="S18" s="163"/>
-      <c r="T18" s="163"/>
-      <c r="U18" s="163"/>
-      <c r="V18" s="163"/>
-      <c r="W18" s="163"/>
-      <c r="X18" s="163"/>
-      <c r="Y18" s="163"/>
-      <c r="Z18" s="163"/>
-      <c r="AA18" s="164"/>
-    </row>
-    <row r="19" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B19" s="227"/>
-      <c r="C19" s="228"/>
-      <c r="D19" s="228"/>
-      <c r="E19" s="228"/>
-      <c r="F19" s="228"/>
-      <c r="G19" s="229"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="136"/>
+      <c r="R18" s="136"/>
+      <c r="S18" s="136"/>
+      <c r="T18" s="136"/>
+      <c r="U18" s="136"/>
+      <c r="V18" s="136"/>
+      <c r="W18" s="136"/>
+      <c r="X18" s="136"/>
+      <c r="Y18" s="136"/>
+      <c r="Z18" s="136"/>
+      <c r="AA18" s="137"/>
+    </row>
+    <row r="19" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="200"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="201"/>
+      <c r="E19" s="201"/>
+      <c r="F19" s="201"/>
+      <c r="G19" s="202"/>
       <c r="H19" s="10" t="s">
         <v>72</v>
       </c>
@@ -7634,33 +7724,33 @@
       <c r="L19" s="55"/>
       <c r="M19" s="56"/>
       <c r="N19" s="57"/>
-      <c r="O19" s="171" t="s">
+      <c r="O19" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="P19" s="172"/>
-      <c r="Q19" s="172"/>
-      <c r="R19" s="172"/>
-      <c r="S19" s="172"/>
-      <c r="T19" s="172" t="s">
+      <c r="P19" s="145"/>
+      <c r="Q19" s="145"/>
+      <c r="R19" s="145"/>
+      <c r="S19" s="145"/>
+      <c r="T19" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="U19" s="172"/>
-      <c r="V19" s="172"/>
-      <c r="W19" s="172"/>
-      <c r="X19" s="172"/>
-      <c r="Y19" s="172" t="s">
+      <c r="U19" s="145"/>
+      <c r="V19" s="145"/>
+      <c r="W19" s="145"/>
+      <c r="X19" s="145"/>
+      <c r="Y19" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="Z19" s="172"/>
-      <c r="AA19" s="173"/>
-    </row>
-    <row r="20" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B20" s="227"/>
-      <c r="C20" s="228"/>
-      <c r="D20" s="228"/>
-      <c r="E20" s="228"/>
-      <c r="F20" s="228"/>
-      <c r="G20" s="229"/>
+      <c r="Z19" s="145"/>
+      <c r="AA19" s="146"/>
+    </row>
+    <row r="20" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="200"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="201"/>
+      <c r="E20" s="201"/>
+      <c r="F20" s="201"/>
+      <c r="G20" s="202"/>
       <c r="H20" s="10" t="s">
         <v>52</v>
       </c>
@@ -7670,33 +7760,33 @@
       <c r="L20" s="55"/>
       <c r="M20" s="56"/>
       <c r="N20" s="57"/>
-      <c r="O20" s="165" t="s">
+      <c r="O20" s="138" t="s">
         <v>45</v>
       </c>
-      <c r="P20" s="166"/>
-      <c r="Q20" s="166"/>
-      <c r="R20" s="166"/>
-      <c r="S20" s="166"/>
-      <c r="T20" s="166" t="s">
+      <c r="P20" s="139"/>
+      <c r="Q20" s="139"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="139"/>
+      <c r="T20" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="U20" s="166"/>
-      <c r="V20" s="166"/>
-      <c r="W20" s="166"/>
-      <c r="X20" s="166"/>
-      <c r="Y20" s="166" t="s">
+      <c r="U20" s="139"/>
+      <c r="V20" s="139"/>
+      <c r="W20" s="139"/>
+      <c r="X20" s="139"/>
+      <c r="Y20" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="Z20" s="166"/>
-      <c r="AA20" s="167"/>
-    </row>
-    <row r="21" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B21" s="227"/>
-      <c r="C21" s="228"/>
-      <c r="D21" s="228"/>
-      <c r="E21" s="228"/>
-      <c r="F21" s="228"/>
-      <c r="G21" s="229"/>
+      <c r="Z20" s="139"/>
+      <c r="AA20" s="140"/>
+    </row>
+    <row r="21" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="200"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="201"/>
+      <c r="E21" s="201"/>
+      <c r="F21" s="201"/>
+      <c r="G21" s="202"/>
       <c r="H21" s="10" t="s">
         <v>54</v>
       </c>
@@ -7706,33 +7796,33 @@
       <c r="L21" s="55"/>
       <c r="M21" s="56"/>
       <c r="N21" s="57"/>
-      <c r="O21" s="165" t="s">
+      <c r="O21" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="166"/>
-      <c r="Q21" s="166"/>
-      <c r="R21" s="166"/>
-      <c r="S21" s="166"/>
-      <c r="T21" s="166" t="s">
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="166"/>
-      <c r="V21" s="166"/>
-      <c r="W21" s="166"/>
-      <c r="X21" s="166"/>
-      <c r="Y21" s="166" t="s">
+      <c r="U21" s="139"/>
+      <c r="V21" s="139"/>
+      <c r="W21" s="139"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="166"/>
-      <c r="AA21" s="167"/>
-    </row>
-    <row r="22" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B22" s="230"/>
-      <c r="C22" s="231"/>
-      <c r="D22" s="231"/>
-      <c r="E22" s="231"/>
-      <c r="F22" s="231"/>
-      <c r="G22" s="232"/>
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="140"/>
+    </row>
+    <row r="22" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="203"/>
+      <c r="C22" s="204"/>
+      <c r="D22" s="204"/>
+      <c r="E22" s="204"/>
+      <c r="F22" s="204"/>
+      <c r="G22" s="205"/>
       <c r="H22" s="15"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
@@ -7740,98 +7830,98 @@
       <c r="L22" s="58"/>
       <c r="M22" s="59"/>
       <c r="N22" s="60"/>
-      <c r="O22" s="168" t="s">
+      <c r="O22" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="P22" s="169"/>
-      <c r="Q22" s="169"/>
-      <c r="R22" s="169"/>
-      <c r="S22" s="169"/>
-      <c r="T22" s="169"/>
-      <c r="U22" s="169"/>
-      <c r="V22" s="169"/>
-      <c r="W22" s="169"/>
-      <c r="X22" s="169"/>
-      <c r="Y22" s="169"/>
-      <c r="Z22" s="169"/>
-      <c r="AA22" s="170"/>
-    </row>
-    <row r="23" spans="1:27" ht="28.5" customHeight="1">
-      <c r="B23" s="174" t="s">
+      <c r="P22" s="142"/>
+      <c r="Q22" s="142"/>
+      <c r="R22" s="142"/>
+      <c r="S22" s="142"/>
+      <c r="T22" s="142"/>
+      <c r="U22" s="142"/>
+      <c r="V22" s="142"/>
+      <c r="W22" s="142"/>
+      <c r="X22" s="142"/>
+      <c r="Y22" s="142"/>
+      <c r="Z22" s="142"/>
+      <c r="AA22" s="143"/>
+    </row>
+    <row r="23" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="174" t="s">
+      <c r="C23" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="186" t="s">
+      <c r="D23" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="177"/>
-      <c r="F23" s="174" t="s">
+      <c r="E23" s="150"/>
+      <c r="F23" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="207" t="s">
+      <c r="G23" s="180" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="208"/>
-      <c r="I23" s="208"/>
-      <c r="J23" s="208"/>
-      <c r="K23" s="208"/>
-      <c r="L23" s="208"/>
-      <c r="M23" s="208"/>
-      <c r="N23" s="209"/>
-      <c r="O23" s="174" t="s">
+      <c r="H23" s="181"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="181"/>
+      <c r="L23" s="181"/>
+      <c r="M23" s="181"/>
+      <c r="N23" s="182"/>
+      <c r="O23" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="P23" s="174" t="s">
+      <c r="P23" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="176" t="s">
+      <c r="Q23" s="149" t="s">
         <v>71</v>
       </c>
-      <c r="R23" s="177"/>
-      <c r="S23" s="186" t="s">
+      <c r="R23" s="150"/>
+      <c r="S23" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="T23" s="177"/>
-      <c r="U23" s="186" t="s">
+      <c r="T23" s="150"/>
+      <c r="U23" s="159" t="s">
         <v>5</v>
       </c>
-      <c r="V23" s="177"/>
-      <c r="W23" s="187" t="s">
+      <c r="V23" s="150"/>
+      <c r="W23" s="160" t="s">
         <v>40</v>
       </c>
-      <c r="X23" s="186" t="s">
+      <c r="X23" s="159" t="s">
         <v>6</v>
       </c>
-      <c r="Y23" s="177"/>
-      <c r="Z23" s="174" t="s">
+      <c r="Y23" s="150"/>
+      <c r="Z23" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="AA23" s="189" t="s">
+      <c r="AA23" s="162" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B24" s="175"/>
-      <c r="C24" s="175"/>
+    <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="148"/>
+      <c r="C24" s="148"/>
       <c r="D24" s="39" t="s">
         <v>24</v>
       </c>
       <c r="E24" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="175"/>
-      <c r="G24" s="210"/>
-      <c r="H24" s="211"/>
-      <c r="I24" s="211"/>
-      <c r="J24" s="211"/>
-      <c r="K24" s="211"/>
-      <c r="L24" s="211"/>
-      <c r="M24" s="211"/>
-      <c r="N24" s="212"/>
-      <c r="O24" s="175"/>
-      <c r="P24" s="175"/>
+      <c r="F24" s="148"/>
+      <c r="G24" s="183"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="184"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="184"/>
+      <c r="M24" s="184"/>
+      <c r="N24" s="185"/>
+      <c r="O24" s="148"/>
+      <c r="P24" s="148"/>
       <c r="Q24" s="39" t="s">
         <v>13</v>
       </c>
@@ -7850,17 +7940,17 @@
       <c r="V24" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="W24" s="188"/>
+      <c r="W24" s="161"/>
       <c r="X24" s="39" t="s">
         <v>11</v>
       </c>
       <c r="Y24" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="Z24" s="175"/>
-      <c r="AA24" s="189"/>
-    </row>
-    <row r="25" spans="1:27" ht="22.5" customHeight="1">
+      <c r="Z24" s="148"/>
+      <c r="AA24" s="162"/>
+    </row>
+    <row r="25" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -7869,14 +7959,14 @@
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="216"/>
-      <c r="H25" s="217"/>
-      <c r="I25" s="217"/>
-      <c r="J25" s="217"/>
-      <c r="K25" s="217"/>
-      <c r="L25" s="217"/>
-      <c r="M25" s="217"/>
-      <c r="N25" s="218"/>
+      <c r="G25" s="189"/>
+      <c r="H25" s="190"/>
+      <c r="I25" s="190"/>
+      <c r="J25" s="190"/>
+      <c r="K25" s="190"/>
+      <c r="L25" s="190"/>
+      <c r="M25" s="190"/>
+      <c r="N25" s="191"/>
       <c r="O25" s="31"/>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
@@ -7891,7 +7981,7 @@
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
     </row>
-    <row r="26" spans="1:27" ht="22.5" customHeight="1">
+    <row r="26" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f>A25+1</f>
         <v>2</v>
@@ -7901,14 +7991,14 @@
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="201"/>
-      <c r="J26" s="201"/>
-      <c r="K26" s="201"/>
-      <c r="L26" s="201"/>
-      <c r="M26" s="201"/>
-      <c r="N26" s="202"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="174"/>
+      <c r="I26" s="174"/>
+      <c r="J26" s="174"/>
+      <c r="K26" s="174"/>
+      <c r="L26" s="174"/>
+      <c r="M26" s="174"/>
+      <c r="N26" s="175"/>
       <c r="O26" s="20"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="42"/>
@@ -7923,7 +8013,7 @@
       <c r="Z26" s="9"/>
       <c r="AA26" s="9"/>
     </row>
-    <row r="27" spans="1:27" ht="22.5" customHeight="1">
+    <row r="27" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" ref="A27:A54" si="2">A26+1</f>
         <v>3</v>
@@ -7933,14 +8023,14 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="201"/>
-      <c r="J27" s="201"/>
-      <c r="K27" s="201"/>
-      <c r="L27" s="201"/>
-      <c r="M27" s="201"/>
-      <c r="N27" s="202"/>
+      <c r="G27" s="173"/>
+      <c r="H27" s="174"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
+      <c r="L27" s="174"/>
+      <c r="M27" s="174"/>
+      <c r="N27" s="175"/>
       <c r="O27" s="20"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
@@ -7955,7 +8045,7 @@
       <c r="Z27" s="9"/>
       <c r="AA27" s="9"/>
     </row>
-    <row r="28" spans="1:27" ht="22.5" customHeight="1">
+    <row r="28" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7965,14 +8055,14 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="201"/>
-      <c r="I28" s="201"/>
-      <c r="J28" s="201"/>
-      <c r="K28" s="201"/>
-      <c r="L28" s="201"/>
-      <c r="M28" s="201"/>
-      <c r="N28" s="202"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="174"/>
+      <c r="L28" s="174"/>
+      <c r="M28" s="174"/>
+      <c r="N28" s="175"/>
       <c r="O28" s="20"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
@@ -7987,7 +8077,7 @@
       <c r="Z28" s="9"/>
       <c r="AA28" s="9"/>
     </row>
-    <row r="29" spans="1:27" ht="22.5" customHeight="1">
+    <row r="29" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7997,14 +8087,14 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="201"/>
-      <c r="J29" s="201"/>
-      <c r="K29" s="201"/>
-      <c r="L29" s="201"/>
-      <c r="M29" s="201"/>
-      <c r="N29" s="202"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="174"/>
+      <c r="N29" s="175"/>
       <c r="O29" s="20"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
@@ -8019,7 +8109,7 @@
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
     </row>
-    <row r="30" spans="1:27" ht="22.5" customHeight="1">
+    <row r="30" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -8029,14 +8119,14 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="201"/>
-      <c r="I30" s="201"/>
-      <c r="J30" s="201"/>
-      <c r="K30" s="201"/>
-      <c r="L30" s="201"/>
-      <c r="M30" s="201"/>
-      <c r="N30" s="202"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="174"/>
+      <c r="L30" s="174"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="175"/>
       <c r="O30" s="20"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
@@ -8051,7 +8141,7 @@
       <c r="Z30" s="9"/>
       <c r="AA30" s="9"/>
     </row>
-    <row r="31" spans="1:27" ht="22.5" customHeight="1">
+    <row r="31" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -8061,14 +8151,14 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="201"/>
-      <c r="J31" s="201"/>
-      <c r="K31" s="201"/>
-      <c r="L31" s="201"/>
-      <c r="M31" s="201"/>
-      <c r="N31" s="202"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="174"/>
+      <c r="L31" s="174"/>
+      <c r="M31" s="174"/>
+      <c r="N31" s="175"/>
       <c r="O31" s="20"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
@@ -8083,7 +8173,7 @@
       <c r="Z31" s="9"/>
       <c r="AA31" s="9"/>
     </row>
-    <row r="32" spans="1:27" ht="22.5" customHeight="1">
+    <row r="32" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -8093,14 +8183,14 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="201"/>
-      <c r="I32" s="201"/>
-      <c r="J32" s="201"/>
-      <c r="K32" s="201"/>
-      <c r="L32" s="201"/>
-      <c r="M32" s="201"/>
-      <c r="N32" s="202"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="174"/>
+      <c r="L32" s="174"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="175"/>
       <c r="O32" s="20"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
@@ -8115,7 +8205,7 @@
       <c r="Z32" s="9"/>
       <c r="AA32" s="9"/>
     </row>
-    <row r="33" spans="1:27" ht="22.5" customHeight="1">
+    <row r="33" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -8125,14 +8215,14 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="201"/>
-      <c r="K33" s="201"/>
-      <c r="L33" s="201"/>
-      <c r="M33" s="201"/>
-      <c r="N33" s="202"/>
+      <c r="G33" s="173"/>
+      <c r="H33" s="174"/>
+      <c r="I33" s="174"/>
+      <c r="J33" s="174"/>
+      <c r="K33" s="174"/>
+      <c r="L33" s="174"/>
+      <c r="M33" s="174"/>
+      <c r="N33" s="175"/>
       <c r="O33" s="20"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
@@ -8147,7 +8237,7 @@
       <c r="Z33" s="9"/>
       <c r="AA33" s="9"/>
     </row>
-    <row r="34" spans="1:27" ht="22.5" customHeight="1">
+    <row r="34" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -8157,14 +8247,14 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="201"/>
-      <c r="I34" s="201"/>
-      <c r="J34" s="201"/>
-      <c r="K34" s="201"/>
-      <c r="L34" s="201"/>
-      <c r="M34" s="201"/>
-      <c r="N34" s="202"/>
+      <c r="G34" s="173"/>
+      <c r="H34" s="174"/>
+      <c r="I34" s="174"/>
+      <c r="J34" s="174"/>
+      <c r="K34" s="174"/>
+      <c r="L34" s="174"/>
+      <c r="M34" s="174"/>
+      <c r="N34" s="175"/>
       <c r="O34" s="20"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
@@ -8179,7 +8269,7 @@
       <c r="Z34" s="9"/>
       <c r="AA34" s="9"/>
     </row>
-    <row r="35" spans="1:27" ht="22.5" customHeight="1">
+    <row r="35" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -8189,14 +8279,14 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="201"/>
-      <c r="J35" s="201"/>
-      <c r="K35" s="201"/>
-      <c r="L35" s="201"/>
-      <c r="M35" s="201"/>
-      <c r="N35" s="202"/>
+      <c r="G35" s="173"/>
+      <c r="H35" s="174"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="174"/>
+      <c r="L35" s="174"/>
+      <c r="M35" s="174"/>
+      <c r="N35" s="175"/>
       <c r="O35" s="20"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
@@ -8211,7 +8301,7 @@
       <c r="Z35" s="9"/>
       <c r="AA35" s="9"/>
     </row>
-    <row r="36" spans="1:27" ht="22.5" customHeight="1">
+    <row r="36" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -8221,14 +8311,14 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="200"/>
-      <c r="H36" s="201"/>
-      <c r="I36" s="201"/>
-      <c r="J36" s="201"/>
-      <c r="K36" s="201"/>
-      <c r="L36" s="201"/>
-      <c r="M36" s="201"/>
-      <c r="N36" s="202"/>
+      <c r="G36" s="173"/>
+      <c r="H36" s="174"/>
+      <c r="I36" s="174"/>
+      <c r="J36" s="174"/>
+      <c r="K36" s="174"/>
+      <c r="L36" s="174"/>
+      <c r="M36" s="174"/>
+      <c r="N36" s="175"/>
       <c r="O36" s="20"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
@@ -8243,7 +8333,7 @@
       <c r="Z36" s="9"/>
       <c r="AA36" s="9"/>
     </row>
-    <row r="37" spans="1:27" ht="22.5" customHeight="1">
+    <row r="37" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -8253,14 +8343,14 @@
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="201"/>
-      <c r="I37" s="201"/>
-      <c r="J37" s="201"/>
-      <c r="K37" s="201"/>
-      <c r="L37" s="201"/>
-      <c r="M37" s="201"/>
-      <c r="N37" s="202"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="174"/>
+      <c r="I37" s="174"/>
+      <c r="J37" s="174"/>
+      <c r="K37" s="174"/>
+      <c r="L37" s="174"/>
+      <c r="M37" s="174"/>
+      <c r="N37" s="175"/>
       <c r="O37" s="20"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
@@ -8275,7 +8365,7 @@
       <c r="Z37" s="9"/>
       <c r="AA37" s="9"/>
     </row>
-    <row r="38" spans="1:27" ht="22.5" customHeight="1">
+    <row r="38" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -8285,14 +8375,14 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
-      <c r="G38" s="200"/>
-      <c r="H38" s="201"/>
-      <c r="I38" s="201"/>
-      <c r="J38" s="201"/>
-      <c r="K38" s="201"/>
-      <c r="L38" s="201"/>
-      <c r="M38" s="201"/>
-      <c r="N38" s="202"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="174"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="174"/>
+      <c r="K38" s="174"/>
+      <c r="L38" s="174"/>
+      <c r="M38" s="174"/>
+      <c r="N38" s="175"/>
       <c r="O38" s="20"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
@@ -8307,7 +8397,7 @@
       <c r="Z38" s="9"/>
       <c r="AA38" s="9"/>
     </row>
-    <row r="39" spans="1:27" ht="22.5" customHeight="1">
+    <row r="39" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -8317,14 +8407,14 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
-      <c r="G39" s="200"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="201"/>
-      <c r="J39" s="201"/>
-      <c r="K39" s="201"/>
-      <c r="L39" s="201"/>
-      <c r="M39" s="201"/>
-      <c r="N39" s="202"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="174"/>
+      <c r="I39" s="174"/>
+      <c r="J39" s="174"/>
+      <c r="K39" s="174"/>
+      <c r="L39" s="174"/>
+      <c r="M39" s="174"/>
+      <c r="N39" s="175"/>
       <c r="O39" s="20"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
@@ -8339,7 +8429,7 @@
       <c r="Z39" s="9"/>
       <c r="AA39" s="9"/>
     </row>
-    <row r="40" spans="1:27" ht="22.5" customHeight="1">
+    <row r="40" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -8349,14 +8439,14 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
-      <c r="G40" s="200"/>
-      <c r="H40" s="201"/>
-      <c r="I40" s="201"/>
-      <c r="J40" s="201"/>
-      <c r="K40" s="201"/>
-      <c r="L40" s="201"/>
-      <c r="M40" s="201"/>
-      <c r="N40" s="202"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="174"/>
+      <c r="I40" s="174"/>
+      <c r="J40" s="174"/>
+      <c r="K40" s="174"/>
+      <c r="L40" s="174"/>
+      <c r="M40" s="174"/>
+      <c r="N40" s="175"/>
       <c r="O40" s="20"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
@@ -8371,7 +8461,7 @@
       <c r="Z40" s="9"/>
       <c r="AA40" s="9"/>
     </row>
-    <row r="41" spans="1:27" ht="22.5" customHeight="1">
+    <row r="41" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -8381,14 +8471,14 @@
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
-      <c r="G41" s="200"/>
-      <c r="H41" s="201"/>
-      <c r="I41" s="201"/>
-      <c r="J41" s="201"/>
-      <c r="K41" s="201"/>
-      <c r="L41" s="201"/>
-      <c r="M41" s="201"/>
-      <c r="N41" s="202"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="174"/>
+      <c r="I41" s="174"/>
+      <c r="J41" s="174"/>
+      <c r="K41" s="174"/>
+      <c r="L41" s="174"/>
+      <c r="M41" s="174"/>
+      <c r="N41" s="175"/>
       <c r="O41" s="20"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
@@ -8403,7 +8493,7 @@
       <c r="Z41" s="9"/>
       <c r="AA41" s="9"/>
     </row>
-    <row r="42" spans="1:27" ht="22.5" customHeight="1">
+    <row r="42" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -8413,14 +8503,14 @@
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
-      <c r="G42" s="200"/>
-      <c r="H42" s="201"/>
-      <c r="I42" s="201"/>
-      <c r="J42" s="201"/>
-      <c r="K42" s="201"/>
-      <c r="L42" s="201"/>
-      <c r="M42" s="201"/>
-      <c r="N42" s="202"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="174"/>
+      <c r="I42" s="174"/>
+      <c r="J42" s="174"/>
+      <c r="K42" s="174"/>
+      <c r="L42" s="174"/>
+      <c r="M42" s="174"/>
+      <c r="N42" s="175"/>
       <c r="O42" s="20"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
@@ -8435,7 +8525,7 @@
       <c r="Z42" s="9"/>
       <c r="AA42" s="9"/>
     </row>
-    <row r="43" spans="1:27" ht="22.5" customHeight="1">
+    <row r="43" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -8445,14 +8535,14 @@
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="200"/>
-      <c r="H43" s="201"/>
-      <c r="I43" s="201"/>
-      <c r="J43" s="201"/>
-      <c r="K43" s="201"/>
-      <c r="L43" s="201"/>
-      <c r="M43" s="201"/>
-      <c r="N43" s="202"/>
+      <c r="G43" s="173"/>
+      <c r="H43" s="174"/>
+      <c r="I43" s="174"/>
+      <c r="J43" s="174"/>
+      <c r="K43" s="174"/>
+      <c r="L43" s="174"/>
+      <c r="M43" s="174"/>
+      <c r="N43" s="175"/>
       <c r="O43" s="20"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
@@ -8467,7 +8557,7 @@
       <c r="Z43" s="9"/>
       <c r="AA43" s="9"/>
     </row>
-    <row r="44" spans="1:27" ht="22.5" customHeight="1">
+    <row r="44" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -8477,14 +8567,14 @@
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="200"/>
-      <c r="H44" s="201"/>
-      <c r="I44" s="201"/>
-      <c r="J44" s="201"/>
-      <c r="K44" s="201"/>
-      <c r="L44" s="201"/>
-      <c r="M44" s="201"/>
-      <c r="N44" s="202"/>
+      <c r="G44" s="173"/>
+      <c r="H44" s="174"/>
+      <c r="I44" s="174"/>
+      <c r="J44" s="174"/>
+      <c r="K44" s="174"/>
+      <c r="L44" s="174"/>
+      <c r="M44" s="174"/>
+      <c r="N44" s="175"/>
       <c r="O44" s="20"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
@@ -8499,7 +8589,7 @@
       <c r="Z44" s="9"/>
       <c r="AA44" s="9"/>
     </row>
-    <row r="45" spans="1:27" ht="22.5" customHeight="1">
+    <row r="45" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -8509,14 +8599,14 @@
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
-      <c r="G45" s="200"/>
-      <c r="H45" s="201"/>
-      <c r="I45" s="201"/>
-      <c r="J45" s="201"/>
-      <c r="K45" s="201"/>
-      <c r="L45" s="201"/>
-      <c r="M45" s="201"/>
-      <c r="N45" s="202"/>
+      <c r="G45" s="173"/>
+      <c r="H45" s="174"/>
+      <c r="I45" s="174"/>
+      <c r="J45" s="174"/>
+      <c r="K45" s="174"/>
+      <c r="L45" s="174"/>
+      <c r="M45" s="174"/>
+      <c r="N45" s="175"/>
       <c r="O45" s="20"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
@@ -8531,7 +8621,7 @@
       <c r="Z45" s="9"/>
       <c r="AA45" s="9"/>
     </row>
-    <row r="46" spans="1:27" ht="22.5" customHeight="1">
+    <row r="46" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -8541,14 +8631,14 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
-      <c r="G46" s="200"/>
-      <c r="H46" s="201"/>
-      <c r="I46" s="201"/>
-      <c r="J46" s="201"/>
-      <c r="K46" s="201"/>
-      <c r="L46" s="201"/>
-      <c r="M46" s="201"/>
-      <c r="N46" s="202"/>
+      <c r="G46" s="173"/>
+      <c r="H46" s="174"/>
+      <c r="I46" s="174"/>
+      <c r="J46" s="174"/>
+      <c r="K46" s="174"/>
+      <c r="L46" s="174"/>
+      <c r="M46" s="174"/>
+      <c r="N46" s="175"/>
       <c r="O46" s="20"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
@@ -8563,7 +8653,7 @@
       <c r="Z46" s="9"/>
       <c r="AA46" s="9"/>
     </row>
-    <row r="47" spans="1:27" ht="22.5" customHeight="1">
+    <row r="47" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -8573,14 +8663,14 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
-      <c r="G47" s="200"/>
-      <c r="H47" s="201"/>
-      <c r="I47" s="201"/>
-      <c r="J47" s="201"/>
-      <c r="K47" s="201"/>
-      <c r="L47" s="201"/>
-      <c r="M47" s="201"/>
-      <c r="N47" s="202"/>
+      <c r="G47" s="173"/>
+      <c r="H47" s="174"/>
+      <c r="I47" s="174"/>
+      <c r="J47" s="174"/>
+      <c r="K47" s="174"/>
+      <c r="L47" s="174"/>
+      <c r="M47" s="174"/>
+      <c r="N47" s="175"/>
       <c r="O47" s="20"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
@@ -8595,7 +8685,7 @@
       <c r="Z47" s="9"/>
       <c r="AA47" s="9"/>
     </row>
-    <row r="48" spans="1:27" ht="22.5" customHeight="1">
+    <row r="48" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -8605,14 +8695,14 @@
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="200"/>
-      <c r="H48" s="201"/>
-      <c r="I48" s="201"/>
-      <c r="J48" s="201"/>
-      <c r="K48" s="201"/>
-      <c r="L48" s="201"/>
-      <c r="M48" s="201"/>
-      <c r="N48" s="202"/>
+      <c r="G48" s="173"/>
+      <c r="H48" s="174"/>
+      <c r="I48" s="174"/>
+      <c r="J48" s="174"/>
+      <c r="K48" s="174"/>
+      <c r="L48" s="174"/>
+      <c r="M48" s="174"/>
+      <c r="N48" s="175"/>
       <c r="O48" s="20"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
@@ -8627,7 +8717,7 @@
       <c r="Z48" s="9"/>
       <c r="AA48" s="9"/>
     </row>
-    <row r="49" spans="1:27" ht="22.5" customHeight="1">
+    <row r="49" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -8637,14 +8727,14 @@
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="200"/>
-      <c r="H49" s="201"/>
-      <c r="I49" s="201"/>
-      <c r="J49" s="201"/>
-      <c r="K49" s="201"/>
-      <c r="L49" s="201"/>
-      <c r="M49" s="201"/>
-      <c r="N49" s="202"/>
+      <c r="G49" s="173"/>
+      <c r="H49" s="174"/>
+      <c r="I49" s="174"/>
+      <c r="J49" s="174"/>
+      <c r="K49" s="174"/>
+      <c r="L49" s="174"/>
+      <c r="M49" s="174"/>
+      <c r="N49" s="175"/>
       <c r="O49" s="20"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
@@ -8659,7 +8749,7 @@
       <c r="Z49" s="9"/>
       <c r="AA49" s="9"/>
     </row>
-    <row r="50" spans="1:27" ht="22.5" customHeight="1">
+    <row r="50" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -8669,14 +8759,14 @@
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
-      <c r="G50" s="200"/>
-      <c r="H50" s="201"/>
-      <c r="I50" s="201"/>
-      <c r="J50" s="201"/>
-      <c r="K50" s="201"/>
-      <c r="L50" s="201"/>
-      <c r="M50" s="201"/>
-      <c r="N50" s="202"/>
+      <c r="G50" s="173"/>
+      <c r="H50" s="174"/>
+      <c r="I50" s="174"/>
+      <c r="J50" s="174"/>
+      <c r="K50" s="174"/>
+      <c r="L50" s="174"/>
+      <c r="M50" s="174"/>
+      <c r="N50" s="175"/>
       <c r="O50" s="20"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="9"/>
@@ -8691,7 +8781,7 @@
       <c r="Z50" s="9"/>
       <c r="AA50" s="9"/>
     </row>
-    <row r="51" spans="1:27" ht="22.5" customHeight="1">
+    <row r="51" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -8701,14 +8791,14 @@
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="200"/>
-      <c r="H51" s="201"/>
-      <c r="I51" s="201"/>
-      <c r="J51" s="201"/>
-      <c r="K51" s="201"/>
-      <c r="L51" s="201"/>
-      <c r="M51" s="201"/>
-      <c r="N51" s="202"/>
+      <c r="G51" s="173"/>
+      <c r="H51" s="174"/>
+      <c r="I51" s="174"/>
+      <c r="J51" s="174"/>
+      <c r="K51" s="174"/>
+      <c r="L51" s="174"/>
+      <c r="M51" s="174"/>
+      <c r="N51" s="175"/>
       <c r="O51" s="20"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
@@ -8723,7 +8813,7 @@
       <c r="Z51" s="9"/>
       <c r="AA51" s="9"/>
     </row>
-    <row r="52" spans="1:27" ht="22.5" customHeight="1">
+    <row r="52" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -8733,14 +8823,14 @@
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="200"/>
-      <c r="H52" s="201"/>
-      <c r="I52" s="201"/>
-      <c r="J52" s="201"/>
-      <c r="K52" s="201"/>
-      <c r="L52" s="201"/>
-      <c r="M52" s="201"/>
-      <c r="N52" s="202"/>
+      <c r="G52" s="173"/>
+      <c r="H52" s="174"/>
+      <c r="I52" s="174"/>
+      <c r="J52" s="174"/>
+      <c r="K52" s="174"/>
+      <c r="L52" s="174"/>
+      <c r="M52" s="174"/>
+      <c r="N52" s="175"/>
       <c r="O52" s="20"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
@@ -8755,7 +8845,7 @@
       <c r="Z52" s="9"/>
       <c r="AA52" s="9"/>
     </row>
-    <row r="53" spans="1:27" ht="22.5" customHeight="1">
+    <row r="53" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -8765,14 +8855,14 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
-      <c r="G53" s="200"/>
-      <c r="H53" s="201"/>
-      <c r="I53" s="201"/>
-      <c r="J53" s="201"/>
-      <c r="K53" s="201"/>
-      <c r="L53" s="201"/>
-      <c r="M53" s="201"/>
-      <c r="N53" s="202"/>
+      <c r="G53" s="173"/>
+      <c r="H53" s="174"/>
+      <c r="I53" s="174"/>
+      <c r="J53" s="174"/>
+      <c r="K53" s="174"/>
+      <c r="L53" s="174"/>
+      <c r="M53" s="174"/>
+      <c r="N53" s="175"/>
       <c r="O53" s="20"/>
       <c r="P53" s="9"/>
       <c r="Q53" s="9"/>
@@ -8787,7 +8877,7 @@
       <c r="Z53" s="9"/>
       <c r="AA53" s="9"/>
     </row>
-    <row r="54" spans="1:27" ht="22.5" customHeight="1">
+    <row r="54" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -8797,14 +8887,14 @@
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
-      <c r="G54" s="213"/>
-      <c r="H54" s="214"/>
-      <c r="I54" s="214"/>
-      <c r="J54" s="214"/>
-      <c r="K54" s="214"/>
-      <c r="L54" s="214"/>
-      <c r="M54" s="214"/>
-      <c r="N54" s="215"/>
+      <c r="G54" s="186"/>
+      <c r="H54" s="187"/>
+      <c r="I54" s="187"/>
+      <c r="J54" s="187"/>
+      <c r="K54" s="187"/>
+      <c r="L54" s="187"/>
+      <c r="M54" s="187"/>
+      <c r="N54" s="188"/>
       <c r="O54" s="20"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
@@ -8819,153 +8909,153 @@
       <c r="Z54" s="9"/>
       <c r="AA54" s="9"/>
     </row>
-    <row r="55" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B55" s="178" t="s">
+    <row r="55" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="151" t="s">
         <v>60</v>
       </c>
-      <c r="C55" s="179"/>
-      <c r="D55" s="179"/>
-      <c r="E55" s="179"/>
-      <c r="F55" s="179"/>
-      <c r="G55" s="180"/>
-      <c r="H55" s="206" t="s">
+      <c r="C55" s="152"/>
+      <c r="D55" s="152"/>
+      <c r="E55" s="152"/>
+      <c r="F55" s="152"/>
+      <c r="G55" s="153"/>
+      <c r="H55" s="179" t="s">
         <v>58</v>
       </c>
-      <c r="I55" s="206"/>
-      <c r="J55" s="206"/>
-      <c r="K55" s="206"/>
-      <c r="L55" s="206"/>
-      <c r="M55" s="206"/>
-      <c r="N55" s="206"/>
-      <c r="O55" s="178" t="s">
+      <c r="I55" s="179"/>
+      <c r="J55" s="179"/>
+      <c r="K55" s="179"/>
+      <c r="L55" s="179"/>
+      <c r="M55" s="179"/>
+      <c r="N55" s="179"/>
+      <c r="O55" s="151" t="s">
         <v>57</v>
       </c>
-      <c r="P55" s="179"/>
-      <c r="Q55" s="179"/>
-      <c r="R55" s="179"/>
-      <c r="S55" s="179"/>
-      <c r="T55" s="179"/>
-      <c r="U55" s="180"/>
-      <c r="V55" s="178" t="s">
+      <c r="P55" s="152"/>
+      <c r="Q55" s="152"/>
+      <c r="R55" s="152"/>
+      <c r="S55" s="152"/>
+      <c r="T55" s="152"/>
+      <c r="U55" s="153"/>
+      <c r="V55" s="151" t="s">
         <v>60</v>
       </c>
-      <c r="W55" s="179"/>
-      <c r="X55" s="179"/>
-      <c r="Y55" s="179"/>
-      <c r="Z55" s="179"/>
-      <c r="AA55" s="180"/>
-    </row>
-    <row r="56" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B56" s="185"/>
-      <c r="C56" s="185"/>
-      <c r="D56" s="185"/>
-      <c r="E56" s="185"/>
-      <c r="F56" s="185"/>
-      <c r="G56" s="203"/>
-      <c r="H56" s="181"/>
-      <c r="I56" s="182"/>
-      <c r="J56" s="182"/>
-      <c r="K56" s="182"/>
-      <c r="L56" s="182"/>
-      <c r="M56" s="182"/>
-      <c r="N56" s="183"/>
-      <c r="O56" s="181"/>
-      <c r="P56" s="182"/>
-      <c r="Q56" s="182"/>
-      <c r="R56" s="182"/>
-      <c r="S56" s="182"/>
-      <c r="T56" s="182"/>
-      <c r="U56" s="183"/>
-      <c r="V56" s="184"/>
-      <c r="W56" s="185"/>
-      <c r="X56" s="185"/>
-      <c r="Y56" s="185"/>
-      <c r="Z56" s="185"/>
-      <c r="AA56" s="185"/>
-    </row>
-    <row r="57" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B57" s="199"/>
-      <c r="C57" s="199"/>
-      <c r="D57" s="199"/>
-      <c r="E57" s="199"/>
-      <c r="F57" s="199"/>
-      <c r="G57" s="204"/>
-      <c r="H57" s="195"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="197"/>
-      <c r="O57" s="195"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="196"/>
-      <c r="T57" s="196"/>
-      <c r="U57" s="197"/>
-      <c r="V57" s="198"/>
-      <c r="W57" s="199"/>
-      <c r="X57" s="199"/>
-      <c r="Y57" s="199"/>
-      <c r="Z57" s="199"/>
-      <c r="AA57" s="199"/>
-    </row>
-    <row r="58" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B58" s="199"/>
-      <c r="C58" s="199"/>
-      <c r="D58" s="199"/>
-      <c r="E58" s="199"/>
-      <c r="F58" s="199"/>
-      <c r="G58" s="204"/>
-      <c r="H58" s="195"/>
-      <c r="I58" s="196"/>
-      <c r="J58" s="196"/>
-      <c r="K58" s="196"/>
-      <c r="L58" s="196"/>
-      <c r="M58" s="196"/>
-      <c r="N58" s="197"/>
-      <c r="O58" s="195"/>
-      <c r="P58" s="196"/>
-      <c r="Q58" s="196"/>
-      <c r="R58" s="196"/>
-      <c r="S58" s="196"/>
-      <c r="T58" s="196"/>
-      <c r="U58" s="197"/>
-      <c r="V58" s="198"/>
-      <c r="W58" s="199"/>
-      <c r="X58" s="199"/>
-      <c r="Y58" s="199"/>
-      <c r="Z58" s="199"/>
-      <c r="AA58" s="199"/>
-    </row>
-    <row r="59" spans="1:27" ht="22.5" customHeight="1">
-      <c r="B59" s="194"/>
-      <c r="C59" s="194"/>
-      <c r="D59" s="194"/>
-      <c r="E59" s="194"/>
-      <c r="F59" s="194"/>
-      <c r="G59" s="205"/>
-      <c r="H59" s="190"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="191"/>
-      <c r="L59" s="191"/>
-      <c r="M59" s="191"/>
-      <c r="N59" s="192"/>
-      <c r="O59" s="190"/>
-      <c r="P59" s="191"/>
-      <c r="Q59" s="191"/>
-      <c r="R59" s="191"/>
-      <c r="S59" s="191"/>
-      <c r="T59" s="191"/>
-      <c r="U59" s="192"/>
-      <c r="V59" s="193"/>
-      <c r="W59" s="194"/>
-      <c r="X59" s="194"/>
-      <c r="Y59" s="194"/>
-      <c r="Z59" s="194"/>
-      <c r="AA59" s="194"/>
+      <c r="W55" s="152"/>
+      <c r="X55" s="152"/>
+      <c r="Y55" s="152"/>
+      <c r="Z55" s="152"/>
+      <c r="AA55" s="153"/>
+    </row>
+    <row r="56" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="158"/>
+      <c r="C56" s="158"/>
+      <c r="D56" s="158"/>
+      <c r="E56" s="158"/>
+      <c r="F56" s="158"/>
+      <c r="G56" s="176"/>
+      <c r="H56" s="154"/>
+      <c r="I56" s="155"/>
+      <c r="J56" s="155"/>
+      <c r="K56" s="155"/>
+      <c r="L56" s="155"/>
+      <c r="M56" s="155"/>
+      <c r="N56" s="156"/>
+      <c r="O56" s="154"/>
+      <c r="P56" s="155"/>
+      <c r="Q56" s="155"/>
+      <c r="R56" s="155"/>
+      <c r="S56" s="155"/>
+      <c r="T56" s="155"/>
+      <c r="U56" s="156"/>
+      <c r="V56" s="157"/>
+      <c r="W56" s="158"/>
+      <c r="X56" s="158"/>
+      <c r="Y56" s="158"/>
+      <c r="Z56" s="158"/>
+      <c r="AA56" s="158"/>
+    </row>
+    <row r="57" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="172"/>
+      <c r="C57" s="172"/>
+      <c r="D57" s="172"/>
+      <c r="E57" s="172"/>
+      <c r="F57" s="172"/>
+      <c r="G57" s="177"/>
+      <c r="H57" s="168"/>
+      <c r="I57" s="169"/>
+      <c r="J57" s="169"/>
+      <c r="K57" s="169"/>
+      <c r="L57" s="169"/>
+      <c r="M57" s="169"/>
+      <c r="N57" s="170"/>
+      <c r="O57" s="168"/>
+      <c r="P57" s="169"/>
+      <c r="Q57" s="169"/>
+      <c r="R57" s="169"/>
+      <c r="S57" s="169"/>
+      <c r="T57" s="169"/>
+      <c r="U57" s="170"/>
+      <c r="V57" s="171"/>
+      <c r="W57" s="172"/>
+      <c r="X57" s="172"/>
+      <c r="Y57" s="172"/>
+      <c r="Z57" s="172"/>
+      <c r="AA57" s="172"/>
+    </row>
+    <row r="58" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="172"/>
+      <c r="C58" s="172"/>
+      <c r="D58" s="172"/>
+      <c r="E58" s="172"/>
+      <c r="F58" s="172"/>
+      <c r="G58" s="177"/>
+      <c r="H58" s="168"/>
+      <c r="I58" s="169"/>
+      <c r="J58" s="169"/>
+      <c r="K58" s="169"/>
+      <c r="L58" s="169"/>
+      <c r="M58" s="169"/>
+      <c r="N58" s="170"/>
+      <c r="O58" s="168"/>
+      <c r="P58" s="169"/>
+      <c r="Q58" s="169"/>
+      <c r="R58" s="169"/>
+      <c r="S58" s="169"/>
+      <c r="T58" s="169"/>
+      <c r="U58" s="170"/>
+      <c r="V58" s="171"/>
+      <c r="W58" s="172"/>
+      <c r="X58" s="172"/>
+      <c r="Y58" s="172"/>
+      <c r="Z58" s="172"/>
+      <c r="AA58" s="172"/>
+    </row>
+    <row r="59" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="167"/>
+      <c r="C59" s="167"/>
+      <c r="D59" s="167"/>
+      <c r="E59" s="167"/>
+      <c r="F59" s="167"/>
+      <c r="G59" s="178"/>
+      <c r="H59" s="163"/>
+      <c r="I59" s="164"/>
+      <c r="J59" s="164"/>
+      <c r="K59" s="164"/>
+      <c r="L59" s="164"/>
+      <c r="M59" s="164"/>
+      <c r="N59" s="165"/>
+      <c r="O59" s="163"/>
+      <c r="P59" s="164"/>
+      <c r="Q59" s="164"/>
+      <c r="R59" s="164"/>
+      <c r="S59" s="164"/>
+      <c r="T59" s="164"/>
+      <c r="U59" s="165"/>
+      <c r="V59" s="166"/>
+      <c r="W59" s="167"/>
+      <c r="X59" s="167"/>
+      <c r="Y59" s="167"/>
+      <c r="Z59" s="167"/>
+      <c r="AA59" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="120">
@@ -9092,7 +9182,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="66" fitToWidth="2" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" fitToWidth="2" orientation="portrait" r:id="rId1"/>
   <headerFooter differentOddEven="1"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="6" max="16383" man="1"/>
@@ -9112,7 +9202,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:Q69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="11.42578125" style="64"/>
     <col min="5" max="5" width="8.140625" style="64" customWidth="1"/>
@@ -9126,47 +9216,47 @@
     <col min="18" max="16384" width="11.42578125" style="64"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="30.75">
-      <c r="B2" s="239" t="s">
+    <row r="2" spans="2:17" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B2" s="212" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="239"/>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="M2" s="239"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="239"/>
-      <c r="P2" s="239"/>
-      <c r="Q2" s="239"/>
-    </row>
-    <row r="5" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B5" s="236" t="s">
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="212"/>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="212"/>
+      <c r="O2" s="212"/>
+      <c r="P2" s="212"/>
+      <c r="Q2" s="212"/>
+    </row>
+    <row r="5" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="209" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="236"/>
-      <c r="D5" s="236"/>
-      <c r="E5" s="236"/>
-      <c r="F5" s="236"/>
-      <c r="G5" s="236"/>
-      <c r="H5" s="236"/>
-      <c r="I5" s="236"/>
-      <c r="J5" s="236"/>
-      <c r="K5" s="236"/>
-      <c r="L5" s="236"/>
-      <c r="M5" s="236"/>
-      <c r="N5" s="236"/>
-      <c r="O5" s="236"/>
-      <c r="P5" s="236"/>
-      <c r="Q5" s="236"/>
-    </row>
-    <row r="6" spans="2:17">
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
+      <c r="M5" s="209"/>
+      <c r="N5" s="209"/>
+      <c r="O5" s="209"/>
+      <c r="P5" s="209"/>
+      <c r="Q5" s="209"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C6" s="64" t="s">
         <v>78</v>
       </c>
@@ -9175,7 +9265,7 @@
       <c r="G6" s="68"/>
       <c r="H6" s="68"/>
     </row>
-    <row r="7" spans="2:17">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C7" s="64" t="s">
         <v>1</v>
       </c>
@@ -9184,7 +9274,7 @@
       <c r="G7" s="69"/>
       <c r="H7" s="69"/>
     </row>
-    <row r="8" spans="2:17">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C8" s="64" t="s">
         <v>83</v>
       </c>
@@ -9196,7 +9286,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="2:17">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C9" s="64" t="s">
         <v>84</v>
       </c>
@@ -9208,7 +9298,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="2:17">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C10" s="64" t="s">
         <v>79</v>
       </c>
@@ -9223,7 +9313,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="2:17">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="L11" s="64" t="s">
         <v>85</v>
       </c>
@@ -9231,39 +9321,39 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B13" s="236" t="s">
+    <row r="13" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="209" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="236"/>
-      <c r="D13" s="236"/>
-      <c r="E13" s="236"/>
-      <c r="F13" s="236"/>
-      <c r="G13" s="236"/>
-      <c r="H13" s="236"/>
-      <c r="I13" s="236"/>
-      <c r="J13" s="236"/>
-      <c r="K13" s="236"/>
-      <c r="L13" s="236"/>
-      <c r="M13" s="236"/>
-      <c r="N13" s="236"/>
-      <c r="O13" s="236"/>
-      <c r="P13" s="236"/>
-      <c r="Q13" s="236"/>
-    </row>
-    <row r="14" spans="2:17">
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
+      <c r="F13" s="209"/>
+      <c r="G13" s="209"/>
+      <c r="H13" s="209"/>
+      <c r="I13" s="209"/>
+      <c r="J13" s="209"/>
+      <c r="K13" s="209"/>
+      <c r="L13" s="209"/>
+      <c r="M13" s="209"/>
+      <c r="N13" s="209"/>
+      <c r="O13" s="209"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C14" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="237" t="s">
+      <c r="E14" s="210" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="237"/>
-      <c r="G14" s="237"/>
-      <c r="H14" s="237"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="210"/>
       <c r="I14" s="70"/>
     </row>
-    <row r="15" spans="2:17">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E15" s="71" t="s">
         <v>89</v>
       </c>
@@ -9274,17 +9364,17 @@
       <c r="K15" s="72"/>
       <c r="L15" s="72"/>
     </row>
-    <row r="16" spans="2:17">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E16" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="238"/>
-      <c r="H16" s="238"/>
+      <c r="G16" s="211"/>
+      <c r="H16" s="211"/>
       <c r="I16" s="70"/>
       <c r="K16" s="72"/>
       <c r="L16" s="72"/>
     </row>
-    <row r="17" spans="2:17">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F17" s="70"/>
       <c r="G17" s="72"/>
       <c r="H17" s="72"/>
@@ -9292,12 +9382,12 @@
       <c r="K17" s="72"/>
       <c r="L17" s="72"/>
     </row>
-    <row r="18" spans="2:17">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C18" s="64" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E19" s="64" t="s">
         <v>93</v>
       </c>
@@ -9305,27 +9395,27 @@
       <c r="I19" s="68"/>
       <c r="J19" s="68"/>
     </row>
-    <row r="21" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B21" s="236" t="s">
+    <row r="21" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="209" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="236"/>
-      <c r="D21" s="236"/>
-      <c r="E21" s="236"/>
-      <c r="F21" s="236"/>
-      <c r="G21" s="236"/>
-      <c r="H21" s="236"/>
-      <c r="I21" s="236"/>
-      <c r="J21" s="236"/>
-      <c r="K21" s="236"/>
-      <c r="L21" s="236"/>
-      <c r="M21" s="236"/>
-      <c r="N21" s="236"/>
-      <c r="O21" s="236"/>
-      <c r="P21" s="236"/>
-      <c r="Q21" s="236"/>
-    </row>
-    <row r="22" spans="2:17">
+      <c r="C21" s="209"/>
+      <c r="D21" s="209"/>
+      <c r="E21" s="209"/>
+      <c r="F21" s="209"/>
+      <c r="G21" s="209"/>
+      <c r="H21" s="209"/>
+      <c r="I21" s="209"/>
+      <c r="J21" s="209"/>
+      <c r="K21" s="209"/>
+      <c r="L21" s="209"/>
+      <c r="M21" s="209"/>
+      <c r="N21" s="209"/>
+      <c r="O21" s="209"/>
+      <c r="P21" s="209"/>
+      <c r="Q21" s="209"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C22" s="64" t="s">
         <v>95</v>
       </c>
@@ -9346,7 +9436,7 @@
       <c r="L22" s="68"/>
       <c r="M22" s="68"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C23" s="64" t="s">
         <v>99</v>
       </c>
@@ -9367,27 +9457,27 @@
       <c r="L23" s="68"/>
       <c r="M23" s="68"/>
     </row>
-    <row r="26" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B26" s="236" t="s">
+    <row r="26" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="209" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="236"/>
-      <c r="D26" s="236"/>
-      <c r="E26" s="236"/>
-      <c r="F26" s="236"/>
-      <c r="G26" s="236"/>
-      <c r="H26" s="236"/>
-      <c r="I26" s="236"/>
-      <c r="J26" s="236"/>
-      <c r="K26" s="236"/>
-      <c r="L26" s="236"/>
-      <c r="M26" s="236"/>
-      <c r="N26" s="236"/>
-      <c r="O26" s="236"/>
-      <c r="P26" s="236"/>
-      <c r="Q26" s="236"/>
-    </row>
-    <row r="27" spans="2:17">
+      <c r="C26" s="209"/>
+      <c r="D26" s="209"/>
+      <c r="E26" s="209"/>
+      <c r="F26" s="209"/>
+      <c r="G26" s="209"/>
+      <c r="H26" s="209"/>
+      <c r="I26" s="209"/>
+      <c r="J26" s="209"/>
+      <c r="K26" s="209"/>
+      <c r="L26" s="209"/>
+      <c r="M26" s="209"/>
+      <c r="N26" s="209"/>
+      <c r="O26" s="209"/>
+      <c r="P26" s="209"/>
+      <c r="Q26" s="209"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C27" s="73" t="s">
         <v>6</v>
       </c>
@@ -9395,7 +9485,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D28" s="64" t="s">
         <v>103</v>
       </c>
@@ -9405,7 +9495,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D29" s="64" t="s">
         <v>104</v>
       </c>
@@ -9415,12 +9505,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="L30" s="64" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" s="73" t="s">
         <v>14</v>
       </c>
@@ -9428,7 +9518,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D32" s="64" t="s">
         <v>105</v>
       </c>
@@ -9438,7 +9528,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="3:15">
+    <row r="33" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D33" s="64" t="s">
         <v>106</v>
       </c>
@@ -9448,7 +9538,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="3:15">
+    <row r="34" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D34" s="64" t="s">
         <v>107</v>
       </c>
@@ -9458,7 +9548,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="3:15">
+    <row r="35" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D35" s="64" t="s">
         <v>108</v>
       </c>
@@ -9467,7 +9557,7 @@
       <c r="H35" s="68"/>
       <c r="I35" s="68"/>
     </row>
-    <row r="36" spans="3:15">
+    <row r="36" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D36" s="64" t="s">
         <v>109</v>
       </c>
@@ -9479,7 +9569,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="3:15">
+    <row r="37" spans="3:15" x14ac:dyDescent="0.25">
       <c r="L37" s="64" t="s">
         <v>123</v>
       </c>
@@ -9489,27 +9579,27 @@
       </c>
       <c r="O37" s="68"/>
     </row>
-    <row r="38" spans="3:15">
+    <row r="38" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C38" s="73" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="3:15">
+    <row r="39" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D39" s="64" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="3:15">
+    <row r="40" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D40" s="64" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="3:15">
+    <row r="41" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D41" s="64" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="3:15">
+    <row r="44" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C44" s="73" t="s">
         <v>125</v>
       </c>
@@ -9517,7 +9607,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="45" spans="3:15">
+    <row r="45" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D45" s="64" t="s">
         <v>126</v>
       </c>
@@ -9525,7 +9615,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="3:15">
+    <row r="46" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D46" s="64" t="s">
         <v>127</v>
       </c>
@@ -9533,7 +9623,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="3:15">
+    <row r="47" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D47" s="64" t="s">
         <v>128</v>
       </c>
@@ -9544,7 +9634,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="3:15">
+    <row r="48" spans="3:15" x14ac:dyDescent="0.25">
       <c r="D48" s="64" t="s">
         <v>129</v>
       </c>
@@ -9552,7 +9642,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="2:17">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D49" s="64" t="s">
         <v>130</v>
       </c>
@@ -9560,32 +9650,32 @@
         <v>131</v>
       </c>
     </row>
-    <row r="50" spans="2:17">
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D50" s="64" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="53" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1">
-      <c r="B53" s="236" t="s">
+    <row r="53" spans="2:17" s="67" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="209" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="236"/>
-      <c r="D53" s="236"/>
-      <c r="E53" s="236"/>
-      <c r="F53" s="236"/>
-      <c r="G53" s="236"/>
-      <c r="H53" s="236"/>
-      <c r="I53" s="236"/>
-      <c r="J53" s="236"/>
-      <c r="K53" s="236"/>
-      <c r="L53" s="236"/>
-      <c r="M53" s="236"/>
-      <c r="N53" s="236"/>
-      <c r="O53" s="236"/>
-      <c r="P53" s="236"/>
-      <c r="Q53" s="236"/>
-    </row>
-    <row r="54" spans="2:17">
+      <c r="C53" s="209"/>
+      <c r="D53" s="209"/>
+      <c r="E53" s="209"/>
+      <c r="F53" s="209"/>
+      <c r="G53" s="209"/>
+      <c r="H53" s="209"/>
+      <c r="I53" s="209"/>
+      <c r="J53" s="209"/>
+      <c r="K53" s="209"/>
+      <c r="L53" s="209"/>
+      <c r="M53" s="209"/>
+      <c r="N53" s="209"/>
+      <c r="O53" s="209"/>
+      <c r="P53" s="209"/>
+      <c r="Q53" s="209"/>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C54" s="64" t="s">
         <v>2</v>
       </c>
@@ -9595,27 +9685,27 @@
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="2:17">
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="65"/>
       <c r="Q64" s="66"/>
     </row>
-    <row r="65" spans="2:17">
+    <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="65"/>
       <c r="Q65" s="66"/>
     </row>
-    <row r="66" spans="2:17">
+    <row r="66" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B66" s="65"/>
       <c r="Q66" s="66"/>
     </row>
-    <row r="67" spans="2:17">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B67" s="65"/>
       <c r="Q67" s="66"/>
     </row>
-    <row r="68" spans="2:17">
+    <row r="68" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B68" s="65"/>
       <c r="Q68" s="66"/>
     </row>
-    <row r="69" spans="2:17">
+    <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B69" s="74"/>
       <c r="C69" s="75"/>
       <c r="D69" s="75"/>
@@ -9654,7 +9744,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FBFCC4C-AA9B-410E-88E2-C384CCD47975}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A2:AY93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="3.85546875" customWidth="1"/>
     <col min="4" max="4" width="2.140625" customWidth="1"/>
@@ -9664,7 +9754,7 @@
     <col min="51" max="51" width="2.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="I2" t="s">
         <v>159</v>
       </c>
@@ -9689,109 +9779,109 @@
       <c r="AL2" s="121"/>
       <c r="AM2" s="121"/>
     </row>
-    <row r="4" spans="1:51" ht="15" customHeight="1">
-      <c r="C4" s="240" t="s">
+    <row r="4" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="213" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="240"/>
-      <c r="E4" s="240"/>
-      <c r="F4" s="240"/>
-      <c r="G4" s="240"/>
-      <c r="H4" s="240"/>
-      <c r="I4" s="240"/>
-      <c r="J4" s="240"/>
-      <c r="K4" s="240"/>
-      <c r="L4" s="240"/>
-      <c r="M4" s="240"/>
-      <c r="N4" s="240"/>
-      <c r="O4" s="240"/>
-      <c r="P4" s="240"/>
-      <c r="Q4" s="240"/>
-      <c r="R4" s="240"/>
-      <c r="S4" s="240"/>
-      <c r="T4" s="240"/>
-      <c r="U4" s="240"/>
-      <c r="V4" s="240"/>
-      <c r="W4" s="240"/>
-      <c r="X4" s="240"/>
-      <c r="Y4" s="240"/>
-      <c r="Z4" s="240"/>
-      <c r="AA4" s="240"/>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
-      <c r="AD4" s="240"/>
-      <c r="AE4" s="240"/>
-      <c r="AF4" s="240"/>
-      <c r="AG4" s="240"/>
-      <c r="AH4" s="240"/>
-      <c r="AI4" s="240"/>
-      <c r="AJ4" s="240"/>
-      <c r="AK4" s="240"/>
-      <c r="AL4" s="240"/>
-      <c r="AM4" s="240"/>
-      <c r="AN4" s="240"/>
-      <c r="AO4" s="240"/>
-      <c r="AP4" s="240"/>
-      <c r="AQ4" s="240"/>
-      <c r="AR4" s="240"/>
-      <c r="AS4" s="240"/>
-      <c r="AT4" s="240"/>
-      <c r="AU4" s="240"/>
-      <c r="AV4" s="240"/>
-      <c r="AW4" s="240"/>
-      <c r="AX4" s="240"/>
-    </row>
-    <row r="5" spans="1:51" ht="15" customHeight="1">
-      <c r="C5" s="240"/>
-      <c r="D5" s="240"/>
-      <c r="E5" s="240"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="240"/>
-      <c r="H5" s="240"/>
-      <c r="I5" s="240"/>
-      <c r="J5" s="240"/>
-      <c r="K5" s="240"/>
-      <c r="L5" s="240"/>
-      <c r="M5" s="240"/>
-      <c r="N5" s="240"/>
-      <c r="O5" s="240"/>
-      <c r="P5" s="240"/>
-      <c r="Q5" s="240"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
-      <c r="AA5" s="240"/>
-      <c r="AB5" s="240"/>
-      <c r="AC5" s="240"/>
-      <c r="AD5" s="240"/>
-      <c r="AE5" s="240"/>
-      <c r="AF5" s="240"/>
-      <c r="AG5" s="240"/>
-      <c r="AH5" s="240"/>
-      <c r="AI5" s="240"/>
-      <c r="AJ5" s="240"/>
-      <c r="AK5" s="240"/>
-      <c r="AL5" s="240"/>
-      <c r="AM5" s="240"/>
-      <c r="AN5" s="240"/>
-      <c r="AO5" s="240"/>
-      <c r="AP5" s="240"/>
-      <c r="AQ5" s="240"/>
-      <c r="AR5" s="240"/>
-      <c r="AS5" s="240"/>
-      <c r="AT5" s="240"/>
-      <c r="AU5" s="240"/>
-      <c r="AV5" s="240"/>
-      <c r="AW5" s="240"/>
-      <c r="AX5" s="240"/>
-    </row>
-    <row r="6" spans="1:51" ht="7.5" hidden="1" customHeight="1">
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="213"/>
+      <c r="U4" s="213"/>
+      <c r="V4" s="213"/>
+      <c r="W4" s="213"/>
+      <c r="X4" s="213"/>
+      <c r="Y4" s="213"/>
+      <c r="Z4" s="213"/>
+      <c r="AA4" s="213"/>
+      <c r="AB4" s="213"/>
+      <c r="AC4" s="213"/>
+      <c r="AD4" s="213"/>
+      <c r="AE4" s="213"/>
+      <c r="AF4" s="213"/>
+      <c r="AG4" s="213"/>
+      <c r="AH4" s="213"/>
+      <c r="AI4" s="213"/>
+      <c r="AJ4" s="213"/>
+      <c r="AK4" s="213"/>
+      <c r="AL4" s="213"/>
+      <c r="AM4" s="213"/>
+      <c r="AN4" s="213"/>
+      <c r="AO4" s="213"/>
+      <c r="AP4" s="213"/>
+      <c r="AQ4" s="213"/>
+      <c r="AR4" s="213"/>
+      <c r="AS4" s="213"/>
+      <c r="AT4" s="213"/>
+      <c r="AU4" s="213"/>
+      <c r="AV4" s="213"/>
+      <c r="AW4" s="213"/>
+      <c r="AX4" s="213"/>
+    </row>
+    <row r="5" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="213"/>
+      <c r="D5" s="213"/>
+      <c r="E5" s="213"/>
+      <c r="F5" s="213"/>
+      <c r="G5" s="213"/>
+      <c r="H5" s="213"/>
+      <c r="I5" s="213"/>
+      <c r="J5" s="213"/>
+      <c r="K5" s="213"/>
+      <c r="L5" s="213"/>
+      <c r="M5" s="213"/>
+      <c r="N5" s="213"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="213"/>
+      <c r="Q5" s="213"/>
+      <c r="R5" s="213"/>
+      <c r="S5" s="213"/>
+      <c r="T5" s="213"/>
+      <c r="U5" s="213"/>
+      <c r="V5" s="213"/>
+      <c r="W5" s="213"/>
+      <c r="X5" s="213"/>
+      <c r="Y5" s="213"/>
+      <c r="Z5" s="213"/>
+      <c r="AA5" s="213"/>
+      <c r="AB5" s="213"/>
+      <c r="AC5" s="213"/>
+      <c r="AD5" s="213"/>
+      <c r="AE5" s="213"/>
+      <c r="AF5" s="213"/>
+      <c r="AG5" s="213"/>
+      <c r="AH5" s="213"/>
+      <c r="AI5" s="213"/>
+      <c r="AJ5" s="213"/>
+      <c r="AK5" s="213"/>
+      <c r="AL5" s="213"/>
+      <c r="AM5" s="213"/>
+      <c r="AN5" s="213"/>
+      <c r="AO5" s="213"/>
+      <c r="AP5" s="213"/>
+      <c r="AQ5" s="213"/>
+      <c r="AR5" s="213"/>
+      <c r="AS5" s="213"/>
+      <c r="AT5" s="213"/>
+      <c r="AU5" s="213"/>
+      <c r="AV5" s="213"/>
+      <c r="AW5" s="213"/>
+      <c r="AX5" s="213"/>
+    </row>
+    <row r="6" spans="1:51" ht="7.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F6">
         <v>11</v>
       </c>
@@ -9886,16 +9976,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:51" ht="6" customHeight="1"/>
-    <row r="8" spans="1:51" ht="6" customHeight="1">
+    <row r="7" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" s="77"/>
       <c r="E8" s="77"/>
       <c r="F8" s="77"/>
-      <c r="G8" s="241" t="str">
+      <c r="G8" s="214" t="str">
         <f>CONCATENATE("-",H6,"°")</f>
         <v>-10°</v>
       </c>
-      <c r="H8" s="241"/>
+      <c r="H8" s="214"/>
       <c r="I8" s="78"/>
       <c r="J8" s="78"/>
       <c r="K8" s="78"/>
@@ -9904,37 +9994,37 @@
       <c r="N8" s="78"/>
       <c r="O8" s="78"/>
       <c r="P8" s="78"/>
-      <c r="Q8" s="242" t="str">
+      <c r="Q8" s="215" t="str">
         <f>CONCATENATE("-",R6,"°")</f>
         <v>-5°</v>
       </c>
-      <c r="R8" s="242"/>
+      <c r="R8" s="215"/>
       <c r="S8" s="78"/>
       <c r="T8" s="78"/>
       <c r="U8" s="78"/>
       <c r="V8" s="78"/>
-      <c r="W8" s="243"/>
-      <c r="X8" s="243"/>
+      <c r="W8" s="216"/>
+      <c r="X8" s="216"/>
       <c r="Y8" s="78"/>
       <c r="Z8" s="78"/>
-      <c r="AA8" s="242" t="str">
+      <c r="AA8" s="215" t="str">
         <f>CONCATENATE(AB6,"°")</f>
         <v>0°</v>
       </c>
-      <c r="AB8" s="242"/>
+      <c r="AB8" s="215"/>
       <c r="AC8" s="78"/>
       <c r="AD8" s="78"/>
-      <c r="AE8" s="244"/>
-      <c r="AF8" s="244"/>
+      <c r="AE8" s="217"/>
+      <c r="AF8" s="217"/>
       <c r="AG8" s="78"/>
       <c r="AH8" s="78"/>
       <c r="AI8" s="78"/>
       <c r="AJ8" s="78"/>
-      <c r="AK8" s="242" t="str">
+      <c r="AK8" s="215" t="str">
         <f>CONCATENATE(AL6,"°")</f>
         <v>5°</v>
       </c>
-      <c r="AL8" s="242"/>
+      <c r="AL8" s="215"/>
       <c r="AM8" s="78"/>
       <c r="AN8" s="78"/>
       <c r="AO8" s="78"/>
@@ -9943,226 +10033,226 @@
       <c r="AR8" s="78"/>
       <c r="AS8" s="78"/>
       <c r="AT8" s="78"/>
-      <c r="AU8" s="242" t="str">
+      <c r="AU8" s="215" t="str">
         <f>CONCATENATE(AV6,"°")</f>
         <v>10°</v>
       </c>
-      <c r="AV8" s="242"/>
+      <c r="AV8" s="215"/>
       <c r="AW8" s="78"/>
       <c r="AX8" s="77"/>
       <c r="AY8" s="77"/>
     </row>
-    <row r="9" spans="1:51" ht="15.75" customHeight="1">
+    <row r="9" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="77"/>
-      <c r="E9" s="245" t="str">
+      <c r="E9" s="218" t="str">
         <f>CONCATENATE("-",F6,"°")</f>
         <v>-11°</v>
       </c>
-      <c r="F9" s="245"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="246" t="str">
+      <c r="F9" s="218"/>
+      <c r="G9" s="214"/>
+      <c r="H9" s="214"/>
+      <c r="I9" s="219" t="str">
         <f>CONCATENATE("-",J6,"°")</f>
         <v>-9°</v>
       </c>
-      <c r="J9" s="246"/>
-      <c r="K9" s="246" t="str">
+      <c r="J9" s="219"/>
+      <c r="K9" s="219" t="str">
         <f>CONCATENATE("-",L6,"°")</f>
         <v>-8°</v>
       </c>
-      <c r="L9" s="246"/>
-      <c r="M9" s="246" t="str">
+      <c r="L9" s="219"/>
+      <c r="M9" s="219" t="str">
         <f>CONCATENATE("-",N6,"°")</f>
         <v>-7°</v>
       </c>
-      <c r="N9" s="246"/>
-      <c r="O9" s="246" t="str">
+      <c r="N9" s="219"/>
+      <c r="O9" s="219" t="str">
         <f>CONCATENATE("-",P6,"°")</f>
         <v>-6°</v>
       </c>
-      <c r="P9" s="246"/>
-      <c r="Q9" s="242"/>
-      <c r="R9" s="242"/>
-      <c r="S9" s="246" t="str">
+      <c r="P9" s="219"/>
+      <c r="Q9" s="215"/>
+      <c r="R9" s="215"/>
+      <c r="S9" s="219" t="str">
         <f>CONCATENATE("-",T6,"°")</f>
         <v>-4°</v>
       </c>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246" t="str">
+      <c r="T9" s="219"/>
+      <c r="U9" s="219" t="str">
         <f>CONCATENATE("-",V6,"°")</f>
         <v>-3°</v>
       </c>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246" t="str">
+      <c r="V9" s="219"/>
+      <c r="W9" s="219" t="str">
         <f>CONCATENATE("-",X6,"°")</f>
         <v>-2°</v>
       </c>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246" t="str">
+      <c r="X9" s="219"/>
+      <c r="Y9" s="219" t="str">
         <f>CONCATENATE("-",Z6,"°")</f>
         <v>-1°</v>
       </c>
-      <c r="Z9" s="246"/>
-      <c r="AA9" s="242"/>
-      <c r="AB9" s="242"/>
-      <c r="AC9" s="246" t="str">
+      <c r="Z9" s="219"/>
+      <c r="AA9" s="215"/>
+      <c r="AB9" s="215"/>
+      <c r="AC9" s="219" t="str">
         <f>CONCATENATE(AD6,"°")</f>
         <v>1°</v>
       </c>
-      <c r="AD9" s="246"/>
-      <c r="AE9" s="246" t="str">
+      <c r="AD9" s="219"/>
+      <c r="AE9" s="219" t="str">
         <f>CONCATENATE(AF6,"°")</f>
         <v>2°</v>
       </c>
-      <c r="AF9" s="246"/>
-      <c r="AG9" s="246" t="str">
+      <c r="AF9" s="219"/>
+      <c r="AG9" s="219" t="str">
         <f>CONCATENATE(AH6,"°")</f>
         <v>3°</v>
       </c>
-      <c r="AH9" s="246"/>
-      <c r="AI9" s="246" t="str">
+      <c r="AH9" s="219"/>
+      <c r="AI9" s="219" t="str">
         <f>CONCATENATE(AJ6,"°")</f>
         <v>4°</v>
       </c>
-      <c r="AJ9" s="246"/>
-      <c r="AK9" s="242"/>
-      <c r="AL9" s="242"/>
-      <c r="AM9" s="246" t="str">
+      <c r="AJ9" s="219"/>
+      <c r="AK9" s="215"/>
+      <c r="AL9" s="215"/>
+      <c r="AM9" s="219" t="str">
         <f>CONCATENATE(AN6,"°")</f>
         <v>6°</v>
       </c>
-      <c r="AN9" s="246"/>
-      <c r="AO9" s="246" t="str">
+      <c r="AN9" s="219"/>
+      <c r="AO9" s="219" t="str">
         <f>CONCATENATE(AP6,"°")</f>
         <v>7°</v>
       </c>
-      <c r="AP9" s="246"/>
-      <c r="AQ9" s="246" t="str">
+      <c r="AP9" s="219"/>
+      <c r="AQ9" s="219" t="str">
         <f>CONCATENATE(AR6,"°")</f>
         <v>8°</v>
       </c>
-      <c r="AR9" s="246"/>
-      <c r="AS9" s="246" t="str">
+      <c r="AR9" s="219"/>
+      <c r="AS9" s="219" t="str">
         <f>CONCATENATE(AT6,"°")</f>
         <v>9°</v>
       </c>
-      <c r="AT9" s="246"/>
-      <c r="AU9" s="242"/>
-      <c r="AV9" s="242"/>
-      <c r="AW9" s="246" t="str">
+      <c r="AT9" s="219"/>
+      <c r="AU9" s="215"/>
+      <c r="AV9" s="215"/>
+      <c r="AW9" s="219" t="str">
         <f>CONCATENATE(AX6,"°")</f>
         <v>11°</v>
       </c>
-      <c r="AX9" s="246"/>
+      <c r="AX9" s="219"/>
       <c r="AY9" s="77"/>
     </row>
-    <row r="10" spans="1:51" ht="6" customHeight="1">
-      <c r="F10" s="247"/>
-      <c r="G10" s="248"/>
-      <c r="H10" s="249"/>
-      <c r="I10" s="247"/>
-      <c r="J10" s="247"/>
-      <c r="K10" s="247"/>
-      <c r="L10" s="247"/>
-      <c r="M10" s="247"/>
-      <c r="N10" s="247"/>
-      <c r="O10" s="247"/>
-      <c r="P10" s="247"/>
-      <c r="Q10" s="248"/>
-      <c r="R10" s="251"/>
-      <c r="S10" s="252"/>
-      <c r="T10" s="247"/>
-      <c r="U10" s="247"/>
-      <c r="V10" s="247"/>
-      <c r="W10" s="247"/>
-      <c r="X10" s="247"/>
-      <c r="Y10" s="247"/>
-      <c r="Z10" s="247"/>
-      <c r="AA10" s="247"/>
-      <c r="AB10" s="249"/>
-      <c r="AC10" s="247"/>
-      <c r="AD10" s="247"/>
-      <c r="AE10" s="247"/>
-      <c r="AF10" s="247"/>
-      <c r="AG10" s="247"/>
-      <c r="AH10" s="247"/>
-      <c r="AI10" s="247"/>
-      <c r="AJ10" s="247"/>
-      <c r="AK10" s="247"/>
-      <c r="AL10" s="249"/>
-      <c r="AM10" s="247"/>
-      <c r="AN10" s="247"/>
-      <c r="AO10" s="247"/>
-      <c r="AP10" s="247"/>
-      <c r="AQ10" s="247"/>
-      <c r="AR10" s="247"/>
-      <c r="AS10" s="247"/>
-      <c r="AT10" s="247"/>
-      <c r="AU10" s="247"/>
-      <c r="AV10" s="249"/>
-      <c r="AW10" s="247"/>
-    </row>
-    <row r="11" spans="1:51" ht="6" customHeight="1">
+    <row r="10" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="220"/>
+      <c r="G10" s="221"/>
+      <c r="H10" s="222"/>
+      <c r="I10" s="220"/>
+      <c r="J10" s="220"/>
+      <c r="K10" s="220"/>
+      <c r="L10" s="220"/>
+      <c r="M10" s="220"/>
+      <c r="N10" s="220"/>
+      <c r="O10" s="220"/>
+      <c r="P10" s="220"/>
+      <c r="Q10" s="221"/>
+      <c r="R10" s="224"/>
+      <c r="S10" s="225"/>
+      <c r="T10" s="220"/>
+      <c r="U10" s="220"/>
+      <c r="V10" s="220"/>
+      <c r="W10" s="220"/>
+      <c r="X10" s="220"/>
+      <c r="Y10" s="220"/>
+      <c r="Z10" s="220"/>
+      <c r="AA10" s="220"/>
+      <c r="AB10" s="222"/>
+      <c r="AC10" s="220"/>
+      <c r="AD10" s="220"/>
+      <c r="AE10" s="220"/>
+      <c r="AF10" s="220"/>
+      <c r="AG10" s="220"/>
+      <c r="AH10" s="220"/>
+      <c r="AI10" s="220"/>
+      <c r="AJ10" s="220"/>
+      <c r="AK10" s="220"/>
+      <c r="AL10" s="222"/>
+      <c r="AM10" s="220"/>
+      <c r="AN10" s="220"/>
+      <c r="AO10" s="220"/>
+      <c r="AP10" s="220"/>
+      <c r="AQ10" s="220"/>
+      <c r="AR10" s="220"/>
+      <c r="AS10" s="220"/>
+      <c r="AT10" s="220"/>
+      <c r="AU10" s="220"/>
+      <c r="AV10" s="222"/>
+      <c r="AW10" s="220"/>
+    </row>
+    <row r="11" spans="1:51" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" s="250" t="str">
+      <c r="C11" s="223" t="str">
         <f>CONCATENATE(B11,"°")</f>
         <v>0°</v>
       </c>
-      <c r="D11" s="250"/>
+      <c r="D11" s="223"/>
       <c r="E11" s="79"/>
-      <c r="F11" s="247"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="249"/>
-      <c r="I11" s="247"/>
-      <c r="J11" s="247"/>
-      <c r="K11" s="247"/>
-      <c r="L11" s="247"/>
-      <c r="M11" s="247"/>
-      <c r="N11" s="247"/>
-      <c r="O11" s="247"/>
-      <c r="P11" s="247"/>
-      <c r="Q11" s="248"/>
-      <c r="R11" s="251"/>
-      <c r="S11" s="252"/>
-      <c r="T11" s="247"/>
-      <c r="U11" s="247"/>
-      <c r="V11" s="247"/>
-      <c r="W11" s="247"/>
-      <c r="X11" s="247"/>
-      <c r="Y11" s="247"/>
-      <c r="Z11" s="247"/>
-      <c r="AA11" s="247"/>
-      <c r="AB11" s="249"/>
-      <c r="AC11" s="247"/>
-      <c r="AD11" s="247"/>
-      <c r="AE11" s="247"/>
-      <c r="AF11" s="247"/>
-      <c r="AG11" s="247"/>
-      <c r="AH11" s="247"/>
-      <c r="AI11" s="247"/>
-      <c r="AJ11" s="247"/>
-      <c r="AK11" s="247"/>
-      <c r="AL11" s="249"/>
-      <c r="AM11" s="247"/>
-      <c r="AN11" s="247"/>
-      <c r="AO11" s="247"/>
-      <c r="AP11" s="247"/>
-      <c r="AQ11" s="247"/>
-      <c r="AR11" s="247"/>
-      <c r="AS11" s="247"/>
-      <c r="AT11" s="247"/>
-      <c r="AU11" s="247"/>
-      <c r="AV11" s="249"/>
-      <c r="AW11" s="247"/>
-    </row>
-    <row r="12" spans="1:51" ht="15" customHeight="1">
-      <c r="C12" s="250"/>
-      <c r="D12" s="250"/>
+      <c r="F11" s="220"/>
+      <c r="G11" s="221"/>
+      <c r="H11" s="222"/>
+      <c r="I11" s="220"/>
+      <c r="J11" s="220"/>
+      <c r="K11" s="220"/>
+      <c r="L11" s="220"/>
+      <c r="M11" s="220"/>
+      <c r="N11" s="220"/>
+      <c r="O11" s="220"/>
+      <c r="P11" s="220"/>
+      <c r="Q11" s="221"/>
+      <c r="R11" s="224"/>
+      <c r="S11" s="225"/>
+      <c r="T11" s="220"/>
+      <c r="U11" s="220"/>
+      <c r="V11" s="220"/>
+      <c r="W11" s="220"/>
+      <c r="X11" s="220"/>
+      <c r="Y11" s="220"/>
+      <c r="Z11" s="220"/>
+      <c r="AA11" s="220"/>
+      <c r="AB11" s="222"/>
+      <c r="AC11" s="220"/>
+      <c r="AD11" s="220"/>
+      <c r="AE11" s="220"/>
+      <c r="AF11" s="220"/>
+      <c r="AG11" s="220"/>
+      <c r="AH11" s="220"/>
+      <c r="AI11" s="220"/>
+      <c r="AJ11" s="220"/>
+      <c r="AK11" s="220"/>
+      <c r="AL11" s="222"/>
+      <c r="AM11" s="220"/>
+      <c r="AN11" s="220"/>
+      <c r="AO11" s="220"/>
+      <c r="AP11" s="220"/>
+      <c r="AQ11" s="220"/>
+      <c r="AR11" s="220"/>
+      <c r="AS11" s="220"/>
+      <c r="AT11" s="220"/>
+      <c r="AU11" s="220"/>
+      <c r="AV11" s="222"/>
+      <c r="AW11" s="220"/>
+    </row>
+    <row r="12" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="223"/>
+      <c r="D12" s="223"/>
       <c r="E12" s="79"/>
       <c r="F12" s="80"/>
       <c r="G12" s="81"/>
@@ -10209,16 +10299,16 @@
       <c r="AV12" s="82"/>
       <c r="AW12" s="80"/>
     </row>
-    <row r="13" spans="1:51" ht="15" customHeight="1">
+    <row r="13" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13">
         <f>B11+$A$11</f>
         <v>20</v>
       </c>
-      <c r="C13" s="250" t="str">
+      <c r="C13" s="223" t="str">
         <f>CONCATENATE(B13,"°")</f>
         <v>20°</v>
       </c>
-      <c r="D13" s="250"/>
+      <c r="D13" s="223"/>
       <c r="E13" s="79"/>
       <c r="F13" s="84"/>
       <c r="G13" s="85"/>
@@ -10265,9 +10355,9 @@
       <c r="AV13" s="86"/>
       <c r="AW13" s="84"/>
     </row>
-    <row r="14" spans="1:51" ht="15" customHeight="1">
-      <c r="C14" s="250"/>
-      <c r="D14" s="250"/>
+    <row r="14" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="223"/>
+      <c r="D14" s="223"/>
       <c r="E14" s="79"/>
       <c r="F14" s="88"/>
       <c r="G14" s="89"/>
@@ -10314,16 +10404,16 @@
       <c r="AV14" s="90"/>
       <c r="AW14" s="88"/>
     </row>
-    <row r="15" spans="1:51" ht="15" customHeight="1">
+    <row r="15" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15">
         <f>B13+$A$11</f>
         <v>40</v>
       </c>
-      <c r="C15" s="250" t="str">
+      <c r="C15" s="223" t="str">
         <f>CONCATENATE(B15,"°")</f>
         <v>40°</v>
       </c>
-      <c r="D15" s="250"/>
+      <c r="D15" s="223"/>
       <c r="E15" s="79"/>
       <c r="F15" s="92"/>
       <c r="G15" s="93"/>
@@ -10370,9 +10460,9 @@
       <c r="AV15" s="94"/>
       <c r="AW15" s="92"/>
     </row>
-    <row r="16" spans="1:51" ht="15" customHeight="1">
-      <c r="C16" s="250"/>
-      <c r="D16" s="250"/>
+    <row r="16" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
       <c r="E16" s="79"/>
       <c r="F16" s="96"/>
       <c r="G16" s="97"/>
@@ -10419,16 +10509,16 @@
       <c r="AV16" s="98"/>
       <c r="AW16" s="96"/>
     </row>
-    <row r="17" spans="2:49" ht="15" customHeight="1">
+    <row r="17" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17">
         <f>B15+$A$11</f>
         <v>60</v>
       </c>
-      <c r="C17" s="250" t="str">
+      <c r="C17" s="223" t="str">
         <f>CONCATENATE(B17,"°")</f>
         <v>60°</v>
       </c>
-      <c r="D17" s="250"/>
+      <c r="D17" s="223"/>
       <c r="E17" s="79"/>
       <c r="F17" s="84"/>
       <c r="G17" s="85"/>
@@ -10475,9 +10565,9 @@
       <c r="AV17" s="86"/>
       <c r="AW17" s="84"/>
     </row>
-    <row r="18" spans="2:49" ht="15" customHeight="1">
-      <c r="C18" s="250"/>
-      <c r="D18" s="250"/>
+    <row r="18" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="223"/>
+      <c r="D18" s="223"/>
       <c r="E18" s="79"/>
       <c r="F18" s="88"/>
       <c r="G18" s="89"/>
@@ -10524,16 +10614,16 @@
       <c r="AV18" s="90"/>
       <c r="AW18" s="88"/>
     </row>
-    <row r="19" spans="2:49" ht="15" customHeight="1">
+    <row r="19" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19">
         <f>B17+$A$11</f>
         <v>80</v>
       </c>
-      <c r="C19" s="250" t="str">
+      <c r="C19" s="223" t="str">
         <f>CONCATENATE(B19,"°")</f>
         <v>80°</v>
       </c>
-      <c r="D19" s="250"/>
+      <c r="D19" s="223"/>
       <c r="E19" s="79"/>
       <c r="F19" s="100"/>
       <c r="G19" s="101"/>
@@ -10580,9 +10670,9 @@
       <c r="AV19" s="102"/>
       <c r="AW19" s="100"/>
     </row>
-    <row r="20" spans="2:49" ht="15" customHeight="1">
-      <c r="C20" s="250"/>
-      <c r="D20" s="250"/>
+    <row r="20" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="223"/>
+      <c r="D20" s="223"/>
       <c r="E20" s="79"/>
       <c r="F20" s="104"/>
       <c r="G20" s="105"/>
@@ -10629,16 +10719,16 @@
       <c r="AV20" s="106"/>
       <c r="AW20" s="104"/>
     </row>
-    <row r="21" spans="2:49" ht="15" customHeight="1">
+    <row r="21" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21">
         <f>B19+$A$11</f>
         <v>100</v>
       </c>
-      <c r="C21" s="250" t="str">
+      <c r="C21" s="223" t="str">
         <f>CONCATENATE(B21,"°")</f>
         <v>100°</v>
       </c>
-      <c r="D21" s="250"/>
+      <c r="D21" s="223"/>
       <c r="E21" s="79"/>
       <c r="F21" s="108"/>
       <c r="G21" s="109"/>
@@ -10685,9 +10775,9 @@
       <c r="AV21" s="110"/>
       <c r="AW21" s="108"/>
     </row>
-    <row r="22" spans="2:49" ht="15" customHeight="1">
-      <c r="C22" s="250"/>
-      <c r="D22" s="250"/>
+    <row r="22" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
       <c r="E22" s="79"/>
       <c r="F22" s="88"/>
       <c r="G22" s="89"/>
@@ -10734,16 +10824,16 @@
       <c r="AV22" s="90"/>
       <c r="AW22" s="88"/>
     </row>
-    <row r="23" spans="2:49" ht="15" customHeight="1">
+    <row r="23" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23">
         <f>B21+$A$11</f>
         <v>120</v>
       </c>
-      <c r="C23" s="250" t="str">
+      <c r="C23" s="223" t="str">
         <f>CONCATENATE(B23,"°")</f>
         <v>120°</v>
       </c>
-      <c r="D23" s="250"/>
+      <c r="D23" s="223"/>
       <c r="E23" s="79"/>
       <c r="F23" s="100"/>
       <c r="G23" s="101"/>
@@ -10790,9 +10880,9 @@
       <c r="AV23" s="102"/>
       <c r="AW23" s="100"/>
     </row>
-    <row r="24" spans="2:49" ht="15" customHeight="1">
-      <c r="C24" s="250"/>
-      <c r="D24" s="250"/>
+    <row r="24" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="223"/>
+      <c r="D24" s="223"/>
       <c r="E24" s="79"/>
       <c r="F24" s="96"/>
       <c r="G24" s="97"/>
@@ -10839,16 +10929,16 @@
       <c r="AV24" s="98"/>
       <c r="AW24" s="96"/>
     </row>
-    <row r="25" spans="2:49" ht="15" customHeight="1">
+    <row r="25" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25">
         <f>B23+$A$11</f>
         <v>140</v>
       </c>
-      <c r="C25" s="250" t="str">
+      <c r="C25" s="223" t="str">
         <f>CONCATENATE(B25,"°")</f>
         <v>140°</v>
       </c>
-      <c r="D25" s="250"/>
+      <c r="D25" s="223"/>
       <c r="E25" s="79"/>
       <c r="F25" s="84"/>
       <c r="G25" s="85"/>
@@ -10895,9 +10985,9 @@
       <c r="AV25" s="86"/>
       <c r="AW25" s="84"/>
     </row>
-    <row r="26" spans="2:49" ht="15" customHeight="1">
-      <c r="C26" s="250"/>
-      <c r="D26" s="250"/>
+    <row r="26" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="223"/>
+      <c r="D26" s="223"/>
       <c r="E26" s="79"/>
       <c r="F26" s="100"/>
       <c r="G26" s="101"/>
@@ -10944,16 +11034,16 @@
       <c r="AV26" s="102"/>
       <c r="AW26" s="100"/>
     </row>
-    <row r="27" spans="2:49" ht="15" customHeight="1">
+    <row r="27" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27">
         <f>B25+$A$11</f>
         <v>160</v>
       </c>
-      <c r="C27" s="250" t="str">
+      <c r="C27" s="223" t="str">
         <f>CONCATENATE(B27,"°")</f>
         <v>160°</v>
       </c>
-      <c r="D27" s="250"/>
+      <c r="D27" s="223"/>
       <c r="E27" s="79"/>
       <c r="F27" s="100"/>
       <c r="G27" s="101"/>
@@ -11000,9 +11090,9 @@
       <c r="AV27" s="102"/>
       <c r="AW27" s="100"/>
     </row>
-    <row r="28" spans="2:49" ht="15" customHeight="1">
-      <c r="C28" s="250"/>
-      <c r="D28" s="250"/>
+    <row r="28" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="223"/>
+      <c r="D28" s="223"/>
       <c r="E28" s="79"/>
       <c r="F28" s="96"/>
       <c r="G28" s="97"/>
@@ -11049,16 +11139,16 @@
       <c r="AV28" s="98"/>
       <c r="AW28" s="96"/>
     </row>
-    <row r="29" spans="2:49" ht="15" customHeight="1">
+    <row r="29" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29">
         <f>B27+$A$11</f>
         <v>180</v>
       </c>
-      <c r="C29" s="250" t="str">
+      <c r="C29" s="223" t="str">
         <f>CONCATENATE(B29,"°")</f>
         <v>180°</v>
       </c>
-      <c r="D29" s="250"/>
+      <c r="D29" s="223"/>
       <c r="E29" s="79"/>
       <c r="F29" s="92"/>
       <c r="G29" s="93"/>
@@ -11105,9 +11195,9 @@
       <c r="AV29" s="94"/>
       <c r="AW29" s="92"/>
     </row>
-    <row r="30" spans="2:49" ht="15" customHeight="1">
-      <c r="C30" s="250"/>
-      <c r="D30" s="250"/>
+    <row r="30" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
       <c r="E30" s="79"/>
       <c r="F30" s="80"/>
       <c r="G30" s="81"/>
@@ -11154,16 +11244,16 @@
       <c r="AV30" s="82"/>
       <c r="AW30" s="80"/>
     </row>
-    <row r="31" spans="2:49" ht="15" customHeight="1">
+    <row r="31" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31">
         <f>B29+$A$11</f>
         <v>200</v>
       </c>
-      <c r="C31" s="250" t="str">
+      <c r="C31" s="223" t="str">
         <f>CONCATENATE(B31,"°")</f>
         <v>200°</v>
       </c>
-      <c r="D31" s="250"/>
+      <c r="D31" s="223"/>
       <c r="E31" s="79"/>
       <c r="F31" s="100"/>
       <c r="G31" s="101"/>
@@ -11210,9 +11300,9 @@
       <c r="AV31" s="102"/>
       <c r="AW31" s="100"/>
     </row>
-    <row r="32" spans="2:49" ht="15" customHeight="1">
-      <c r="C32" s="250"/>
-      <c r="D32" s="250"/>
+    <row r="32" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
       <c r="E32" s="79"/>
       <c r="F32" s="96"/>
       <c r="G32" s="97"/>
@@ -11259,16 +11349,16 @@
       <c r="AV32" s="98"/>
       <c r="AW32" s="96"/>
     </row>
-    <row r="33" spans="2:49" ht="15" customHeight="1">
+    <row r="33" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33">
         <f>B31+$A$11</f>
         <v>220</v>
       </c>
-      <c r="C33" s="250" t="str">
+      <c r="C33" s="223" t="str">
         <f>CONCATENATE(B33,"°")</f>
         <v>220°</v>
       </c>
-      <c r="D33" s="250"/>
+      <c r="D33" s="223"/>
       <c r="E33" s="79"/>
       <c r="F33" s="84"/>
       <c r="G33" s="85"/>
@@ -11315,9 +11405,9 @@
       <c r="AV33" s="86"/>
       <c r="AW33" s="84"/>
     </row>
-    <row r="34" spans="2:49" ht="15" customHeight="1">
-      <c r="C34" s="250"/>
-      <c r="D34" s="250"/>
+    <row r="34" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
       <c r="E34" s="79"/>
       <c r="F34" s="100"/>
       <c r="G34" s="101"/>
@@ -11364,16 +11454,16 @@
       <c r="AV34" s="102"/>
       <c r="AW34" s="100"/>
     </row>
-    <row r="35" spans="2:49" ht="15" customHeight="1">
+    <row r="35" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35">
         <f>B33+$A$11</f>
         <v>240</v>
       </c>
-      <c r="C35" s="250" t="str">
+      <c r="C35" s="223" t="str">
         <f>CONCATENATE(B35,"°")</f>
         <v>240°</v>
       </c>
-      <c r="D35" s="250"/>
+      <c r="D35" s="223"/>
       <c r="E35" s="79"/>
       <c r="F35" s="100"/>
       <c r="G35" s="101"/>
@@ -11420,9 +11510,9 @@
       <c r="AV35" s="102"/>
       <c r="AW35" s="100"/>
     </row>
-    <row r="36" spans="2:49" ht="15" customHeight="1">
-      <c r="C36" s="250"/>
-      <c r="D36" s="250"/>
+    <row r="36" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
       <c r="E36" s="79"/>
       <c r="F36" s="96"/>
       <c r="G36" s="97"/>
@@ -11469,16 +11559,16 @@
       <c r="AV36" s="98"/>
       <c r="AW36" s="96"/>
     </row>
-    <row r="37" spans="2:49" ht="15" customHeight="1">
+    <row r="37" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37">
         <f>B35+$A$11</f>
         <v>260</v>
       </c>
-      <c r="C37" s="250" t="str">
+      <c r="C37" s="223" t="str">
         <f>CONCATENATE(B37,"°")</f>
         <v>260°</v>
       </c>
-      <c r="D37" s="250"/>
+      <c r="D37" s="223"/>
       <c r="E37" s="79"/>
       <c r="F37" s="84"/>
       <c r="G37" s="85"/>
@@ -11525,9 +11615,9 @@
       <c r="AV37" s="86"/>
       <c r="AW37" s="84"/>
     </row>
-    <row r="38" spans="2:49" ht="15" customHeight="1">
-      <c r="C38" s="250"/>
-      <c r="D38" s="250"/>
+    <row r="38" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="223"/>
+      <c r="D38" s="223"/>
       <c r="E38" s="79"/>
       <c r="F38" s="92"/>
       <c r="G38" s="93"/>
@@ -11574,16 +11664,16 @@
       <c r="AV38" s="94"/>
       <c r="AW38" s="92"/>
     </row>
-    <row r="39" spans="2:49" ht="15" customHeight="1">
+    <row r="39" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39">
         <f>B37+$A$11</f>
         <v>280</v>
       </c>
-      <c r="C39" s="250" t="str">
+      <c r="C39" s="223" t="str">
         <f>CONCATENATE(B39,"°")</f>
         <v>280°</v>
       </c>
-      <c r="D39" s="250"/>
+      <c r="D39" s="223"/>
       <c r="E39" s="79"/>
       <c r="F39" s="80"/>
       <c r="G39" s="81"/>
@@ -11630,9 +11720,9 @@
       <c r="AV39" s="82"/>
       <c r="AW39" s="80"/>
     </row>
-    <row r="40" spans="2:49" ht="15" customHeight="1">
-      <c r="C40" s="250"/>
-      <c r="D40" s="250"/>
+    <row r="40" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="223"/>
+      <c r="D40" s="223"/>
       <c r="E40" s="79"/>
       <c r="F40" s="96"/>
       <c r="G40" s="97"/>
@@ -11679,16 +11769,16 @@
       <c r="AV40" s="98"/>
       <c r="AW40" s="96"/>
     </row>
-    <row r="41" spans="2:49" ht="15" customHeight="1">
+    <row r="41" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41">
         <f>B39+$A$11</f>
         <v>300</v>
       </c>
-      <c r="C41" s="250" t="str">
+      <c r="C41" s="223" t="str">
         <f>CONCATENATE(B41,"°")</f>
         <v>300°</v>
       </c>
-      <c r="D41" s="250"/>
+      <c r="D41" s="223"/>
       <c r="E41" s="79"/>
       <c r="F41" s="84"/>
       <c r="G41" s="85"/>
@@ -11735,9 +11825,9 @@
       <c r="AV41" s="86"/>
       <c r="AW41" s="84"/>
     </row>
-    <row r="42" spans="2:49" ht="15" customHeight="1">
-      <c r="C42" s="250"/>
-      <c r="D42" s="250"/>
+    <row r="42" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="223"/>
+      <c r="D42" s="223"/>
       <c r="E42" s="79"/>
       <c r="F42" s="100"/>
       <c r="G42" s="101"/>
@@ -11784,16 +11874,16 @@
       <c r="AV42" s="102"/>
       <c r="AW42" s="100"/>
     </row>
-    <row r="43" spans="2:49" ht="15" customHeight="1">
+    <row r="43" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43">
         <f>B41+$A$11</f>
         <v>320</v>
       </c>
-      <c r="C43" s="250" t="str">
+      <c r="C43" s="223" t="str">
         <f>CONCATENATE(B43,"°")</f>
         <v>320°</v>
       </c>
-      <c r="D43" s="250"/>
+      <c r="D43" s="223"/>
       <c r="E43" s="79"/>
       <c r="F43" s="100"/>
       <c r="G43" s="101"/>
@@ -11840,9 +11930,9 @@
       <c r="AV43" s="102"/>
       <c r="AW43" s="100"/>
     </row>
-    <row r="44" spans="2:49" ht="15" customHeight="1">
-      <c r="C44" s="250"/>
-      <c r="D44" s="250"/>
+    <row r="44" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="223"/>
+      <c r="D44" s="223"/>
       <c r="E44" s="79"/>
       <c r="F44" s="96"/>
       <c r="G44" s="97"/>
@@ -11889,16 +11979,16 @@
       <c r="AV44" s="98"/>
       <c r="AW44" s="96"/>
     </row>
-    <row r="45" spans="2:49" ht="15" customHeight="1">
+    <row r="45" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45">
         <f>B43+$A$11</f>
         <v>340</v>
       </c>
-      <c r="C45" s="250" t="str">
+      <c r="C45" s="223" t="str">
         <f>CONCATENATE(B45,"°")</f>
         <v>340°</v>
       </c>
-      <c r="D45" s="250"/>
+      <c r="D45" s="223"/>
       <c r="E45" s="79"/>
       <c r="F45" s="84"/>
       <c r="G45" s="85"/>
@@ -11945,9 +12035,9 @@
       <c r="AV45" s="86"/>
       <c r="AW45" s="84"/>
     </row>
-    <row r="46" spans="2:49" ht="15" customHeight="1">
-      <c r="C46" s="250"/>
-      <c r="D46" s="250"/>
+    <row r="46" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="223"/>
+      <c r="D46" s="223"/>
       <c r="E46" s="79"/>
       <c r="F46" s="100"/>
       <c r="G46" s="101"/>
@@ -11994,15 +12084,15 @@
       <c r="AV46" s="102"/>
       <c r="AW46" s="100"/>
     </row>
-    <row r="47" spans="2:49" ht="15" customHeight="1">
+    <row r="47" spans="2:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47">
         <v>0</v>
       </c>
-      <c r="C47" s="250" t="str">
+      <c r="C47" s="223" t="str">
         <f>CONCATENATE(B47,"°")</f>
         <v>0°</v>
       </c>
-      <c r="D47" s="250"/>
+      <c r="D47" s="223"/>
       <c r="E47" s="79"/>
       <c r="F47" s="92"/>
       <c r="G47" s="93"/>
@@ -12049,9 +12139,9 @@
       <c r="AV47" s="94"/>
       <c r="AW47" s="92"/>
     </row>
-    <row r="48" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C48" s="250"/>
-      <c r="D48" s="250"/>
+    <row r="48" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="223"/>
+      <c r="D48" s="223"/>
       <c r="E48" s="79"/>
       <c r="F48" s="80"/>
       <c r="G48" s="81"/>
@@ -12098,16 +12188,16 @@
       <c r="AV48" s="82"/>
       <c r="AW48" s="80"/>
     </row>
-    <row r="49" spans="2:49" ht="11.25" customHeight="1">
+    <row r="49" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49">
         <f>B47+$A$11</f>
         <v>20</v>
       </c>
-      <c r="C49" s="250" t="str">
+      <c r="C49" s="223" t="str">
         <f>CONCATENATE(B49,"°")</f>
         <v>20°</v>
       </c>
-      <c r="D49" s="250"/>
+      <c r="D49" s="223"/>
       <c r="E49" s="79"/>
       <c r="F49" s="113"/>
       <c r="G49" s="114"/>
@@ -12154,276 +12244,276 @@
       <c r="AV49" s="115"/>
       <c r="AW49" s="113"/>
     </row>
-    <row r="50" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C50" s="250"/>
-      <c r="D50" s="250"/>
+    <row r="50" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="223"/>
+      <c r="D50" s="223"/>
       <c r="E50" s="79"/>
       <c r="F50" s="79"/>
       <c r="G50" s="79"/>
     </row>
-    <row r="51" spans="2:49" ht="11.25" customHeight="1">
+    <row r="51" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51">
         <f>B49+$A$11</f>
         <v>40</v>
       </c>
-      <c r="C51" s="250" t="str">
+      <c r="C51" s="223" t="str">
         <f>CONCATENATE(B51,"°")</f>
         <v>40°</v>
       </c>
-      <c r="D51" s="253"/>
+      <c r="D51" s="226"/>
       <c r="E51" s="79"/>
       <c r="F51" s="79"/>
       <c r="G51" s="79"/>
     </row>
-    <row r="52" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C52" s="250"/>
-      <c r="D52" s="253"/>
+    <row r="52" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="223"/>
+      <c r="D52" s="226"/>
       <c r="E52" s="79"/>
       <c r="F52" s="79"/>
       <c r="G52" s="79"/>
     </row>
-    <row r="53" spans="2:49" ht="11.25" customHeight="1">
+    <row r="53" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53">
         <f>B51+$A$11</f>
         <v>60</v>
       </c>
-      <c r="C53" s="250" t="str">
+      <c r="C53" s="223" t="str">
         <f>CONCATENATE(B53,"°")</f>
         <v>60°</v>
       </c>
-      <c r="D53" s="253"/>
+      <c r="D53" s="226"/>
       <c r="E53" s="79"/>
       <c r="F53" s="79"/>
       <c r="G53" s="79"/>
     </row>
-    <row r="54" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C54" s="250"/>
-      <c r="D54" s="253"/>
+    <row r="54" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C54" s="223"/>
+      <c r="D54" s="226"/>
       <c r="E54" s="79"/>
       <c r="F54" s="79"/>
       <c r="G54" s="79"/>
     </row>
-    <row r="55" spans="2:49" ht="11.25" customHeight="1">
+    <row r="55" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55">
         <f>B53+$A$11</f>
         <v>80</v>
       </c>
-      <c r="C55" s="250" t="str">
+      <c r="C55" s="223" t="str">
         <f>CONCATENATE(B55,"°")</f>
         <v>80°</v>
       </c>
-      <c r="D55" s="253"/>
+      <c r="D55" s="226"/>
       <c r="E55" s="79"/>
       <c r="F55" s="79"/>
       <c r="G55" s="79"/>
     </row>
-    <row r="56" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C56" s="250"/>
-      <c r="D56" s="253"/>
+    <row r="56" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="223"/>
+      <c r="D56" s="226"/>
       <c r="E56" s="79"/>
       <c r="F56" s="79"/>
       <c r="G56" s="79"/>
     </row>
-    <row r="57" spans="2:49" ht="11.25" customHeight="1">
+    <row r="57" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57">
         <f>B55+$A$11</f>
         <v>100</v>
       </c>
-      <c r="C57" s="250" t="str">
+      <c r="C57" s="223" t="str">
         <f>CONCATENATE(B57,"°")</f>
         <v>100°</v>
       </c>
-      <c r="D57" s="253"/>
+      <c r="D57" s="226"/>
       <c r="E57" s="79"/>
       <c r="F57" s="79"/>
       <c r="G57" s="79"/>
     </row>
-    <row r="58" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C58" s="250"/>
-      <c r="D58" s="253"/>
+    <row r="58" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C58" s="223"/>
+      <c r="D58" s="226"/>
       <c r="E58" s="79"/>
       <c r="F58" s="79"/>
       <c r="G58" s="79"/>
     </row>
-    <row r="59" spans="2:49" ht="11.25" customHeight="1">
+    <row r="59" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59">
         <f>B57+$A$11</f>
         <v>120</v>
       </c>
-      <c r="C59" s="250" t="str">
+      <c r="C59" s="223" t="str">
         <f>CONCATENATE(B59,"°")</f>
         <v>120°</v>
       </c>
-      <c r="D59" s="253"/>
+      <c r="D59" s="226"/>
       <c r="E59" s="79"/>
       <c r="F59" s="79"/>
       <c r="G59" s="79"/>
     </row>
-    <row r="60" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C60" s="250"/>
-      <c r="D60" s="253"/>
+    <row r="60" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C60" s="223"/>
+      <c r="D60" s="226"/>
       <c r="E60" s="79"/>
       <c r="F60" s="79"/>
       <c r="G60" s="79"/>
     </row>
-    <row r="61" spans="2:49" ht="11.25" customHeight="1">
+    <row r="61" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61">
         <f>B59+$A$11</f>
         <v>140</v>
       </c>
-      <c r="C61" s="250" t="str">
+      <c r="C61" s="223" t="str">
         <f>CONCATENATE(B61,"°")</f>
         <v>140°</v>
       </c>
-      <c r="D61" s="253"/>
+      <c r="D61" s="226"/>
       <c r="E61" s="79"/>
       <c r="F61" s="79"/>
       <c r="G61" s="79"/>
     </row>
-    <row r="62" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C62" s="250"/>
-      <c r="D62" s="253"/>
+    <row r="62" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="223"/>
+      <c r="D62" s="226"/>
       <c r="E62" s="79"/>
       <c r="F62" s="79"/>
       <c r="G62" s="79"/>
     </row>
-    <row r="63" spans="2:49" ht="11.25" customHeight="1">
+    <row r="63" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63">
         <f>B61+$A$11</f>
         <v>160</v>
       </c>
-      <c r="C63" s="250" t="str">
+      <c r="C63" s="223" t="str">
         <f>CONCATENATE(B63,"°")</f>
         <v>160°</v>
       </c>
-      <c r="D63" s="253"/>
+      <c r="D63" s="226"/>
       <c r="E63" s="79"/>
       <c r="F63" s="79"/>
       <c r="G63" s="79"/>
     </row>
-    <row r="64" spans="2:49" ht="11.25" customHeight="1">
-      <c r="C64" s="250"/>
-      <c r="D64" s="253"/>
+    <row r="64" spans="2:49" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="223"/>
+      <c r="D64" s="226"/>
       <c r="E64" s="79"/>
       <c r="F64" s="79"/>
       <c r="G64" s="79"/>
     </row>
-    <row r="65" spans="1:31" ht="11.25" customHeight="1">
+    <row r="65" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65">
         <f>B63+$A$11</f>
         <v>180</v>
       </c>
-      <c r="C65" s="250" t="str">
+      <c r="C65" s="223" t="str">
         <f>CONCATENATE(B65,"°")</f>
         <v>180°</v>
       </c>
-      <c r="D65" s="253"/>
+      <c r="D65" s="226"/>
       <c r="E65" s="79"/>
       <c r="F65" s="79"/>
       <c r="G65" s="79"/>
     </row>
-    <row r="66" spans="1:31" ht="11.25" customHeight="1">
-      <c r="C66" s="250"/>
-      <c r="D66" s="253"/>
+    <row r="66" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C66" s="223"/>
+      <c r="D66" s="226"/>
       <c r="E66" s="79"/>
       <c r="F66" s="79"/>
       <c r="G66" s="79"/>
     </row>
-    <row r="67" spans="1:31" ht="11.25" customHeight="1">
+    <row r="67" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67">
         <f>B65+$A$11</f>
         <v>200</v>
       </c>
-      <c r="C67" s="250" t="str">
+      <c r="C67" s="223" t="str">
         <f>CONCATENATE(B67,"°")</f>
         <v>200°</v>
       </c>
-      <c r="D67" s="253"/>
+      <c r="D67" s="226"/>
       <c r="E67" s="79"/>
       <c r="F67" s="79"/>
       <c r="G67" s="79"/>
     </row>
-    <row r="68" spans="1:31" ht="11.25" customHeight="1">
-      <c r="C68" s="250"/>
-      <c r="D68" s="253"/>
+    <row r="68" spans="1:31" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C68" s="223"/>
+      <c r="D68" s="226"/>
       <c r="E68" s="79"/>
       <c r="F68" s="79"/>
       <c r="G68" s="79"/>
     </row>
-    <row r="71" spans="1:31">
-      <c r="A71" s="240" t="s">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A71" s="213" t="s">
         <v>143</v>
       </c>
-      <c r="B71" s="240"/>
-      <c r="C71" s="240"/>
-      <c r="D71" s="240"/>
-      <c r="E71" s="240"/>
-      <c r="F71" s="240"/>
-      <c r="G71" s="240"/>
-      <c r="H71" s="240"/>
-      <c r="I71" s="240"/>
-      <c r="J71" s="240"/>
-      <c r="K71" s="240"/>
-      <c r="L71" s="240"/>
-      <c r="M71" s="240"/>
-      <c r="N71" s="240"/>
-      <c r="O71" s="240"/>
-      <c r="P71" s="240"/>
-      <c r="Q71" s="240"/>
-      <c r="R71" s="240"/>
-      <c r="S71" s="240"/>
-      <c r="T71" s="240"/>
-      <c r="U71" s="240"/>
-      <c r="V71" s="240"/>
-      <c r="W71" s="240"/>
-      <c r="X71" s="240"/>
-      <c r="Y71" s="240"/>
-      <c r="Z71" s="240"/>
-      <c r="AA71" s="240"/>
-      <c r="AB71" s="240"/>
-      <c r="AC71" s="240"/>
-      <c r="AD71" s="240"/>
-      <c r="AE71" s="240"/>
-    </row>
-    <row r="72" spans="1:31">
-      <c r="A72" s="240"/>
-      <c r="B72" s="240"/>
-      <c r="C72" s="240"/>
-      <c r="D72" s="240"/>
-      <c r="E72" s="240"/>
-      <c r="F72" s="240"/>
-      <c r="G72" s="240"/>
-      <c r="H72" s="240"/>
-      <c r="I72" s="240"/>
-      <c r="J72" s="240"/>
-      <c r="K72" s="240"/>
-      <c r="L72" s="240"/>
-      <c r="M72" s="240"/>
-      <c r="N72" s="240"/>
-      <c r="O72" s="240"/>
-      <c r="P72" s="240"/>
-      <c r="Q72" s="240"/>
-      <c r="R72" s="240"/>
-      <c r="S72" s="240"/>
-      <c r="T72" s="240"/>
-      <c r="U72" s="240"/>
-      <c r="V72" s="240"/>
-      <c r="W72" s="240"/>
-      <c r="X72" s="240"/>
-      <c r="Y72" s="240"/>
-      <c r="Z72" s="240"/>
-      <c r="AA72" s="240"/>
-      <c r="AB72" s="240"/>
-      <c r="AC72" s="240"/>
-      <c r="AD72" s="240"/>
-      <c r="AE72" s="240"/>
-    </row>
-    <row r="74" spans="1:31">
+      <c r="B71" s="213"/>
+      <c r="C71" s="213"/>
+      <c r="D71" s="213"/>
+      <c r="E71" s="213"/>
+      <c r="F71" s="213"/>
+      <c r="G71" s="213"/>
+      <c r="H71" s="213"/>
+      <c r="I71" s="213"/>
+      <c r="J71" s="213"/>
+      <c r="K71" s="213"/>
+      <c r="L71" s="213"/>
+      <c r="M71" s="213"/>
+      <c r="N71" s="213"/>
+      <c r="O71" s="213"/>
+      <c r="P71" s="213"/>
+      <c r="Q71" s="213"/>
+      <c r="R71" s="213"/>
+      <c r="S71" s="213"/>
+      <c r="T71" s="213"/>
+      <c r="U71" s="213"/>
+      <c r="V71" s="213"/>
+      <c r="W71" s="213"/>
+      <c r="X71" s="213"/>
+      <c r="Y71" s="213"/>
+      <c r="Z71" s="213"/>
+      <c r="AA71" s="213"/>
+      <c r="AB71" s="213"/>
+      <c r="AC71" s="213"/>
+      <c r="AD71" s="213"/>
+      <c r="AE71" s="213"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A72" s="213"/>
+      <c r="B72" s="213"/>
+      <c r="C72" s="213"/>
+      <c r="D72" s="213"/>
+      <c r="E72" s="213"/>
+      <c r="F72" s="213"/>
+      <c r="G72" s="213"/>
+      <c r="H72" s="213"/>
+      <c r="I72" s="213"/>
+      <c r="J72" s="213"/>
+      <c r="K72" s="213"/>
+      <c r="L72" s="213"/>
+      <c r="M72" s="213"/>
+      <c r="N72" s="213"/>
+      <c r="O72" s="213"/>
+      <c r="P72" s="213"/>
+      <c r="Q72" s="213"/>
+      <c r="R72" s="213"/>
+      <c r="S72" s="213"/>
+      <c r="T72" s="213"/>
+      <c r="U72" s="213"/>
+      <c r="V72" s="213"/>
+      <c r="W72" s="213"/>
+      <c r="X72" s="213"/>
+      <c r="Y72" s="213"/>
+      <c r="Z72" s="213"/>
+      <c r="AA72" s="213"/>
+      <c r="AB72" s="213"/>
+      <c r="AC72" s="213"/>
+      <c r="AD72" s="213"/>
+      <c r="AE72" s="213"/>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C75" s="118" t="s">
         <v>145</v>
       </c>
@@ -12435,22 +12525,22 @@
       <c r="I75" s="118"/>
       <c r="J75" s="118"/>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="D76" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
       <c r="D77" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
       <c r="D78" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
       <c r="D79" s="119" t="s">
         <v>149</v>
       </c>
@@ -12461,7 +12551,7 @@
       <c r="I79" s="120"/>
       <c r="J79" s="120"/>
     </row>
-    <row r="81" spans="3:10">
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C81" s="118" t="s">
         <v>150</v>
       </c>
@@ -12473,12 +12563,12 @@
       <c r="I81" s="118"/>
       <c r="J81" s="118"/>
     </row>
-    <row r="82" spans="3:10">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D82" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="84" spans="3:10">
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C84" s="118" t="s">
         <v>152</v>
       </c>
@@ -12490,22 +12580,22 @@
       <c r="I84" s="118"/>
       <c r="J84" s="118"/>
     </row>
-    <row r="85" spans="3:10">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D85" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="87" spans="3:10">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="3:10">
+    <row r="88" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D88" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="89" spans="3:10">
+    <row r="89" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D89" t="s">
         <v>156</v>
       </c>
@@ -12513,13 +12603,13 @@
         <v>157</v>
       </c>
     </row>
-    <row r="90" spans="3:10">
+    <row r="90" spans="3:10" x14ac:dyDescent="0.25">
       <c r="I90" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="92" spans="3:10" ht="15" customHeight="1"/>
-    <row r="93" spans="3:10" ht="15" customHeight="1"/>
+    <row r="92" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="78">
     <mergeCell ref="C63:D64"/>
@@ -12609,509 +12699,885 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0BD825D-624A-4408-8B17-148EE9846B74}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:P16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="249" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="227" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="228" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="228"/>
+      <c r="I2" s="229"/>
+      <c r="J2" s="229" t="s">
+        <v>179</v>
+      </c>
+      <c r="K2" s="229"/>
+      <c r="L2" s="230"/>
+      <c r="M2" s="230"/>
+      <c r="N2" s="230"/>
+      <c r="O2" s="230"/>
+      <c r="P2" s="230"/>
+    </row>
+    <row r="3" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="250"/>
+      <c r="C3" s="227" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="228"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="228" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="228"/>
+      <c r="I3" s="229"/>
+      <c r="J3" s="229" t="s">
+        <v>178</v>
+      </c>
+      <c r="K3" s="229"/>
+      <c r="L3" s="230"/>
+      <c r="M3" s="230"/>
+      <c r="N3" s="230"/>
+      <c r="O3" s="230"/>
+      <c r="P3" s="230"/>
+    </row>
+    <row r="4" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="250"/>
+      <c r="C4" s="227" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="228"/>
+      <c r="E4" s="228"/>
+      <c r="F4" s="228"/>
+      <c r="G4" s="228" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="228"/>
+      <c r="I4" s="229"/>
+      <c r="J4" s="229" t="s">
+        <v>177</v>
+      </c>
+      <c r="K4" s="229"/>
+      <c r="L4" s="230"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+    </row>
+    <row r="5" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="250"/>
+      <c r="C5" s="227" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="228"/>
+      <c r="E5" s="228"/>
+      <c r="F5" s="228"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="229"/>
+      <c r="L5" s="230"/>
+      <c r="M5" s="230"/>
+      <c r="N5" s="230"/>
+      <c r="O5" s="230"/>
+      <c r="P5" s="230"/>
+    </row>
+    <row r="6" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="250"/>
+      <c r="C6" s="227" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="228"/>
+      <c r="E6" s="228"/>
+      <c r="F6" s="228"/>
+      <c r="G6" s="228"/>
+      <c r="H6" s="228"/>
+      <c r="I6" s="229"/>
+      <c r="J6" s="229"/>
+      <c r="K6" s="229"/>
+      <c r="L6" s="230"/>
+      <c r="M6" s="230"/>
+      <c r="N6" s="230"/>
+      <c r="O6" s="230"/>
+      <c r="P6" s="230"/>
+    </row>
+    <row r="7" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="251"/>
+      <c r="C7" s="227" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="228"/>
+      <c r="E7" s="228"/>
+      <c r="F7" s="228"/>
+      <c r="G7" s="228" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="228"/>
+      <c r="I7" s="229"/>
+      <c r="J7" s="229" t="s">
+        <v>176</v>
+      </c>
+      <c r="K7" s="229"/>
+      <c r="L7" s="230"/>
+      <c r="M7" s="230"/>
+      <c r="N7" s="230"/>
+      <c r="O7" s="230"/>
+      <c r="P7" s="230"/>
+    </row>
+    <row r="8" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="249" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="227" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="231" t="s">
+        <v>199</v>
+      </c>
+      <c r="L8" s="232" t="s">
+        <v>198</v>
+      </c>
+      <c r="M8" s="233"/>
+      <c r="N8" s="232" t="s">
+        <v>197</v>
+      </c>
+      <c r="O8" s="234"/>
+      <c r="P8" s="233"/>
+    </row>
+    <row r="9" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="250"/>
+      <c r="C9" s="227" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="228"/>
+      <c r="E9" s="228"/>
+      <c r="F9" s="228"/>
+      <c r="G9" s="228"/>
+      <c r="H9" s="228"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="236"/>
+      <c r="M9" s="237"/>
+      <c r="N9" s="236"/>
+      <c r="O9" s="238"/>
+      <c r="P9" s="237"/>
+    </row>
+    <row r="10" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="250"/>
+      <c r="C10" s="227" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="228"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="228"/>
+      <c r="I10" s="229"/>
+      <c r="J10" s="229"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="237"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="238"/>
+      <c r="P10" s="237"/>
+    </row>
+    <row r="11" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="250"/>
+      <c r="C11" s="227" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="228"/>
+      <c r="E11" s="228"/>
+      <c r="F11" s="228"/>
+      <c r="G11" s="228"/>
+      <c r="H11" s="228"/>
+      <c r="I11" s="229"/>
+      <c r="J11" s="229"/>
+      <c r="K11" s="235"/>
+      <c r="L11" s="236"/>
+      <c r="M11" s="237"/>
+      <c r="N11" s="236"/>
+      <c r="O11" s="238"/>
+      <c r="P11" s="237"/>
+    </row>
+    <row r="12" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="250"/>
+      <c r="C12" s="227" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="228"/>
+      <c r="E12" s="228"/>
+      <c r="F12" s="228"/>
+      <c r="G12" s="228"/>
+      <c r="H12" s="228"/>
+      <c r="I12" s="229"/>
+      <c r="J12" s="229"/>
+      <c r="K12" s="235"/>
+      <c r="L12" s="236"/>
+      <c r="M12" s="237"/>
+      <c r="N12" s="236"/>
+      <c r="O12" s="238"/>
+      <c r="P12" s="237"/>
+    </row>
+    <row r="13" spans="2:16" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="251"/>
+      <c r="C13" s="227" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="228"/>
+      <c r="G13" s="228"/>
+      <c r="H13" s="228"/>
+      <c r="I13" s="229"/>
+      <c r="J13" s="229"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="240"/>
+      <c r="M13" s="241"/>
+      <c r="N13" s="240"/>
+      <c r="O13" s="242"/>
+      <c r="P13" s="241"/>
+    </row>
+    <row r="14" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="249" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="227" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="243" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="243" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="228">
+        <v>5</v>
+      </c>
+      <c r="G14" s="228">
+        <v>10</v>
+      </c>
+      <c r="H14" s="228">
+        <v>15</v>
+      </c>
+      <c r="I14" s="229">
+        <v>20</v>
+      </c>
+      <c r="J14" s="229">
+        <v>25</v>
+      </c>
+      <c r="K14" s="229">
+        <v>30</v>
+      </c>
+      <c r="L14" s="230">
+        <v>35</v>
+      </c>
+      <c r="M14" s="230">
+        <v>45</v>
+      </c>
+      <c r="N14" s="230">
+        <v>55</v>
+      </c>
+      <c r="O14" s="230">
+        <v>65</v>
+      </c>
+      <c r="P14" s="230" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="250"/>
+      <c r="C15" s="247" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="243" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="244" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" s="243" t="s">
+        <v>181</v>
+      </c>
+      <c r="G15" s="243" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" s="243" t="s">
+        <v>183</v>
+      </c>
+      <c r="I15" s="245" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="245" t="s">
+        <v>185</v>
+      </c>
+      <c r="K15" s="245" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" s="246" t="s">
+        <v>187</v>
+      </c>
+      <c r="M15" s="246" t="s">
+        <v>188</v>
+      </c>
+      <c r="N15" s="246" t="s">
+        <v>189</v>
+      </c>
+      <c r="O15" s="246" t="s">
+        <v>190</v>
+      </c>
+      <c r="P15" s="230" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="251"/>
+      <c r="C16" s="248"/>
+      <c r="D16" s="228" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16" s="228" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="228" t="s">
+        <v>165</v>
+      </c>
+      <c r="G16" s="228" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="228" t="s">
+        <v>167</v>
+      </c>
+      <c r="I16" s="229" t="s">
+        <v>168</v>
+      </c>
+      <c r="J16" s="229" t="s">
+        <v>169</v>
+      </c>
+      <c r="K16" s="229" t="s">
+        <v>170</v>
+      </c>
+      <c r="L16" s="230" t="s">
+        <v>171</v>
+      </c>
+      <c r="M16" s="230" t="s">
+        <v>172</v>
+      </c>
+      <c r="N16" s="230" t="s">
+        <v>173</v>
+      </c>
+      <c r="O16" s="230" t="s">
+        <v>174</v>
+      </c>
+      <c r="P16" s="230" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="B8:B13"/>
+    <mergeCell ref="K8:K13"/>
+    <mergeCell ref="L8:M13"/>
+    <mergeCell ref="N8:P13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C15:C16"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="71" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3A626A-F594-4ACC-8BDC-51B1277D6487}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Y26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.7109375" defaultRowHeight="17.25" customHeight="1"/>
+  <dimension ref="A4:AD17"/>
+  <sheetFormatPr defaultColWidth="5.28515625" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" style="123"/>
-    <col min="2" max="3" width="14.7109375" style="122"/>
-    <col min="4" max="4" width="14.7109375" style="123"/>
-    <col min="5" max="5" width="20.42578125" style="122" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="123"/>
-    <col min="7" max="7" width="14.7109375" style="122"/>
-    <col min="8" max="8" width="14.7109375" style="123"/>
-    <col min="9" max="9" width="14.7109375" style="122"/>
-    <col min="10" max="10" width="14.7109375" style="123"/>
-    <col min="11" max="11" width="14.7109375" style="122"/>
-    <col min="12" max="12" width="14.7109375" style="123"/>
-    <col min="13" max="13" width="14.7109375" style="122"/>
-    <col min="14" max="14" width="14.7109375" style="123"/>
-    <col min="15" max="15" width="14.7109375" style="122"/>
-    <col min="16" max="16" width="14.7109375" style="123"/>
-    <col min="17" max="17" width="14.7109375" style="122"/>
-    <col min="18" max="18" width="14.7109375" style="123"/>
-    <col min="19" max="19" width="14.7109375" style="122"/>
-    <col min="20" max="20" width="14.7109375" style="123"/>
-    <col min="21" max="21" width="14.7109375" style="122"/>
-    <col min="22" max="22" width="14.7109375" style="123"/>
-    <col min="23" max="23" width="14.7109375" style="122"/>
-    <col min="24" max="24" width="14.7109375" style="123"/>
-    <col min="25" max="25" width="14.7109375" style="122"/>
-    <col min="26" max="16384" width="14.7109375" style="123"/>
+    <col min="24" max="24" width="6" customWidth="1"/>
+    <col min="25" max="25" width="6.140625" customWidth="1"/>
+    <col min="27" max="28" width="11.85546875" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" customWidth="1"/>
+    <col min="30" max="30" width="11.85546875" style="123" customWidth="1"/>
+    <col min="31" max="16384" width="5.28515625" style="123"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="17.25" customHeight="1" thickBot="1"/>
-    <row r="2" spans="2:15" ht="17.25" customHeight="1">
-      <c r="B2" s="254" t="s">
+    <row r="4" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+    </row>
+    <row r="5" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+    </row>
+    <row r="6" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+    </row>
+    <row r="7" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+    </row>
+    <row r="8" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8" s="252" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y8" s="252"/>
+      <c r="Z8" s="252"/>
+      <c r="AA8" s="252"/>
+      <c r="AB8" s="252"/>
+      <c r="AC8" s="252"/>
+    </row>
+    <row r="9" spans="1:30" s="122" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+    </row>
+    <row r="10" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10" s="253"/>
+      <c r="W10" s="254"/>
+      <c r="X10" s="265"/>
+      <c r="Y10" s="261" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z10" s="259" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="255"/>
-      <c r="D2" s="256"/>
-      <c r="E2" s="259" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="260"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="260"/>
-      <c r="I2" s="261"/>
-      <c r="J2" s="259" t="s">
-        <v>187</v>
-      </c>
-      <c r="K2" s="260"/>
-      <c r="L2" s="260"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="261"/>
-      <c r="O2"/>
-    </row>
-    <row r="3" spans="2:15" ht="17.25" customHeight="1" thickBot="1">
-      <c r="B3" s="257" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="124" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="125" t="s">
+      <c r="AA10" s="257" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="126" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="126" t="s">
-        <v>162</v>
-      </c>
-      <c r="H3" s="126" t="s">
-        <v>163</v>
-      </c>
-      <c r="I3" s="124" t="s">
-        <v>164</v>
-      </c>
-      <c r="J3" s="125" t="s">
-        <v>161</v>
-      </c>
-      <c r="K3" s="126" t="s">
-        <v>165</v>
-      </c>
-      <c r="L3" s="126" t="s">
-        <v>162</v>
-      </c>
-      <c r="M3" s="126" t="s">
-        <v>163</v>
-      </c>
-      <c r="N3" s="124" t="s">
-        <v>164</v>
-      </c>
-      <c r="O3"/>
-    </row>
-    <row r="4" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B4" s="127" t="s">
+      <c r="AB10" s="257" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="128" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="143" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="131" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="131" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="131" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="132" t="s">
-        <v>90</v>
-      </c>
-      <c r="J4" s="130" t="s">
-        <v>90</v>
-      </c>
-      <c r="K4" s="131" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" s="131" t="s">
-        <v>90</v>
-      </c>
-      <c r="M4" s="131" t="s">
-        <v>90</v>
-      </c>
-      <c r="N4" s="132" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B5" s="133" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="134" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="135" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="133" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="137" t="s">
-        <v>90</v>
-      </c>
-      <c r="J5" s="133" t="s">
-        <v>90</v>
-      </c>
-      <c r="K5" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="L5" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="M5" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="N5" s="137" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B6" s="133" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" s="138" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="137">
-        <v>5</v>
-      </c>
-      <c r="E6" s="133" t="s">
-        <v>204</v>
-      </c>
-      <c r="F6" s="136" t="s">
+      <c r="AC10" s="257" t="s">
+        <v>201</v>
+      </c>
+      <c r="AD10" s="255"/>
+    </row>
+    <row r="11" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="255"/>
+      <c r="X11" s="262" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="266"/>
+      <c r="Z11" s="259"/>
+      <c r="AA11" s="257"/>
+      <c r="AB11" s="257"/>
+      <c r="AC11" s="257"/>
+      <c r="AD11" s="255"/>
+    </row>
+    <row r="12" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12" s="253"/>
+      <c r="W12" s="256"/>
+      <c r="X12" s="263" t="s">
         <v>202</v>
       </c>
-      <c r="G6" s="136" t="s">
-        <v>202</v>
-      </c>
-      <c r="H6" s="136" t="s">
-        <v>201</v>
-      </c>
-      <c r="I6" s="137" t="s">
-        <v>201</v>
-      </c>
-      <c r="J6" s="133"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="137"/>
-    </row>
-    <row r="7" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B7" s="133" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="138" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="137">
-        <v>10</v>
-      </c>
-      <c r="E7" s="133" t="s">
+      <c r="Y12" s="264"/>
+      <c r="Z12" s="260" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA12" s="258" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB12" s="258" t="s">
+        <v>179</v>
+      </c>
+      <c r="AC12" s="258" t="s">
+        <v>179</v>
+      </c>
+      <c r="AD12" s="255"/>
+    </row>
+    <row r="13" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13" s="253"/>
+      <c r="W13" s="253"/>
+      <c r="X13" s="263" t="s">
         <v>203</v>
       </c>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136" t="s">
-        <v>202</v>
-      </c>
-      <c r="H7" s="136"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="133" t="s">
-        <v>184</v>
-      </c>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136" t="s">
-        <v>185</v>
-      </c>
-      <c r="M7" s="136" t="s">
-        <v>186</v>
-      </c>
-      <c r="N7" s="137" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B8" s="133" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="138" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="137">
-        <v>15</v>
-      </c>
-      <c r="E8" s="133" t="s">
+      <c r="Y13" s="264"/>
+      <c r="Z13" s="260" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA13" s="258" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB13" s="258" t="s">
         <v>178</v>
       </c>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="133"/>
-      <c r="K8" s="136"/>
-      <c r="L8" s="136"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="137"/>
-    </row>
-    <row r="9" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B9" s="133" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="138" t="s">
-        <v>192</v>
-      </c>
-      <c r="D9" s="137">
-        <v>20</v>
-      </c>
-      <c r="E9" s="133" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="136"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="137"/>
-    </row>
-    <row r="10" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B10" s="139" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="140" t="s">
-        <v>193</v>
-      </c>
-      <c r="D10" s="141">
-        <v>25</v>
-      </c>
-      <c r="E10" s="139"/>
-      <c r="F10" s="142"/>
-      <c r="G10" s="142"/>
-      <c r="H10" s="142"/>
-      <c r="I10" s="141"/>
-      <c r="J10" s="139" t="s">
-        <v>183</v>
-      </c>
-      <c r="K10" s="142"/>
-      <c r="L10" s="142" t="s">
-        <v>184</v>
-      </c>
-      <c r="M10" s="142" t="s">
-        <v>185</v>
-      </c>
-      <c r="N10" s="141" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B11" s="139" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11" s="140" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="141">
-        <v>30</v>
-      </c>
-      <c r="E11" s="139"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="142"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="139"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="142"/>
-      <c r="N11" s="141"/>
-    </row>
-    <row r="12" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B12" s="144" t="s">
-        <v>173</v>
-      </c>
-      <c r="C12" s="145" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="146">
-        <v>35</v>
-      </c>
-      <c r="E12" s="144" t="s">
-        <v>206</v>
-      </c>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="146"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="146"/>
-    </row>
-    <row r="13" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1">
-      <c r="B13" s="144" t="s">
-        <v>174</v>
-      </c>
-      <c r="C13" s="145" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="146">
-        <v>45</v>
-      </c>
-      <c r="E13" s="144" t="s">
-        <v>206</v>
-      </c>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="146"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="146"/>
-    </row>
-    <row r="14" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1" thickBot="1">
-      <c r="B14" s="144" t="s">
-        <v>175</v>
-      </c>
-      <c r="C14" s="145" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="146">
-        <v>55</v>
-      </c>
-      <c r="E14" s="262" t="s">
-        <v>205</v>
-      </c>
-      <c r="F14" s="263"/>
-      <c r="G14" s="263"/>
-      <c r="H14" s="263"/>
-      <c r="I14" s="264"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="147"/>
-      <c r="N14" s="146"/>
-    </row>
-    <row r="15" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1" thickBot="1">
-      <c r="B15" s="144" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="145" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="146">
-        <v>65</v>
-      </c>
-      <c r="E15" s="262" t="s">
-        <v>205</v>
-      </c>
-      <c r="F15" s="263"/>
-      <c r="G15" s="263"/>
-      <c r="H15" s="263"/>
-      <c r="I15" s="264"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="147"/>
-      <c r="L15" s="147"/>
-      <c r="M15" s="147"/>
-      <c r="N15" s="146"/>
-    </row>
-    <row r="16" spans="2:15" s="122" customFormat="1" ht="52.5" customHeight="1" thickBot="1">
-      <c r="B16" s="148" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="149" t="s">
-        <v>199</v>
-      </c>
-      <c r="D16" s="150" t="s">
-        <v>199</v>
-      </c>
-      <c r="E16" s="262" t="s">
-        <v>205</v>
-      </c>
-      <c r="F16" s="263"/>
-      <c r="G16" s="263"/>
-      <c r="H16" s="263"/>
-      <c r="I16" s="264"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="149"/>
-      <c r="L16" s="149"/>
-      <c r="M16" s="149"/>
-      <c r="N16" s="150"/>
-    </row>
-    <row r="17" spans="2:19" customFormat="1" ht="17.25" customHeight="1"/>
-    <row r="18" spans="2:19" ht="17.25" customHeight="1">
-      <c r="B18" s="123"/>
-      <c r="C18" s="123"/>
-      <c r="E18" s="123"/>
-      <c r="G18" s="123"/>
-      <c r="I18" s="123"/>
-    </row>
-    <row r="19" spans="2:19" ht="17.25" customHeight="1">
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="G19" s="123"/>
-      <c r="I19" s="123"/>
-    </row>
-    <row r="22" spans="2:19" ht="17.25" customHeight="1">
-      <c r="G22" s="123"/>
-      <c r="I22" s="123"/>
-      <c r="K22" s="123"/>
-      <c r="M22" s="123"/>
-      <c r="O22" s="123"/>
-      <c r="Q22" s="123"/>
-      <c r="S22" s="123"/>
-    </row>
-    <row r="25" spans="2:19" ht="17.25" customHeight="1">
-      <c r="D25" s="123" t="s">
-        <v>180</v>
-      </c>
-      <c r="E25" s="122" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19" ht="17.25" customHeight="1">
-      <c r="D26" s="123" t="s">
+      <c r="AC13" s="258" t="s">
         <v>179</v>
       </c>
-      <c r="E26" s="122" t="s">
-        <v>182</v>
-      </c>
-    </row>
+      <c r="AD13" s="255"/>
+    </row>
+    <row r="14" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14" s="253"/>
+      <c r="W14" s="253"/>
+      <c r="X14" s="253"/>
+      <c r="Y14" s="253"/>
+      <c r="Z14" s="253"/>
+      <c r="AA14" s="253"/>
+      <c r="AB14" s="253"/>
+      <c r="AC14" s="253"/>
+      <c r="AD14" s="255"/>
+    </row>
+    <row r="15" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+    </row>
+    <row r="16" spans="1:30" s="122" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+    </row>
+    <row r="17" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="E16:I16"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="E14:I14"/>
+    <mergeCell ref="X8:AC8"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="AB10:AB11"/>
+    <mergeCell ref="AC10:AC11"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
